--- a/nurse_scheduler_complete.xlsx
+++ b/nurse_scheduler_complete.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\송민영\Desktop\근무표 프로그램\완전판\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\송민영\Desktop\근무표 프로그램\완전판 웹사이트로 돌아감\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4839305-AB91-4728-90CD-AE4C587F9B90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A021BE15-1AFD-483D-B8A9-FA7BFD5F6038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8970" yWindow="2985" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="설명서" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="279">
   <si>
     <t>Scheduler Controls</t>
   </si>
@@ -421,9 +421,6 @@
     <t>2. 이름(오타) 통일:</t>
   </si>
   <si>
-    <t>Nurses 시트에 적힌 이름과 OffRequests, ShiftPreferences 등 간호사 이름이 들어간 모든 시트의 이름과 순서가 반드시 일치해야 합니다. (간호사 퇴사/입사로 인원을 수정할 때는 세 시트 모두 똑같이 수정해 주세요. 복사 붙여넣기 추천)</t>
-  </si>
-  <si>
     <t>3. 불가능한 조건 조심:</t>
   </si>
   <si>
@@ -431,84 +428,6 @@
   </si>
   <si>
     <t xml:space="preserve"> 4. 시트의 이름, 입력란 외 이름, 입력란의 행과 열을 바꾸면 프로그램이 인식하지 못합니다!</t>
-  </si>
-  <si>
-    <t>(스케줄 작성 완료 후 엑셀을 저장 후 종료한 뒤에 .exe 파일을 더블클릭하시면 됩니다!)</t>
-  </si>
-  <si>
-    <t>액셀 파일과 실행 exe 파일을 한 폴더안에 넣어야 작동이 됩니다! 엑셀과 프로그램 파일 이름을 바꾸지 마세요!</t>
-  </si>
-  <si>
-    <t>프로그램창 (CMD) 해석</t>
-  </si>
-  <si>
-    <t>근무표 작성이 완료되면 까만 창 맨 아래에 두 줄의 영어 메시지가 뜹니다. 이것은 AI(인공지능)가 스케줄을 짜면서 겪은 과정과 결과물의 점수를 알려주는 보고서입니다.</t>
-  </si>
-  <si>
-    <t>1️⃣ Solver status (컴퓨터의 최종 상태 보고)</t>
-  </si>
-  <si>
-    <t>컴퓨터가 근무표를 성공적으로 완성했는지, 아니면 규칙이 너무 빡빡해서 실패했는지를 알려줍니다.</t>
-  </si>
-  <si>
-    <t>OPTIMAL (가장 이상적!)</t>
-  </si>
-  <si>
-    <t>의미: 주어진 조건 안에서 수학적으로 가장 완벽하고 공평한 1등 스케줄을 찾아냈습니다</t>
-  </si>
-  <si>
-    <t>상태: 안심하고 엑셀 근무표를 확인하시면 됩니다.</t>
-  </si>
-  <si>
-    <t>FEASIBLE (쓸만한 스케줄 완성)</t>
-  </si>
-  <si>
-    <t>의미: 100점짜리 정답인지는 확신할 수 없지만, 모든 절대 규칙(Hard)을 완벽하게 지킨 스케줄을 일단 완성했습니다</t>
-  </si>
-  <si>
-    <t>상태: 엑셀 근무표를 그대로 사용하셔도 무방합니다. (더 완벽한 결과를 원하시면 Setup 시트의 시간을 늘리고 다시 돌려보세요.)</t>
-  </si>
-  <si>
-    <t>INFEASIBLE (작성 실패 - 규칙 충돌) 🚨</t>
-  </si>
-  <si>
-    <t>의미: 스케줄을 짤 수가 없습니다! 조건들이 서로 모순됩니다</t>
-  </si>
-  <si>
-    <t>상태: 근무표 작성에 실패하여 엑셀이 업데이트되지 않습니다. (주로 1순위 오프가 너무 많거나, 출근할 인원이 부족할 때 발생합니다. 인원이나 오프를 수정하고 다시 돌려주세요.)</t>
-  </si>
-  <si>
-    <t>UNKNOWN (작성 실패 - 시간 초과) 🚨</t>
-  </si>
-  <si>
-    <t>의미: 규칙이 너무 복잡해서 제한 시간 안에 단 한 개의 스케줄도 완성하지 못했습니다.</t>
-  </si>
-  <si>
-    <t>상태: Setup 시트의 Solver time limit (sec) 시간을 600초 이상으로 넉넉히 늘리거나, 연속 근무 제한을 살짝 풀어주세요.</t>
-  </si>
-  <si>
-    <t>2️⃣ Objective value (AI의 스케줄 채점표 / 벌점)</t>
-  </si>
-  <si>
-    <t>의미: 이 숫자는 인공지능이 스케줄을 짜면서 받은 벌점(Penalty)의 총합입니다.</t>
-  </si>
-  <si>
-    <t>해석 방법: "숫자가 낮을수록(0에 가까울수록) 훌륭한 근무표입니다!"</t>
-  </si>
-  <si>
-    <t>컴퓨터는 무조건 이 벌점을 낮추기 위해 수백만 번의 경우의 수를 계산합니다.</t>
-  </si>
-  <si>
-    <t>벌점이 올라가는(숫자가 커지는) 이유:</t>
-  </si>
-  <si>
-    <t>1. 선생님들이 신청한 듀티(E or D 등)를 어쩔 수 없이 못 들어줬을 때</t>
-  </si>
-  <si>
-    <t>2. 2순위, 3순위 오프 신청을 반려하고 출근시켰을 때</t>
-  </si>
-  <si>
-    <t>3. 간호사들 간의 총 근무 일수나 나이트 개수가 공평하게 딱 떨어지지 않았을 때</t>
   </si>
   <si>
     <t>Nurse Name</t>
@@ -927,13 +846,743 @@
   </si>
   <si>
     <t>간호사50</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Nurses </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시트에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>적힌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이름과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> OffRequests, ShiftPreferences </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>등</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>간호사</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이름이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>들어간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모든</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시트의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이름과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>순서가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>반드시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>일치해야</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>합니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>. (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>간호사</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>퇴사</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>입사로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>인원을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수정할</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>때는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>세</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모두</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>똑같이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수정해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>주세요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>자동 반영 되는데 간호사 순서 밀림에 주의해주세요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>🌐 [웹사이트 실행 방법]</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. 이 엑셀 파일에 근무 조건과 오프 신청을 모두 입력한 뒤 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>저장하고 닫습니다.</t>
+    </r>
+  </si>
+  <si>
+    <t>2. 스케줄러 웹사이트에 접속합니다. (여기에 선생님의 웹사이트 주소 링크를 적어주세요!)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3. 웹사이트 화면에 저장한 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>엑셀 파일을 마우스로 끌어다 놓고 [🚀 AI 근무표 자동 생성 시작] 버튼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>을 누릅니다.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>🤖 [AI 결과 메시지 해석]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 웹사이트에서 버튼을 누른 뒤 나오는 알림창의 의미입니다.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>✅ 성공 (초록색 알림창 &amp; 풍선):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI가 완벽한 근무표를 찾았습니다! 다운로드 버튼을 눌러 확인하세요.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>🚨 규칙 충돌 에러 (빨간색 알림창):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 스케줄을 짤 수 없습니다! 조건들이 서로 모순됩니다. (주로 1순위 오프가 너무 많거나, 나이트 출근 인원이 부족할 때 발생합니다. 인원이나 오프를 수정하고 다시 올려주세요.)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>🚨 시간 초과 에러 (빨간색 알림창):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 규칙이 너무 복잡해서 제한 시간 내에 풀지 못했습니다. Setup 시트의 제한 시간을 300초 이상으로 넉넉히 늘리거나 규칙을 살짝 풀어주세요.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">4. 계산이 끝나고 풍선이 터지면 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📥</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 다운로드]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 버튼을 눌러 완성된 근무표를 확인하세요! </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(팁: 엑셀 파일 이름은 '4월_최종근무표.xlsx' 처럼 마음대로 바꿔서 올려도 작동합니다!)</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🎯</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI가 받은 벌점(Objective Value):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 성공 메시지에 표시되는 점수로, AI가 스케줄을 짜면서 어쩔 수 없이 받은 페널티의 총합입니다. **"숫자가 낮을수록(0에 가까울수록) 훌륭하고 공평한 근무표"**라는 뜻입니다!</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> (오프 반려, 주니어 나이트 쏠림 등이 생길 때마다 벌점이 올라갑니다.)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="34">
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1104,12 +1753,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial Unicode MS"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
@@ -1180,9 +1823,43 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
-      <sz val="16"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
@@ -1191,21 +1868,10 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
-      <color rgb="FFFF0000"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
+      <name val="Segoe UI Emoji"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -1378,7 +2044,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1482,9 +2148,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1501,26 +2164,26 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
@@ -1528,61 +2191,59 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1592,14 +2253,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1951,7 +2617,7 @@
       <c r="H3" s="25"/>
       <c r="I3" s="24"/>
       <c r="K3" s="34" t="s">
-        <v>255</v>
+        <v>228</v>
       </c>
       <c r="X3" s="33"/>
     </row>
@@ -2354,7 +3020,7 @@
       <c r="J105" s="44"/>
     </row>
     <row r="106" spans="1:10">
-      <c r="A106" s="82" t="s">
+      <c r="A106" s="81" t="s">
         <v>114</v>
       </c>
       <c r="B106" s="44"/>
@@ -2460,8 +3126,8 @@
       </c>
     </row>
     <row r="127" spans="1:1">
-      <c r="A127" s="47" t="s">
-        <v>125</v>
+      <c r="A127" s="93" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="128" spans="1:1">
@@ -2469,12 +3135,12 @@
     </row>
     <row r="129" spans="1:1">
       <c r="A129" s="45" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" s="41" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="131" spans="1:1">
@@ -2482,153 +3148,136 @@
     </row>
     <row r="132" spans="1:1">
       <c r="A132" s="45" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="134" spans="1:1" ht="26.25" customHeight="1">
-      <c r="A134" s="86" t="s">
-        <v>129</v>
+      <c r="A134" s="17" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="135" spans="1:1" ht="26.25" customHeight="1">
-      <c r="A135" s="91" t="s">
-        <v>130</v>
-      </c>
+      <c r="A135" s="19"/>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" s="19" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" s="19"/>
     </row>
     <row r="138" spans="1:1" ht="20.25" customHeight="1">
-      <c r="A138" s="95" t="s">
-        <v>131</v>
+      <c r="A138" s="19" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="139" spans="1:1">
-      <c r="A139" t="s">
-        <v>132</v>
+      <c r="A139" s="19"/>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" s="19" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="141" spans="1:1" ht="21.75" customHeight="1">
-      <c r="A141" s="18" t="s">
-        <v>133</v>
+      <c r="A141" s="19"/>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" s="19" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="143" spans="1:1">
-      <c r="A143" t="s">
-        <v>134</v>
-      </c>
+      <c r="A143" s="16"/>
     </row>
     <row r="144" spans="1:1">
-      <c r="A144" s="16"/>
-    </row>
-    <row r="145" spans="1:1">
-      <c r="A145" s="92" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="146" spans="1:1">
-      <c r="A146" s="93" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="147" spans="1:1">
-      <c r="A147" s="93" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="148" spans="1:1">
-      <c r="A148" s="16"/>
-    </row>
-    <row r="149" spans="1:1">
-      <c r="A149" s="92" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="150" spans="1:1">
-      <c r="A150" s="93" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="151" spans="1:1">
-      <c r="A151" s="93" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="152" spans="1:1">
-      <c r="A152" s="16"/>
-    </row>
-    <row r="153" spans="1:1">
-      <c r="A153" s="92" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="154" spans="1:1">
-      <c r="A154" s="93" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="155" spans="1:1">
-      <c r="A155" s="93" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="156" spans="1:1">
+      <c r="A144" s="17" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5">
+      <c r="A145" s="19"/>
+    </row>
+    <row r="146" spans="1:5">
+      <c r="A146" s="90" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5">
+      <c r="A147" s="19"/>
+    </row>
+    <row r="148" spans="1:5">
+      <c r="A148" s="90" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5">
+      <c r="A149" s="19"/>
+    </row>
+    <row r="150" spans="1:5">
+      <c r="A150" s="90" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5">
+      <c r="A151" s="19"/>
+    </row>
+    <row r="152" spans="1:5">
+      <c r="A152" s="97" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5">
+      <c r="A153" s="89"/>
+      <c r="E153" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5">
+      <c r="A154" s="90"/>
+    </row>
+    <row r="155" spans="1:5">
+      <c r="A155" s="90"/>
+    </row>
+    <row r="156" spans="1:5">
       <c r="A156" s="16"/>
     </row>
-    <row r="157" spans="1:1">
-      <c r="A157" s="92" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="158" spans="1:1">
-      <c r="A158" s="93" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="159" spans="1:1">
-      <c r="A159" s="93" t="s">
-        <v>146</v>
-      </c>
+    <row r="157" spans="1:5">
+      <c r="A157" s="89"/>
+    </row>
+    <row r="158" spans="1:5">
+      <c r="A158" s="90"/>
+    </row>
+    <row r="159" spans="1:5">
+      <c r="A159" s="90"/>
     </row>
     <row r="161" spans="1:1" ht="21.75" customHeight="1">
-      <c r="A161" s="18" t="s">
-        <v>147</v>
-      </c>
+      <c r="A161" s="18"/>
     </row>
     <row r="162" spans="1:1">
       <c r="A162" s="16"/>
     </row>
     <row r="163" spans="1:1">
-      <c r="A163" s="17" t="s">
-        <v>148</v>
-      </c>
+      <c r="A163" s="17"/>
     </row>
     <row r="164" spans="1:1">
-      <c r="A164" s="17" t="s">
-        <v>149</v>
-      </c>
+      <c r="A164" s="17"/>
     </row>
     <row r="166" spans="1:1">
-      <c r="A166" s="19" t="s">
-        <v>150</v>
-      </c>
+      <c r="A166" s="19"/>
     </row>
     <row r="167" spans="1:1">
-      <c r="A167" s="93" t="s">
-        <v>151</v>
-      </c>
+      <c r="A167" s="90"/>
     </row>
     <row r="168" spans="1:1">
-      <c r="A168" s="94" t="s">
-        <v>152</v>
-      </c>
+      <c r="A168" s="91"/>
     </row>
     <row r="169" spans="1:1">
-      <c r="A169" s="94" t="s">
-        <v>153</v>
-      </c>
+      <c r="A169" s="91"/>
     </row>
     <row r="170" spans="1:1">
-      <c r="A170" s="94" t="s">
-        <v>154</v>
-      </c>
+      <c r="A170" s="91"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -2650,22 +3299,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>197</v>
+        <v>170</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>236</v>
+        <v>209</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>223</v>
+        <v>196</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>237</v>
+        <v>210</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>239</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -2689,68 +3338,68 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="5" t="s">
-        <v>197</v>
+        <v>170</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>240</v>
+        <v>213</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>241</v>
+        <v>214</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>242</v>
+        <v>215</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>243</v>
+        <v>216</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>244</v>
+        <v>217</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>245</v>
+        <v>218</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>246</v>
+        <v>219</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>247</v>
+        <v>220</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="I2" s="96"/>
+      <c r="I2" s="92"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="I3" s="96"/>
+      <c r="I3" s="92"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="I4" s="96"/>
+      <c r="I4" s="92"/>
     </row>
     <row r="5" spans="1:9">
-      <c r="I5" s="96"/>
+      <c r="I5" s="92"/>
     </row>
     <row r="6" spans="1:9">
-      <c r="I6" s="96"/>
+      <c r="I6" s="92"/>
     </row>
     <row r="7" spans="1:9">
-      <c r="I7" s="96"/>
+      <c r="I7" s="92"/>
     </row>
     <row r="8" spans="1:9">
-      <c r="I8" s="96"/>
+      <c r="I8" s="92"/>
     </row>
     <row r="9" spans="1:9">
-      <c r="I9" s="96"/>
+      <c r="I9" s="92"/>
     </row>
     <row r="10" spans="1:9">
-      <c r="I10" s="96"/>
+      <c r="I10" s="92"/>
     </row>
     <row r="11" spans="1:9">
-      <c r="I11" s="96"/>
+      <c r="I11" s="92"/>
     </row>
     <row r="12" spans="1:9">
-      <c r="I12" s="96"/>
+      <c r="I12" s="92"/>
     </row>
     <row r="13" spans="1:9">
-      <c r="I13" s="96"/>
+      <c r="I13" s="92"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -2769,125 +3418,125 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="5" t="s">
-        <v>236</v>
+        <v>209</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="C1" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>250</v>
-      </c>
       <c r="F1" s="5" t="s">
-        <v>251</v>
+        <v>224</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>252</v>
+        <v>225</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>253</v>
+        <v>226</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>254</v>
+        <v>227</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="I2" s="96"/>
+      <c r="I2" s="92"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="I3" s="96"/>
+      <c r="I3" s="92"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="I4" s="96"/>
+      <c r="I4" s="92"/>
     </row>
     <row r="5" spans="1:9">
-      <c r="I5" s="96"/>
+      <c r="I5" s="92"/>
     </row>
     <row r="6" spans="1:9">
-      <c r="I6" s="96"/>
+      <c r="I6" s="92"/>
     </row>
     <row r="7" spans="1:9">
-      <c r="I7" s="96"/>
+      <c r="I7" s="92"/>
     </row>
     <row r="8" spans="1:9">
-      <c r="I8" s="96"/>
+      <c r="I8" s="92"/>
     </row>
     <row r="9" spans="1:9">
-      <c r="I9" s="96"/>
+      <c r="I9" s="92"/>
     </row>
     <row r="10" spans="1:9">
-      <c r="I10" s="96"/>
+      <c r="I10" s="92"/>
     </row>
     <row r="11" spans="1:9">
-      <c r="I11" s="96"/>
+      <c r="I11" s="92"/>
     </row>
     <row r="12" spans="1:9">
-      <c r="I12" s="96"/>
+      <c r="I12" s="92"/>
     </row>
     <row r="13" spans="1:9">
-      <c r="I13" s="96"/>
+      <c r="I13" s="92"/>
     </row>
     <row r="14" spans="1:9">
-      <c r="I14" s="96"/>
+      <c r="I14" s="92"/>
     </row>
     <row r="15" spans="1:9">
-      <c r="I15" s="96"/>
+      <c r="I15" s="92"/>
     </row>
     <row r="16" spans="1:9">
-      <c r="I16" s="96"/>
+      <c r="I16" s="92"/>
     </row>
     <row r="17" spans="9:9">
-      <c r="I17" s="96"/>
+      <c r="I17" s="92"/>
     </row>
     <row r="18" spans="9:9">
-      <c r="I18" s="96"/>
+      <c r="I18" s="92"/>
     </row>
     <row r="19" spans="9:9">
-      <c r="I19" s="96"/>
+      <c r="I19" s="92"/>
     </row>
     <row r="20" spans="9:9">
-      <c r="I20" s="96"/>
+      <c r="I20" s="92"/>
     </row>
     <row r="21" spans="9:9">
-      <c r="I21" s="96"/>
+      <c r="I21" s="92"/>
     </row>
     <row r="22" spans="9:9">
-      <c r="I22" s="96"/>
+      <c r="I22" s="92"/>
     </row>
     <row r="23" spans="9:9">
-      <c r="I23" s="96"/>
+      <c r="I23" s="92"/>
     </row>
     <row r="24" spans="9:9">
-      <c r="I24" s="96"/>
+      <c r="I24" s="92"/>
     </row>
     <row r="25" spans="9:9">
-      <c r="I25" s="96"/>
+      <c r="I25" s="92"/>
     </row>
     <row r="26" spans="9:9">
-      <c r="I26" s="96"/>
+      <c r="I26" s="92"/>
     </row>
     <row r="27" spans="9:9">
-      <c r="I27" s="96"/>
+      <c r="I27" s="92"/>
     </row>
     <row r="28" spans="9:9">
-      <c r="I28" s="96"/>
+      <c r="I28" s="92"/>
     </row>
     <row r="29" spans="9:9">
-      <c r="I29" s="96"/>
+      <c r="I29" s="92"/>
     </row>
     <row r="30" spans="9:9">
-      <c r="I30" s="96"/>
+      <c r="I30" s="92"/>
     </row>
     <row r="31" spans="9:9">
-      <c r="I31" s="96"/>
+      <c r="I31" s="92"/>
     </row>
     <row r="32" spans="9:9">
-      <c r="I32" s="96"/>
+      <c r="I32" s="92"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -2907,18 +3556,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="97" t="s">
+      <c r="A1" s="94" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="98"/>
-      <c r="C1" s="98"/>
-      <c r="D1" s="98"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="49">
+      <c r="B2" s="48">
         <v>2026</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -2932,7 +3581,7 @@
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="49">
+      <c r="B3" s="48">
         <v>3</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -2946,7 +3595,7 @@
       <c r="A4" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="49">
+      <c r="B4" s="48">
         <v>11</v>
       </c>
       <c r="C4" t="s">
@@ -2955,14 +3604,14 @@
       <c r="D4" s="2"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="B5" s="50"/>
+      <c r="B5" s="49"/>
       <c r="D5" s="10"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="49">
+      <c r="B6" s="48">
         <v>3</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -2974,7 +3623,7 @@
       <c r="A7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="49">
+      <c r="B7" s="48">
         <v>3</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -2986,7 +3635,7 @@
       <c r="A8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="49">
+      <c r="B8" s="48">
         <v>2</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -2998,7 +3647,7 @@
       <c r="A9" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="51">
+      <c r="B9" s="50">
         <v>0</v>
       </c>
       <c r="C9" s="10" t="s">
@@ -3008,7 +3657,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2"/>
-      <c r="B10" s="52"/>
+      <c r="B10" s="51"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
@@ -3016,7 +3665,7 @@
       <c r="A11" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="49">
+      <c r="B11" s="48">
         <v>2</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -3028,7 +3677,7 @@
       <c r="A12" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="49">
+      <c r="B12" s="48">
         <v>2</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -3040,7 +3689,7 @@
       <c r="A13" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="49">
+      <c r="B13" s="48">
         <v>2</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -3052,7 +3701,7 @@
       <c r="A14" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="51">
+      <c r="B14" s="50">
         <v>0</v>
       </c>
       <c r="C14" s="10" t="s">
@@ -3062,7 +3711,7 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2"/>
-      <c r="B15" s="52"/>
+      <c r="B15" s="51"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
     </row>
@@ -3070,7 +3719,7 @@
       <c r="A16" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="49">
+      <c r="B16" s="48">
         <v>5</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -3082,7 +3731,7 @@
       <c r="A17" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="51">
+      <c r="B17" s="50">
         <v>4</v>
       </c>
       <c r="C17" s="10" t="s">
@@ -3094,7 +3743,7 @@
       <c r="A18" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="51">
+      <c r="B18" s="50">
         <v>4</v>
       </c>
       <c r="C18" s="10" t="s">
@@ -3106,7 +3755,7 @@
       <c r="A19" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="49">
+      <c r="B19" s="48">
         <v>3</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -3118,7 +3767,7 @@
       <c r="A20" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B20" s="51">
+      <c r="B20" s="50">
         <v>2</v>
       </c>
       <c r="C20" t="s">
@@ -3130,7 +3779,7 @@
       <c r="A21" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B21" s="49">
+      <c r="B21" s="48">
         <v>2</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -3140,7 +3789,7 @@
     </row>
     <row r="22" spans="1:17">
       <c r="A22" s="9"/>
-      <c r="B22" s="51"/>
+      <c r="B22" s="50"/>
       <c r="C22" s="10"/>
       <c r="D22" s="10"/>
     </row>
@@ -3148,10 +3797,10 @@
       <c r="A23" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="49">
+      <c r="B23" s="48">
         <v>10</v>
       </c>
-      <c r="C23" s="48" t="s">
+      <c r="C23" s="47" t="s">
         <v>38</v>
       </c>
       <c r="D23" s="2"/>
@@ -3160,7 +3809,7 @@
       <c r="A24" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="49">
+      <c r="B24" s="48">
         <v>100</v>
       </c>
       <c r="C24" s="2" t="s">
@@ -3172,7 +3821,7 @@
       <c r="A25" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="49">
+      <c r="B25" s="48">
         <v>10</v>
       </c>
       <c r="C25" s="2" t="s">
@@ -3184,7 +3833,7 @@
       <c r="A26" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B26" s="49">
+      <c r="B26" s="48">
         <v>10</v>
       </c>
       <c r="C26" s="2" t="s">
@@ -3196,7 +3845,7 @@
       <c r="A27" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B27" s="51">
+      <c r="B27" s="50">
         <v>4</v>
       </c>
       <c r="C27" s="10" t="s">
@@ -3208,7 +3857,7 @@
       <c r="A28" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B28" s="51">
+      <c r="B28" s="50">
         <v>10</v>
       </c>
       <c r="C28" s="10" t="s">
@@ -3220,7 +3869,7 @@
       <c r="A29" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B29" s="49">
+      <c r="B29" s="48">
         <v>2</v>
       </c>
       <c r="C29" s="2" t="s">
@@ -3241,326 +3890,326 @@
       <c r="D31" s="39"/>
     </row>
     <row r="32" spans="1:17" ht="17.25" customHeight="1">
-      <c r="A32" s="65" t="s">
+      <c r="A32" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="B32" s="54"/>
-      <c r="C32" s="54"/>
-      <c r="D32" s="54"/>
-      <c r="E32" s="54"/>
-      <c r="F32" s="54"/>
-      <c r="G32" s="54"/>
-      <c r="H32" s="54"/>
-      <c r="I32" s="54"/>
-      <c r="J32" s="54"/>
-      <c r="K32" s="54"/>
-      <c r="L32" s="54"/>
-      <c r="M32" s="54"/>
-      <c r="N32" s="54"/>
-      <c r="O32" s="54"/>
-      <c r="P32" s="54"/>
-      <c r="Q32" s="55"/>
+      <c r="B32" s="53"/>
+      <c r="C32" s="53"/>
+      <c r="D32" s="53"/>
+      <c r="E32" s="53"/>
+      <c r="F32" s="53"/>
+      <c r="G32" s="53"/>
+      <c r="H32" s="53"/>
+      <c r="I32" s="53"/>
+      <c r="J32" s="53"/>
+      <c r="K32" s="53"/>
+      <c r="L32" s="53"/>
+      <c r="M32" s="53"/>
+      <c r="N32" s="53"/>
+      <c r="O32" s="53"/>
+      <c r="P32" s="53"/>
+      <c r="Q32" s="54"/>
     </row>
     <row r="33" spans="1:17" ht="17.25" customHeight="1">
-      <c r="A33" s="56" t="s">
+      <c r="A33" s="55" t="s">
         <v>52</v>
       </c>
-      <c r="B33" s="57"/>
-      <c r="C33" s="57"/>
-      <c r="D33" s="57"/>
-      <c r="E33" s="57"/>
-      <c r="F33" s="57"/>
-      <c r="G33" s="57"/>
-      <c r="H33" s="57"/>
-      <c r="I33" s="57"/>
-      <c r="J33" s="57"/>
-      <c r="K33" s="57"/>
-      <c r="L33" s="57"/>
-      <c r="M33" s="57"/>
-      <c r="N33" s="57"/>
-      <c r="O33" s="57"/>
-      <c r="P33" s="57"/>
-      <c r="Q33" s="58"/>
+      <c r="B33" s="56"/>
+      <c r="C33" s="56"/>
+      <c r="D33" s="56"/>
+      <c r="E33" s="56"/>
+      <c r="F33" s="56"/>
+      <c r="G33" s="56"/>
+      <c r="H33" s="56"/>
+      <c r="I33" s="56"/>
+      <c r="J33" s="56"/>
+      <c r="K33" s="56"/>
+      <c r="L33" s="56"/>
+      <c r="M33" s="56"/>
+      <c r="N33" s="56"/>
+      <c r="O33" s="56"/>
+      <c r="P33" s="56"/>
+      <c r="Q33" s="57"/>
     </row>
     <row r="34" spans="1:17" ht="17.25" customHeight="1">
-      <c r="A34" s="59"/>
-      <c r="B34" s="57"/>
-      <c r="C34" s="57"/>
-      <c r="D34" s="57"/>
-      <c r="E34" s="57"/>
-      <c r="F34" s="57"/>
-      <c r="G34" s="57"/>
-      <c r="H34" s="57"/>
-      <c r="I34" s="57"/>
-      <c r="J34" s="57"/>
-      <c r="K34" s="57"/>
-      <c r="L34" s="57"/>
-      <c r="M34" s="57"/>
-      <c r="N34" s="57"/>
-      <c r="O34" s="57"/>
-      <c r="P34" s="57"/>
-      <c r="Q34" s="58"/>
+      <c r="A34" s="58"/>
+      <c r="B34" s="56"/>
+      <c r="C34" s="56"/>
+      <c r="D34" s="56"/>
+      <c r="E34" s="56"/>
+      <c r="F34" s="56"/>
+      <c r="G34" s="56"/>
+      <c r="H34" s="56"/>
+      <c r="I34" s="56"/>
+      <c r="J34" s="56"/>
+      <c r="K34" s="56"/>
+      <c r="L34" s="56"/>
+      <c r="M34" s="56"/>
+      <c r="N34" s="56"/>
+      <c r="O34" s="56"/>
+      <c r="P34" s="56"/>
+      <c r="Q34" s="57"/>
     </row>
     <row r="35" spans="1:17" ht="17.25" customHeight="1">
-      <c r="A35" s="56" t="s">
+      <c r="A35" s="55" t="s">
         <v>53</v>
       </c>
-      <c r="B35" s="57"/>
-      <c r="C35" s="57"/>
-      <c r="D35" s="57"/>
-      <c r="E35" s="57"/>
-      <c r="F35" s="57"/>
-      <c r="G35" s="57"/>
-      <c r="H35" s="57"/>
-      <c r="I35" s="57"/>
-      <c r="J35" s="57"/>
-      <c r="K35" s="57"/>
-      <c r="L35" s="57"/>
-      <c r="M35" s="57"/>
-      <c r="N35" s="57"/>
-      <c r="O35" s="57"/>
-      <c r="P35" s="57"/>
-      <c r="Q35" s="58"/>
+      <c r="B35" s="56"/>
+      <c r="C35" s="56"/>
+      <c r="D35" s="56"/>
+      <c r="E35" s="56"/>
+      <c r="F35" s="56"/>
+      <c r="G35" s="56"/>
+      <c r="H35" s="56"/>
+      <c r="I35" s="56"/>
+      <c r="J35" s="56"/>
+      <c r="K35" s="56"/>
+      <c r="L35" s="56"/>
+      <c r="M35" s="56"/>
+      <c r="N35" s="56"/>
+      <c r="O35" s="56"/>
+      <c r="P35" s="56"/>
+      <c r="Q35" s="57"/>
     </row>
     <row r="36" spans="1:17" ht="17.25" customHeight="1">
-      <c r="A36" s="59"/>
-      <c r="B36" s="57"/>
-      <c r="C36" s="57"/>
-      <c r="D36" s="57"/>
-      <c r="E36" s="57"/>
-      <c r="F36" s="57"/>
-      <c r="G36" s="57"/>
-      <c r="H36" s="57"/>
-      <c r="I36" s="57"/>
-      <c r="J36" s="57"/>
-      <c r="K36" s="57"/>
-      <c r="L36" s="57"/>
-      <c r="M36" s="57"/>
-      <c r="N36" s="57"/>
-      <c r="O36" s="57"/>
-      <c r="P36" s="57"/>
-      <c r="Q36" s="58"/>
+      <c r="A36" s="58"/>
+      <c r="B36" s="56"/>
+      <c r="C36" s="56"/>
+      <c r="D36" s="56"/>
+      <c r="E36" s="56"/>
+      <c r="F36" s="56"/>
+      <c r="G36" s="56"/>
+      <c r="H36" s="56"/>
+      <c r="I36" s="56"/>
+      <c r="J36" s="56"/>
+      <c r="K36" s="56"/>
+      <c r="L36" s="56"/>
+      <c r="M36" s="56"/>
+      <c r="N36" s="56"/>
+      <c r="O36" s="56"/>
+      <c r="P36" s="56"/>
+      <c r="Q36" s="57"/>
     </row>
     <row r="37" spans="1:17" ht="17.25" customHeight="1">
-      <c r="A37" s="56" t="s">
+      <c r="A37" s="55" t="s">
         <v>54</v>
       </c>
-      <c r="B37" s="57"/>
-      <c r="C37" s="57"/>
-      <c r="D37" s="57"/>
-      <c r="E37" s="57"/>
-      <c r="F37" s="57"/>
-      <c r="G37" s="57"/>
-      <c r="H37" s="57"/>
-      <c r="I37" s="57"/>
-      <c r="J37" s="57"/>
-      <c r="K37" s="57"/>
-      <c r="L37" s="57"/>
-      <c r="M37" s="57"/>
-      <c r="N37" s="57"/>
-      <c r="O37" s="57"/>
-      <c r="P37" s="57"/>
-      <c r="Q37" s="58"/>
+      <c r="B37" s="56"/>
+      <c r="C37" s="56"/>
+      <c r="D37" s="56"/>
+      <c r="E37" s="56"/>
+      <c r="F37" s="56"/>
+      <c r="G37" s="56"/>
+      <c r="H37" s="56"/>
+      <c r="I37" s="56"/>
+      <c r="J37" s="56"/>
+      <c r="K37" s="56"/>
+      <c r="L37" s="56"/>
+      <c r="M37" s="56"/>
+      <c r="N37" s="56"/>
+      <c r="O37" s="56"/>
+      <c r="P37" s="56"/>
+      <c r="Q37" s="57"/>
     </row>
     <row r="38" spans="1:17" ht="17.25" customHeight="1">
-      <c r="A38" s="60"/>
-      <c r="B38" s="57"/>
-      <c r="C38" s="57"/>
-      <c r="D38" s="57"/>
-      <c r="E38" s="57"/>
-      <c r="F38" s="57"/>
-      <c r="G38" s="57"/>
-      <c r="H38" s="57"/>
-      <c r="I38" s="57"/>
-      <c r="J38" s="57"/>
-      <c r="K38" s="57"/>
-      <c r="L38" s="57"/>
-      <c r="M38" s="57"/>
-      <c r="N38" s="57"/>
-      <c r="O38" s="57"/>
-      <c r="P38" s="57"/>
-      <c r="Q38" s="58"/>
+      <c r="A38" s="59"/>
+      <c r="B38" s="56"/>
+      <c r="C38" s="56"/>
+      <c r="D38" s="56"/>
+      <c r="E38" s="56"/>
+      <c r="F38" s="56"/>
+      <c r="G38" s="56"/>
+      <c r="H38" s="56"/>
+      <c r="I38" s="56"/>
+      <c r="J38" s="56"/>
+      <c r="K38" s="56"/>
+      <c r="L38" s="56"/>
+      <c r="M38" s="56"/>
+      <c r="N38" s="56"/>
+      <c r="O38" s="56"/>
+      <c r="P38" s="56"/>
+      <c r="Q38" s="57"/>
     </row>
     <row r="39" spans="1:17" ht="17.25" customHeight="1">
-      <c r="A39" s="61" t="s">
+      <c r="A39" s="60" t="s">
         <v>55</v>
       </c>
-      <c r="B39" s="57"/>
-      <c r="C39" s="57"/>
-      <c r="D39" s="57"/>
-      <c r="E39" s="57"/>
-      <c r="F39" s="57"/>
-      <c r="G39" s="57"/>
-      <c r="H39" s="57"/>
-      <c r="I39" s="57"/>
-      <c r="J39" s="57"/>
-      <c r="K39" s="57"/>
-      <c r="L39" s="57"/>
-      <c r="M39" s="57"/>
-      <c r="N39" s="57"/>
-      <c r="O39" s="57"/>
-      <c r="P39" s="57"/>
-      <c r="Q39" s="58"/>
+      <c r="B39" s="56"/>
+      <c r="C39" s="56"/>
+      <c r="D39" s="56"/>
+      <c r="E39" s="56"/>
+      <c r="F39" s="56"/>
+      <c r="G39" s="56"/>
+      <c r="H39" s="56"/>
+      <c r="I39" s="56"/>
+      <c r="J39" s="56"/>
+      <c r="K39" s="56"/>
+      <c r="L39" s="56"/>
+      <c r="M39" s="56"/>
+      <c r="N39" s="56"/>
+      <c r="O39" s="56"/>
+      <c r="P39" s="56"/>
+      <c r="Q39" s="57"/>
     </row>
     <row r="40" spans="1:17" ht="17.25" customHeight="1">
-      <c r="A40" s="60"/>
-      <c r="B40" s="57"/>
-      <c r="C40" s="57"/>
-      <c r="D40" s="57"/>
-      <c r="E40" s="57"/>
-      <c r="F40" s="57"/>
-      <c r="G40" s="57"/>
-      <c r="H40" s="57"/>
-      <c r="I40" s="57"/>
-      <c r="J40" s="57"/>
-      <c r="K40" s="57"/>
-      <c r="L40" s="57"/>
-      <c r="M40" s="57"/>
-      <c r="N40" s="57"/>
-      <c r="O40" s="57"/>
-      <c r="P40" s="57"/>
-      <c r="Q40" s="58"/>
+      <c r="A40" s="59"/>
+      <c r="B40" s="56"/>
+      <c r="C40" s="56"/>
+      <c r="D40" s="56"/>
+      <c r="E40" s="56"/>
+      <c r="F40" s="56"/>
+      <c r="G40" s="56"/>
+      <c r="H40" s="56"/>
+      <c r="I40" s="56"/>
+      <c r="J40" s="56"/>
+      <c r="K40" s="56"/>
+      <c r="L40" s="56"/>
+      <c r="M40" s="56"/>
+      <c r="N40" s="56"/>
+      <c r="O40" s="56"/>
+      <c r="P40" s="56"/>
+      <c r="Q40" s="57"/>
     </row>
     <row r="41" spans="1:17" ht="17.25" customHeight="1">
-      <c r="A41" s="61" t="s">
+      <c r="A41" s="60" t="s">
         <v>56</v>
       </c>
-      <c r="B41" s="57"/>
-      <c r="C41" s="57"/>
-      <c r="D41" s="57"/>
-      <c r="E41" s="57"/>
-      <c r="F41" s="57"/>
-      <c r="G41" s="57"/>
-      <c r="H41" s="57"/>
-      <c r="I41" s="57"/>
-      <c r="J41" s="57"/>
-      <c r="K41" s="57"/>
-      <c r="L41" s="57"/>
-      <c r="M41" s="57"/>
-      <c r="N41" s="57"/>
-      <c r="O41" s="57"/>
-      <c r="P41" s="57"/>
-      <c r="Q41" s="58"/>
+      <c r="B41" s="56"/>
+      <c r="C41" s="56"/>
+      <c r="D41" s="56"/>
+      <c r="E41" s="56"/>
+      <c r="F41" s="56"/>
+      <c r="G41" s="56"/>
+      <c r="H41" s="56"/>
+      <c r="I41" s="56"/>
+      <c r="J41" s="56"/>
+      <c r="K41" s="56"/>
+      <c r="L41" s="56"/>
+      <c r="M41" s="56"/>
+      <c r="N41" s="56"/>
+      <c r="O41" s="56"/>
+      <c r="P41" s="56"/>
+      <c r="Q41" s="57"/>
     </row>
     <row r="42" spans="1:17" ht="17.25" customHeight="1">
-      <c r="A42" s="60"/>
-      <c r="B42" s="57"/>
-      <c r="C42" s="57"/>
-      <c r="D42" s="57"/>
-      <c r="E42" s="57"/>
-      <c r="F42" s="57"/>
-      <c r="G42" s="57"/>
-      <c r="H42" s="57"/>
-      <c r="I42" s="57"/>
-      <c r="J42" s="57"/>
-      <c r="K42" s="57"/>
-      <c r="L42" s="57"/>
-      <c r="M42" s="57"/>
-      <c r="N42" s="57"/>
-      <c r="O42" s="57"/>
-      <c r="P42" s="57"/>
-      <c r="Q42" s="58"/>
+      <c r="A42" s="59"/>
+      <c r="B42" s="56"/>
+      <c r="C42" s="56"/>
+      <c r="D42" s="56"/>
+      <c r="E42" s="56"/>
+      <c r="F42" s="56"/>
+      <c r="G42" s="56"/>
+      <c r="H42" s="56"/>
+      <c r="I42" s="56"/>
+      <c r="J42" s="56"/>
+      <c r="K42" s="56"/>
+      <c r="L42" s="56"/>
+      <c r="M42" s="56"/>
+      <c r="N42" s="56"/>
+      <c r="O42" s="56"/>
+      <c r="P42" s="56"/>
+      <c r="Q42" s="57"/>
     </row>
     <row r="43" spans="1:17" ht="17.25" customHeight="1">
-      <c r="A43" s="61" t="s">
+      <c r="A43" s="60" t="s">
         <v>57</v>
       </c>
-      <c r="B43" s="57"/>
-      <c r="C43" s="57"/>
-      <c r="D43" s="57"/>
-      <c r="E43" s="57"/>
-      <c r="F43" s="57"/>
-      <c r="G43" s="57"/>
-      <c r="H43" s="57"/>
-      <c r="I43" s="57"/>
-      <c r="J43" s="57"/>
-      <c r="K43" s="57"/>
-      <c r="L43" s="57"/>
-      <c r="M43" s="57"/>
-      <c r="N43" s="57"/>
-      <c r="O43" s="57"/>
-      <c r="P43" s="57"/>
-      <c r="Q43" s="58"/>
+      <c r="B43" s="56"/>
+      <c r="C43" s="56"/>
+      <c r="D43" s="56"/>
+      <c r="E43" s="56"/>
+      <c r="F43" s="56"/>
+      <c r="G43" s="56"/>
+      <c r="H43" s="56"/>
+      <c r="I43" s="56"/>
+      <c r="J43" s="56"/>
+      <c r="K43" s="56"/>
+      <c r="L43" s="56"/>
+      <c r="M43" s="56"/>
+      <c r="N43" s="56"/>
+      <c r="O43" s="56"/>
+      <c r="P43" s="56"/>
+      <c r="Q43" s="57"/>
     </row>
     <row r="44" spans="1:17" ht="17.25" customHeight="1">
-      <c r="A44" s="60"/>
-      <c r="B44" s="57"/>
-      <c r="C44" s="57"/>
-      <c r="D44" s="57"/>
-      <c r="E44" s="57"/>
-      <c r="F44" s="57"/>
-      <c r="G44" s="57"/>
-      <c r="H44" s="57"/>
-      <c r="I44" s="57"/>
-      <c r="J44" s="57"/>
-      <c r="K44" s="57"/>
-      <c r="L44" s="57"/>
-      <c r="M44" s="57"/>
-      <c r="N44" s="57"/>
-      <c r="O44" s="57"/>
-      <c r="P44" s="57"/>
-      <c r="Q44" s="58"/>
+      <c r="A44" s="59"/>
+      <c r="B44" s="56"/>
+      <c r="C44" s="56"/>
+      <c r="D44" s="56"/>
+      <c r="E44" s="56"/>
+      <c r="F44" s="56"/>
+      <c r="G44" s="56"/>
+      <c r="H44" s="56"/>
+      <c r="I44" s="56"/>
+      <c r="J44" s="56"/>
+      <c r="K44" s="56"/>
+      <c r="L44" s="56"/>
+      <c r="M44" s="56"/>
+      <c r="N44" s="56"/>
+      <c r="O44" s="56"/>
+      <c r="P44" s="56"/>
+      <c r="Q44" s="57"/>
     </row>
     <row r="45" spans="1:17" ht="17.25" customHeight="1">
-      <c r="A45" s="61" t="s">
+      <c r="A45" s="60" t="s">
         <v>58</v>
       </c>
-      <c r="B45" s="57"/>
-      <c r="C45" s="57"/>
-      <c r="D45" s="57"/>
-      <c r="E45" s="57"/>
-      <c r="F45" s="57"/>
-      <c r="G45" s="57"/>
-      <c r="H45" s="57"/>
-      <c r="I45" s="57"/>
-      <c r="J45" s="57"/>
-      <c r="K45" s="57"/>
-      <c r="L45" s="57"/>
-      <c r="M45" s="57"/>
-      <c r="N45" s="57"/>
-      <c r="O45" s="57"/>
-      <c r="P45" s="57"/>
-      <c r="Q45" s="58"/>
+      <c r="B45" s="56"/>
+      <c r="C45" s="56"/>
+      <c r="D45" s="56"/>
+      <c r="E45" s="56"/>
+      <c r="F45" s="56"/>
+      <c r="G45" s="56"/>
+      <c r="H45" s="56"/>
+      <c r="I45" s="56"/>
+      <c r="J45" s="56"/>
+      <c r="K45" s="56"/>
+      <c r="L45" s="56"/>
+      <c r="M45" s="56"/>
+      <c r="N45" s="56"/>
+      <c r="O45" s="56"/>
+      <c r="P45" s="56"/>
+      <c r="Q45" s="57"/>
     </row>
     <row r="46" spans="1:17" ht="17.25" customHeight="1">
-      <c r="A46" s="59"/>
-      <c r="B46" s="57"/>
-      <c r="C46" s="57"/>
-      <c r="D46" s="57"/>
-      <c r="E46" s="57"/>
-      <c r="F46" s="57"/>
-      <c r="G46" s="57"/>
-      <c r="H46" s="57"/>
-      <c r="I46" s="57"/>
-      <c r="J46" s="57"/>
-      <c r="K46" s="57"/>
-      <c r="L46" s="57"/>
-      <c r="M46" s="57"/>
-      <c r="N46" s="57"/>
-      <c r="O46" s="57"/>
-      <c r="P46" s="57"/>
-      <c r="Q46" s="58"/>
+      <c r="A46" s="58"/>
+      <c r="B46" s="56"/>
+      <c r="C46" s="56"/>
+      <c r="D46" s="56"/>
+      <c r="E46" s="56"/>
+      <c r="F46" s="56"/>
+      <c r="G46" s="56"/>
+      <c r="H46" s="56"/>
+      <c r="I46" s="56"/>
+      <c r="J46" s="56"/>
+      <c r="K46" s="56"/>
+      <c r="L46" s="56"/>
+      <c r="M46" s="56"/>
+      <c r="N46" s="56"/>
+      <c r="O46" s="56"/>
+      <c r="P46" s="56"/>
+      <c r="Q46" s="57"/>
     </row>
     <row r="47" spans="1:17" ht="18" customHeight="1" thickBot="1">
-      <c r="A47" s="62" t="s">
+      <c r="A47" s="61" t="s">
         <v>59</v>
       </c>
-      <c r="B47" s="63"/>
-      <c r="C47" s="63"/>
-      <c r="D47" s="63"/>
-      <c r="E47" s="63"/>
-      <c r="F47" s="63"/>
-      <c r="G47" s="63"/>
-      <c r="H47" s="63"/>
-      <c r="I47" s="63"/>
-      <c r="J47" s="63"/>
-      <c r="K47" s="63"/>
-      <c r="L47" s="63"/>
-      <c r="M47" s="63"/>
-      <c r="N47" s="63"/>
-      <c r="O47" s="63"/>
-      <c r="P47" s="63"/>
-      <c r="Q47" s="64"/>
+      <c r="B47" s="62"/>
+      <c r="C47" s="62"/>
+      <c r="D47" s="62"/>
+      <c r="E47" s="62"/>
+      <c r="F47" s="62"/>
+      <c r="G47" s="62"/>
+      <c r="H47" s="62"/>
+      <c r="I47" s="62"/>
+      <c r="J47" s="62"/>
+      <c r="K47" s="62"/>
+      <c r="L47" s="62"/>
+      <c r="M47" s="62"/>
+      <c r="N47" s="62"/>
+      <c r="O47" s="62"/>
+      <c r="P47" s="62"/>
+      <c r="Q47" s="63"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3585,26 +4234,26 @@
   <sheetData>
     <row r="1" spans="1:27" ht="17.25" customHeight="1" thickBot="1">
       <c r="A1" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="B1" s="68" t="s">
-        <v>156</v>
-      </c>
-      <c r="C1" s="68" t="s">
-        <v>157</v>
-      </c>
-      <c r="D1" s="68" t="s">
-        <v>158</v>
-      </c>
-      <c r="E1" s="68" t="s">
-        <v>159</v>
+        <v>128</v>
+      </c>
+      <c r="B1" s="67" t="s">
+        <v>129</v>
+      </c>
+      <c r="C1" s="67" t="s">
+        <v>130</v>
+      </c>
+      <c r="D1" s="67" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1" s="67" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:27">
-      <c r="A2" s="87" t="s">
-        <v>160</v>
-      </c>
-      <c r="H2" s="69" t="s">
+      <c r="A2" s="85" t="s">
+        <v>133</v>
+      </c>
+      <c r="H2" s="68" t="s">
         <v>51</v>
       </c>
       <c r="I2" s="29"/>
@@ -3629,121 +4278,121 @@
     </row>
     <row r="3" spans="1:27">
       <c r="A3" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="H3" s="53" t="s">
-        <v>162</v>
+        <v>134</v>
+      </c>
+      <c r="H3" s="52" t="s">
+        <v>135</v>
       </c>
       <c r="AA3" s="33"/>
     </row>
     <row r="4" spans="1:27">
-      <c r="A4" s="87" t="s">
-        <v>163</v>
-      </c>
-      <c r="H4" s="53" t="s">
-        <v>164</v>
+      <c r="A4" s="85" t="s">
+        <v>136</v>
+      </c>
+      <c r="H4" s="52" t="s">
+        <v>137</v>
       </c>
       <c r="AA4" s="33"/>
     </row>
     <row r="5" spans="1:27">
       <c r="A5" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="H5" s="53" t="s">
-        <v>166</v>
+        <v>138</v>
+      </c>
+      <c r="H5" s="52" t="s">
+        <v>139</v>
       </c>
       <c r="AA5" s="33"/>
     </row>
     <row r="6" spans="1:27">
-      <c r="A6" s="87" t="s">
-        <v>167</v>
-      </c>
-      <c r="H6" s="73"/>
+      <c r="A6" s="85" t="s">
+        <v>140</v>
+      </c>
+      <c r="H6" s="72"/>
       <c r="AA6" s="33"/>
     </row>
     <row r="7" spans="1:27">
       <c r="A7" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="H7" s="73" t="s">
-        <v>169</v>
+        <v>141</v>
+      </c>
+      <c r="H7" s="72" t="s">
+        <v>142</v>
       </c>
       <c r="AA7" s="33"/>
     </row>
     <row r="8" spans="1:27">
-      <c r="A8" s="87" t="s">
-        <v>170</v>
-      </c>
-      <c r="H8" s="73" t="s">
-        <v>171</v>
+      <c r="A8" s="85" t="s">
+        <v>143</v>
+      </c>
+      <c r="H8" s="72" t="s">
+        <v>144</v>
       </c>
       <c r="AA8" s="33"/>
     </row>
     <row r="9" spans="1:27">
       <c r="A9" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="H9" s="73" t="s">
-        <v>173</v>
+        <v>145</v>
+      </c>
+      <c r="H9" s="72" t="s">
+        <v>146</v>
       </c>
       <c r="AA9" s="33"/>
     </row>
     <row r="10" spans="1:27">
-      <c r="A10" s="87" t="s">
-        <v>174</v>
-      </c>
-      <c r="H10" s="73"/>
+      <c r="A10" s="85" t="s">
+        <v>147</v>
+      </c>
+      <c r="H10" s="72"/>
       <c r="AA10" s="33"/>
     </row>
     <row r="11" spans="1:27">
       <c r="A11" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="H11" s="73" t="s">
-        <v>176</v>
+        <v>148</v>
+      </c>
+      <c r="H11" s="72" t="s">
+        <v>149</v>
       </c>
       <c r="AA11" s="33"/>
     </row>
     <row r="12" spans="1:27">
-      <c r="A12" s="87" t="s">
-        <v>177</v>
-      </c>
-      <c r="H12" s="73"/>
+      <c r="A12" s="85" t="s">
+        <v>150</v>
+      </c>
+      <c r="H12" s="72"/>
       <c r="AA12" s="33"/>
     </row>
     <row r="13" spans="1:27">
       <c r="A13" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="H13" s="74" t="s">
-        <v>159</v>
+        <v>151</v>
+      </c>
+      <c r="H13" s="73" t="s">
+        <v>132</v>
       </c>
       <c r="AA13" s="33"/>
     </row>
     <row r="14" spans="1:27">
-      <c r="A14" s="87" t="s">
-        <v>256</v>
-      </c>
-      <c r="H14" s="74" t="s">
-        <v>179</v>
+      <c r="A14" s="85" t="s">
+        <v>229</v>
+      </c>
+      <c r="H14" s="73" t="s">
+        <v>152</v>
       </c>
       <c r="AA14" s="33"/>
     </row>
     <row r="15" spans="1:27">
       <c r="A15" s="13" t="s">
-        <v>257</v>
-      </c>
-      <c r="H15" s="75" t="s">
-        <v>180</v>
+        <v>230</v>
+      </c>
+      <c r="H15" s="74" t="s">
+        <v>153</v>
       </c>
       <c r="AA15" s="33"/>
     </row>
     <row r="16" spans="1:27" ht="17.25" customHeight="1" thickBot="1">
-      <c r="A16" s="87" t="s">
-        <v>258</v>
-      </c>
-      <c r="H16" s="76" t="s">
-        <v>181</v>
+      <c r="A16" s="85" t="s">
+        <v>231</v>
+      </c>
+      <c r="H16" s="75" t="s">
+        <v>154</v>
       </c>
       <c r="I16" s="37"/>
       <c r="J16" s="37"/>
@@ -3767,285 +4416,285 @@
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>259</v>
+        <v>232</v>
       </c>
     </row>
     <row r="18" spans="1:14">
-      <c r="A18" s="87" t="s">
-        <v>260</v>
+      <c r="A18" s="85" t="s">
+        <v>233</v>
       </c>
       <c r="H18" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="I18" s="66"/>
-      <c r="J18" s="66"/>
-      <c r="K18" s="66"/>
-      <c r="L18" s="66"/>
-      <c r="M18" s="66"/>
-      <c r="N18" s="66"/>
+      <c r="I18" s="65"/>
+      <c r="J18" s="65"/>
+      <c r="K18" s="65"/>
+      <c r="L18" s="65"/>
+      <c r="M18" s="65"/>
+      <c r="N18" s="65"/>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>261</v>
-      </c>
-      <c r="H19" s="88"/>
-      <c r="I19" s="66"/>
-      <c r="J19" s="66"/>
-      <c r="K19" s="66"/>
-      <c r="L19" s="66"/>
-      <c r="M19" s="66"/>
-      <c r="N19" s="66"/>
+        <v>234</v>
+      </c>
+      <c r="H19" s="86"/>
+      <c r="I19" s="65"/>
+      <c r="J19" s="65"/>
+      <c r="K19" s="65"/>
+      <c r="L19" s="65"/>
+      <c r="M19" s="65"/>
+      <c r="N19" s="65"/>
     </row>
     <row r="20" spans="1:14">
-      <c r="A20" s="87" t="s">
-        <v>262</v>
-      </c>
-      <c r="H20" s="89" t="s">
+      <c r="A20" s="85" t="s">
+        <v>235</v>
+      </c>
+      <c r="H20" s="87" t="s">
         <v>94</v>
       </c>
-      <c r="I20" s="66"/>
-      <c r="J20" s="66"/>
-      <c r="K20" s="66"/>
-      <c r="L20" s="66"/>
-      <c r="M20" s="66"/>
-      <c r="N20" s="66"/>
+      <c r="I20" s="65"/>
+      <c r="J20" s="65"/>
+      <c r="K20" s="65"/>
+      <c r="L20" s="65"/>
+      <c r="M20" s="65"/>
+      <c r="N20" s="65"/>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="13" t="s">
-        <v>263</v>
-      </c>
-      <c r="H21" s="90"/>
-      <c r="I21" s="66"/>
-      <c r="J21" s="66"/>
-      <c r="K21" s="66"/>
-      <c r="L21" s="66"/>
-      <c r="M21" s="66"/>
-      <c r="N21" s="66"/>
+        <v>236</v>
+      </c>
+      <c r="H21" s="88"/>
+      <c r="I21" s="65"/>
+      <c r="J21" s="65"/>
+      <c r="K21" s="65"/>
+      <c r="L21" s="65"/>
+      <c r="M21" s="65"/>
+      <c r="N21" s="65"/>
     </row>
     <row r="22" spans="1:14">
-      <c r="A22" s="87" t="s">
-        <v>264</v>
-      </c>
-      <c r="H22" s="89" t="s">
+      <c r="A22" s="85" t="s">
+        <v>237</v>
+      </c>
+      <c r="H22" s="87" t="s">
         <v>95</v>
       </c>
-      <c r="I22" s="66"/>
-      <c r="J22" s="66"/>
-      <c r="K22" s="66"/>
-      <c r="L22" s="66"/>
-      <c r="M22" s="66"/>
-      <c r="N22" s="66"/>
+      <c r="I22" s="65"/>
+      <c r="J22" s="65"/>
+      <c r="K22" s="65"/>
+      <c r="L22" s="65"/>
+      <c r="M22" s="65"/>
+      <c r="N22" s="65"/>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="13" t="s">
-        <v>265</v>
-      </c>
-      <c r="H23" s="90"/>
-      <c r="I23" s="66"/>
-      <c r="J23" s="66"/>
-      <c r="K23" s="66"/>
-      <c r="L23" s="66"/>
-      <c r="M23" s="66"/>
-      <c r="N23" s="66"/>
+        <v>238</v>
+      </c>
+      <c r="H23" s="88"/>
+      <c r="I23" s="65"/>
+      <c r="J23" s="65"/>
+      <c r="K23" s="65"/>
+      <c r="L23" s="65"/>
+      <c r="M23" s="65"/>
+      <c r="N23" s="65"/>
     </row>
     <row r="24" spans="1:14">
-      <c r="A24" s="87" t="s">
-        <v>266</v>
-      </c>
-      <c r="H24" s="89" t="s">
+      <c r="A24" s="85" t="s">
+        <v>239</v>
+      </c>
+      <c r="H24" s="87" t="s">
         <v>96</v>
       </c>
-      <c r="I24" s="66"/>
-      <c r="J24" s="66"/>
-      <c r="K24" s="66"/>
-      <c r="L24" s="66"/>
-      <c r="M24" s="66"/>
-      <c r="N24" s="66"/>
+      <c r="I24" s="65"/>
+      <c r="J24" s="65"/>
+      <c r="K24" s="65"/>
+      <c r="L24" s="65"/>
+      <c r="M24" s="65"/>
+      <c r="N24" s="65"/>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="13" t="s">
-        <v>267</v>
-      </c>
-      <c r="H25" s="90"/>
-      <c r="I25" s="66"/>
-      <c r="J25" s="66"/>
-      <c r="K25" s="66"/>
-      <c r="L25" s="66"/>
-      <c r="M25" s="66"/>
-      <c r="N25" s="66"/>
+        <v>240</v>
+      </c>
+      <c r="H25" s="88"/>
+      <c r="I25" s="65"/>
+      <c r="J25" s="65"/>
+      <c r="K25" s="65"/>
+      <c r="L25" s="65"/>
+      <c r="M25" s="65"/>
+      <c r="N25" s="65"/>
     </row>
     <row r="26" spans="1:14">
-      <c r="A26" s="87" t="s">
-        <v>268</v>
-      </c>
-      <c r="H26" s="89" t="s">
+      <c r="A26" s="85" t="s">
+        <v>241</v>
+      </c>
+      <c r="H26" s="87" t="s">
         <v>97</v>
       </c>
-      <c r="I26" s="66"/>
-      <c r="J26" s="66"/>
-      <c r="K26" s="66"/>
-      <c r="L26" s="66"/>
-      <c r="M26" s="66"/>
-      <c r="N26" s="66"/>
+      <c r="I26" s="65"/>
+      <c r="J26" s="65"/>
+      <c r="K26" s="65"/>
+      <c r="L26" s="65"/>
+      <c r="M26" s="65"/>
+      <c r="N26" s="65"/>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
-        <v>269</v>
-      </c>
-      <c r="H27" s="90"/>
-      <c r="I27" s="66"/>
-      <c r="J27" s="66"/>
-      <c r="K27" s="66"/>
-      <c r="L27" s="66"/>
-      <c r="M27" s="66"/>
-      <c r="N27" s="66"/>
+        <v>242</v>
+      </c>
+      <c r="H27" s="88"/>
+      <c r="I27" s="65"/>
+      <c r="J27" s="65"/>
+      <c r="K27" s="65"/>
+      <c r="L27" s="65"/>
+      <c r="M27" s="65"/>
+      <c r="N27" s="65"/>
     </row>
     <row r="28" spans="1:14">
-      <c r="A28" s="87" t="s">
-        <v>270</v>
-      </c>
-      <c r="H28" s="89" t="s">
+      <c r="A28" s="85" t="s">
+        <v>243</v>
+      </c>
+      <c r="H28" s="87" t="s">
         <v>98</v>
       </c>
-      <c r="I28" s="66"/>
-      <c r="J28" s="66"/>
-      <c r="K28" s="66"/>
-      <c r="L28" s="66"/>
-      <c r="M28" s="66"/>
-      <c r="N28" s="66"/>
+      <c r="I28" s="65"/>
+      <c r="J28" s="65"/>
+      <c r="K28" s="65"/>
+      <c r="L28" s="65"/>
+      <c r="M28" s="65"/>
+      <c r="N28" s="65"/>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
-        <v>271</v>
-      </c>
-      <c r="H29" s="90"/>
-      <c r="I29" s="66"/>
-      <c r="J29" s="66"/>
-      <c r="K29" s="66"/>
-      <c r="L29" s="66"/>
-      <c r="M29" s="66"/>
-      <c r="N29" s="66"/>
+        <v>244</v>
+      </c>
+      <c r="H29" s="88"/>
+      <c r="I29" s="65"/>
+      <c r="J29" s="65"/>
+      <c r="K29" s="65"/>
+      <c r="L29" s="65"/>
+      <c r="M29" s="65"/>
+      <c r="N29" s="65"/>
     </row>
     <row r="30" spans="1:14">
-      <c r="A30" s="87" t="s">
-        <v>272</v>
-      </c>
-      <c r="H30" s="89" t="s">
+      <c r="A30" s="85" t="s">
+        <v>245</v>
+      </c>
+      <c r="H30" s="87" t="s">
         <v>99</v>
       </c>
-      <c r="I30" s="66"/>
-      <c r="J30" s="66"/>
-      <c r="K30" s="66"/>
-      <c r="L30" s="66"/>
-      <c r="M30" s="66"/>
-      <c r="N30" s="66"/>
+      <c r="I30" s="65"/>
+      <c r="J30" s="65"/>
+      <c r="K30" s="65"/>
+      <c r="L30" s="65"/>
+      <c r="M30" s="65"/>
+      <c r="N30" s="65"/>
     </row>
     <row r="31" spans="1:14">
-      <c r="A31" s="87" t="s">
-        <v>273</v>
+      <c r="A31" s="85" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="13" t="s">
-        <v>274</v>
+        <v>247</v>
       </c>
       <c r="H32" s="23" t="s">
-        <v>182</v>
+        <v>155</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="87" t="s">
-        <v>275</v>
+      <c r="A33" s="85" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="13" t="s">
-        <v>276</v>
+        <v>249</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="87" t="s">
-        <v>277</v>
+      <c r="A35" s="85" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="13" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="87" t="s">
-        <v>279</v>
+      <c r="A37" s="85" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="13" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="87" t="s">
-        <v>281</v>
+      <c r="A39" s="85" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="13" t="s">
-        <v>282</v>
+        <v>255</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="87" t="s">
-        <v>283</v>
+      <c r="A41" s="85" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="13" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="87" t="s">
-        <v>285</v>
+      <c r="A43" s="85" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="13" t="s">
-        <v>286</v>
+        <v>259</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="87" t="s">
-        <v>287</v>
+      <c r="A45" s="85" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="13" t="s">
-        <v>288</v>
+        <v>261</v>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="87" t="s">
-        <v>289</v>
+      <c r="A47" s="85" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="13" t="s">
-        <v>290</v>
+        <v>263</v>
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="87" t="s">
-        <v>291</v>
+      <c r="A49" s="85" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="13" t="s">
-        <v>292</v>
+        <v>265</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="13" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -4066,16 +4715,16 @@
   <sheetData>
     <row r="1" spans="1:19" ht="17.25" customHeight="1" thickBot="1">
       <c r="A1" s="1" t="s">
-        <v>183</v>
+        <v>156</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>184</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2" spans="1:19">
       <c r="A2" s="12"/>
       <c r="B2" s="4"/>
-      <c r="E2" s="69" t="s">
+      <c r="E2" s="68" t="s">
         <v>51</v>
       </c>
       <c r="F2" s="29"/>
@@ -4096,116 +4745,116 @@
     <row r="3" spans="1:19">
       <c r="A3" s="12"/>
       <c r="B3" s="4"/>
-      <c r="E3" s="70" t="s">
-        <v>185</v>
+      <c r="E3" s="69" t="s">
+        <v>158</v>
       </c>
       <c r="S3" s="33"/>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
-      <c r="E4" s="71"/>
+      <c r="E4" s="70"/>
       <c r="S4" s="33"/>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
-      <c r="E5" s="70" t="s">
-        <v>186</v>
+      <c r="E5" s="69" t="s">
+        <v>159</v>
       </c>
       <c r="S5" s="33"/>
     </row>
     <row r="6" spans="1:19">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
-      <c r="E6" s="71"/>
+      <c r="E6" s="70"/>
       <c r="S6" s="33"/>
     </row>
     <row r="7" spans="1:19">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
-      <c r="E7" s="70" t="s">
-        <v>187</v>
+      <c r="E7" s="69" t="s">
+        <v>160</v>
       </c>
       <c r="S7" s="33"/>
     </row>
     <row r="8" spans="1:19">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
-      <c r="E8" s="70" t="s">
-        <v>188</v>
+      <c r="E8" s="69" t="s">
+        <v>161</v>
       </c>
       <c r="S8" s="33"/>
     </row>
     <row r="9" spans="1:19">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
-      <c r="E9" s="71" t="s">
-        <v>189</v>
+      <c r="E9" s="70" t="s">
+        <v>162</v>
       </c>
       <c r="S9" s="33"/>
     </row>
     <row r="10" spans="1:19">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
-      <c r="E10" s="71"/>
+      <c r="E10" s="70"/>
       <c r="S10" s="33"/>
     </row>
     <row r="11" spans="1:19">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
-      <c r="E11" s="70" t="s">
-        <v>190</v>
+      <c r="E11" s="69" t="s">
+        <v>163</v>
       </c>
       <c r="S11" s="33"/>
     </row>
     <row r="12" spans="1:19">
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
-      <c r="E12" s="70" t="s">
-        <v>191</v>
+      <c r="E12" s="69" t="s">
+        <v>164</v>
       </c>
       <c r="S12" s="33"/>
     </row>
     <row r="13" spans="1:19">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
-      <c r="E13" s="70" t="s">
-        <v>192</v>
+      <c r="E13" s="69" t="s">
+        <v>165</v>
       </c>
       <c r="S13" s="33"/>
     </row>
     <row r="14" spans="1:19">
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
-      <c r="E14" s="71" t="s">
-        <v>193</v>
+      <c r="E14" s="70" t="s">
+        <v>166</v>
       </c>
       <c r="S14" s="33"/>
     </row>
     <row r="15" spans="1:19">
-      <c r="E15" s="71"/>
+      <c r="E15" s="70"/>
       <c r="S15" s="33"/>
     </row>
     <row r="16" spans="1:19">
-      <c r="E16" s="71"/>
+      <c r="E16" s="70"/>
       <c r="S16" s="33"/>
     </row>
     <row r="17" spans="5:19">
-      <c r="E17" s="70" t="s">
-        <v>194</v>
+      <c r="E17" s="69" t="s">
+        <v>167</v>
       </c>
       <c r="S17" s="33"/>
     </row>
     <row r="18" spans="5:19">
-      <c r="E18" s="70" t="s">
-        <v>195</v>
+      <c r="E18" s="69" t="s">
+        <v>168</v>
       </c>
       <c r="S18" s="33"/>
     </row>
     <row r="19" spans="5:19" ht="17.25" customHeight="1" thickBot="1">
-      <c r="E19" s="72" t="s">
-        <v>196</v>
+      <c r="E19" s="71" t="s">
+        <v>169</v>
       </c>
       <c r="F19" s="37"/>
       <c r="G19" s="37"/>
@@ -4241,17 +4890,17 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>197</v>
+        <v>170</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>198</v>
+        <v>171</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>199</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="87" t="str">
+      <c r="A2" s="85" t="str">
         <f>IF(Nurses!A2="","",Nurses!A2)</f>
         <v>간호사1</v>
       </c>
@@ -4262,18 +4911,18 @@
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="87" t="str">
+      <c r="A3" s="85" t="str">
         <f>IF(Nurses!A3="","",Nurses!A3)</f>
         <v>간호사2</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
       <c r="F3" s="11" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="87" t="str">
+      <c r="A4" s="85" t="str">
         <f>IF(Nurses!A4="","",Nurses!A4)</f>
         <v>간호사3</v>
       </c>
@@ -4281,7 +4930,7 @@
       <c r="C4" s="4"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="87" t="str">
+      <c r="A5" s="85" t="str">
         <f>IF(Nurses!A5="","",Nurses!A5)</f>
         <v>간호사4</v>
       </c>
@@ -4289,7 +4938,7 @@
       <c r="C5" s="4"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="87" t="str">
+      <c r="A6" s="85" t="str">
         <f>IF(Nurses!A6="","",Nurses!A6)</f>
         <v>간호사5</v>
       </c>
@@ -4297,7 +4946,7 @@
       <c r="C6" s="4"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="87" t="str">
+      <c r="A7" s="85" t="str">
         <f>IF(Nurses!A7="","",Nurses!A7)</f>
         <v>간호사6</v>
       </c>
@@ -4305,7 +4954,7 @@
       <c r="C7" s="4"/>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="87" t="str">
+      <c r="A8" s="85" t="str">
         <f>IF(Nurses!A8="","",Nurses!A8)</f>
         <v>간호사7</v>
       </c>
@@ -4313,7 +4962,7 @@
       <c r="C8" s="4"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="87" t="str">
+      <c r="A9" s="85" t="str">
         <f>IF(Nurses!A9="","",Nurses!A9)</f>
         <v>간호사8</v>
       </c>
@@ -4321,7 +4970,7 @@
       <c r="C9" s="4"/>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="87" t="str">
+      <c r="A10" s="85" t="str">
         <f>IF(Nurses!A10="","",Nurses!A10)</f>
         <v>간호사9</v>
       </c>
@@ -4329,7 +4978,7 @@
       <c r="C10" s="4"/>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="87" t="str">
+      <c r="A11" s="85" t="str">
         <f>IF(Nurses!A11="","",Nurses!A11)</f>
         <v>간호사10</v>
       </c>
@@ -4337,7 +4986,7 @@
       <c r="C11" s="4"/>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="87" t="str">
+      <c r="A12" s="85" t="str">
         <f>IF(Nurses!A12="","",Nurses!A12)</f>
         <v>간호사11</v>
       </c>
@@ -4345,7 +4994,7 @@
       <c r="C12" s="4"/>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="87" t="str">
+      <c r="A13" s="85" t="str">
         <f>IF(Nurses!A13="","",Nurses!A13)</f>
         <v>간호사12</v>
       </c>
@@ -4353,7 +5002,7 @@
       <c r="C13" s="4"/>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="87" t="str">
+      <c r="A14" s="85" t="str">
         <f>IF(Nurses!A14="","",Nurses!A14)</f>
         <v>간호사13</v>
       </c>
@@ -4361,7 +5010,7 @@
       <c r="C14" s="4"/>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="87" t="str">
+      <c r="A15" s="85" t="str">
         <f>IF(Nurses!A15="","",Nurses!A15)</f>
         <v>간호사14</v>
       </c>
@@ -4369,7 +5018,7 @@
       <c r="C15" s="4"/>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="87" t="str">
+      <c r="A16" s="85" t="str">
         <f>IF(Nurses!A16="","",Nurses!A16)</f>
         <v>간호사15</v>
       </c>
@@ -4377,7 +5026,7 @@
       <c r="C16" s="4"/>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="87" t="str">
+      <c r="A17" s="85" t="str">
         <f>IF(Nurses!A17="","",Nurses!A17)</f>
         <v>간호사16</v>
       </c>
@@ -4385,7 +5034,7 @@
       <c r="C17" s="4"/>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="87" t="str">
+      <c r="A18" s="85" t="str">
         <f>IF(Nurses!A18="","",Nurses!A18)</f>
         <v>간호사17</v>
       </c>
@@ -4393,7 +5042,7 @@
       <c r="C18" s="4"/>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="87" t="str">
+      <c r="A19" s="85" t="str">
         <f>IF(Nurses!A19="","",Nurses!A19)</f>
         <v>간호사18</v>
       </c>
@@ -4401,7 +5050,7 @@
       <c r="C19" s="4"/>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="87" t="str">
+      <c r="A20" s="85" t="str">
         <f>IF(Nurses!A20="","",Nurses!A20)</f>
         <v>간호사19</v>
       </c>
@@ -4409,7 +5058,7 @@
       <c r="C20" s="4"/>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="87" t="str">
+      <c r="A21" s="85" t="str">
         <f>IF(Nurses!A21="","",Nurses!A21)</f>
         <v>간호사20</v>
       </c>
@@ -4417,7 +5066,7 @@
       <c r="C21" s="4"/>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="87" t="str">
+      <c r="A22" s="85" t="str">
         <f>IF(Nurses!A22="","",Nurses!A22)</f>
         <v>간호사21</v>
       </c>
@@ -4425,7 +5074,7 @@
       <c r="C22" s="4"/>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="87" t="str">
+      <c r="A23" s="85" t="str">
         <f>IF(Nurses!A23="","",Nurses!A23)</f>
         <v>간호사22</v>
       </c>
@@ -4433,7 +5082,7 @@
       <c r="C23" s="4"/>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="87" t="str">
+      <c r="A24" s="85" t="str">
         <f>IF(Nurses!A24="","",Nurses!A24)</f>
         <v>간호사23</v>
       </c>
@@ -4441,7 +5090,7 @@
       <c r="C24" s="4"/>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="87" t="str">
+      <c r="A25" s="85" t="str">
         <f>IF(Nurses!A25="","",Nurses!A25)</f>
         <v>간호사24</v>
       </c>
@@ -4449,7 +5098,7 @@
       <c r="C25" s="4"/>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="87" t="str">
+      <c r="A26" s="85" t="str">
         <f>IF(Nurses!A26="","",Nurses!A26)</f>
         <v>간호사25</v>
       </c>
@@ -4457,7 +5106,7 @@
       <c r="C26" s="4"/>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="87" t="str">
+      <c r="A27" s="85" t="str">
         <f>IF(Nurses!A27="","",Nurses!A27)</f>
         <v>간호사26</v>
       </c>
@@ -4465,7 +5114,7 @@
       <c r="C27" s="4"/>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="87" t="str">
+      <c r="A28" s="85" t="str">
         <f>IF(Nurses!A28="","",Nurses!A28)</f>
         <v>간호사27</v>
       </c>
@@ -4473,7 +5122,7 @@
       <c r="C28" s="4"/>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="87" t="str">
+      <c r="A29" s="85" t="str">
         <f>IF(Nurses!A29="","",Nurses!A29)</f>
         <v>간호사28</v>
       </c>
@@ -4481,7 +5130,7 @@
       <c r="C29" s="4"/>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="87" t="str">
+      <c r="A30" s="85" t="str">
         <f>IF(Nurses!A30="","",Nurses!A30)</f>
         <v>간호사29</v>
       </c>
@@ -4489,7 +5138,7 @@
       <c r="C30" s="4"/>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="87" t="str">
+      <c r="A31" s="85" t="str">
         <f>IF(Nurses!A31="","",Nurses!A31)</f>
         <v>간호사30</v>
       </c>
@@ -4497,7 +5146,7 @@
       <c r="C31" s="4"/>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="87" t="str">
+      <c r="A32" s="85" t="str">
         <f>IF(Nurses!A32="","",Nurses!A32)</f>
         <v>간호사31</v>
       </c>
@@ -4505,7 +5154,7 @@
       <c r="C32" s="4"/>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="87" t="str">
+      <c r="A33" s="85" t="str">
         <f>IF(Nurses!A33="","",Nurses!A33)</f>
         <v>간호사32</v>
       </c>
@@ -4513,7 +5162,7 @@
       <c r="C33" s="4"/>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="87" t="str">
+      <c r="A34" s="85" t="str">
         <f>IF(Nurses!A34="","",Nurses!A34)</f>
         <v>간호사33</v>
       </c>
@@ -4521,7 +5170,7 @@
       <c r="C34" s="4"/>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="87" t="str">
+      <c r="A35" s="85" t="str">
         <f>IF(Nurses!A35="","",Nurses!A35)</f>
         <v>간호사34</v>
       </c>
@@ -4529,7 +5178,7 @@
       <c r="C35" s="4"/>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="87" t="str">
+      <c r="A36" s="85" t="str">
         <f>IF(Nurses!A36="","",Nurses!A36)</f>
         <v>간호사35</v>
       </c>
@@ -4537,7 +5186,7 @@
       <c r="C36" s="4"/>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="87" t="str">
+      <c r="A37" s="85" t="str">
         <f>IF(Nurses!A37="","",Nurses!A37)</f>
         <v>간호사36</v>
       </c>
@@ -4545,7 +5194,7 @@
       <c r="C37" s="4"/>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38" s="87" t="str">
+      <c r="A38" s="85" t="str">
         <f>IF(Nurses!A38="","",Nurses!A38)</f>
         <v>간호사37</v>
       </c>
@@ -4553,7 +5202,7 @@
       <c r="C38" s="4"/>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="87" t="str">
+      <c r="A39" s="85" t="str">
         <f>IF(Nurses!A39="","",Nurses!A39)</f>
         <v>간호사38</v>
       </c>
@@ -4561,7 +5210,7 @@
       <c r="C39" s="4"/>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="87" t="str">
+      <c r="A40" s="85" t="str">
         <f>IF(Nurses!A40="","",Nurses!A40)</f>
         <v>간호사39</v>
       </c>
@@ -4569,7 +5218,7 @@
       <c r="C40" s="4"/>
     </row>
     <row r="41" spans="1:3">
-      <c r="A41" s="87" t="str">
+      <c r="A41" s="85" t="str">
         <f>IF(Nurses!A41="","",Nurses!A41)</f>
         <v>간호사40</v>
       </c>
@@ -4577,7 +5226,7 @@
       <c r="C41" s="4"/>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="87" t="str">
+      <c r="A42" s="85" t="str">
         <f>IF(Nurses!A42="","",Nurses!A42)</f>
         <v>간호사41</v>
       </c>
@@ -4585,7 +5234,7 @@
       <c r="C42" s="4"/>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="87" t="str">
+      <c r="A43" s="85" t="str">
         <f>IF(Nurses!A43="","",Nurses!A43)</f>
         <v>간호사42</v>
       </c>
@@ -4593,7 +5242,7 @@
       <c r="C43" s="4"/>
     </row>
     <row r="44" spans="1:3">
-      <c r="A44" s="87" t="str">
+      <c r="A44" s="85" t="str">
         <f>IF(Nurses!A44="","",Nurses!A44)</f>
         <v>간호사43</v>
       </c>
@@ -4601,7 +5250,7 @@
       <c r="C44" s="4"/>
     </row>
     <row r="45" spans="1:3">
-      <c r="A45" s="87" t="str">
+      <c r="A45" s="85" t="str">
         <f>IF(Nurses!A45="","",Nurses!A45)</f>
         <v>간호사44</v>
       </c>
@@ -4609,7 +5258,7 @@
       <c r="C45" s="4"/>
     </row>
     <row r="46" spans="1:3">
-      <c r="A46" s="87" t="str">
+      <c r="A46" s="85" t="str">
         <f>IF(Nurses!A46="","",Nurses!A46)</f>
         <v>간호사45</v>
       </c>
@@ -4617,7 +5266,7 @@
       <c r="C46" s="4"/>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47" s="87" t="str">
+      <c r="A47" s="85" t="str">
         <f>IF(Nurses!A47="","",Nurses!A47)</f>
         <v>간호사46</v>
       </c>
@@ -4625,7 +5274,7 @@
       <c r="C47" s="4"/>
     </row>
     <row r="48" spans="1:3">
-      <c r="A48" s="87" t="str">
+      <c r="A48" s="85" t="str">
         <f>IF(Nurses!A48="","",Nurses!A48)</f>
         <v>간호사47</v>
       </c>
@@ -4633,7 +5282,7 @@
       <c r="C48" s="4"/>
     </row>
     <row r="49" spans="1:3">
-      <c r="A49" s="87" t="str">
+      <c r="A49" s="85" t="str">
         <f>IF(Nurses!A49="","",Nurses!A49)</f>
         <v>간호사48</v>
       </c>
@@ -4641,7 +5290,7 @@
       <c r="C49" s="4"/>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="87" t="str">
+      <c r="A50" s="85" t="str">
         <f>IF(Nurses!A50="","",Nurses!A50)</f>
         <v>간호사49</v>
       </c>
@@ -4649,7 +5298,7 @@
       <c r="C50" s="4"/>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" s="87" t="str">
+      <c r="A51" s="85" t="str">
         <f>IF(Nurses!A51="","",Nurses!A51)</f>
         <v>간호사50</v>
       </c>
@@ -4673,7 +5322,7 @@
   <sheetData>
     <row r="1" spans="1:45" ht="17.25" customHeight="1">
       <c r="A1" s="5" t="s">
-        <v>197</v>
+        <v>170</v>
       </c>
       <c r="B1" s="5">
         <v>1</v>
@@ -4769,12 +5418,12 @@
         <v>31</v>
       </c>
       <c r="AG1" s="6"/>
-      <c r="AH1" s="78" t="s">
+      <c r="AH1" s="77" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:45" ht="17.25" customHeight="1">
-      <c r="A2" s="87" t="str">
+      <c r="A2" s="85" t="str">
         <f>IF(Nurses!A2="","",Nurses!A2)</f>
         <v>간호사1</v>
       </c>
@@ -4810,23 +5459,23 @@
       <c r="AE2" s="7"/>
       <c r="AF2" s="7"/>
       <c r="AG2" s="6"/>
-      <c r="AH2" s="79" t="s">
-        <v>201</v>
-      </c>
-      <c r="AI2" s="77"/>
-      <c r="AJ2" s="77"/>
-      <c r="AK2" s="77"/>
-      <c r="AL2" s="77"/>
-      <c r="AM2" s="77"/>
-      <c r="AN2" s="77"/>
-      <c r="AO2" s="77"/>
-      <c r="AP2" s="77"/>
-      <c r="AQ2" s="77"/>
-      <c r="AR2" s="77"/>
-      <c r="AS2" s="77"/>
+      <c r="AH2" s="78" t="s">
+        <v>174</v>
+      </c>
+      <c r="AI2" s="76"/>
+      <c r="AJ2" s="76"/>
+      <c r="AK2" s="76"/>
+      <c r="AL2" s="76"/>
+      <c r="AM2" s="76"/>
+      <c r="AN2" s="76"/>
+      <c r="AO2" s="76"/>
+      <c r="AP2" s="76"/>
+      <c r="AQ2" s="76"/>
+      <c r="AR2" s="76"/>
+      <c r="AS2" s="76"/>
     </row>
     <row r="3" spans="1:45" ht="17.25" customHeight="1">
-      <c r="A3" s="87" t="str">
+      <c r="A3" s="85" t="str">
         <f>IF(Nurses!A3="","",Nurses!A3)</f>
         <v>간호사2</v>
       </c>
@@ -4862,23 +5511,23 @@
       <c r="AE3" s="7"/>
       <c r="AF3" s="7"/>
       <c r="AG3" s="6"/>
-      <c r="AH3" s="80" t="s">
-        <v>202</v>
-      </c>
-      <c r="AI3" s="77"/>
-      <c r="AJ3" s="77"/>
-      <c r="AK3" s="77"/>
-      <c r="AL3" s="77"/>
-      <c r="AM3" s="77"/>
-      <c r="AN3" s="77"/>
-      <c r="AO3" s="77"/>
-      <c r="AP3" s="77"/>
-      <c r="AQ3" s="77"/>
-      <c r="AR3" s="77"/>
-      <c r="AS3" s="77"/>
+      <c r="AH3" s="79" t="s">
+        <v>175</v>
+      </c>
+      <c r="AI3" s="76"/>
+      <c r="AJ3" s="76"/>
+      <c r="AK3" s="76"/>
+      <c r="AL3" s="76"/>
+      <c r="AM3" s="76"/>
+      <c r="AN3" s="76"/>
+      <c r="AO3" s="76"/>
+      <c r="AP3" s="76"/>
+      <c r="AQ3" s="76"/>
+      <c r="AR3" s="76"/>
+      <c r="AS3" s="76"/>
     </row>
     <row r="4" spans="1:45" ht="17.25" customHeight="1">
-      <c r="A4" s="87" t="str">
+      <c r="A4" s="85" t="str">
         <f>IF(Nurses!A4="","",Nurses!A4)</f>
         <v>간호사3</v>
       </c>
@@ -4914,23 +5563,23 @@
       <c r="AE4" s="7"/>
       <c r="AF4" s="7"/>
       <c r="AG4" s="6"/>
-      <c r="AH4" s="80" t="s">
-        <v>203</v>
-      </c>
-      <c r="AI4" s="77"/>
-      <c r="AJ4" s="77"/>
-      <c r="AK4" s="77"/>
-      <c r="AL4" s="77"/>
-      <c r="AM4" s="77"/>
-      <c r="AN4" s="77"/>
-      <c r="AO4" s="77"/>
-      <c r="AP4" s="77"/>
-      <c r="AQ4" s="77"/>
-      <c r="AR4" s="77"/>
-      <c r="AS4" s="77"/>
+      <c r="AH4" s="79" t="s">
+        <v>176</v>
+      </c>
+      <c r="AI4" s="76"/>
+      <c r="AJ4" s="76"/>
+      <c r="AK4" s="76"/>
+      <c r="AL4" s="76"/>
+      <c r="AM4" s="76"/>
+      <c r="AN4" s="76"/>
+      <c r="AO4" s="76"/>
+      <c r="AP4" s="76"/>
+      <c r="AQ4" s="76"/>
+      <c r="AR4" s="76"/>
+      <c r="AS4" s="76"/>
     </row>
     <row r="5" spans="1:45" ht="17.25" customHeight="1">
-      <c r="A5" s="87" t="str">
+      <c r="A5" s="85" t="str">
         <f>IF(Nurses!A5="","",Nurses!A5)</f>
         <v>간호사4</v>
       </c>
@@ -4966,21 +5615,21 @@
       <c r="AE5" s="7"/>
       <c r="AF5" s="7"/>
       <c r="AG5" s="6"/>
-      <c r="AH5" s="80"/>
-      <c r="AI5" s="77"/>
-      <c r="AJ5" s="77"/>
-      <c r="AK5" s="77"/>
-      <c r="AL5" s="77"/>
-      <c r="AM5" s="77"/>
-      <c r="AN5" s="77"/>
-      <c r="AO5" s="77"/>
-      <c r="AP5" s="77"/>
-      <c r="AQ5" s="77"/>
-      <c r="AR5" s="77"/>
-      <c r="AS5" s="77"/>
+      <c r="AH5" s="79"/>
+      <c r="AI5" s="76"/>
+      <c r="AJ5" s="76"/>
+      <c r="AK5" s="76"/>
+      <c r="AL5" s="76"/>
+      <c r="AM5" s="76"/>
+      <c r="AN5" s="76"/>
+      <c r="AO5" s="76"/>
+      <c r="AP5" s="76"/>
+      <c r="AQ5" s="76"/>
+      <c r="AR5" s="76"/>
+      <c r="AS5" s="76"/>
     </row>
     <row r="6" spans="1:45" ht="17.25" customHeight="1">
-      <c r="A6" s="87" t="str">
+      <c r="A6" s="85" t="str">
         <f>IF(Nurses!A6="","",Nurses!A6)</f>
         <v>간호사5</v>
       </c>
@@ -5016,23 +5665,23 @@
       <c r="AE6" s="7"/>
       <c r="AF6" s="7"/>
       <c r="AG6" s="6"/>
-      <c r="AH6" s="79" t="s">
-        <v>204</v>
-      </c>
-      <c r="AI6" s="77"/>
-      <c r="AJ6" s="77"/>
-      <c r="AK6" s="77"/>
-      <c r="AL6" s="77"/>
-      <c r="AM6" s="77"/>
-      <c r="AN6" s="77"/>
-      <c r="AO6" s="77"/>
-      <c r="AP6" s="77"/>
-      <c r="AQ6" s="77"/>
-      <c r="AR6" s="77"/>
-      <c r="AS6" s="77"/>
+      <c r="AH6" s="78" t="s">
+        <v>177</v>
+      </c>
+      <c r="AI6" s="76"/>
+      <c r="AJ6" s="76"/>
+      <c r="AK6" s="76"/>
+      <c r="AL6" s="76"/>
+      <c r="AM6" s="76"/>
+      <c r="AN6" s="76"/>
+      <c r="AO6" s="76"/>
+      <c r="AP6" s="76"/>
+      <c r="AQ6" s="76"/>
+      <c r="AR6" s="76"/>
+      <c r="AS6" s="76"/>
     </row>
     <row r="7" spans="1:45" ht="17.25" customHeight="1">
-      <c r="A7" s="87" t="str">
+      <c r="A7" s="85" t="str">
         <f>IF(Nurses!A7="","",Nurses!A7)</f>
         <v>간호사6</v>
       </c>
@@ -5068,23 +5717,23 @@
       <c r="AE7" s="7"/>
       <c r="AF7" s="7"/>
       <c r="AG7" s="6"/>
-      <c r="AH7" s="80" t="s">
-        <v>205</v>
-      </c>
-      <c r="AI7" s="77"/>
-      <c r="AJ7" s="77"/>
-      <c r="AK7" s="77"/>
-      <c r="AL7" s="77"/>
-      <c r="AM7" s="77"/>
-      <c r="AN7" s="77"/>
-      <c r="AO7" s="77"/>
-      <c r="AP7" s="77"/>
-      <c r="AQ7" s="77"/>
-      <c r="AR7" s="77"/>
-      <c r="AS7" s="77"/>
+      <c r="AH7" s="79" t="s">
+        <v>178</v>
+      </c>
+      <c r="AI7" s="76"/>
+      <c r="AJ7" s="76"/>
+      <c r="AK7" s="76"/>
+      <c r="AL7" s="76"/>
+      <c r="AM7" s="76"/>
+      <c r="AN7" s="76"/>
+      <c r="AO7" s="76"/>
+      <c r="AP7" s="76"/>
+      <c r="AQ7" s="76"/>
+      <c r="AR7" s="76"/>
+      <c r="AS7" s="76"/>
     </row>
     <row r="8" spans="1:45" ht="17.25" customHeight="1">
-      <c r="A8" s="87" t="str">
+      <c r="A8" s="85" t="str">
         <f>IF(Nurses!A8="","",Nurses!A8)</f>
         <v>간호사7</v>
       </c>
@@ -5120,21 +5769,21 @@
       <c r="AE8" s="7"/>
       <c r="AF8" s="7"/>
       <c r="AG8" s="6"/>
-      <c r="AH8" s="81"/>
-      <c r="AI8" s="77"/>
-      <c r="AJ8" s="77"/>
-      <c r="AK8" s="77"/>
-      <c r="AL8" s="77"/>
-      <c r="AM8" s="77"/>
-      <c r="AN8" s="77"/>
-      <c r="AO8" s="77"/>
-      <c r="AP8" s="77"/>
-      <c r="AQ8" s="77"/>
-      <c r="AR8" s="77"/>
-      <c r="AS8" s="77"/>
+      <c r="AH8" s="80"/>
+      <c r="AI8" s="76"/>
+      <c r="AJ8" s="76"/>
+      <c r="AK8" s="76"/>
+      <c r="AL8" s="76"/>
+      <c r="AM8" s="76"/>
+      <c r="AN8" s="76"/>
+      <c r="AO8" s="76"/>
+      <c r="AP8" s="76"/>
+      <c r="AQ8" s="76"/>
+      <c r="AR8" s="76"/>
+      <c r="AS8" s="76"/>
     </row>
     <row r="9" spans="1:45" ht="17.25" customHeight="1">
-      <c r="A9" s="87" t="str">
+      <c r="A9" s="85" t="str">
         <f>IF(Nurses!A9="","",Nurses!A9)</f>
         <v>간호사8</v>
       </c>
@@ -5170,23 +5819,23 @@
       <c r="AE9" s="7"/>
       <c r="AF9" s="7"/>
       <c r="AG9" s="6"/>
-      <c r="AH9" s="79" t="s">
-        <v>206</v>
-      </c>
-      <c r="AI9" s="77"/>
-      <c r="AJ9" s="77"/>
-      <c r="AK9" s="77"/>
-      <c r="AL9" s="77"/>
-      <c r="AM9" s="77"/>
-      <c r="AN9" s="77"/>
-      <c r="AO9" s="77"/>
-      <c r="AP9" s="77"/>
-      <c r="AQ9" s="77"/>
-      <c r="AR9" s="77"/>
-      <c r="AS9" s="77"/>
+      <c r="AH9" s="78" t="s">
+        <v>179</v>
+      </c>
+      <c r="AI9" s="76"/>
+      <c r="AJ9" s="76"/>
+      <c r="AK9" s="76"/>
+      <c r="AL9" s="76"/>
+      <c r="AM9" s="76"/>
+      <c r="AN9" s="76"/>
+      <c r="AO9" s="76"/>
+      <c r="AP9" s="76"/>
+      <c r="AQ9" s="76"/>
+      <c r="AR9" s="76"/>
+      <c r="AS9" s="76"/>
     </row>
     <row r="10" spans="1:45" ht="17.25" customHeight="1">
-      <c r="A10" s="87" t="str">
+      <c r="A10" s="85" t="str">
         <f>IF(Nurses!A10="","",Nurses!A10)</f>
         <v>간호사9</v>
       </c>
@@ -5222,23 +5871,23 @@
       <c r="AE10" s="7"/>
       <c r="AF10" s="7"/>
       <c r="AG10" s="6"/>
-      <c r="AH10" s="80" t="s">
-        <v>207</v>
-      </c>
-      <c r="AI10" s="77"/>
-      <c r="AJ10" s="77"/>
-      <c r="AK10" s="77"/>
-      <c r="AL10" s="77"/>
-      <c r="AM10" s="77"/>
-      <c r="AN10" s="77"/>
-      <c r="AO10" s="77"/>
-      <c r="AP10" s="77"/>
-      <c r="AQ10" s="77"/>
-      <c r="AR10" s="77"/>
-      <c r="AS10" s="77"/>
+      <c r="AH10" s="79" t="s">
+        <v>180</v>
+      </c>
+      <c r="AI10" s="76"/>
+      <c r="AJ10" s="76"/>
+      <c r="AK10" s="76"/>
+      <c r="AL10" s="76"/>
+      <c r="AM10" s="76"/>
+      <c r="AN10" s="76"/>
+      <c r="AO10" s="76"/>
+      <c r="AP10" s="76"/>
+      <c r="AQ10" s="76"/>
+      <c r="AR10" s="76"/>
+      <c r="AS10" s="76"/>
     </row>
     <row r="11" spans="1:45" ht="17.25" customHeight="1">
-      <c r="A11" s="87" t="str">
+      <c r="A11" s="85" t="str">
         <f>IF(Nurses!A11="","",Nurses!A11)</f>
         <v>간호사10</v>
       </c>
@@ -5274,21 +5923,21 @@
       <c r="AE11" s="7"/>
       <c r="AF11" s="7"/>
       <c r="AG11" s="6"/>
-      <c r="AH11" s="81"/>
-      <c r="AI11" s="77"/>
-      <c r="AJ11" s="77"/>
-      <c r="AK11" s="77"/>
-      <c r="AL11" s="77"/>
-      <c r="AM11" s="77"/>
-      <c r="AN11" s="77"/>
-      <c r="AO11" s="77"/>
-      <c r="AP11" s="77"/>
-      <c r="AQ11" s="77"/>
-      <c r="AR11" s="77"/>
-      <c r="AS11" s="77"/>
+      <c r="AH11" s="80"/>
+      <c r="AI11" s="76"/>
+      <c r="AJ11" s="76"/>
+      <c r="AK11" s="76"/>
+      <c r="AL11" s="76"/>
+      <c r="AM11" s="76"/>
+      <c r="AN11" s="76"/>
+      <c r="AO11" s="76"/>
+      <c r="AP11" s="76"/>
+      <c r="AQ11" s="76"/>
+      <c r="AR11" s="76"/>
+      <c r="AS11" s="76"/>
     </row>
     <row r="12" spans="1:45" ht="17.25" customHeight="1">
-      <c r="A12" s="87" t="str">
+      <c r="A12" s="85" t="str">
         <f>IF(Nurses!A12="","",Nurses!A12)</f>
         <v>간호사11</v>
       </c>
@@ -5324,23 +5973,23 @@
       <c r="AE12" s="7"/>
       <c r="AF12" s="7"/>
       <c r="AG12" s="6"/>
-      <c r="AH12" s="80" t="s">
-        <v>208</v>
-      </c>
-      <c r="AI12" s="77"/>
-      <c r="AJ12" s="77"/>
-      <c r="AK12" s="77"/>
-      <c r="AL12" s="77"/>
-      <c r="AM12" s="77"/>
-      <c r="AN12" s="77"/>
-      <c r="AO12" s="77"/>
-      <c r="AP12" s="77"/>
-      <c r="AQ12" s="77"/>
-      <c r="AR12" s="77"/>
-      <c r="AS12" s="77"/>
+      <c r="AH12" s="79" t="s">
+        <v>181</v>
+      </c>
+      <c r="AI12" s="76"/>
+      <c r="AJ12" s="76"/>
+      <c r="AK12" s="76"/>
+      <c r="AL12" s="76"/>
+      <c r="AM12" s="76"/>
+      <c r="AN12" s="76"/>
+      <c r="AO12" s="76"/>
+      <c r="AP12" s="76"/>
+      <c r="AQ12" s="76"/>
+      <c r="AR12" s="76"/>
+      <c r="AS12" s="76"/>
     </row>
     <row r="13" spans="1:45" ht="17.25" customHeight="1">
-      <c r="A13" s="87" t="str">
+      <c r="A13" s="85" t="str">
         <f>IF(Nurses!A13="","",Nurses!A13)</f>
         <v>간호사12</v>
       </c>
@@ -5376,23 +6025,23 @@
       <c r="AE13" s="7"/>
       <c r="AF13" s="7"/>
       <c r="AG13" s="6"/>
-      <c r="AH13" s="81" t="s">
-        <v>209</v>
-      </c>
-      <c r="AI13" s="77"/>
-      <c r="AJ13" s="77"/>
-      <c r="AK13" s="77"/>
-      <c r="AL13" s="77"/>
-      <c r="AM13" s="77"/>
-      <c r="AN13" s="77"/>
-      <c r="AO13" s="77"/>
-      <c r="AP13" s="77"/>
-      <c r="AQ13" s="77"/>
-      <c r="AR13" s="77"/>
-      <c r="AS13" s="77"/>
+      <c r="AH13" s="80" t="s">
+        <v>182</v>
+      </c>
+      <c r="AI13" s="76"/>
+      <c r="AJ13" s="76"/>
+      <c r="AK13" s="76"/>
+      <c r="AL13" s="76"/>
+      <c r="AM13" s="76"/>
+      <c r="AN13" s="76"/>
+      <c r="AO13" s="76"/>
+      <c r="AP13" s="76"/>
+      <c r="AQ13" s="76"/>
+      <c r="AR13" s="76"/>
+      <c r="AS13" s="76"/>
     </row>
     <row r="14" spans="1:45" ht="17.25" customHeight="1">
-      <c r="A14" s="87" t="str">
+      <c r="A14" s="85" t="str">
         <f>IF(Nurses!A14="","",Nurses!A14)</f>
         <v>간호사13</v>
       </c>
@@ -5427,23 +6076,23 @@
       <c r="AD14" s="7"/>
       <c r="AE14" s="7"/>
       <c r="AF14" s="7"/>
-      <c r="AH14" s="81" t="s">
-        <v>210</v>
-      </c>
-      <c r="AI14" s="77"/>
-      <c r="AJ14" s="77"/>
-      <c r="AK14" s="77"/>
-      <c r="AL14" s="77"/>
-      <c r="AM14" s="77"/>
-      <c r="AN14" s="77"/>
-      <c r="AO14" s="77"/>
-      <c r="AP14" s="77"/>
-      <c r="AQ14" s="77"/>
-      <c r="AR14" s="77"/>
-      <c r="AS14" s="77"/>
+      <c r="AH14" s="80" t="s">
+        <v>183</v>
+      </c>
+      <c r="AI14" s="76"/>
+      <c r="AJ14" s="76"/>
+      <c r="AK14" s="76"/>
+      <c r="AL14" s="76"/>
+      <c r="AM14" s="76"/>
+      <c r="AN14" s="76"/>
+      <c r="AO14" s="76"/>
+      <c r="AP14" s="76"/>
+      <c r="AQ14" s="76"/>
+      <c r="AR14" s="76"/>
+      <c r="AS14" s="76"/>
     </row>
     <row r="15" spans="1:45">
-      <c r="A15" s="87" t="str">
+      <c r="A15" s="85" t="str">
         <f>IF(Nurses!A15="","",Nurses!A15)</f>
         <v>간호사14</v>
       </c>
@@ -5480,7 +6129,7 @@
       <c r="AF15" s="7"/>
     </row>
     <row r="16" spans="1:45">
-      <c r="A16" s="87" t="str">
+      <c r="A16" s="85" t="str">
         <f>IF(Nurses!A16="","",Nurses!A16)</f>
         <v>간호사15</v>
       </c>
@@ -5517,7 +6166,7 @@
       <c r="AF16" s="7"/>
     </row>
     <row r="17" spans="1:34">
-      <c r="A17" s="87" t="str">
+      <c r="A17" s="85" t="str">
         <f>IF(Nurses!A17="","",Nurses!A17)</f>
         <v>간호사16</v>
       </c>
@@ -5554,7 +6203,7 @@
       <c r="AF17" s="7"/>
     </row>
     <row r="18" spans="1:34">
-      <c r="A18" s="87" t="str">
+      <c r="A18" s="85" t="str">
         <f>IF(Nurses!A18="","",Nurses!A18)</f>
         <v>간호사17</v>
       </c>
@@ -5592,7 +6241,7 @@
       <c r="AH18" s="19"/>
     </row>
     <row r="19" spans="1:34">
-      <c r="A19" s="87" t="str">
+      <c r="A19" s="85" t="str">
         <f>IF(Nurses!A19="","",Nurses!A19)</f>
         <v>간호사18</v>
       </c>
@@ -5629,7 +6278,7 @@
       <c r="AF19" s="7"/>
     </row>
     <row r="20" spans="1:34">
-      <c r="A20" s="87" t="str">
+      <c r="A20" s="85" t="str">
         <f>IF(Nurses!A20="","",Nurses!A20)</f>
         <v>간호사19</v>
       </c>
@@ -5667,7 +6316,7 @@
       <c r="AH20" s="16"/>
     </row>
     <row r="21" spans="1:34">
-      <c r="A21" s="87" t="str">
+      <c r="A21" s="85" t="str">
         <f>IF(Nurses!A21="","",Nurses!A21)</f>
         <v>간호사20</v>
       </c>
@@ -5704,7 +6353,7 @@
       <c r="AF21" s="7"/>
     </row>
     <row r="22" spans="1:34">
-      <c r="A22" s="87" t="str">
+      <c r="A22" s="85" t="str">
         <f>IF(Nurses!A22="","",Nurses!A22)</f>
         <v>간호사21</v>
       </c>
@@ -5741,7 +6390,7 @@
       <c r="AF22" s="7"/>
     </row>
     <row r="23" spans="1:34">
-      <c r="A23" s="87" t="str">
+      <c r="A23" s="85" t="str">
         <f>IF(Nurses!A23="","",Nurses!A23)</f>
         <v>간호사22</v>
       </c>
@@ -5778,7 +6427,7 @@
       <c r="AF23" s="7"/>
     </row>
     <row r="24" spans="1:34">
-      <c r="A24" s="87" t="str">
+      <c r="A24" s="85" t="str">
         <f>IF(Nurses!A24="","",Nurses!A24)</f>
         <v>간호사23</v>
       </c>
@@ -5815,7 +6464,7 @@
       <c r="AF24" s="7"/>
     </row>
     <row r="25" spans="1:34">
-      <c r="A25" s="87" t="str">
+      <c r="A25" s="85" t="str">
         <f>IF(Nurses!A25="","",Nurses!A25)</f>
         <v>간호사24</v>
       </c>
@@ -5853,7 +6502,7 @@
       <c r="AH25" s="19"/>
     </row>
     <row r="26" spans="1:34">
-      <c r="A26" s="87" t="str">
+      <c r="A26" s="85" t="str">
         <f>IF(Nurses!A26="","",Nurses!A26)</f>
         <v>간호사25</v>
       </c>
@@ -5891,7 +6540,7 @@
       <c r="AH26" s="19"/>
     </row>
     <row r="27" spans="1:34">
-      <c r="A27" s="87" t="str">
+      <c r="A27" s="85" t="str">
         <f>IF(Nurses!A27="","",Nurses!A27)</f>
         <v>간호사26</v>
       </c>
@@ -5928,7 +6577,7 @@
       <c r="AF27" s="7"/>
     </row>
     <row r="28" spans="1:34">
-      <c r="A28" s="87" t="str">
+      <c r="A28" s="85" t="str">
         <f>IF(Nurses!A28="","",Nurses!A28)</f>
         <v>간호사27</v>
       </c>
@@ -5965,7 +6614,7 @@
       <c r="AF28" s="7"/>
     </row>
     <row r="29" spans="1:34">
-      <c r="A29" s="87" t="str">
+      <c r="A29" s="85" t="str">
         <f>IF(Nurses!A29="","",Nurses!A29)</f>
         <v>간호사28</v>
       </c>
@@ -6002,7 +6651,7 @@
       <c r="AF29" s="7"/>
     </row>
     <row r="30" spans="1:34">
-      <c r="A30" s="87" t="str">
+      <c r="A30" s="85" t="str">
         <f>IF(Nurses!A30="","",Nurses!A30)</f>
         <v>간호사29</v>
       </c>
@@ -6039,7 +6688,7 @@
       <c r="AF30" s="7"/>
     </row>
     <row r="31" spans="1:34">
-      <c r="A31" s="87" t="str">
+      <c r="A31" s="85" t="str">
         <f>IF(Nurses!A31="","",Nurses!A31)</f>
         <v>간호사30</v>
       </c>
@@ -6076,7 +6725,7 @@
       <c r="AF31" s="7"/>
     </row>
     <row r="32" spans="1:34">
-      <c r="A32" s="87" t="str">
+      <c r="A32" s="85" t="str">
         <f>IF(Nurses!A32="","",Nurses!A32)</f>
         <v>간호사31</v>
       </c>
@@ -6113,7 +6762,7 @@
       <c r="AF32" s="7"/>
     </row>
     <row r="33" spans="1:32">
-      <c r="A33" s="87" t="str">
+      <c r="A33" s="85" t="str">
         <f>IF(Nurses!A33="","",Nurses!A33)</f>
         <v>간호사32</v>
       </c>
@@ -6150,7 +6799,7 @@
       <c r="AF33" s="7"/>
     </row>
     <row r="34" spans="1:32">
-      <c r="A34" s="87" t="str">
+      <c r="A34" s="85" t="str">
         <f>IF(Nurses!A34="","",Nurses!A34)</f>
         <v>간호사33</v>
       </c>
@@ -6187,7 +6836,7 @@
       <c r="AF34" s="7"/>
     </row>
     <row r="35" spans="1:32">
-      <c r="A35" s="87" t="str">
+      <c r="A35" s="85" t="str">
         <f>IF(Nurses!A35="","",Nurses!A35)</f>
         <v>간호사34</v>
       </c>
@@ -6224,7 +6873,7 @@
       <c r="AF35" s="7"/>
     </row>
     <row r="36" spans="1:32">
-      <c r="A36" s="87" t="str">
+      <c r="A36" s="85" t="str">
         <f>IF(Nurses!A36="","",Nurses!A36)</f>
         <v>간호사35</v>
       </c>
@@ -6261,7 +6910,7 @@
       <c r="AF36" s="7"/>
     </row>
     <row r="37" spans="1:32">
-      <c r="A37" s="87" t="str">
+      <c r="A37" s="85" t="str">
         <f>IF(Nurses!A37="","",Nurses!A37)</f>
         <v>간호사36</v>
       </c>
@@ -6298,7 +6947,7 @@
       <c r="AF37" s="7"/>
     </row>
     <row r="38" spans="1:32">
-      <c r="A38" s="87" t="str">
+      <c r="A38" s="85" t="str">
         <f>IF(Nurses!A38="","",Nurses!A38)</f>
         <v>간호사37</v>
       </c>
@@ -6335,7 +6984,7 @@
       <c r="AF38" s="7"/>
     </row>
     <row r="39" spans="1:32">
-      <c r="A39" s="87" t="str">
+      <c r="A39" s="85" t="str">
         <f>IF(Nurses!A39="","",Nurses!A39)</f>
         <v>간호사38</v>
       </c>
@@ -6372,7 +7021,7 @@
       <c r="AF39" s="7"/>
     </row>
     <row r="40" spans="1:32">
-      <c r="A40" s="87" t="str">
+      <c r="A40" s="85" t="str">
         <f>IF(Nurses!A40="","",Nurses!A40)</f>
         <v>간호사39</v>
       </c>
@@ -6409,7 +7058,7 @@
       <c r="AF40" s="7"/>
     </row>
     <row r="41" spans="1:32">
-      <c r="A41" s="87" t="str">
+      <c r="A41" s="85" t="str">
         <f>IF(Nurses!A41="","",Nurses!A41)</f>
         <v>간호사40</v>
       </c>
@@ -6446,7 +7095,7 @@
       <c r="AF41" s="7"/>
     </row>
     <row r="42" spans="1:32">
-      <c r="A42" s="87" t="str">
+      <c r="A42" s="85" t="str">
         <f>IF(Nurses!A42="","",Nurses!A42)</f>
         <v>간호사41</v>
       </c>
@@ -6483,7 +7132,7 @@
       <c r="AF42" s="7"/>
     </row>
     <row r="43" spans="1:32">
-      <c r="A43" s="87" t="str">
+      <c r="A43" s="85" t="str">
         <f>IF(Nurses!A43="","",Nurses!A43)</f>
         <v>간호사42</v>
       </c>
@@ -6520,7 +7169,7 @@
       <c r="AF43" s="7"/>
     </row>
     <row r="44" spans="1:32">
-      <c r="A44" s="87" t="str">
+      <c r="A44" s="85" t="str">
         <f>IF(Nurses!A44="","",Nurses!A44)</f>
         <v>간호사43</v>
       </c>
@@ -6557,7 +7206,7 @@
       <c r="AF44" s="7"/>
     </row>
     <row r="45" spans="1:32">
-      <c r="A45" s="87" t="str">
+      <c r="A45" s="85" t="str">
         <f>IF(Nurses!A45="","",Nurses!A45)</f>
         <v>간호사44</v>
       </c>
@@ -6594,7 +7243,7 @@
       <c r="AF45" s="7"/>
     </row>
     <row r="46" spans="1:32">
-      <c r="A46" s="87" t="str">
+      <c r="A46" s="85" t="str">
         <f>IF(Nurses!A46="","",Nurses!A46)</f>
         <v>간호사45</v>
       </c>
@@ -6631,7 +7280,7 @@
       <c r="AF46" s="7"/>
     </row>
     <row r="47" spans="1:32">
-      <c r="A47" s="87" t="str">
+      <c r="A47" s="85" t="str">
         <f>IF(Nurses!A47="","",Nurses!A47)</f>
         <v>간호사46</v>
       </c>
@@ -6668,7 +7317,7 @@
       <c r="AF47" s="7"/>
     </row>
     <row r="48" spans="1:32">
-      <c r="A48" s="87" t="str">
+      <c r="A48" s="85" t="str">
         <f>IF(Nurses!A48="","",Nurses!A48)</f>
         <v>간호사47</v>
       </c>
@@ -6705,7 +7354,7 @@
       <c r="AF48" s="7"/>
     </row>
     <row r="49" spans="1:32">
-      <c r="A49" s="87" t="str">
+      <c r="A49" s="85" t="str">
         <f>IF(Nurses!A49="","",Nurses!A49)</f>
         <v>간호사48</v>
       </c>
@@ -6742,7 +7391,7 @@
       <c r="AF49" s="7"/>
     </row>
     <row r="50" spans="1:32">
-      <c r="A50" s="87" t="str">
+      <c r="A50" s="85" t="str">
         <f>IF(Nurses!A50="","",Nurses!A50)</f>
         <v>간호사49</v>
       </c>
@@ -6779,7 +7428,7 @@
       <c r="AF50" s="7"/>
     </row>
     <row r="51" spans="1:32">
-      <c r="A51" s="87" t="str">
+      <c r="A51" s="85" t="str">
         <f>IF(Nurses!A51="","",Nurses!A51)</f>
         <v>간호사50</v>
       </c>
@@ -6832,7 +7481,7 @@
   <sheetData>
     <row r="1" spans="1:42">
       <c r="A1" s="5" t="s">
-        <v>197</v>
+        <v>170</v>
       </c>
       <c r="B1" s="5">
         <v>1</v>
@@ -6929,7 +7578,7 @@
       </c>
     </row>
     <row r="2" spans="1:42">
-      <c r="A2" s="87" t="str">
+      <c r="A2" s="85" t="str">
         <f>IF(Nurses!A2="","",Nurses!A2)</f>
         <v>간호사1</v>
       </c>
@@ -6966,7 +7615,7 @@
       <c r="AF2" s="7"/>
     </row>
     <row r="3" spans="1:42">
-      <c r="A3" s="87" t="str">
+      <c r="A3" s="85" t="str">
         <f>IF(Nurses!A3="","",Nurses!A3)</f>
         <v>간호사2</v>
       </c>
@@ -7007,7 +7656,7 @@
       </c>
     </row>
     <row r="4" spans="1:42">
-      <c r="A4" s="87" t="str">
+      <c r="A4" s="85" t="str">
         <f>IF(Nurses!A4="","",Nurses!A4)</f>
         <v>간호사3</v>
       </c>
@@ -7043,20 +7692,20 @@
       <c r="AE4" s="7"/>
       <c r="AF4" s="7"/>
       <c r="AG4" s="6"/>
-      <c r="AH4" s="67" t="s">
-        <v>211</v>
-      </c>
-      <c r="AI4" s="83"/>
-      <c r="AJ4" s="83"/>
-      <c r="AK4" s="83"/>
-      <c r="AL4" s="83"/>
-      <c r="AM4" s="83"/>
-      <c r="AN4" s="83"/>
-      <c r="AO4" s="83"/>
-      <c r="AP4" s="83"/>
+      <c r="AH4" s="66" t="s">
+        <v>184</v>
+      </c>
+      <c r="AI4" s="82"/>
+      <c r="AJ4" s="82"/>
+      <c r="AK4" s="82"/>
+      <c r="AL4" s="82"/>
+      <c r="AM4" s="82"/>
+      <c r="AN4" s="82"/>
+      <c r="AO4" s="82"/>
+      <c r="AP4" s="82"/>
     </row>
     <row r="5" spans="1:42">
-      <c r="A5" s="87" t="str">
+      <c r="A5" s="85" t="str">
         <f>IF(Nurses!A5="","",Nurses!A5)</f>
         <v>간호사4</v>
       </c>
@@ -7092,18 +7741,18 @@
       <c r="AE5" s="7"/>
       <c r="AF5" s="7"/>
       <c r="AG5" s="6"/>
-      <c r="AH5" s="67"/>
-      <c r="AI5" s="83"/>
-      <c r="AJ5" s="83"/>
-      <c r="AK5" s="83"/>
-      <c r="AL5" s="83"/>
-      <c r="AM5" s="83"/>
-      <c r="AN5" s="83"/>
-      <c r="AO5" s="83"/>
-      <c r="AP5" s="83"/>
+      <c r="AH5" s="66"/>
+      <c r="AI5" s="82"/>
+      <c r="AJ5" s="82"/>
+      <c r="AK5" s="82"/>
+      <c r="AL5" s="82"/>
+      <c r="AM5" s="82"/>
+      <c r="AN5" s="82"/>
+      <c r="AO5" s="82"/>
+      <c r="AP5" s="82"/>
     </row>
     <row r="6" spans="1:42">
-      <c r="A6" s="87" t="str">
+      <c r="A6" s="85" t="str">
         <f>IF(Nurses!A6="","",Nurses!A6)</f>
         <v>간호사5</v>
       </c>
@@ -7139,20 +7788,20 @@
       <c r="AE6" s="7"/>
       <c r="AF6" s="7"/>
       <c r="AG6" s="6"/>
-      <c r="AH6" s="82" t="s">
-        <v>212</v>
-      </c>
-      <c r="AI6" s="83"/>
-      <c r="AJ6" s="83"/>
-      <c r="AK6" s="83"/>
-      <c r="AL6" s="83"/>
-      <c r="AM6" s="83"/>
-      <c r="AN6" s="83"/>
-      <c r="AO6" s="83"/>
-      <c r="AP6" s="83"/>
+      <c r="AH6" s="81" t="s">
+        <v>185</v>
+      </c>
+      <c r="AI6" s="82"/>
+      <c r="AJ6" s="82"/>
+      <c r="AK6" s="82"/>
+      <c r="AL6" s="82"/>
+      <c r="AM6" s="82"/>
+      <c r="AN6" s="82"/>
+      <c r="AO6" s="82"/>
+      <c r="AP6" s="82"/>
     </row>
     <row r="7" spans="1:42">
-      <c r="A7" s="87" t="str">
+      <c r="A7" s="85" t="str">
         <f>IF(Nurses!A7="","",Nurses!A7)</f>
         <v>간호사6</v>
       </c>
@@ -7188,18 +7837,18 @@
       <c r="AE7" s="7"/>
       <c r="AF7" s="7"/>
       <c r="AG7" s="6"/>
-      <c r="AH7" s="67"/>
-      <c r="AI7" s="83"/>
-      <c r="AJ7" s="83"/>
-      <c r="AK7" s="83"/>
-      <c r="AL7" s="83"/>
-      <c r="AM7" s="83"/>
-      <c r="AN7" s="83"/>
-      <c r="AO7" s="83"/>
-      <c r="AP7" s="83"/>
+      <c r="AH7" s="66"/>
+      <c r="AI7" s="82"/>
+      <c r="AJ7" s="82"/>
+      <c r="AK7" s="82"/>
+      <c r="AL7" s="82"/>
+      <c r="AM7" s="82"/>
+      <c r="AN7" s="82"/>
+      <c r="AO7" s="82"/>
+      <c r="AP7" s="82"/>
     </row>
     <row r="8" spans="1:42">
-      <c r="A8" s="87" t="str">
+      <c r="A8" s="85" t="str">
         <f>IF(Nurses!A8="","",Nurses!A8)</f>
         <v>간호사7</v>
       </c>
@@ -7235,20 +7884,20 @@
       <c r="AE8" s="7"/>
       <c r="AF8" s="7"/>
       <c r="AG8" s="6"/>
-      <c r="AH8" s="67" t="s">
-        <v>213</v>
-      </c>
-      <c r="AI8" s="83"/>
-      <c r="AJ8" s="83"/>
-      <c r="AK8" s="83"/>
-      <c r="AL8" s="83"/>
-      <c r="AM8" s="83"/>
-      <c r="AN8" s="83"/>
-      <c r="AO8" s="83"/>
-      <c r="AP8" s="83"/>
+      <c r="AH8" s="66" t="s">
+        <v>186</v>
+      </c>
+      <c r="AI8" s="82"/>
+      <c r="AJ8" s="82"/>
+      <c r="AK8" s="82"/>
+      <c r="AL8" s="82"/>
+      <c r="AM8" s="82"/>
+      <c r="AN8" s="82"/>
+      <c r="AO8" s="82"/>
+      <c r="AP8" s="82"/>
     </row>
     <row r="9" spans="1:42">
-      <c r="A9" s="87" t="str">
+      <c r="A9" s="85" t="str">
         <f>IF(Nurses!A9="","",Nurses!A9)</f>
         <v>간호사8</v>
       </c>
@@ -7284,18 +7933,18 @@
       <c r="AE9" s="7"/>
       <c r="AF9" s="7"/>
       <c r="AG9" s="6"/>
-      <c r="AH9" s="84"/>
-      <c r="AI9" s="83"/>
-      <c r="AJ9" s="83"/>
-      <c r="AK9" s="83"/>
-      <c r="AL9" s="83"/>
-      <c r="AM9" s="83"/>
-      <c r="AN9" s="83"/>
-      <c r="AO9" s="83"/>
-      <c r="AP9" s="83"/>
+      <c r="AH9" s="83"/>
+      <c r="AI9" s="82"/>
+      <c r="AJ9" s="82"/>
+      <c r="AK9" s="82"/>
+      <c r="AL9" s="82"/>
+      <c r="AM9" s="82"/>
+      <c r="AN9" s="82"/>
+      <c r="AO9" s="82"/>
+      <c r="AP9" s="82"/>
     </row>
     <row r="10" spans="1:42">
-      <c r="A10" s="87" t="str">
+      <c r="A10" s="85" t="str">
         <f>IF(Nurses!A10="","",Nurses!A10)</f>
         <v>간호사9</v>
       </c>
@@ -7331,20 +7980,20 @@
       <c r="AE10" s="7"/>
       <c r="AF10" s="7"/>
       <c r="AG10" s="6"/>
-      <c r="AH10" s="85" t="s">
-        <v>214</v>
-      </c>
-      <c r="AI10" s="83"/>
-      <c r="AJ10" s="83"/>
-      <c r="AK10" s="83"/>
-      <c r="AL10" s="83"/>
-      <c r="AM10" s="83"/>
-      <c r="AN10" s="83"/>
-      <c r="AO10" s="83"/>
-      <c r="AP10" s="83"/>
+      <c r="AH10" s="84" t="s">
+        <v>187</v>
+      </c>
+      <c r="AI10" s="82"/>
+      <c r="AJ10" s="82"/>
+      <c r="AK10" s="82"/>
+      <c r="AL10" s="82"/>
+      <c r="AM10" s="82"/>
+      <c r="AN10" s="82"/>
+      <c r="AO10" s="82"/>
+      <c r="AP10" s="82"/>
     </row>
     <row r="11" spans="1:42">
-      <c r="A11" s="87" t="str">
+      <c r="A11" s="85" t="str">
         <f>IF(Nurses!A11="","",Nurses!A11)</f>
         <v>간호사10</v>
       </c>
@@ -7382,7 +8031,7 @@
       <c r="AG11" s="6"/>
     </row>
     <row r="12" spans="1:42">
-      <c r="A12" s="87" t="str">
+      <c r="A12" s="85" t="str">
         <f>IF(Nurses!A12="","",Nurses!A12)</f>
         <v>간호사11</v>
       </c>
@@ -7420,7 +8069,7 @@
       <c r="AG12" s="6"/>
     </row>
     <row r="13" spans="1:42">
-      <c r="A13" s="87" t="str">
+      <c r="A13" s="85" t="str">
         <f>IF(Nurses!A13="","",Nurses!A13)</f>
         <v>간호사12</v>
       </c>
@@ -7458,7 +8107,7 @@
       <c r="AG13" s="6"/>
     </row>
     <row r="14" spans="1:42">
-      <c r="A14" s="87" t="str">
+      <c r="A14" s="85" t="str">
         <f>IF(Nurses!A14="","",Nurses!A14)</f>
         <v>간호사13</v>
       </c>
@@ -7495,7 +8144,7 @@
       <c r="AF14" s="7"/>
     </row>
     <row r="15" spans="1:42">
-      <c r="A15" s="87" t="str">
+      <c r="A15" s="85" t="str">
         <f>IF(Nurses!A15="","",Nurses!A15)</f>
         <v>간호사14</v>
       </c>
@@ -7532,7 +8181,7 @@
       <c r="AF15" s="7"/>
     </row>
     <row r="16" spans="1:42">
-      <c r="A16" s="87" t="str">
+      <c r="A16" s="85" t="str">
         <f>IF(Nurses!A16="","",Nurses!A16)</f>
         <v>간호사15</v>
       </c>
@@ -7569,7 +8218,7 @@
       <c r="AF16" s="7"/>
     </row>
     <row r="17" spans="1:32">
-      <c r="A17" s="87" t="str">
+      <c r="A17" s="85" t="str">
         <f>IF(Nurses!A17="","",Nurses!A17)</f>
         <v>간호사16</v>
       </c>
@@ -7606,7 +8255,7 @@
       <c r="AF17" s="7"/>
     </row>
     <row r="18" spans="1:32">
-      <c r="A18" s="87" t="str">
+      <c r="A18" s="85" t="str">
         <f>IF(Nurses!A18="","",Nurses!A18)</f>
         <v>간호사17</v>
       </c>
@@ -7643,7 +8292,7 @@
       <c r="AF18" s="7"/>
     </row>
     <row r="19" spans="1:32">
-      <c r="A19" s="87" t="str">
+      <c r="A19" s="85" t="str">
         <f>IF(Nurses!A19="","",Nurses!A19)</f>
         <v>간호사18</v>
       </c>
@@ -7680,7 +8329,7 @@
       <c r="AF19" s="7"/>
     </row>
     <row r="20" spans="1:32">
-      <c r="A20" s="87" t="str">
+      <c r="A20" s="85" t="str">
         <f>IF(Nurses!A20="","",Nurses!A20)</f>
         <v>간호사19</v>
       </c>
@@ -7717,7 +8366,7 @@
       <c r="AF20" s="7"/>
     </row>
     <row r="21" spans="1:32">
-      <c r="A21" s="87" t="str">
+      <c r="A21" s="85" t="str">
         <f>IF(Nurses!A21="","",Nurses!A21)</f>
         <v>간호사20</v>
       </c>
@@ -7754,7 +8403,7 @@
       <c r="AF21" s="7"/>
     </row>
     <row r="22" spans="1:32">
-      <c r="A22" s="87" t="str">
+      <c r="A22" s="85" t="str">
         <f>IF(Nurses!A22="","",Nurses!A22)</f>
         <v>간호사21</v>
       </c>
@@ -7791,7 +8440,7 @@
       <c r="AF22" s="7"/>
     </row>
     <row r="23" spans="1:32">
-      <c r="A23" s="87" t="str">
+      <c r="A23" s="85" t="str">
         <f>IF(Nurses!A23="","",Nurses!A23)</f>
         <v>간호사22</v>
       </c>
@@ -7828,7 +8477,7 @@
       <c r="AF23" s="7"/>
     </row>
     <row r="24" spans="1:32">
-      <c r="A24" s="87" t="str">
+      <c r="A24" s="85" t="str">
         <f>IF(Nurses!A24="","",Nurses!A24)</f>
         <v>간호사23</v>
       </c>
@@ -7865,7 +8514,7 @@
       <c r="AF24" s="7"/>
     </row>
     <row r="25" spans="1:32">
-      <c r="A25" s="87" t="str">
+      <c r="A25" s="85" t="str">
         <f>IF(Nurses!A25="","",Nurses!A25)</f>
         <v>간호사24</v>
       </c>
@@ -7902,7 +8551,7 @@
       <c r="AF25" s="7"/>
     </row>
     <row r="26" spans="1:32">
-      <c r="A26" s="87" t="str">
+      <c r="A26" s="85" t="str">
         <f>IF(Nurses!A26="","",Nurses!A26)</f>
         <v>간호사25</v>
       </c>
@@ -7939,7 +8588,7 @@
       <c r="AF26" s="7"/>
     </row>
     <row r="27" spans="1:32">
-      <c r="A27" s="87" t="str">
+      <c r="A27" s="85" t="str">
         <f>IF(Nurses!A27="","",Nurses!A27)</f>
         <v>간호사26</v>
       </c>
@@ -7976,7 +8625,7 @@
       <c r="AF27" s="7"/>
     </row>
     <row r="28" spans="1:32">
-      <c r="A28" s="87" t="str">
+      <c r="A28" s="85" t="str">
         <f>IF(Nurses!A28="","",Nurses!A28)</f>
         <v>간호사27</v>
       </c>
@@ -8013,7 +8662,7 @@
       <c r="AF28" s="7"/>
     </row>
     <row r="29" spans="1:32">
-      <c r="A29" s="87" t="str">
+      <c r="A29" s="85" t="str">
         <f>IF(Nurses!A29="","",Nurses!A29)</f>
         <v>간호사28</v>
       </c>
@@ -8050,7 +8699,7 @@
       <c r="AF29" s="7"/>
     </row>
     <row r="30" spans="1:32">
-      <c r="A30" s="87" t="str">
+      <c r="A30" s="85" t="str">
         <f>IF(Nurses!A30="","",Nurses!A30)</f>
         <v>간호사29</v>
       </c>
@@ -8087,7 +8736,7 @@
       <c r="AF30" s="7"/>
     </row>
     <row r="31" spans="1:32">
-      <c r="A31" s="87" t="str">
+      <c r="A31" s="85" t="str">
         <f>IF(Nurses!A31="","",Nurses!A31)</f>
         <v>간호사30</v>
       </c>
@@ -8124,7 +8773,7 @@
       <c r="AF31" s="7"/>
     </row>
     <row r="32" spans="1:32">
-      <c r="A32" s="87" t="str">
+      <c r="A32" s="85" t="str">
         <f>IF(Nurses!A32="","",Nurses!A32)</f>
         <v>간호사31</v>
       </c>
@@ -8161,7 +8810,7 @@
       <c r="AF32" s="7"/>
     </row>
     <row r="33" spans="1:32">
-      <c r="A33" s="87" t="str">
+      <c r="A33" s="85" t="str">
         <f>IF(Nurses!A33="","",Nurses!A33)</f>
         <v>간호사32</v>
       </c>
@@ -8198,7 +8847,7 @@
       <c r="AF33" s="7"/>
     </row>
     <row r="34" spans="1:32">
-      <c r="A34" s="87" t="str">
+      <c r="A34" s="85" t="str">
         <f>IF(Nurses!A34="","",Nurses!A34)</f>
         <v>간호사33</v>
       </c>
@@ -8235,7 +8884,7 @@
       <c r="AF34" s="7"/>
     </row>
     <row r="35" spans="1:32">
-      <c r="A35" s="87" t="str">
+      <c r="A35" s="85" t="str">
         <f>IF(Nurses!A35="","",Nurses!A35)</f>
         <v>간호사34</v>
       </c>
@@ -8272,7 +8921,7 @@
       <c r="AF35" s="7"/>
     </row>
     <row r="36" spans="1:32">
-      <c r="A36" s="87" t="str">
+      <c r="A36" s="85" t="str">
         <f>IF(Nurses!A36="","",Nurses!A36)</f>
         <v>간호사35</v>
       </c>
@@ -8309,7 +8958,7 @@
       <c r="AF36" s="7"/>
     </row>
     <row r="37" spans="1:32">
-      <c r="A37" s="87" t="str">
+      <c r="A37" s="85" t="str">
         <f>IF(Nurses!A37="","",Nurses!A37)</f>
         <v>간호사36</v>
       </c>
@@ -8346,7 +8995,7 @@
       <c r="AF37" s="7"/>
     </row>
     <row r="38" spans="1:32">
-      <c r="A38" s="87" t="str">
+      <c r="A38" s="85" t="str">
         <f>IF(Nurses!A38="","",Nurses!A38)</f>
         <v>간호사37</v>
       </c>
@@ -8383,7 +9032,7 @@
       <c r="AF38" s="7"/>
     </row>
     <row r="39" spans="1:32">
-      <c r="A39" s="87" t="str">
+      <c r="A39" s="85" t="str">
         <f>IF(Nurses!A39="","",Nurses!A39)</f>
         <v>간호사38</v>
       </c>
@@ -8420,7 +9069,7 @@
       <c r="AF39" s="7"/>
     </row>
     <row r="40" spans="1:32">
-      <c r="A40" s="87" t="str">
+      <c r="A40" s="85" t="str">
         <f>IF(Nurses!A40="","",Nurses!A40)</f>
         <v>간호사39</v>
       </c>
@@ -8457,7 +9106,7 @@
       <c r="AF40" s="7"/>
     </row>
     <row r="41" spans="1:32">
-      <c r="A41" s="87" t="str">
+      <c r="A41" s="85" t="str">
         <f>IF(Nurses!A41="","",Nurses!A41)</f>
         <v>간호사40</v>
       </c>
@@ -8494,7 +9143,7 @@
       <c r="AF41" s="7"/>
     </row>
     <row r="42" spans="1:32">
-      <c r="A42" s="87" t="str">
+      <c r="A42" s="85" t="str">
         <f>IF(Nurses!A42="","",Nurses!A42)</f>
         <v>간호사41</v>
       </c>
@@ -8531,7 +9180,7 @@
       <c r="AF42" s="7"/>
     </row>
     <row r="43" spans="1:32">
-      <c r="A43" s="87" t="str">
+      <c r="A43" s="85" t="str">
         <f>IF(Nurses!A43="","",Nurses!A43)</f>
         <v>간호사42</v>
       </c>
@@ -8568,7 +9217,7 @@
       <c r="AF43" s="7"/>
     </row>
     <row r="44" spans="1:32">
-      <c r="A44" s="87" t="str">
+      <c r="A44" s="85" t="str">
         <f>IF(Nurses!A44="","",Nurses!A44)</f>
         <v>간호사43</v>
       </c>
@@ -8605,7 +9254,7 @@
       <c r="AF44" s="7"/>
     </row>
     <row r="45" spans="1:32">
-      <c r="A45" s="87" t="str">
+      <c r="A45" s="85" t="str">
         <f>IF(Nurses!A45="","",Nurses!A45)</f>
         <v>간호사44</v>
       </c>
@@ -8642,7 +9291,7 @@
       <c r="AF45" s="7"/>
     </row>
     <row r="46" spans="1:32">
-      <c r="A46" s="87" t="str">
+      <c r="A46" s="85" t="str">
         <f>IF(Nurses!A46="","",Nurses!A46)</f>
         <v>간호사45</v>
       </c>
@@ -8679,7 +9328,7 @@
       <c r="AF46" s="7"/>
     </row>
     <row r="47" spans="1:32">
-      <c r="A47" s="87" t="str">
+      <c r="A47" s="85" t="str">
         <f>IF(Nurses!A47="","",Nurses!A47)</f>
         <v>간호사46</v>
       </c>
@@ -8716,7 +9365,7 @@
       <c r="AF47" s="7"/>
     </row>
     <row r="48" spans="1:32">
-      <c r="A48" s="87" t="str">
+      <c r="A48" s="85" t="str">
         <f>IF(Nurses!A48="","",Nurses!A48)</f>
         <v>간호사47</v>
       </c>
@@ -8753,7 +9402,7 @@
       <c r="AF48" s="7"/>
     </row>
     <row r="49" spans="1:32">
-      <c r="A49" s="87" t="str">
+      <c r="A49" s="85" t="str">
         <f>IF(Nurses!A49="","",Nurses!A49)</f>
         <v>간호사48</v>
       </c>
@@ -8790,7 +9439,7 @@
       <c r="AF49" s="7"/>
     </row>
     <row r="50" spans="1:32">
-      <c r="A50" s="87" t="str">
+      <c r="A50" s="85" t="str">
         <f>IF(Nurses!A50="","",Nurses!A50)</f>
         <v>간호사49</v>
       </c>
@@ -8827,7 +9476,7 @@
       <c r="AF50" s="7"/>
     </row>
     <row r="51" spans="1:32">
-      <c r="A51" s="87" t="str">
+      <c r="A51" s="85" t="str">
         <f>IF(Nurses!A51="","",Nurses!A51)</f>
         <v>간호사50</v>
       </c>
@@ -8880,26 +9529,26 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="14" t="s">
-        <v>155</v>
+        <v>128</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>215</v>
+        <v>188</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>216</v>
+        <v>189</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>218</v>
+        <v>191</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>219</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:17">
-      <c r="A2" s="87" t="str">
+      <c r="A2" s="85" t="str">
         <f>IF(Nurses!A2="","",Nurses!A2)</f>
         <v>간호사1</v>
       </c>
@@ -8915,12 +9564,12 @@
       <c r="Q2" s="11"/>
     </row>
     <row r="3" spans="1:17">
-      <c r="A3" s="87" t="str">
+      <c r="A3" s="85" t="str">
         <f>IF(Nurses!A3="","",Nurses!A3)</f>
         <v>간호사2</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>220</v>
+        <v>193</v>
       </c>
       <c r="K3" s="11"/>
       <c r="L3" s="11"/>
@@ -8931,292 +9580,292 @@
       <c r="Q3" s="11"/>
     </row>
     <row r="4" spans="1:17">
-      <c r="A4" s="87" t="str">
+      <c r="A4" s="85" t="str">
         <f>IF(Nurses!A4="","",Nurses!A4)</f>
         <v>간호사3</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>221</v>
+        <v>194</v>
       </c>
     </row>
     <row r="5" spans="1:17">
-      <c r="A5" s="87" t="str">
+      <c r="A5" s="85" t="str">
         <f>IF(Nurses!A5="","",Nurses!A5)</f>
         <v>간호사4</v>
       </c>
     </row>
     <row r="6" spans="1:17">
-      <c r="A6" s="87" t="str">
+      <c r="A6" s="85" t="str">
         <f>IF(Nurses!A6="","",Nurses!A6)</f>
         <v>간호사5</v>
       </c>
     </row>
     <row r="7" spans="1:17">
-      <c r="A7" s="87" t="str">
+      <c r="A7" s="85" t="str">
         <f>IF(Nurses!A7="","",Nurses!A7)</f>
         <v>간호사6</v>
       </c>
     </row>
     <row r="8" spans="1:17">
-      <c r="A8" s="87" t="str">
+      <c r="A8" s="85" t="str">
         <f>IF(Nurses!A8="","",Nurses!A8)</f>
         <v>간호사7</v>
       </c>
     </row>
     <row r="9" spans="1:17">
-      <c r="A9" s="87" t="str">
+      <c r="A9" s="85" t="str">
         <f>IF(Nurses!A9="","",Nurses!A9)</f>
         <v>간호사8</v>
       </c>
     </row>
     <row r="10" spans="1:17">
-      <c r="A10" s="87" t="str">
+      <c r="A10" s="85" t="str">
         <f>IF(Nurses!A10="","",Nurses!A10)</f>
         <v>간호사9</v>
       </c>
     </row>
     <row r="11" spans="1:17">
-      <c r="A11" s="87" t="str">
+      <c r="A11" s="85" t="str">
         <f>IF(Nurses!A11="","",Nurses!A11)</f>
         <v>간호사10</v>
       </c>
     </row>
     <row r="12" spans="1:17">
-      <c r="A12" s="87" t="str">
+      <c r="A12" s="85" t="str">
         <f>IF(Nurses!A12="","",Nurses!A12)</f>
         <v>간호사11</v>
       </c>
     </row>
     <row r="13" spans="1:17">
-      <c r="A13" s="87" t="str">
+      <c r="A13" s="85" t="str">
         <f>IF(Nurses!A13="","",Nurses!A13)</f>
         <v>간호사12</v>
       </c>
     </row>
     <row r="14" spans="1:17">
-      <c r="A14" s="87" t="str">
+      <c r="A14" s="85" t="str">
         <f>IF(Nurses!A14="","",Nurses!A14)</f>
         <v>간호사13</v>
       </c>
     </row>
     <row r="15" spans="1:17">
-      <c r="A15" s="87" t="str">
+      <c r="A15" s="85" t="str">
         <f>IF(Nurses!A15="","",Nurses!A15)</f>
         <v>간호사14</v>
       </c>
     </row>
     <row r="16" spans="1:17">
-      <c r="A16" s="87" t="str">
+      <c r="A16" s="85" t="str">
         <f>IF(Nurses!A16="","",Nurses!A16)</f>
         <v>간호사15</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="87" t="str">
+      <c r="A17" s="85" t="str">
         <f>IF(Nurses!A17="","",Nurses!A17)</f>
         <v>간호사16</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="87" t="str">
+      <c r="A18" s="85" t="str">
         <f>IF(Nurses!A18="","",Nurses!A18)</f>
         <v>간호사17</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="87" t="str">
+      <c r="A19" s="85" t="str">
         <f>IF(Nurses!A19="","",Nurses!A19)</f>
         <v>간호사18</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="87" t="str">
+      <c r="A20" s="85" t="str">
         <f>IF(Nurses!A20="","",Nurses!A20)</f>
         <v>간호사19</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="87" t="str">
+      <c r="A21" s="85" t="str">
         <f>IF(Nurses!A21="","",Nurses!A21)</f>
         <v>간호사20</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="87" t="str">
+      <c r="A22" s="85" t="str">
         <f>IF(Nurses!A22="","",Nurses!A22)</f>
         <v>간호사21</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="87" t="str">
+      <c r="A23" s="85" t="str">
         <f>IF(Nurses!A23="","",Nurses!A23)</f>
         <v>간호사22</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="87" t="str">
+      <c r="A24" s="85" t="str">
         <f>IF(Nurses!A24="","",Nurses!A24)</f>
         <v>간호사23</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="87" t="str">
+      <c r="A25" s="85" t="str">
         <f>IF(Nurses!A25="","",Nurses!A25)</f>
         <v>간호사24</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="87" t="str">
+      <c r="A26" s="85" t="str">
         <f>IF(Nurses!A26="","",Nurses!A26)</f>
         <v>간호사25</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="87" t="str">
+      <c r="A27" s="85" t="str">
         <f>IF(Nurses!A27="","",Nurses!A27)</f>
         <v>간호사26</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="87" t="str">
+      <c r="A28" s="85" t="str">
         <f>IF(Nurses!A28="","",Nurses!A28)</f>
         <v>간호사27</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="87" t="str">
+      <c r="A29" s="85" t="str">
         <f>IF(Nurses!A29="","",Nurses!A29)</f>
         <v>간호사28</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="87" t="str">
+      <c r="A30" s="85" t="str">
         <f>IF(Nurses!A30="","",Nurses!A30)</f>
         <v>간호사29</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="87" t="str">
+      <c r="A31" s="85" t="str">
         <f>IF(Nurses!A31="","",Nurses!A31)</f>
         <v>간호사30</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="87" t="str">
+      <c r="A32" s="85" t="str">
         <f>IF(Nurses!A32="","",Nurses!A32)</f>
         <v>간호사31</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="87" t="str">
+      <c r="A33" s="85" t="str">
         <f>IF(Nurses!A33="","",Nurses!A33)</f>
         <v>간호사32</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="87" t="str">
+      <c r="A34" s="85" t="str">
         <f>IF(Nurses!A34="","",Nurses!A34)</f>
         <v>간호사33</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="87" t="str">
+      <c r="A35" s="85" t="str">
         <f>IF(Nurses!A35="","",Nurses!A35)</f>
         <v>간호사34</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="87" t="str">
+      <c r="A36" s="85" t="str">
         <f>IF(Nurses!A36="","",Nurses!A36)</f>
         <v>간호사35</v>
       </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="87" t="str">
+      <c r="A37" s="85" t="str">
         <f>IF(Nurses!A37="","",Nurses!A37)</f>
         <v>간호사36</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="87" t="str">
+      <c r="A38" s="85" t="str">
         <f>IF(Nurses!A38="","",Nurses!A38)</f>
         <v>간호사37</v>
       </c>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="87" t="str">
+      <c r="A39" s="85" t="str">
         <f>IF(Nurses!A39="","",Nurses!A39)</f>
         <v>간호사38</v>
       </c>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="87" t="str">
+      <c r="A40" s="85" t="str">
         <f>IF(Nurses!A40="","",Nurses!A40)</f>
         <v>간호사39</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="87" t="str">
+      <c r="A41" s="85" t="str">
         <f>IF(Nurses!A41="","",Nurses!A41)</f>
         <v>간호사40</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="87" t="str">
+      <c r="A42" s="85" t="str">
         <f>IF(Nurses!A42="","",Nurses!A42)</f>
         <v>간호사41</v>
       </c>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="87" t="str">
+      <c r="A43" s="85" t="str">
         <f>IF(Nurses!A43="","",Nurses!A43)</f>
         <v>간호사42</v>
       </c>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" s="87" t="str">
+      <c r="A44" s="85" t="str">
         <f>IF(Nurses!A44="","",Nurses!A44)</f>
         <v>간호사43</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="87" t="str">
+      <c r="A45" s="85" t="str">
         <f>IF(Nurses!A45="","",Nurses!A45)</f>
         <v>간호사44</v>
       </c>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" s="87" t="str">
+      <c r="A46" s="85" t="str">
         <f>IF(Nurses!A46="","",Nurses!A46)</f>
         <v>간호사45</v>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="87" t="str">
+      <c r="A47" s="85" t="str">
         <f>IF(Nurses!A47="","",Nurses!A47)</f>
         <v>간호사46</v>
       </c>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" s="87" t="str">
+      <c r="A48" s="85" t="str">
         <f>IF(Nurses!A48="","",Nurses!A48)</f>
         <v>간호사47</v>
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="87" t="str">
+      <c r="A49" s="85" t="str">
         <f>IF(Nurses!A49="","",Nurses!A49)</f>
         <v>간호사48</v>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="87" t="str">
+      <c r="A50" s="85" t="str">
         <f>IF(Nurses!A50="","",Nurses!A50)</f>
         <v>간호사49</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="87" t="str">
+      <c r="A51" s="85" t="str">
         <f>IF(Nurses!A51="","",Nurses!A51)</f>
         <v>간호사50</v>
       </c>
@@ -9238,147 +9887,147 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42">
-      <c r="A1" s="99" t="s">
-        <v>222</v>
-      </c>
-      <c r="B1" s="98"/>
-      <c r="C1" s="98"/>
-      <c r="D1" s="98"/>
-      <c r="E1" s="98"/>
-      <c r="F1" s="98"/>
-      <c r="G1" s="98"/>
-      <c r="H1" s="98"/>
-      <c r="I1" s="98"/>
-      <c r="J1" s="98"/>
-      <c r="K1" s="98"/>
-      <c r="L1" s="98"/>
-      <c r="M1" s="98"/>
-      <c r="N1" s="98"/>
-      <c r="O1" s="98"/>
-      <c r="P1" s="98"/>
-      <c r="Q1" s="98"/>
-      <c r="R1" s="98"/>
-      <c r="S1" s="98"/>
-      <c r="T1" s="98"/>
-      <c r="U1" s="98"/>
-      <c r="V1" s="98"/>
-      <c r="W1" s="98"/>
-      <c r="X1" s="98"/>
-      <c r="Y1" s="98"/>
-      <c r="Z1" s="98"/>
-      <c r="AA1" s="98"/>
-      <c r="AB1" s="98"/>
-      <c r="AC1" s="98"/>
-      <c r="AD1" s="98"/>
-      <c r="AE1" s="98"/>
-      <c r="AF1" s="98"/>
-      <c r="AG1" s="98"/>
-      <c r="AH1" s="98"/>
-      <c r="AI1" s="98"/>
-      <c r="AJ1" s="98"/>
-      <c r="AK1" s="98"/>
-      <c r="AL1" s="98"/>
-      <c r="AM1" s="98"/>
-      <c r="AN1" s="98"/>
-      <c r="AO1" s="98"/>
-      <c r="AP1" s="98"/>
+      <c r="A1" s="96" t="s">
+        <v>195</v>
+      </c>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
+      <c r="E1" s="95"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="95"/>
+      <c r="H1" s="95"/>
+      <c r="I1" s="95"/>
+      <c r="J1" s="95"/>
+      <c r="K1" s="95"/>
+      <c r="L1" s="95"/>
+      <c r="M1" s="95"/>
+      <c r="N1" s="95"/>
+      <c r="O1" s="95"/>
+      <c r="P1" s="95"/>
+      <c r="Q1" s="95"/>
+      <c r="R1" s="95"/>
+      <c r="S1" s="95"/>
+      <c r="T1" s="95"/>
+      <c r="U1" s="95"/>
+      <c r="V1" s="95"/>
+      <c r="W1" s="95"/>
+      <c r="X1" s="95"/>
+      <c r="Y1" s="95"/>
+      <c r="Z1" s="95"/>
+      <c r="AA1" s="95"/>
+      <c r="AB1" s="95"/>
+      <c r="AC1" s="95"/>
+      <c r="AD1" s="95"/>
+      <c r="AE1" s="95"/>
+      <c r="AF1" s="95"/>
+      <c r="AG1" s="95"/>
+      <c r="AH1" s="95"/>
+      <c r="AI1" s="95"/>
+      <c r="AJ1" s="95"/>
+      <c r="AK1" s="95"/>
+      <c r="AL1" s="95"/>
+      <c r="AM1" s="95"/>
+      <c r="AN1" s="95"/>
+      <c r="AO1" s="95"/>
+      <c r="AP1" s="95"/>
     </row>
     <row r="2" spans="1:42">
       <c r="A2" s="8" t="s">
-        <v>223</v>
+        <v>196</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>225</v>
+        <v>198</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>225</v>
+        <v>198</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>225</v>
+        <v>198</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>225</v>
+        <v>198</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>225</v>
+        <v>198</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>225</v>
+        <v>198</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>225</v>
+        <v>198</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>225</v>
+        <v>198</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>225</v>
+        <v>198</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>225</v>
+        <v>198</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>225</v>
+        <v>198</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>225</v>
+        <v>198</v>
       </c>
       <c r="S2" s="6" t="s">
-        <v>225</v>
+        <v>198</v>
       </c>
       <c r="T2" s="6" t="s">
-        <v>225</v>
+        <v>198</v>
       </c>
       <c r="U2" s="6" t="s">
-        <v>225</v>
+        <v>198</v>
       </c>
       <c r="V2" s="6" t="s">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="W2" s="6" t="s">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="X2" s="6" t="s">
-        <v>225</v>
+        <v>198</v>
       </c>
       <c r="Y2" s="6" t="s">
-        <v>225</v>
+        <v>198</v>
       </c>
       <c r="Z2" s="6" t="s">
-        <v>225</v>
+        <v>198</v>
       </c>
       <c r="AA2" s="6" t="s">
-        <v>225</v>
+        <v>198</v>
       </c>
       <c r="AB2" s="6" t="s">
-        <v>225</v>
+        <v>198</v>
       </c>
       <c r="AC2" s="6" t="s">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="AD2" s="6" t="s">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="AE2" s="6" t="s">
-        <v>225</v>
+        <v>198</v>
       </c>
       <c r="AF2" s="6" t="s">
-        <v>225</v>
+        <v>198</v>
       </c>
       <c r="AG2" s="6"/>
       <c r="AH2" s="6"/>
@@ -9393,7 +10042,7 @@
     </row>
     <row r="3" spans="1:42">
       <c r="A3" s="5" t="s">
-        <v>197</v>
+        <v>170</v>
       </c>
       <c r="B3" s="5">
         <v>1</v>
@@ -9489,169 +10138,169 @@
         <v>31</v>
       </c>
       <c r="AG3" s="5" t="s">
-        <v>226</v>
+        <v>199</v>
       </c>
       <c r="AH3" s="5" t="s">
-        <v>227</v>
+        <v>200</v>
       </c>
       <c r="AI3" s="5" t="s">
-        <v>228</v>
+        <v>201</v>
       </c>
       <c r="AJ3" s="5" t="s">
-        <v>229</v>
+        <v>202</v>
       </c>
       <c r="AK3" s="5" t="s">
-        <v>230</v>
+        <v>203</v>
       </c>
       <c r="AL3" s="5" t="s">
-        <v>231</v>
+        <v>204</v>
       </c>
       <c r="AM3" s="5" t="s">
-        <v>232</v>
+        <v>205</v>
       </c>
       <c r="AN3" s="5" t="s">
-        <v>233</v>
+        <v>206</v>
       </c>
       <c r="AO3" s="5" t="s">
-        <v>234</v>
+        <v>207</v>
       </c>
       <c r="AP3" s="5" t="s">
-        <v>235</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" spans="1:42">
       <c r="A4" t="s">
-        <v>160</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:42">
       <c r="A5" t="s">
-        <v>161</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:42">
       <c r="A6" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:42">
       <c r="A7" t="s">
-        <v>165</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:42">
       <c r="A8" t="s">
-        <v>167</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" spans="1:42">
       <c r="A9" t="s">
-        <v>168</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10" spans="1:42">
       <c r="A10" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11" spans="1:42">
       <c r="A11" t="s">
-        <v>172</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" spans="1:42">
       <c r="A12" t="s">
-        <v>174</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:42">
       <c r="A13" t="s">
-        <v>175</v>
+        <v>148</v>
       </c>
     </row>
     <row r="14" spans="1:42">
       <c r="A14" t="s">
-        <v>177</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:42">
       <c r="A15" t="s">
-        <v>178</v>
+        <v>151</v>
       </c>
     </row>
     <row r="16" spans="1:42">
       <c r="A16" t="s">
-        <v>256</v>
+        <v>229</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>257</v>
+        <v>230</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>258</v>
+        <v>231</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>259</v>
+        <v>232</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>260</v>
+        <v>233</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>261</v>
+        <v>234</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>262</v>
+        <v>235</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>263</v>
+        <v>236</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>264</v>
+        <v>237</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>265</v>
+        <v>238</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>266</v>
+        <v>239</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>267</v>
+        <v>240</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>268</v>
+        <v>241</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>269</v>
+        <v>242</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>270</v>
+        <v>243</v>
       </c>
     </row>
   </sheetData>

--- a/nurse_scheduler_complete.xlsx
+++ b/nurse_scheduler_complete.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\송민영\Desktop\근무표 프로그램\완전판 웹사이트로 돌아감\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\송민영\Desktop\근무표 프로그램\완전판\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A021BE15-1AFD-483D-B8A9-FA7BFD5F6038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B5250F5-1CD9-4DA5-9A4D-534A8BFDE805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8970" yWindow="2985" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="설명서" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="296">
   <si>
     <t>Scheduler Controls</t>
   </si>
@@ -232,9 +232,6 @@
     <t xml:space="preserve">만든사람: </t>
   </si>
   <si>
-    <t>성균관대 기계공학부 20학번 김정진</t>
-  </si>
-  <si>
     <t>동남보건대 간호학과 21학번 송민영</t>
   </si>
   <si>
@@ -428,6 +425,84 @@
   </si>
   <si>
     <t xml:space="preserve"> 4. 시트의 이름, 입력란 외 이름, 입력란의 행과 열을 바꾸면 프로그램이 인식하지 못합니다!</t>
+  </si>
+  <si>
+    <t>(스케줄 작성 완료 후 엑셀을 저장 후 종료한 뒤에 .exe 파일을 더블클릭하시면 됩니다!)</t>
+  </si>
+  <si>
+    <t>액셀 파일과 실행 exe 파일을 한 폴더안에 넣어야 작동이 됩니다! 엑셀과 프로그램 파일 이름을 바꾸지 마세요!</t>
+  </si>
+  <si>
+    <t>프로그램창 (CMD) 해석</t>
+  </si>
+  <si>
+    <t>근무표 작성이 완료되면 까만 창 맨 아래에 두 줄의 영어 메시지가 뜹니다. 이것은 AI(인공지능)가 스케줄을 짜면서 겪은 과정과 결과물의 점수를 알려주는 보고서입니다.</t>
+  </si>
+  <si>
+    <t>1️⃣ Solver status (컴퓨터의 최종 상태 보고)</t>
+  </si>
+  <si>
+    <t>컴퓨터가 근무표를 성공적으로 완성했는지, 아니면 규칙이 너무 빡빡해서 실패했는지를 알려줍니다.</t>
+  </si>
+  <si>
+    <t>OPTIMAL (가장 이상적!)</t>
+  </si>
+  <si>
+    <t>의미: 주어진 조건 안에서 수학적으로 가장 완벽하고 공평한 1등 스케줄을 찾아냈습니다</t>
+  </si>
+  <si>
+    <t>상태: 안심하고 엑셀 근무표를 확인하시면 됩니다.</t>
+  </si>
+  <si>
+    <t>FEASIBLE (쓸만한 스케줄 완성)</t>
+  </si>
+  <si>
+    <t>의미: 100점짜리 정답인지는 확신할 수 없지만, 모든 절대 규칙(Hard)을 완벽하게 지킨 스케줄을 일단 완성했습니다</t>
+  </si>
+  <si>
+    <t>상태: 엑셀 근무표를 그대로 사용하셔도 무방합니다. (더 완벽한 결과를 원하시면 Setup 시트의 시간을 늘리고 다시 돌려보세요.)</t>
+  </si>
+  <si>
+    <t>INFEASIBLE (작성 실패 - 규칙 충돌) 🚨</t>
+  </si>
+  <si>
+    <t>의미: 스케줄을 짤 수가 없습니다! 조건들이 서로 모순됩니다</t>
+  </si>
+  <si>
+    <t>상태: 근무표 작성에 실패하여 엑셀이 업데이트되지 않습니다. (주로 1순위 오프가 너무 많거나, 출근할 인원이 부족할 때 발생합니다. 인원이나 오프를 수정하고 다시 돌려주세요.)</t>
+  </si>
+  <si>
+    <t>UNKNOWN (작성 실패 - 시간 초과) 🚨</t>
+  </si>
+  <si>
+    <t>의미: 규칙이 너무 복잡해서 제한 시간 안에 단 한 개의 스케줄도 완성하지 못했습니다.</t>
+  </si>
+  <si>
+    <t>상태: Setup 시트의 Solver time limit (sec) 시간을 600초 이상으로 넉넉히 늘리거나, 연속 근무 제한을 살짝 풀어주세요.</t>
+  </si>
+  <si>
+    <t>2️⃣ Objective value (AI의 스케줄 채점표 / 벌점)</t>
+  </si>
+  <si>
+    <t>의미: 이 숫자는 인공지능이 스케줄을 짜면서 받은 벌점(Penalty)의 총합입니다.</t>
+  </si>
+  <si>
+    <t>해석 방법: "숫자가 낮을수록(0에 가까울수록) 훌륭한 근무표입니다!"</t>
+  </si>
+  <si>
+    <t>컴퓨터는 무조건 이 벌점을 낮추기 위해 수백만 번의 경우의 수를 계산합니다.</t>
+  </si>
+  <si>
+    <t>벌점이 올라가는(숫자가 커지는) 이유:</t>
+  </si>
+  <si>
+    <t>1. 선생님들이 신청한 듀티(E or D 등)를 어쩔 수 없이 못 들어줬을 때</t>
+  </si>
+  <si>
+    <t>2. 2순위, 3순위 오프 신청을 반려하고 출근시켰을 때</t>
+  </si>
+  <si>
+    <t>3. 간호사들 간의 총 근무 일수나 나이트 개수가 공평하게 딱 떨어지지 않았을 때</t>
   </si>
   <si>
     <t>Nurse Name</t>
@@ -848,733 +923,19 @@
     <t>간호사50</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Nurses </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>시트에</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>적힌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>이름과</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> OffRequests, ShiftPreferences </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>등</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>간호사</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>이름이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>들어간</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>모든</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>시트의</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>이름과</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>순서가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>반드시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>일치해야</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>합니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>. (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>간호사</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>퇴사</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>입사로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>인원을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>수정할</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>때는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>세</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>시트</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>모두</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>똑같이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>수정해</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>주세요</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>자동 반영 되는데 간호사 순서 밀림에 주의해주세요</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
+    <t>Nurses 시트에 적힌 이름과 OffRequests, ShiftPreferences 등 간호사 이름이 들어간 모든 시트의 이름과 순서가 반드시 일치해야 합니다. (간호사 퇴사/입사로 인원을 수정할 때는 세 시트 모두 똑같이 수정해 주세요. 자동 반영 되는데 간호사 순서 밀림에 주의해주세요)</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>🌐 [웹사이트 실행 방법]</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. 이 엑셀 파일에 근무 조건과 오프 신청을 모두 입력한 뒤 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>저장하고 닫습니다.</t>
-    </r>
-  </si>
-  <si>
-    <t>2. 스케줄러 웹사이트에 접속합니다. (여기에 선생님의 웹사이트 주소 링크를 적어주세요!)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">3. 웹사이트 화면에 저장한 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>엑셀 파일을 마우스로 끌어다 놓고 [🚀 AI 근무표 자동 생성 시작] 버튼</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>을 누릅니다.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>🤖 [AI 결과 메시지 해석]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 웹사이트에서 버튼을 누른 뒤 나오는 알림창의 의미입니다.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>✅ 성공 (초록색 알림창 &amp; 풍선):</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> AI가 완벽한 근무표를 찾았습니다! 다운로드 버튼을 눌러 확인하세요.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>🚨 규칙 충돌 에러 (빨간색 알림창):</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 스케줄을 짤 수 없습니다! 조건들이 서로 모순됩니다. (주로 1순위 오프가 너무 많거나, 나이트 출근 인원이 부족할 때 발생합니다. 인원이나 오프를 수정하고 다시 올려주세요.)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>🚨 시간 초과 에러 (빨간색 알림창):</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 규칙이 너무 복잡해서 제한 시간 내에 풀지 못했습니다. Setup 시트의 제한 시간을 300초 이상으로 넉넉히 늘리거나 규칙을 살짝 풀어주세요.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">4. 계산이 끝나고 풍선이 터지면 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📥</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 다운로드]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 버튼을 눌러 완성된 근무표를 확인하세요! </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(팁: 엑셀 파일 이름은 '4월_최종근무표.xlsx' 처럼 마음대로 바꿔서 올려도 작동합니다!)</t>
-    </r>
+    <t>성균관대 기계공학부 20학번 김정진</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>🎯</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> AI가 받은 벌점(Objective Value):</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 성공 메시지에 표시되는 점수로, AI가 스케줄을 짜면서 어쩔 수 없이 받은 페널티의 총합입니다. **"숫자가 낮을수록(0에 가까울수록) 훌륭하고 공평한 근무표"**라는 뜻입니다!</t>
-    </r>
+    <t>막내 여부(Y)</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> (오프 반려, 주니어 나이트 쏠림 등이 생길 때마다 벌점이 올라갑니다.)</t>
+    <t>막내 여부: 막내 여부를 두 명 이상 Y 체크하면 막내끼리는 같은 듀티에 가급적 배치하지 않습니다</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1582,7 +943,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="37">
+  <fonts count="34">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1753,6 +1114,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
@@ -1823,43 +1190,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial Unicode MS"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
-      <sz val="11"/>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
@@ -1868,10 +1201,21 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
       <color theme="1"/>
-      <name val="Segoe UI Emoji"/>
-      <family val="2"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
@@ -2044,7 +1388,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2113,11 +1457,9 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2148,6 +1490,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2164,26 +1509,26 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
@@ -2191,59 +1536,58 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -2253,10 +1597,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="3"/>
     </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2264,8 +1607,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2585,29 +1929,24 @@
         <v>61</v>
       </c>
       <c r="L1" s="27"/>
-      <c r="M1" s="28" t="s">
+      <c r="M1" s="94" t="s">
         <v>62</v>
       </c>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="29"/>
-      <c r="R1" s="29"/>
-      <c r="S1" s="29"/>
-      <c r="T1" s="29"/>
-      <c r="U1" s="29"/>
-      <c r="V1" s="29"/>
-      <c r="W1" s="29"/>
-      <c r="X1" s="30"/>
+      <c r="S1" s="28"/>
+      <c r="T1" s="28"/>
+      <c r="U1" s="28"/>
+      <c r="V1" s="28"/>
+      <c r="W1" s="28"/>
+      <c r="X1" s="29"/>
     </row>
     <row r="2" spans="1:24" ht="38.25" customHeight="1">
       <c r="A2" s="21"/>
-      <c r="K2" s="31"/>
+      <c r="K2" s="30"/>
       <c r="L2" s="25"/>
-      <c r="M2" s="32" t="s">
-        <v>63</v>
-      </c>
-      <c r="X2" s="33"/>
+      <c r="M2" s="94" t="s">
+        <v>293</v>
+      </c>
+      <c r="X2" s="31"/>
     </row>
     <row r="3" spans="1:24" ht="33.75" customHeight="1">
       <c r="D3" s="25"/>
@@ -2616,10 +1955,10 @@
       <c r="G3" s="25"/>
       <c r="H3" s="25"/>
       <c r="I3" s="24"/>
-      <c r="K3" s="34" t="s">
-        <v>228</v>
-      </c>
-      <c r="X3" s="33"/>
+      <c r="K3" s="32" t="s">
+        <v>253</v>
+      </c>
+      <c r="X3" s="31"/>
     </row>
     <row r="4" spans="1:24" ht="32.25" customHeight="1" thickBot="1">
       <c r="D4" s="25"/>
@@ -2628,41 +1967,41 @@
       <c r="G4" s="25"/>
       <c r="H4" s="25"/>
       <c r="I4" s="24"/>
-      <c r="K4" s="35" t="s">
-        <v>64</v>
-      </c>
-      <c r="L4" s="36"/>
-      <c r="M4" s="37"/>
-      <c r="N4" s="37"/>
-      <c r="O4" s="37"/>
-      <c r="P4" s="37"/>
-      <c r="Q4" s="37"/>
-      <c r="R4" s="37"/>
-      <c r="S4" s="37"/>
-      <c r="T4" s="37"/>
-      <c r="U4" s="37"/>
-      <c r="V4" s="37"/>
-      <c r="W4" s="37"/>
-      <c r="X4" s="38"/>
+      <c r="K4" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="L4" s="34"/>
+      <c r="M4" s="35"/>
+      <c r="N4" s="35"/>
+      <c r="O4" s="35"/>
+      <c r="P4" s="35"/>
+      <c r="Q4" s="35"/>
+      <c r="R4" s="35"/>
+      <c r="S4" s="35"/>
+      <c r="T4" s="35"/>
+      <c r="U4" s="35"/>
+      <c r="V4" s="35"/>
+      <c r="W4" s="35"/>
+      <c r="X4" s="36"/>
     </row>
     <row r="6" spans="1:24" ht="15.75" customHeight="1">
       <c r="A6" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:24" ht="26.25" customHeight="1">
       <c r="A8" s="22" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:24">
       <c r="A10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:24">
       <c r="A12" s="23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:24">
@@ -2670,7 +2009,7 @@
     </row>
     <row r="14" spans="1:24">
       <c r="A14" s="17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:24">
@@ -2678,7 +2017,7 @@
     </row>
     <row r="16" spans="1:24">
       <c r="A16" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:1">
@@ -2686,7 +2025,7 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="1:1">
@@ -2694,7 +2033,7 @@
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -2702,12 +2041,12 @@
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="23" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="25" spans="1:1">
@@ -2715,12 +2054,12 @@
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29" spans="1:1">
@@ -2728,7 +2067,7 @@
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31" spans="1:1">
@@ -2736,7 +2075,7 @@
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" spans="1:1">
@@ -2744,12 +2083,12 @@
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37" spans="1:1">
@@ -2757,22 +2096,22 @@
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42" spans="1:1" ht="26.25" customHeight="1">
       <c r="A42" s="15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="46" spans="1:1" ht="21.75" customHeight="1">
       <c r="A46" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="47" spans="1:1">
@@ -2780,7 +2119,7 @@
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="49" spans="1:1">
@@ -2788,7 +2127,7 @@
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="51" spans="1:1">
@@ -2796,7 +2135,7 @@
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="53" spans="1:1">
@@ -2804,7 +2143,7 @@
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="55" spans="1:1">
@@ -2812,7 +2151,7 @@
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="57" spans="1:1">
@@ -2820,12 +2159,12 @@
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="60" spans="1:1" ht="21.75" customHeight="1">
       <c r="A60" s="18" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="61" spans="1:1">
@@ -2833,7 +2172,7 @@
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="63" spans="1:1">
@@ -2841,7 +2180,7 @@
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="65" spans="1:1">
@@ -2849,7 +2188,7 @@
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="20" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="67" spans="1:1">
@@ -2857,7 +2196,7 @@
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="20" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="69" spans="1:1">
@@ -2865,7 +2204,7 @@
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="20" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="71" spans="1:1">
@@ -2873,7 +2212,7 @@
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="20" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="73" spans="1:1">
@@ -2881,7 +2220,7 @@
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="75" spans="1:1">
@@ -2889,7 +2228,7 @@
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="77" spans="1:1">
@@ -2897,7 +2236,7 @@
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="79" spans="1:1">
@@ -2905,7 +2244,7 @@
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="17" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="81" spans="1:1">
@@ -2913,12 +2252,12 @@
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="17" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="19" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="84" spans="1:1">
@@ -2926,7 +2265,7 @@
     </row>
     <row r="86" spans="1:1" ht="21.75" customHeight="1">
       <c r="A86" s="18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="87" spans="1:1">
@@ -2934,7 +2273,7 @@
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="89" spans="1:1">
@@ -2942,7 +2281,7 @@
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="17" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="91" spans="1:1">
@@ -2950,7 +2289,7 @@
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="19" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="93" spans="1:1">
@@ -2958,7 +2297,7 @@
     </row>
     <row r="94" spans="1:1">
       <c r="A94" s="20" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="95" spans="1:1">
@@ -2966,7 +2305,7 @@
     </row>
     <row r="96" spans="1:1">
       <c r="A96" s="20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="97" spans="1:10">
@@ -2974,7 +2313,7 @@
     </row>
     <row r="98" spans="1:10">
       <c r="A98" s="20" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="99" spans="1:10">
@@ -2982,86 +2321,86 @@
     </row>
     <row r="100" spans="1:10">
       <c r="A100" s="19" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="102" spans="1:10" ht="21.75" customHeight="1">
       <c r="A102" s="18" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="103" spans="1:10">
       <c r="A103" s="16"/>
     </row>
     <row r="104" spans="1:10">
-      <c r="A104" s="43" t="s">
+      <c r="A104" s="41" t="s">
+        <v>112</v>
+      </c>
+      <c r="B104" s="42"/>
+      <c r="C104" s="42"/>
+      <c r="D104" s="42"/>
+      <c r="E104" s="42"/>
+      <c r="F104" s="42"/>
+      <c r="G104" s="42"/>
+      <c r="H104" s="42"/>
+      <c r="I104" s="42"/>
+      <c r="J104" s="42"/>
+    </row>
+    <row r="105" spans="1:10">
+      <c r="A105" s="41"/>
+      <c r="B105" s="42"/>
+      <c r="C105" s="42"/>
+      <c r="D105" s="42"/>
+      <c r="E105" s="42"/>
+      <c r="F105" s="42"/>
+      <c r="G105" s="42"/>
+      <c r="H105" s="42"/>
+      <c r="I105" s="42"/>
+      <c r="J105" s="42"/>
+    </row>
+    <row r="106" spans="1:10">
+      <c r="A106" s="79" t="s">
         <v>113</v>
       </c>
-      <c r="B104" s="44"/>
-      <c r="C104" s="44"/>
-      <c r="D104" s="44"/>
-      <c r="E104" s="44"/>
-      <c r="F104" s="44"/>
-      <c r="G104" s="44"/>
-      <c r="H104" s="44"/>
-      <c r="I104" s="44"/>
-      <c r="J104" s="44"/>
-    </row>
-    <row r="105" spans="1:10">
-      <c r="A105" s="43"/>
-      <c r="B105" s="44"/>
-      <c r="C105" s="44"/>
-      <c r="D105" s="44"/>
-      <c r="E105" s="44"/>
-      <c r="F105" s="44"/>
-      <c r="G105" s="44"/>
-      <c r="H105" s="44"/>
-      <c r="I105" s="44"/>
-      <c r="J105" s="44"/>
-    </row>
-    <row r="106" spans="1:10">
-      <c r="A106" s="81" t="s">
+      <c r="B106" s="42"/>
+      <c r="C106" s="42"/>
+      <c r="D106" s="42"/>
+      <c r="E106" s="42"/>
+      <c r="F106" s="42"/>
+      <c r="G106" s="42"/>
+      <c r="H106" s="42"/>
+      <c r="I106" s="42"/>
+      <c r="J106" s="42"/>
+    </row>
+    <row r="107" spans="1:10">
+      <c r="A107" s="41"/>
+      <c r="B107" s="42"/>
+      <c r="C107" s="42"/>
+      <c r="D107" s="42"/>
+      <c r="E107" s="42"/>
+      <c r="F107" s="42"/>
+      <c r="G107" s="42"/>
+      <c r="H107" s="42"/>
+      <c r="I107" s="42"/>
+      <c r="J107" s="42"/>
+    </row>
+    <row r="108" spans="1:10">
+      <c r="A108" s="41" t="s">
         <v>114</v>
       </c>
-      <c r="B106" s="44"/>
-      <c r="C106" s="44"/>
-      <c r="D106" s="44"/>
-      <c r="E106" s="44"/>
-      <c r="F106" s="44"/>
-      <c r="G106" s="44"/>
-      <c r="H106" s="44"/>
-      <c r="I106" s="44"/>
-      <c r="J106" s="44"/>
-    </row>
-    <row r="107" spans="1:10">
-      <c r="A107" s="43"/>
-      <c r="B107" s="44"/>
-      <c r="C107" s="44"/>
-      <c r="D107" s="44"/>
-      <c r="E107" s="44"/>
-      <c r="F107" s="44"/>
-      <c r="G107" s="44"/>
-      <c r="H107" s="44"/>
-      <c r="I107" s="44"/>
-      <c r="J107" s="44"/>
-    </row>
-    <row r="108" spans="1:10">
-      <c r="A108" s="43" t="s">
-        <v>115</v>
-      </c>
-      <c r="B108" s="44"/>
-      <c r="C108" s="44"/>
-      <c r="D108" s="44"/>
-      <c r="E108" s="44"/>
-      <c r="F108" s="44"/>
-      <c r="G108" s="44"/>
-      <c r="H108" s="44"/>
-      <c r="I108" s="44"/>
-      <c r="J108" s="44"/>
+      <c r="B108" s="42"/>
+      <c r="C108" s="42"/>
+      <c r="D108" s="42"/>
+      <c r="E108" s="42"/>
+      <c r="F108" s="42"/>
+      <c r="G108" s="42"/>
+      <c r="H108" s="42"/>
+      <c r="I108" s="42"/>
+      <c r="J108" s="42"/>
     </row>
     <row r="110" spans="1:10" ht="21.75" customHeight="1">
       <c r="A110" s="18" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="111" spans="1:10">
@@ -3069,7 +2408,7 @@
     </row>
     <row r="112" spans="1:10">
       <c r="A112" s="17" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="113" spans="1:1">
@@ -3077,7 +2416,7 @@
     </row>
     <row r="114" spans="1:1">
       <c r="A114" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="115" spans="1:1">
@@ -3085,12 +2424,12 @@
     </row>
     <row r="116" spans="1:1">
       <c r="A116" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="119" spans="1:1">
@@ -3098,186 +2437,203 @@
     </row>
     <row r="120" spans="1:1">
       <c r="A120" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="121" spans="1:1">
       <c r="A121" s="11"/>
     </row>
     <row r="122" spans="1:1" ht="26.25" customHeight="1">
-      <c r="A122" s="40" t="s">
-        <v>122</v>
+      <c r="A122" s="38" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" s="16"/>
     </row>
     <row r="124" spans="1:1">
-      <c r="A124" s="45" t="s">
+      <c r="A124" s="43" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" s="44"/>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" s="43" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="125" spans="1:1">
-      <c r="A125" s="46"/>
-    </row>
-    <row r="126" spans="1:1">
-      <c r="A126" s="45" t="s">
+    <row r="127" spans="1:1">
+      <c r="A127" s="45" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" s="44"/>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" s="43" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="127" spans="1:1">
-      <c r="A127" s="93" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1">
-      <c r="A128" s="46"/>
-    </row>
-    <row r="129" spans="1:1">
-      <c r="A129" s="45" t="s">
+    <row r="130" spans="1:1">
+      <c r="A130" s="39" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="130" spans="1:1">
-      <c r="A130" s="41" t="s">
+    <row r="131" spans="1:1">
+      <c r="A131" s="44"/>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" s="43" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="131" spans="1:1">
-      <c r="A131" s="46"/>
-    </row>
-    <row r="132" spans="1:1">
-      <c r="A132" s="45" t="s">
+    <row r="134" spans="1:1" ht="26.25" customHeight="1">
+      <c r="A134" s="83" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="134" spans="1:1" ht="26.25" customHeight="1">
-      <c r="A134" s="17" t="s">
-        <v>268</v>
-      </c>
-    </row>
     <row r="135" spans="1:1" ht="26.25" customHeight="1">
-      <c r="A135" s="19"/>
-    </row>
-    <row r="136" spans="1:1">
-      <c r="A136" s="19" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="137" spans="1:1">
-      <c r="A137" s="19"/>
+      <c r="A135" s="88" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="138" spans="1:1" ht="20.25" customHeight="1">
-      <c r="A138" s="19" t="s">
-        <v>270</v>
+      <c r="A138" s="92" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="139" spans="1:1">
-      <c r="A139" s="19"/>
-    </row>
-    <row r="140" spans="1:1">
-      <c r="A140" s="19" t="s">
-        <v>271</v>
+      <c r="A139" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="141" spans="1:1" ht="21.75" customHeight="1">
-      <c r="A141" s="19"/>
-    </row>
-    <row r="142" spans="1:1">
-      <c r="A142" s="19" t="s">
-        <v>276</v>
+      <c r="A141" s="18" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="143" spans="1:1">
-      <c r="A143" s="16"/>
+      <c r="A143" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="144" spans="1:1">
-      <c r="A144" s="17" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5">
-      <c r="A145" s="19"/>
-    </row>
-    <row r="146" spans="1:5">
+      <c r="A144" s="16"/>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" s="89" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
       <c r="A146" s="90" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5">
-      <c r="A147" s="19"/>
-    </row>
-    <row r="148" spans="1:5">
-      <c r="A148" s="90" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5">
-      <c r="A149" s="19"/>
-    </row>
-    <row r="150" spans="1:5">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147" s="90" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" s="16"/>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" s="89" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
       <c r="A150" s="90" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5">
-      <c r="A151" s="19"/>
-    </row>
-    <row r="152" spans="1:5">
-      <c r="A152" s="97" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5">
-      <c r="A153" s="89"/>
-      <c r="E153" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5">
-      <c r="A154" s="90"/>
-    </row>
-    <row r="155" spans="1:5">
-      <c r="A155" s="90"/>
-    </row>
-    <row r="156" spans="1:5">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" s="90" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152" s="16"/>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153" s="89" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154" s="90" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155" s="90" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
       <c r="A156" s="16"/>
     </row>
-    <row r="157" spans="1:5">
-      <c r="A157" s="89"/>
-    </row>
-    <row r="158" spans="1:5">
-      <c r="A158" s="90"/>
-    </row>
-    <row r="159" spans="1:5">
-      <c r="A159" s="90"/>
+    <row r="157" spans="1:1">
+      <c r="A157" s="89" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158" s="90" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159" s="90" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="161" spans="1:1" ht="21.75" customHeight="1">
-      <c r="A161" s="18"/>
+      <c r="A161" s="18" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="162" spans="1:1">
       <c r="A162" s="16"/>
     </row>
     <row r="163" spans="1:1">
-      <c r="A163" s="17"/>
+      <c r="A163" s="17" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="164" spans="1:1">
-      <c r="A164" s="17"/>
+      <c r="A164" s="17" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="166" spans="1:1">
-      <c r="A166" s="19"/>
+      <c r="A166" s="19" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="167" spans="1:1">
-      <c r="A167" s="90"/>
+      <c r="A167" s="90" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="168" spans="1:1">
-      <c r="A168" s="91"/>
+      <c r="A168" s="91" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="169" spans="1:1">
-      <c r="A169" s="91"/>
+      <c r="A169" s="91" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="170" spans="1:1">
-      <c r="A170" s="91"/>
+      <c r="A170" s="91" t="s">
+        <v>152</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -3299,22 +2655,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>170</v>
+        <v>195</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>209</v>
+        <v>234</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>196</v>
+        <v>221</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>210</v>
+        <v>235</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>211</v>
+        <v>236</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>212</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -3338,68 +2694,68 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="5" t="s">
-        <v>170</v>
+        <v>195</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>213</v>
+        <v>238</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>214</v>
+        <v>239</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>215</v>
+        <v>240</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>217</v>
+        <v>242</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>218</v>
+        <v>243</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>219</v>
+        <v>244</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>220</v>
+        <v>245</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="I2" s="92"/>
+      <c r="I2" s="93"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="I3" s="92"/>
+      <c r="I3" s="93"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="I4" s="92"/>
+      <c r="I4" s="93"/>
     </row>
     <row r="5" spans="1:9">
-      <c r="I5" s="92"/>
+      <c r="I5" s="93"/>
     </row>
     <row r="6" spans="1:9">
-      <c r="I6" s="92"/>
+      <c r="I6" s="93"/>
     </row>
     <row r="7" spans="1:9">
-      <c r="I7" s="92"/>
+      <c r="I7" s="93"/>
     </row>
     <row r="8" spans="1:9">
-      <c r="I8" s="92"/>
+      <c r="I8" s="93"/>
     </row>
     <row r="9" spans="1:9">
-      <c r="I9" s="92"/>
+      <c r="I9" s="93"/>
     </row>
     <row r="10" spans="1:9">
-      <c r="I10" s="92"/>
+      <c r="I10" s="93"/>
     </row>
     <row r="11" spans="1:9">
-      <c r="I11" s="92"/>
+      <c r="I11" s="93"/>
     </row>
     <row r="12" spans="1:9">
-      <c r="I12" s="92"/>
+      <c r="I12" s="93"/>
     </row>
     <row r="13" spans="1:9">
-      <c r="I13" s="92"/>
+      <c r="I13" s="93"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -3418,125 +2774,125 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="5" t="s">
-        <v>209</v>
+        <v>234</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>196</v>
+        <v>221</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>221</v>
+        <v>246</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>222</v>
+        <v>247</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>223</v>
+        <v>248</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>224</v>
+        <v>249</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>227</v>
+        <v>252</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="I2" s="92"/>
+      <c r="I2" s="93"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="I3" s="92"/>
+      <c r="I3" s="93"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="I4" s="92"/>
+      <c r="I4" s="93"/>
     </row>
     <row r="5" spans="1:9">
-      <c r="I5" s="92"/>
+      <c r="I5" s="93"/>
     </row>
     <row r="6" spans="1:9">
-      <c r="I6" s="92"/>
+      <c r="I6" s="93"/>
     </row>
     <row r="7" spans="1:9">
-      <c r="I7" s="92"/>
+      <c r="I7" s="93"/>
     </row>
     <row r="8" spans="1:9">
-      <c r="I8" s="92"/>
+      <c r="I8" s="93"/>
     </row>
     <row r="9" spans="1:9">
-      <c r="I9" s="92"/>
+      <c r="I9" s="93"/>
     </row>
     <row r="10" spans="1:9">
-      <c r="I10" s="92"/>
+      <c r="I10" s="93"/>
     </row>
     <row r="11" spans="1:9">
-      <c r="I11" s="92"/>
+      <c r="I11" s="93"/>
     </row>
     <row r="12" spans="1:9">
-      <c r="I12" s="92"/>
+      <c r="I12" s="93"/>
     </row>
     <row r="13" spans="1:9">
-      <c r="I13" s="92"/>
+      <c r="I13" s="93"/>
     </row>
     <row r="14" spans="1:9">
-      <c r="I14" s="92"/>
+      <c r="I14" s="93"/>
     </row>
     <row r="15" spans="1:9">
-      <c r="I15" s="92"/>
+      <c r="I15" s="93"/>
     </row>
     <row r="16" spans="1:9">
-      <c r="I16" s="92"/>
+      <c r="I16" s="93"/>
     </row>
     <row r="17" spans="9:9">
-      <c r="I17" s="92"/>
+      <c r="I17" s="93"/>
     </row>
     <row r="18" spans="9:9">
-      <c r="I18" s="92"/>
+      <c r="I18" s="93"/>
     </row>
     <row r="19" spans="9:9">
-      <c r="I19" s="92"/>
+      <c r="I19" s="93"/>
     </row>
     <row r="20" spans="9:9">
-      <c r="I20" s="92"/>
+      <c r="I20" s="93"/>
     </row>
     <row r="21" spans="9:9">
-      <c r="I21" s="92"/>
+      <c r="I21" s="93"/>
     </row>
     <row r="22" spans="9:9">
-      <c r="I22" s="92"/>
+      <c r="I22" s="93"/>
     </row>
     <row r="23" spans="9:9">
-      <c r="I23" s="92"/>
+      <c r="I23" s="93"/>
     </row>
     <row r="24" spans="9:9">
-      <c r="I24" s="92"/>
+      <c r="I24" s="93"/>
     </row>
     <row r="25" spans="9:9">
-      <c r="I25" s="92"/>
+      <c r="I25" s="93"/>
     </row>
     <row r="26" spans="9:9">
-      <c r="I26" s="92"/>
+      <c r="I26" s="93"/>
     </row>
     <row r="27" spans="9:9">
-      <c r="I27" s="92"/>
+      <c r="I27" s="93"/>
     </row>
     <row r="28" spans="9:9">
-      <c r="I28" s="92"/>
+      <c r="I28" s="93"/>
     </row>
     <row r="29" spans="9:9">
-      <c r="I29" s="92"/>
+      <c r="I29" s="93"/>
     </row>
     <row r="30" spans="9:9">
-      <c r="I30" s="92"/>
+      <c r="I30" s="93"/>
     </row>
     <row r="31" spans="9:9">
-      <c r="I31" s="92"/>
+      <c r="I31" s="93"/>
     </row>
     <row r="32" spans="9:9">
-      <c r="I32" s="92"/>
+      <c r="I32" s="93"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -3556,18 +2912,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="94" t="s">
+      <c r="A1" s="95" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="95"/>
-      <c r="C1" s="95"/>
-      <c r="D1" s="95"/>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="48">
+      <c r="B2" s="47">
         <v>2026</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -3581,7 +2937,7 @@
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="48">
+      <c r="B3" s="47">
         <v>3</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -3595,7 +2951,7 @@
       <c r="A4" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="48">
+      <c r="B4" s="47">
         <v>11</v>
       </c>
       <c r="C4" t="s">
@@ -3604,14 +2960,14 @@
       <c r="D4" s="2"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="B5" s="49"/>
+      <c r="B5" s="48"/>
       <c r="D5" s="10"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="48">
+      <c r="B6" s="47">
         <v>3</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -3623,7 +2979,7 @@
       <c r="A7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="48">
+      <c r="B7" s="47">
         <v>3</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -3635,7 +2991,7 @@
       <c r="A8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="48">
+      <c r="B8" s="47">
         <v>2</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -3647,7 +3003,7 @@
       <c r="A9" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="50">
+      <c r="B9" s="49">
         <v>0</v>
       </c>
       <c r="C9" s="10" t="s">
@@ -3657,7 +3013,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2"/>
-      <c r="B10" s="51"/>
+      <c r="B10" s="50"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
@@ -3665,7 +3021,7 @@
       <c r="A11" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="48">
+      <c r="B11" s="47">
         <v>2</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -3677,7 +3033,7 @@
       <c r="A12" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="48">
+      <c r="B12" s="47">
         <v>2</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -3689,7 +3045,7 @@
       <c r="A13" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="48">
+      <c r="B13" s="47">
         <v>2</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -3701,7 +3057,7 @@
       <c r="A14" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="50">
+      <c r="B14" s="49">
         <v>0</v>
       </c>
       <c r="C14" s="10" t="s">
@@ -3711,7 +3067,7 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2"/>
-      <c r="B15" s="51"/>
+      <c r="B15" s="50"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
     </row>
@@ -3719,7 +3075,7 @@
       <c r="A16" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="48">
+      <c r="B16" s="47">
         <v>5</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -3731,7 +3087,7 @@
       <c r="A17" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="50">
+      <c r="B17" s="49">
         <v>4</v>
       </c>
       <c r="C17" s="10" t="s">
@@ -3743,7 +3099,7 @@
       <c r="A18" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="50">
+      <c r="B18" s="49">
         <v>4</v>
       </c>
       <c r="C18" s="10" t="s">
@@ -3755,7 +3111,7 @@
       <c r="A19" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="48">
+      <c r="B19" s="47">
         <v>3</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -3767,7 +3123,7 @@
       <c r="A20" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B20" s="50">
+      <c r="B20" s="49">
         <v>2</v>
       </c>
       <c r="C20" t="s">
@@ -3779,7 +3135,7 @@
       <c r="A21" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B21" s="48">
+      <c r="B21" s="47">
         <v>2</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -3789,7 +3145,7 @@
     </row>
     <row r="22" spans="1:17">
       <c r="A22" s="9"/>
-      <c r="B22" s="50"/>
+      <c r="B22" s="49"/>
       <c r="C22" s="10"/>
       <c r="D22" s="10"/>
     </row>
@@ -3797,10 +3153,10 @@
       <c r="A23" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="48">
+      <c r="B23" s="47">
         <v>10</v>
       </c>
-      <c r="C23" s="47" t="s">
+      <c r="C23" s="46" t="s">
         <v>38</v>
       </c>
       <c r="D23" s="2"/>
@@ -3809,7 +3165,7 @@
       <c r="A24" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="48">
+      <c r="B24" s="47">
         <v>100</v>
       </c>
       <c r="C24" s="2" t="s">
@@ -3821,7 +3177,7 @@
       <c r="A25" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="48">
+      <c r="B25" s="47">
         <v>10</v>
       </c>
       <c r="C25" s="2" t="s">
@@ -3833,7 +3189,7 @@
       <c r="A26" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B26" s="48">
+      <c r="B26" s="47">
         <v>10</v>
       </c>
       <c r="C26" s="2" t="s">
@@ -3845,7 +3201,7 @@
       <c r="A27" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B27" s="50">
+      <c r="B27" s="49">
         <v>4</v>
       </c>
       <c r="C27" s="10" t="s">
@@ -3857,7 +3213,7 @@
       <c r="A28" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B28" s="50">
+      <c r="B28" s="49">
         <v>10</v>
       </c>
       <c r="C28" s="10" t="s">
@@ -3869,7 +3225,7 @@
       <c r="A29" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B29" s="48">
+      <c r="B29" s="47">
         <v>2</v>
       </c>
       <c r="C29" s="2" t="s">
@@ -3884,332 +3240,332 @@
       <c r="D30" s="2"/>
     </row>
     <row r="31" spans="1:17" ht="17.25" customHeight="1" thickBot="1">
-      <c r="A31" s="39"/>
-      <c r="B31" s="39"/>
-      <c r="C31" s="39"/>
-      <c r="D31" s="39"/>
+      <c r="A31" s="37"/>
+      <c r="B31" s="37"/>
+      <c r="C31" s="37"/>
+      <c r="D31" s="37"/>
     </row>
     <row r="32" spans="1:17" ht="17.25" customHeight="1">
-      <c r="A32" s="64" t="s">
+      <c r="A32" s="63" t="s">
         <v>51</v>
       </c>
-      <c r="B32" s="53"/>
-      <c r="C32" s="53"/>
-      <c r="D32" s="53"/>
-      <c r="E32" s="53"/>
-      <c r="F32" s="53"/>
-      <c r="G32" s="53"/>
-      <c r="H32" s="53"/>
-      <c r="I32" s="53"/>
-      <c r="J32" s="53"/>
-      <c r="K32" s="53"/>
-      <c r="L32" s="53"/>
-      <c r="M32" s="53"/>
-      <c r="N32" s="53"/>
-      <c r="O32" s="53"/>
-      <c r="P32" s="53"/>
-      <c r="Q32" s="54"/>
+      <c r="B32" s="52"/>
+      <c r="C32" s="52"/>
+      <c r="D32" s="52"/>
+      <c r="E32" s="52"/>
+      <c r="F32" s="52"/>
+      <c r="G32" s="52"/>
+      <c r="H32" s="52"/>
+      <c r="I32" s="52"/>
+      <c r="J32" s="52"/>
+      <c r="K32" s="52"/>
+      <c r="L32" s="52"/>
+      <c r="M32" s="52"/>
+      <c r="N32" s="52"/>
+      <c r="O32" s="52"/>
+      <c r="P32" s="52"/>
+      <c r="Q32" s="53"/>
     </row>
     <row r="33" spans="1:17" ht="17.25" customHeight="1">
-      <c r="A33" s="55" t="s">
+      <c r="A33" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="B33" s="56"/>
-      <c r="C33" s="56"/>
-      <c r="D33" s="56"/>
-      <c r="E33" s="56"/>
-      <c r="F33" s="56"/>
-      <c r="G33" s="56"/>
-      <c r="H33" s="56"/>
-      <c r="I33" s="56"/>
-      <c r="J33" s="56"/>
-      <c r="K33" s="56"/>
-      <c r="L33" s="56"/>
-      <c r="M33" s="56"/>
-      <c r="N33" s="56"/>
-      <c r="O33" s="56"/>
-      <c r="P33" s="56"/>
-      <c r="Q33" s="57"/>
+      <c r="B33" s="55"/>
+      <c r="C33" s="55"/>
+      <c r="D33" s="55"/>
+      <c r="E33" s="55"/>
+      <c r="F33" s="55"/>
+      <c r="G33" s="55"/>
+      <c r="H33" s="55"/>
+      <c r="I33" s="55"/>
+      <c r="J33" s="55"/>
+      <c r="K33" s="55"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="55"/>
+      <c r="N33" s="55"/>
+      <c r="O33" s="55"/>
+      <c r="P33" s="55"/>
+      <c r="Q33" s="56"/>
     </row>
     <row r="34" spans="1:17" ht="17.25" customHeight="1">
-      <c r="A34" s="58"/>
-      <c r="B34" s="56"/>
-      <c r="C34" s="56"/>
-      <c r="D34" s="56"/>
-      <c r="E34" s="56"/>
-      <c r="F34" s="56"/>
-      <c r="G34" s="56"/>
-      <c r="H34" s="56"/>
-      <c r="I34" s="56"/>
-      <c r="J34" s="56"/>
-      <c r="K34" s="56"/>
-      <c r="L34" s="56"/>
-      <c r="M34" s="56"/>
-      <c r="N34" s="56"/>
-      <c r="O34" s="56"/>
-      <c r="P34" s="56"/>
-      <c r="Q34" s="57"/>
+      <c r="A34" s="57"/>
+      <c r="B34" s="55"/>
+      <c r="C34" s="55"/>
+      <c r="D34" s="55"/>
+      <c r="E34" s="55"/>
+      <c r="F34" s="55"/>
+      <c r="G34" s="55"/>
+      <c r="H34" s="55"/>
+      <c r="I34" s="55"/>
+      <c r="J34" s="55"/>
+      <c r="K34" s="55"/>
+      <c r="L34" s="55"/>
+      <c r="M34" s="55"/>
+      <c r="N34" s="55"/>
+      <c r="O34" s="55"/>
+      <c r="P34" s="55"/>
+      <c r="Q34" s="56"/>
     </row>
     <row r="35" spans="1:17" ht="17.25" customHeight="1">
-      <c r="A35" s="55" t="s">
+      <c r="A35" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="B35" s="56"/>
-      <c r="C35" s="56"/>
-      <c r="D35" s="56"/>
-      <c r="E35" s="56"/>
-      <c r="F35" s="56"/>
-      <c r="G35" s="56"/>
-      <c r="H35" s="56"/>
-      <c r="I35" s="56"/>
-      <c r="J35" s="56"/>
-      <c r="K35" s="56"/>
-      <c r="L35" s="56"/>
-      <c r="M35" s="56"/>
-      <c r="N35" s="56"/>
-      <c r="O35" s="56"/>
-      <c r="P35" s="56"/>
-      <c r="Q35" s="57"/>
+      <c r="B35" s="55"/>
+      <c r="C35" s="55"/>
+      <c r="D35" s="55"/>
+      <c r="E35" s="55"/>
+      <c r="F35" s="55"/>
+      <c r="G35" s="55"/>
+      <c r="H35" s="55"/>
+      <c r="I35" s="55"/>
+      <c r="J35" s="55"/>
+      <c r="K35" s="55"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="55"/>
+      <c r="N35" s="55"/>
+      <c r="O35" s="55"/>
+      <c r="P35" s="55"/>
+      <c r="Q35" s="56"/>
     </row>
     <row r="36" spans="1:17" ht="17.25" customHeight="1">
-      <c r="A36" s="58"/>
-      <c r="B36" s="56"/>
-      <c r="C36" s="56"/>
-      <c r="D36" s="56"/>
-      <c r="E36" s="56"/>
-      <c r="F36" s="56"/>
-      <c r="G36" s="56"/>
-      <c r="H36" s="56"/>
-      <c r="I36" s="56"/>
-      <c r="J36" s="56"/>
-      <c r="K36" s="56"/>
-      <c r="L36" s="56"/>
-      <c r="M36" s="56"/>
-      <c r="N36" s="56"/>
-      <c r="O36" s="56"/>
-      <c r="P36" s="56"/>
-      <c r="Q36" s="57"/>
+      <c r="A36" s="57"/>
+      <c r="B36" s="55"/>
+      <c r="C36" s="55"/>
+      <c r="D36" s="55"/>
+      <c r="E36" s="55"/>
+      <c r="F36" s="55"/>
+      <c r="G36" s="55"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="55"/>
+      <c r="J36" s="55"/>
+      <c r="K36" s="55"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="55"/>
+      <c r="N36" s="55"/>
+      <c r="O36" s="55"/>
+      <c r="P36" s="55"/>
+      <c r="Q36" s="56"/>
     </row>
     <row r="37" spans="1:17" ht="17.25" customHeight="1">
-      <c r="A37" s="55" t="s">
+      <c r="A37" s="54" t="s">
         <v>54</v>
       </c>
-      <c r="B37" s="56"/>
-      <c r="C37" s="56"/>
-      <c r="D37" s="56"/>
-      <c r="E37" s="56"/>
-      <c r="F37" s="56"/>
-      <c r="G37" s="56"/>
-      <c r="H37" s="56"/>
-      <c r="I37" s="56"/>
-      <c r="J37" s="56"/>
-      <c r="K37" s="56"/>
-      <c r="L37" s="56"/>
-      <c r="M37" s="56"/>
-      <c r="N37" s="56"/>
-      <c r="O37" s="56"/>
-      <c r="P37" s="56"/>
-      <c r="Q37" s="57"/>
+      <c r="B37" s="55"/>
+      <c r="C37" s="55"/>
+      <c r="D37" s="55"/>
+      <c r="E37" s="55"/>
+      <c r="F37" s="55"/>
+      <c r="G37" s="55"/>
+      <c r="H37" s="55"/>
+      <c r="I37" s="55"/>
+      <c r="J37" s="55"/>
+      <c r="K37" s="55"/>
+      <c r="L37" s="55"/>
+      <c r="M37" s="55"/>
+      <c r="N37" s="55"/>
+      <c r="O37" s="55"/>
+      <c r="P37" s="55"/>
+      <c r="Q37" s="56"/>
     </row>
     <row r="38" spans="1:17" ht="17.25" customHeight="1">
-      <c r="A38" s="59"/>
-      <c r="B38" s="56"/>
-      <c r="C38" s="56"/>
-      <c r="D38" s="56"/>
-      <c r="E38" s="56"/>
-      <c r="F38" s="56"/>
-      <c r="G38" s="56"/>
-      <c r="H38" s="56"/>
-      <c r="I38" s="56"/>
-      <c r="J38" s="56"/>
-      <c r="K38" s="56"/>
-      <c r="L38" s="56"/>
-      <c r="M38" s="56"/>
-      <c r="N38" s="56"/>
-      <c r="O38" s="56"/>
-      <c r="P38" s="56"/>
-      <c r="Q38" s="57"/>
+      <c r="A38" s="58"/>
+      <c r="B38" s="55"/>
+      <c r="C38" s="55"/>
+      <c r="D38" s="55"/>
+      <c r="E38" s="55"/>
+      <c r="F38" s="55"/>
+      <c r="G38" s="55"/>
+      <c r="H38" s="55"/>
+      <c r="I38" s="55"/>
+      <c r="J38" s="55"/>
+      <c r="K38" s="55"/>
+      <c r="L38" s="55"/>
+      <c r="M38" s="55"/>
+      <c r="N38" s="55"/>
+      <c r="O38" s="55"/>
+      <c r="P38" s="55"/>
+      <c r="Q38" s="56"/>
     </row>
     <row r="39" spans="1:17" ht="17.25" customHeight="1">
-      <c r="A39" s="60" t="s">
+      <c r="A39" s="59" t="s">
         <v>55</v>
       </c>
-      <c r="B39" s="56"/>
-      <c r="C39" s="56"/>
-      <c r="D39" s="56"/>
-      <c r="E39" s="56"/>
-      <c r="F39" s="56"/>
-      <c r="G39" s="56"/>
-      <c r="H39" s="56"/>
-      <c r="I39" s="56"/>
-      <c r="J39" s="56"/>
-      <c r="K39" s="56"/>
-      <c r="L39" s="56"/>
-      <c r="M39" s="56"/>
-      <c r="N39" s="56"/>
-      <c r="O39" s="56"/>
-      <c r="P39" s="56"/>
-      <c r="Q39" s="57"/>
+      <c r="B39" s="55"/>
+      <c r="C39" s="55"/>
+      <c r="D39" s="55"/>
+      <c r="E39" s="55"/>
+      <c r="F39" s="55"/>
+      <c r="G39" s="55"/>
+      <c r="H39" s="55"/>
+      <c r="I39" s="55"/>
+      <c r="J39" s="55"/>
+      <c r="K39" s="55"/>
+      <c r="L39" s="55"/>
+      <c r="M39" s="55"/>
+      <c r="N39" s="55"/>
+      <c r="O39" s="55"/>
+      <c r="P39" s="55"/>
+      <c r="Q39" s="56"/>
     </row>
     <row r="40" spans="1:17" ht="17.25" customHeight="1">
-      <c r="A40" s="59"/>
-      <c r="B40" s="56"/>
-      <c r="C40" s="56"/>
-      <c r="D40" s="56"/>
-      <c r="E40" s="56"/>
-      <c r="F40" s="56"/>
-      <c r="G40" s="56"/>
-      <c r="H40" s="56"/>
-      <c r="I40" s="56"/>
-      <c r="J40" s="56"/>
-      <c r="K40" s="56"/>
-      <c r="L40" s="56"/>
-      <c r="M40" s="56"/>
-      <c r="N40" s="56"/>
-      <c r="O40" s="56"/>
-      <c r="P40" s="56"/>
-      <c r="Q40" s="57"/>
+      <c r="A40" s="58"/>
+      <c r="B40" s="55"/>
+      <c r="C40" s="55"/>
+      <c r="D40" s="55"/>
+      <c r="E40" s="55"/>
+      <c r="F40" s="55"/>
+      <c r="G40" s="55"/>
+      <c r="H40" s="55"/>
+      <c r="I40" s="55"/>
+      <c r="J40" s="55"/>
+      <c r="K40" s="55"/>
+      <c r="L40" s="55"/>
+      <c r="M40" s="55"/>
+      <c r="N40" s="55"/>
+      <c r="O40" s="55"/>
+      <c r="P40" s="55"/>
+      <c r="Q40" s="56"/>
     </row>
     <row r="41" spans="1:17" ht="17.25" customHeight="1">
-      <c r="A41" s="60" t="s">
+      <c r="A41" s="59" t="s">
         <v>56</v>
       </c>
-      <c r="B41" s="56"/>
-      <c r="C41" s="56"/>
-      <c r="D41" s="56"/>
-      <c r="E41" s="56"/>
-      <c r="F41" s="56"/>
-      <c r="G41" s="56"/>
-      <c r="H41" s="56"/>
-      <c r="I41" s="56"/>
-      <c r="J41" s="56"/>
-      <c r="K41" s="56"/>
-      <c r="L41" s="56"/>
-      <c r="M41" s="56"/>
-      <c r="N41" s="56"/>
-      <c r="O41" s="56"/>
-      <c r="P41" s="56"/>
-      <c r="Q41" s="57"/>
+      <c r="B41" s="55"/>
+      <c r="C41" s="55"/>
+      <c r="D41" s="55"/>
+      <c r="E41" s="55"/>
+      <c r="F41" s="55"/>
+      <c r="G41" s="55"/>
+      <c r="H41" s="55"/>
+      <c r="I41" s="55"/>
+      <c r="J41" s="55"/>
+      <c r="K41" s="55"/>
+      <c r="L41" s="55"/>
+      <c r="M41" s="55"/>
+      <c r="N41" s="55"/>
+      <c r="O41" s="55"/>
+      <c r="P41" s="55"/>
+      <c r="Q41" s="56"/>
     </row>
     <row r="42" spans="1:17" ht="17.25" customHeight="1">
-      <c r="A42" s="59"/>
-      <c r="B42" s="56"/>
-      <c r="C42" s="56"/>
-      <c r="D42" s="56"/>
-      <c r="E42" s="56"/>
-      <c r="F42" s="56"/>
-      <c r="G42" s="56"/>
-      <c r="H42" s="56"/>
-      <c r="I42" s="56"/>
-      <c r="J42" s="56"/>
-      <c r="K42" s="56"/>
-      <c r="L42" s="56"/>
-      <c r="M42" s="56"/>
-      <c r="N42" s="56"/>
-      <c r="O42" s="56"/>
-      <c r="P42" s="56"/>
-      <c r="Q42" s="57"/>
+      <c r="A42" s="58"/>
+      <c r="B42" s="55"/>
+      <c r="C42" s="55"/>
+      <c r="D42" s="55"/>
+      <c r="E42" s="55"/>
+      <c r="F42" s="55"/>
+      <c r="G42" s="55"/>
+      <c r="H42" s="55"/>
+      <c r="I42" s="55"/>
+      <c r="J42" s="55"/>
+      <c r="K42" s="55"/>
+      <c r="L42" s="55"/>
+      <c r="M42" s="55"/>
+      <c r="N42" s="55"/>
+      <c r="O42" s="55"/>
+      <c r="P42" s="55"/>
+      <c r="Q42" s="56"/>
     </row>
     <row r="43" spans="1:17" ht="17.25" customHeight="1">
-      <c r="A43" s="60" t="s">
+      <c r="A43" s="59" t="s">
         <v>57</v>
       </c>
-      <c r="B43" s="56"/>
-      <c r="C43" s="56"/>
-      <c r="D43" s="56"/>
-      <c r="E43" s="56"/>
-      <c r="F43" s="56"/>
-      <c r="G43" s="56"/>
-      <c r="H43" s="56"/>
-      <c r="I43" s="56"/>
-      <c r="J43" s="56"/>
-      <c r="K43" s="56"/>
-      <c r="L43" s="56"/>
-      <c r="M43" s="56"/>
-      <c r="N43" s="56"/>
-      <c r="O43" s="56"/>
-      <c r="P43" s="56"/>
-      <c r="Q43" s="57"/>
+      <c r="B43" s="55"/>
+      <c r="C43" s="55"/>
+      <c r="D43" s="55"/>
+      <c r="E43" s="55"/>
+      <c r="F43" s="55"/>
+      <c r="G43" s="55"/>
+      <c r="H43" s="55"/>
+      <c r="I43" s="55"/>
+      <c r="J43" s="55"/>
+      <c r="K43" s="55"/>
+      <c r="L43" s="55"/>
+      <c r="M43" s="55"/>
+      <c r="N43" s="55"/>
+      <c r="O43" s="55"/>
+      <c r="P43" s="55"/>
+      <c r="Q43" s="56"/>
     </row>
     <row r="44" spans="1:17" ht="17.25" customHeight="1">
-      <c r="A44" s="59"/>
-      <c r="B44" s="56"/>
-      <c r="C44" s="56"/>
-      <c r="D44" s="56"/>
-      <c r="E44" s="56"/>
-      <c r="F44" s="56"/>
-      <c r="G44" s="56"/>
-      <c r="H44" s="56"/>
-      <c r="I44" s="56"/>
-      <c r="J44" s="56"/>
-      <c r="K44" s="56"/>
-      <c r="L44" s="56"/>
-      <c r="M44" s="56"/>
-      <c r="N44" s="56"/>
-      <c r="O44" s="56"/>
-      <c r="P44" s="56"/>
-      <c r="Q44" s="57"/>
+      <c r="A44" s="58"/>
+      <c r="B44" s="55"/>
+      <c r="C44" s="55"/>
+      <c r="D44" s="55"/>
+      <c r="E44" s="55"/>
+      <c r="F44" s="55"/>
+      <c r="G44" s="55"/>
+      <c r="H44" s="55"/>
+      <c r="I44" s="55"/>
+      <c r="J44" s="55"/>
+      <c r="K44" s="55"/>
+      <c r="L44" s="55"/>
+      <c r="M44" s="55"/>
+      <c r="N44" s="55"/>
+      <c r="O44" s="55"/>
+      <c r="P44" s="55"/>
+      <c r="Q44" s="56"/>
     </row>
     <row r="45" spans="1:17" ht="17.25" customHeight="1">
-      <c r="A45" s="60" t="s">
+      <c r="A45" s="59" t="s">
         <v>58</v>
       </c>
-      <c r="B45" s="56"/>
-      <c r="C45" s="56"/>
-      <c r="D45" s="56"/>
-      <c r="E45" s="56"/>
-      <c r="F45" s="56"/>
-      <c r="G45" s="56"/>
-      <c r="H45" s="56"/>
-      <c r="I45" s="56"/>
-      <c r="J45" s="56"/>
-      <c r="K45" s="56"/>
-      <c r="L45" s="56"/>
-      <c r="M45" s="56"/>
-      <c r="N45" s="56"/>
-      <c r="O45" s="56"/>
-      <c r="P45" s="56"/>
-      <c r="Q45" s="57"/>
+      <c r="B45" s="55"/>
+      <c r="C45" s="55"/>
+      <c r="D45" s="55"/>
+      <c r="E45" s="55"/>
+      <c r="F45" s="55"/>
+      <c r="G45" s="55"/>
+      <c r="H45" s="55"/>
+      <c r="I45" s="55"/>
+      <c r="J45" s="55"/>
+      <c r="K45" s="55"/>
+      <c r="L45" s="55"/>
+      <c r="M45" s="55"/>
+      <c r="N45" s="55"/>
+      <c r="O45" s="55"/>
+      <c r="P45" s="55"/>
+      <c r="Q45" s="56"/>
     </row>
     <row r="46" spans="1:17" ht="17.25" customHeight="1">
-      <c r="A46" s="58"/>
-      <c r="B46" s="56"/>
-      <c r="C46" s="56"/>
-      <c r="D46" s="56"/>
-      <c r="E46" s="56"/>
-      <c r="F46" s="56"/>
-      <c r="G46" s="56"/>
-      <c r="H46" s="56"/>
-      <c r="I46" s="56"/>
-      <c r="J46" s="56"/>
-      <c r="K46" s="56"/>
-      <c r="L46" s="56"/>
-      <c r="M46" s="56"/>
-      <c r="N46" s="56"/>
-      <c r="O46" s="56"/>
-      <c r="P46" s="56"/>
-      <c r="Q46" s="57"/>
+      <c r="A46" s="57"/>
+      <c r="B46" s="55"/>
+      <c r="C46" s="55"/>
+      <c r="D46" s="55"/>
+      <c r="E46" s="55"/>
+      <c r="F46" s="55"/>
+      <c r="G46" s="55"/>
+      <c r="H46" s="55"/>
+      <c r="I46" s="55"/>
+      <c r="J46" s="55"/>
+      <c r="K46" s="55"/>
+      <c r="L46" s="55"/>
+      <c r="M46" s="55"/>
+      <c r="N46" s="55"/>
+      <c r="O46" s="55"/>
+      <c r="P46" s="55"/>
+      <c r="Q46" s="56"/>
     </row>
     <row r="47" spans="1:17" ht="18" customHeight="1" thickBot="1">
-      <c r="A47" s="61" t="s">
+      <c r="A47" s="60" t="s">
         <v>59</v>
       </c>
-      <c r="B47" s="62"/>
-      <c r="C47" s="62"/>
-      <c r="D47" s="62"/>
-      <c r="E47" s="62"/>
-      <c r="F47" s="62"/>
-      <c r="G47" s="62"/>
-      <c r="H47" s="62"/>
-      <c r="I47" s="62"/>
-      <c r="J47" s="62"/>
-      <c r="K47" s="62"/>
-      <c r="L47" s="62"/>
-      <c r="M47" s="62"/>
-      <c r="N47" s="62"/>
-      <c r="O47" s="62"/>
-      <c r="P47" s="62"/>
-      <c r="Q47" s="63"/>
+      <c r="B47" s="61"/>
+      <c r="C47" s="61"/>
+      <c r="D47" s="61"/>
+      <c r="E47" s="61"/>
+      <c r="F47" s="61"/>
+      <c r="G47" s="61"/>
+      <c r="H47" s="61"/>
+      <c r="I47" s="61"/>
+      <c r="J47" s="61"/>
+      <c r="K47" s="61"/>
+      <c r="L47" s="61"/>
+      <c r="M47" s="61"/>
+      <c r="N47" s="61"/>
+      <c r="O47" s="61"/>
+      <c r="P47" s="61"/>
+      <c r="Q47" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4230,471 +3586,751 @@
     <col min="2" max="2" width="11.625" customWidth="1"/>
     <col min="3" max="3" width="20.125" customWidth="1"/>
     <col min="4" max="4" width="18.875" customWidth="1"/>
+    <col min="6" max="6" width="14.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="17.25" customHeight="1" thickBot="1">
       <c r="A1" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B1" s="67" t="s">
-        <v>129</v>
-      </c>
-      <c r="C1" s="67" t="s">
-        <v>130</v>
-      </c>
-      <c r="D1" s="67" t="s">
-        <v>131</v>
-      </c>
-      <c r="E1" s="67" t="s">
-        <v>132</v>
+        <v>153</v>
+      </c>
+      <c r="B1" s="66" t="s">
+        <v>154</v>
+      </c>
+      <c r="C1" s="66" t="s">
+        <v>155</v>
+      </c>
+      <c r="D1" s="66" t="s">
+        <v>156</v>
+      </c>
+      <c r="E1" s="66" t="s">
+        <v>157</v>
+      </c>
+      <c r="F1" s="66" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="2" spans="1:27">
-      <c r="A2" s="85" t="s">
-        <v>133</v>
-      </c>
-      <c r="H2" s="68" t="s">
+      <c r="A2" s="84" t="s">
+        <v>158</v>
+      </c>
+      <c r="H2" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-      <c r="M2" s="29"/>
-      <c r="N2" s="29"/>
-      <c r="O2" s="29"/>
-      <c r="P2" s="29"/>
-      <c r="Q2" s="29"/>
-      <c r="R2" s="29"/>
-      <c r="S2" s="29"/>
-      <c r="T2" s="29"/>
-      <c r="U2" s="29"/>
-      <c r="V2" s="29"/>
-      <c r="W2" s="29"/>
-      <c r="X2" s="29"/>
-      <c r="Y2" s="29"/>
-      <c r="Z2" s="29"/>
-      <c r="AA2" s="30"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
+      <c r="P2" s="28"/>
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="28"/>
+      <c r="T2" s="28"/>
+      <c r="U2" s="28"/>
+      <c r="V2" s="28"/>
+      <c r="W2" s="28"/>
+      <c r="X2" s="28"/>
+      <c r="Y2" s="28"/>
+      <c r="Z2" s="28"/>
+      <c r="AA2" s="29"/>
     </row>
     <row r="3" spans="1:27">
       <c r="A3" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="H3" s="52" t="s">
-        <v>135</v>
-      </c>
-      <c r="AA3" s="33"/>
+        <v>159</v>
+      </c>
+      <c r="H3" s="51" t="s">
+        <v>160</v>
+      </c>
+      <c r="I3" s="98"/>
+      <c r="J3" s="98"/>
+      <c r="K3" s="98"/>
+      <c r="L3" s="98"/>
+      <c r="M3" s="98"/>
+      <c r="N3" s="98"/>
+      <c r="O3" s="98"/>
+      <c r="P3" s="98"/>
+      <c r="Q3" s="98"/>
+      <c r="R3" s="98"/>
+      <c r="S3" s="98"/>
+      <c r="T3" s="98"/>
+      <c r="U3" s="98"/>
+      <c r="V3" s="98"/>
+      <c r="W3" s="98"/>
+      <c r="X3" s="98"/>
+      <c r="Y3" s="98"/>
+      <c r="Z3" s="98"/>
+      <c r="AA3" s="31"/>
     </row>
     <row r="4" spans="1:27">
-      <c r="A4" s="85" t="s">
-        <v>136</v>
-      </c>
-      <c r="H4" s="52" t="s">
-        <v>137</v>
-      </c>
-      <c r="AA4" s="33"/>
+      <c r="A4" s="84" t="s">
+        <v>161</v>
+      </c>
+      <c r="H4" s="51" t="s">
+        <v>162</v>
+      </c>
+      <c r="I4" s="98"/>
+      <c r="J4" s="98"/>
+      <c r="K4" s="98"/>
+      <c r="L4" s="98"/>
+      <c r="M4" s="98"/>
+      <c r="N4" s="98"/>
+      <c r="O4" s="98"/>
+      <c r="P4" s="98"/>
+      <c r="Q4" s="98"/>
+      <c r="R4" s="98"/>
+      <c r="S4" s="98"/>
+      <c r="T4" s="98"/>
+      <c r="U4" s="98"/>
+      <c r="V4" s="98"/>
+      <c r="W4" s="98"/>
+      <c r="X4" s="98"/>
+      <c r="Y4" s="98"/>
+      <c r="Z4" s="98"/>
+      <c r="AA4" s="31"/>
     </row>
     <row r="5" spans="1:27">
       <c r="A5" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="H5" s="52" t="s">
-        <v>139</v>
-      </c>
-      <c r="AA5" s="33"/>
+        <v>163</v>
+      </c>
+      <c r="H5" s="51" t="s">
+        <v>164</v>
+      </c>
+      <c r="I5" s="98"/>
+      <c r="J5" s="98"/>
+      <c r="K5" s="98"/>
+      <c r="L5" s="98"/>
+      <c r="M5" s="98"/>
+      <c r="N5" s="98"/>
+      <c r="O5" s="98"/>
+      <c r="P5" s="98"/>
+      <c r="Q5" s="98"/>
+      <c r="R5" s="98"/>
+      <c r="S5" s="98"/>
+      <c r="T5" s="98"/>
+      <c r="U5" s="98"/>
+      <c r="V5" s="98"/>
+      <c r="W5" s="98"/>
+      <c r="X5" s="98"/>
+      <c r="Y5" s="98"/>
+      <c r="Z5" s="98"/>
+      <c r="AA5" s="31"/>
     </row>
     <row r="6" spans="1:27">
-      <c r="A6" s="85" t="s">
-        <v>140</v>
-      </c>
-      <c r="H6" s="72"/>
-      <c r="AA6" s="33"/>
+      <c r="A6" s="84" t="s">
+        <v>165</v>
+      </c>
+      <c r="H6" s="71"/>
+      <c r="I6" s="98"/>
+      <c r="J6" s="98"/>
+      <c r="K6" s="98"/>
+      <c r="L6" s="98"/>
+      <c r="M6" s="98"/>
+      <c r="N6" s="98"/>
+      <c r="O6" s="98"/>
+      <c r="P6" s="98"/>
+      <c r="Q6" s="98"/>
+      <c r="R6" s="98"/>
+      <c r="S6" s="98"/>
+      <c r="T6" s="98"/>
+      <c r="U6" s="98"/>
+      <c r="V6" s="98"/>
+      <c r="W6" s="98"/>
+      <c r="X6" s="98"/>
+      <c r="Y6" s="98"/>
+      <c r="Z6" s="98"/>
+      <c r="AA6" s="31"/>
     </row>
     <row r="7" spans="1:27">
       <c r="A7" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="H7" s="72" t="s">
-        <v>142</v>
-      </c>
-      <c r="AA7" s="33"/>
+        <v>166</v>
+      </c>
+      <c r="H7" s="71" t="s">
+        <v>167</v>
+      </c>
+      <c r="I7" s="98"/>
+      <c r="J7" s="98"/>
+      <c r="K7" s="98"/>
+      <c r="L7" s="98"/>
+      <c r="M7" s="98"/>
+      <c r="N7" s="98"/>
+      <c r="O7" s="98"/>
+      <c r="P7" s="98"/>
+      <c r="Q7" s="98"/>
+      <c r="R7" s="98"/>
+      <c r="S7" s="98"/>
+      <c r="T7" s="98"/>
+      <c r="U7" s="98"/>
+      <c r="V7" s="98"/>
+      <c r="W7" s="98"/>
+      <c r="X7" s="98"/>
+      <c r="Y7" s="98"/>
+      <c r="Z7" s="98"/>
+      <c r="AA7" s="31"/>
     </row>
     <row r="8" spans="1:27">
-      <c r="A8" s="85" t="s">
-        <v>143</v>
-      </c>
-      <c r="H8" s="72" t="s">
-        <v>144</v>
-      </c>
-      <c r="AA8" s="33"/>
+      <c r="A8" s="84" t="s">
+        <v>168</v>
+      </c>
+      <c r="H8" s="71" t="s">
+        <v>169</v>
+      </c>
+      <c r="I8" s="98"/>
+      <c r="J8" s="98"/>
+      <c r="K8" s="98"/>
+      <c r="L8" s="98"/>
+      <c r="M8" s="98"/>
+      <c r="N8" s="98"/>
+      <c r="O8" s="98"/>
+      <c r="P8" s="98"/>
+      <c r="Q8" s="98"/>
+      <c r="R8" s="98"/>
+      <c r="S8" s="98"/>
+      <c r="T8" s="98"/>
+      <c r="U8" s="98"/>
+      <c r="V8" s="98"/>
+      <c r="W8" s="98"/>
+      <c r="X8" s="98"/>
+      <c r="Y8" s="98"/>
+      <c r="Z8" s="98"/>
+      <c r="AA8" s="31"/>
     </row>
     <row r="9" spans="1:27">
       <c r="A9" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="H9" s="72" t="s">
-        <v>146</v>
-      </c>
-      <c r="AA9" s="33"/>
+        <v>170</v>
+      </c>
+      <c r="H9" s="71" t="s">
+        <v>171</v>
+      </c>
+      <c r="I9" s="98"/>
+      <c r="J9" s="98"/>
+      <c r="K9" s="98"/>
+      <c r="L9" s="98"/>
+      <c r="M9" s="98"/>
+      <c r="N9" s="98"/>
+      <c r="O9" s="98"/>
+      <c r="P9" s="98"/>
+      <c r="Q9" s="98"/>
+      <c r="R9" s="98"/>
+      <c r="S9" s="98"/>
+      <c r="T9" s="98"/>
+      <c r="U9" s="98"/>
+      <c r="V9" s="98"/>
+      <c r="W9" s="98"/>
+      <c r="X9" s="98"/>
+      <c r="Y9" s="98"/>
+      <c r="Z9" s="98"/>
+      <c r="AA9" s="31"/>
     </row>
     <row r="10" spans="1:27">
-      <c r="A10" s="85" t="s">
-        <v>147</v>
-      </c>
-      <c r="H10" s="72"/>
-      <c r="AA10" s="33"/>
+      <c r="A10" s="84" t="s">
+        <v>172</v>
+      </c>
+      <c r="H10" s="71"/>
+      <c r="I10" s="98"/>
+      <c r="J10" s="98"/>
+      <c r="K10" s="98"/>
+      <c r="L10" s="98"/>
+      <c r="M10" s="98"/>
+      <c r="N10" s="98"/>
+      <c r="O10" s="98"/>
+      <c r="P10" s="98"/>
+      <c r="Q10" s="98"/>
+      <c r="R10" s="98"/>
+      <c r="S10" s="98"/>
+      <c r="T10" s="98"/>
+      <c r="U10" s="98"/>
+      <c r="V10" s="98"/>
+      <c r="W10" s="98"/>
+      <c r="X10" s="98"/>
+      <c r="Y10" s="98"/>
+      <c r="Z10" s="98"/>
+      <c r="AA10" s="31"/>
     </row>
     <row r="11" spans="1:27">
       <c r="A11" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="H11" s="72" t="s">
-        <v>149</v>
-      </c>
-      <c r="AA11" s="33"/>
+        <v>173</v>
+      </c>
+      <c r="H11" s="71" t="s">
+        <v>174</v>
+      </c>
+      <c r="I11" s="98"/>
+      <c r="J11" s="98"/>
+      <c r="K11" s="98"/>
+      <c r="L11" s="98"/>
+      <c r="M11" s="98"/>
+      <c r="N11" s="98"/>
+      <c r="O11" s="98"/>
+      <c r="P11" s="98"/>
+      <c r="Q11" s="98"/>
+      <c r="R11" s="98"/>
+      <c r="S11" s="98"/>
+      <c r="T11" s="98"/>
+      <c r="U11" s="98"/>
+      <c r="V11" s="98"/>
+      <c r="W11" s="98"/>
+      <c r="X11" s="98"/>
+      <c r="Y11" s="98"/>
+      <c r="Z11" s="98"/>
+      <c r="AA11" s="31"/>
     </row>
     <row r="12" spans="1:27">
-      <c r="A12" s="85" t="s">
-        <v>150</v>
-      </c>
-      <c r="H12" s="72"/>
-      <c r="AA12" s="33"/>
+      <c r="A12" s="84" t="s">
+        <v>175</v>
+      </c>
+      <c r="H12" s="71"/>
+      <c r="I12" s="98"/>
+      <c r="J12" s="98"/>
+      <c r="K12" s="98"/>
+      <c r="L12" s="98"/>
+      <c r="M12" s="98"/>
+      <c r="N12" s="98"/>
+      <c r="O12" s="98"/>
+      <c r="P12" s="98"/>
+      <c r="Q12" s="98"/>
+      <c r="R12" s="98"/>
+      <c r="S12" s="98"/>
+      <c r="T12" s="98"/>
+      <c r="U12" s="98"/>
+      <c r="V12" s="98"/>
+      <c r="W12" s="98"/>
+      <c r="X12" s="98"/>
+      <c r="Y12" s="98"/>
+      <c r="Z12" s="98"/>
+      <c r="AA12" s="31"/>
     </row>
     <row r="13" spans="1:27">
       <c r="A13" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="H13" s="73" t="s">
-        <v>132</v>
-      </c>
-      <c r="AA13" s="33"/>
+        <v>176</v>
+      </c>
+      <c r="H13" s="72" t="s">
+        <v>157</v>
+      </c>
+      <c r="I13" s="98"/>
+      <c r="J13" s="98"/>
+      <c r="K13" s="98"/>
+      <c r="L13" s="98"/>
+      <c r="M13" s="98"/>
+      <c r="N13" s="98"/>
+      <c r="O13" s="98"/>
+      <c r="P13" s="98"/>
+      <c r="Q13" s="98"/>
+      <c r="R13" s="98"/>
+      <c r="S13" s="98"/>
+      <c r="T13" s="98"/>
+      <c r="U13" s="98"/>
+      <c r="V13" s="98"/>
+      <c r="W13" s="98"/>
+      <c r="X13" s="98"/>
+      <c r="Y13" s="98"/>
+      <c r="Z13" s="98"/>
+      <c r="AA13" s="31"/>
     </row>
     <row r="14" spans="1:27">
-      <c r="A14" s="85" t="s">
-        <v>229</v>
-      </c>
-      <c r="H14" s="73" t="s">
-        <v>152</v>
-      </c>
-      <c r="AA14" s="33"/>
+      <c r="A14" s="84" t="s">
+        <v>254</v>
+      </c>
+      <c r="H14" s="72" t="s">
+        <v>177</v>
+      </c>
+      <c r="I14" s="98"/>
+      <c r="J14" s="98"/>
+      <c r="K14" s="98"/>
+      <c r="L14" s="98"/>
+      <c r="M14" s="98"/>
+      <c r="N14" s="98"/>
+      <c r="O14" s="98"/>
+      <c r="P14" s="98"/>
+      <c r="Q14" s="98"/>
+      <c r="R14" s="98"/>
+      <c r="S14" s="98"/>
+      <c r="T14" s="98"/>
+      <c r="U14" s="98"/>
+      <c r="V14" s="98"/>
+      <c r="W14" s="98"/>
+      <c r="X14" s="98"/>
+      <c r="Y14" s="98"/>
+      <c r="Z14" s="98"/>
+      <c r="AA14" s="31"/>
     </row>
     <row r="15" spans="1:27">
       <c r="A15" s="13" t="s">
-        <v>230</v>
-      </c>
-      <c r="H15" s="74" t="s">
-        <v>153</v>
-      </c>
-      <c r="AA15" s="33"/>
-    </row>
-    <row r="16" spans="1:27" ht="17.25" customHeight="1" thickBot="1">
-      <c r="A16" s="85" t="s">
-        <v>231</v>
-      </c>
-      <c r="H16" s="75" t="s">
-        <v>154</v>
-      </c>
-      <c r="I16" s="37"/>
-      <c r="J16" s="37"/>
-      <c r="K16" s="37"/>
-      <c r="L16" s="37"/>
-      <c r="M16" s="37"/>
-      <c r="N16" s="37"/>
-      <c r="O16" s="37"/>
-      <c r="P16" s="37"/>
-      <c r="Q16" s="37"/>
-      <c r="R16" s="37"/>
-      <c r="S16" s="37"/>
-      <c r="T16" s="37"/>
-      <c r="U16" s="37"/>
-      <c r="V16" s="37"/>
-      <c r="W16" s="37"/>
-      <c r="X16" s="37"/>
-      <c r="Y16" s="37"/>
-      <c r="Z16" s="37"/>
-      <c r="AA16" s="38"/>
-    </row>
-    <row r="17" spans="1:14">
+        <v>255</v>
+      </c>
+      <c r="H15" s="73" t="s">
+        <v>178</v>
+      </c>
+      <c r="I15" s="98"/>
+      <c r="J15" s="98"/>
+      <c r="K15" s="98"/>
+      <c r="L15" s="98"/>
+      <c r="M15" s="98"/>
+      <c r="N15" s="98"/>
+      <c r="O15" s="98"/>
+      <c r="P15" s="98"/>
+      <c r="Q15" s="98"/>
+      <c r="R15" s="98"/>
+      <c r="S15" s="98"/>
+      <c r="T15" s="98"/>
+      <c r="U15" s="98"/>
+      <c r="V15" s="98"/>
+      <c r="W15" s="98"/>
+      <c r="X15" s="98"/>
+      <c r="Y15" s="98"/>
+      <c r="Z15" s="98"/>
+      <c r="AA15" s="31"/>
+    </row>
+    <row r="16" spans="1:27" ht="17.25" customHeight="1">
+      <c r="A16" s="84" t="s">
+        <v>256</v>
+      </c>
+      <c r="H16" s="73" t="s">
+        <v>179</v>
+      </c>
+      <c r="I16" s="98"/>
+      <c r="J16" s="98"/>
+      <c r="K16" s="98"/>
+      <c r="L16" s="98"/>
+      <c r="M16" s="98"/>
+      <c r="N16" s="98"/>
+      <c r="O16" s="98"/>
+      <c r="P16" s="98"/>
+      <c r="Q16" s="98"/>
+      <c r="R16" s="98"/>
+      <c r="S16" s="98"/>
+      <c r="T16" s="98"/>
+      <c r="U16" s="98"/>
+      <c r="V16" s="98"/>
+      <c r="W16" s="98"/>
+      <c r="X16" s="98"/>
+      <c r="Y16" s="98"/>
+      <c r="Z16" s="98"/>
+      <c r="AA16" s="31"/>
+    </row>
+    <row r="17" spans="1:27">
       <c r="A17" s="13" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
-      <c r="A18" s="85" t="s">
-        <v>233</v>
-      </c>
-      <c r="H18" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="H17" s="73"/>
+      <c r="I17" s="98"/>
+      <c r="J17" s="98"/>
+      <c r="K17" s="98"/>
+      <c r="L17" s="98"/>
+      <c r="M17" s="98"/>
+      <c r="N17" s="98"/>
+      <c r="O17" s="98"/>
+      <c r="P17" s="98"/>
+      <c r="Q17" s="98"/>
+      <c r="R17" s="98"/>
+      <c r="S17" s="98"/>
+      <c r="T17" s="98"/>
+      <c r="U17" s="98"/>
+      <c r="V17" s="98"/>
+      <c r="W17" s="98"/>
+      <c r="X17" s="98"/>
+      <c r="Y17" s="98"/>
+      <c r="Z17" s="98"/>
+      <c r="AA17" s="31"/>
+    </row>
+    <row r="18" spans="1:27" ht="17.25" thickBot="1">
+      <c r="A18" s="84" t="s">
+        <v>258</v>
+      </c>
+      <c r="H18" s="99" t="s">
+        <v>295</v>
+      </c>
+      <c r="I18" s="35"/>
+      <c r="J18" s="35"/>
+      <c r="K18" s="35"/>
+      <c r="L18" s="35"/>
+      <c r="M18" s="35"/>
+      <c r="N18" s="35"/>
+      <c r="O18" s="35"/>
+      <c r="P18" s="35"/>
+      <c r="Q18" s="35"/>
+      <c r="R18" s="35"/>
+      <c r="S18" s="35"/>
+      <c r="T18" s="35"/>
+      <c r="U18" s="35"/>
+      <c r="V18" s="35"/>
+      <c r="W18" s="35"/>
+      <c r="X18" s="35"/>
+      <c r="Y18" s="35"/>
+      <c r="Z18" s="35"/>
+      <c r="AA18" s="36"/>
+    </row>
+    <row r="19" spans="1:27">
+      <c r="A19" s="13" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27">
+      <c r="A20" s="84" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27">
+      <c r="A21" s="13" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27">
+      <c r="A22" s="84" t="s">
+        <v>262</v>
+      </c>
+      <c r="H22" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="I22" s="64"/>
+      <c r="J22" s="64"/>
+      <c r="K22" s="64"/>
+      <c r="L22" s="64"/>
+      <c r="M22" s="64"/>
+      <c r="N22" s="64"/>
+    </row>
+    <row r="23" spans="1:27">
+      <c r="A23" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="H23" s="85"/>
+      <c r="I23" s="64"/>
+      <c r="J23" s="64"/>
+      <c r="K23" s="64"/>
+      <c r="L23" s="64"/>
+      <c r="M23" s="64"/>
+      <c r="N23" s="64"/>
+    </row>
+    <row r="24" spans="1:27">
+      <c r="A24" s="84" t="s">
+        <v>264</v>
+      </c>
+      <c r="H24" s="86" t="s">
         <v>93</v>
       </c>
-      <c r="I18" s="65"/>
-      <c r="J18" s="65"/>
-      <c r="K18" s="65"/>
-      <c r="L18" s="65"/>
-      <c r="M18" s="65"/>
-      <c r="N18" s="65"/>
-    </row>
-    <row r="19" spans="1:14">
-      <c r="A19" s="13" t="s">
-        <v>234</v>
-      </c>
-      <c r="H19" s="86"/>
-      <c r="I19" s="65"/>
-      <c r="J19" s="65"/>
-      <c r="K19" s="65"/>
-      <c r="L19" s="65"/>
-      <c r="M19" s="65"/>
-      <c r="N19" s="65"/>
-    </row>
-    <row r="20" spans="1:14">
-      <c r="A20" s="85" t="s">
-        <v>235</v>
-      </c>
-      <c r="H20" s="87" t="s">
+      <c r="I24" s="64"/>
+      <c r="J24" s="64"/>
+      <c r="K24" s="64"/>
+      <c r="L24" s="64"/>
+      <c r="M24" s="64"/>
+      <c r="N24" s="64"/>
+    </row>
+    <row r="25" spans="1:27">
+      <c r="A25" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="H25" s="87"/>
+      <c r="I25" s="64"/>
+      <c r="J25" s="64"/>
+      <c r="K25" s="64"/>
+      <c r="L25" s="64"/>
+      <c r="M25" s="64"/>
+      <c r="N25" s="64"/>
+    </row>
+    <row r="26" spans="1:27">
+      <c r="A26" s="84" t="s">
+        <v>266</v>
+      </c>
+      <c r="H26" s="86" t="s">
         <v>94</v>
       </c>
-      <c r="I20" s="65"/>
-      <c r="J20" s="65"/>
-      <c r="K20" s="65"/>
-      <c r="L20" s="65"/>
-      <c r="M20" s="65"/>
-      <c r="N20" s="65"/>
-    </row>
-    <row r="21" spans="1:14">
-      <c r="A21" s="13" t="s">
-        <v>236</v>
-      </c>
-      <c r="H21" s="88"/>
-      <c r="I21" s="65"/>
-      <c r="J21" s="65"/>
-      <c r="K21" s="65"/>
-      <c r="L21" s="65"/>
-      <c r="M21" s="65"/>
-      <c r="N21" s="65"/>
-    </row>
-    <row r="22" spans="1:14">
-      <c r="A22" s="85" t="s">
-        <v>237</v>
-      </c>
-      <c r="H22" s="87" t="s">
+      <c r="I26" s="64"/>
+      <c r="J26" s="64"/>
+      <c r="K26" s="64"/>
+      <c r="L26" s="64"/>
+      <c r="M26" s="64"/>
+      <c r="N26" s="64"/>
+    </row>
+    <row r="27" spans="1:27">
+      <c r="A27" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="H27" s="87"/>
+      <c r="I27" s="64"/>
+      <c r="J27" s="64"/>
+      <c r="K27" s="64"/>
+      <c r="L27" s="64"/>
+      <c r="M27" s="64"/>
+      <c r="N27" s="64"/>
+    </row>
+    <row r="28" spans="1:27">
+      <c r="A28" s="84" t="s">
+        <v>268</v>
+      </c>
+      <c r="H28" s="86" t="s">
         <v>95</v>
       </c>
-      <c r="I22" s="65"/>
-      <c r="J22" s="65"/>
-      <c r="K22" s="65"/>
-      <c r="L22" s="65"/>
-      <c r="M22" s="65"/>
-      <c r="N22" s="65"/>
-    </row>
-    <row r="23" spans="1:14">
-      <c r="A23" s="13" t="s">
-        <v>238</v>
-      </c>
-      <c r="H23" s="88"/>
-      <c r="I23" s="65"/>
-      <c r="J23" s="65"/>
-      <c r="K23" s="65"/>
-      <c r="L23" s="65"/>
-      <c r="M23" s="65"/>
-      <c r="N23" s="65"/>
-    </row>
-    <row r="24" spans="1:14">
-      <c r="A24" s="85" t="s">
-        <v>239</v>
-      </c>
-      <c r="H24" s="87" t="s">
+      <c r="I28" s="64"/>
+      <c r="J28" s="64"/>
+      <c r="K28" s="64"/>
+      <c r="L28" s="64"/>
+      <c r="M28" s="64"/>
+      <c r="N28" s="64"/>
+    </row>
+    <row r="29" spans="1:27">
+      <c r="A29" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="H29" s="87"/>
+      <c r="I29" s="64"/>
+      <c r="J29" s="64"/>
+      <c r="K29" s="64"/>
+      <c r="L29" s="64"/>
+      <c r="M29" s="64"/>
+      <c r="N29" s="64"/>
+    </row>
+    <row r="30" spans="1:27">
+      <c r="A30" s="84" t="s">
+        <v>270</v>
+      </c>
+      <c r="H30" s="86" t="s">
         <v>96</v>
       </c>
-      <c r="I24" s="65"/>
-      <c r="J24" s="65"/>
-      <c r="K24" s="65"/>
-      <c r="L24" s="65"/>
-      <c r="M24" s="65"/>
-      <c r="N24" s="65"/>
-    </row>
-    <row r="25" spans="1:14">
-      <c r="A25" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="H25" s="88"/>
-      <c r="I25" s="65"/>
-      <c r="J25" s="65"/>
-      <c r="K25" s="65"/>
-      <c r="L25" s="65"/>
-      <c r="M25" s="65"/>
-      <c r="N25" s="65"/>
-    </row>
-    <row r="26" spans="1:14">
-      <c r="A26" s="85" t="s">
-        <v>241</v>
-      </c>
-      <c r="H26" s="87" t="s">
+      <c r="I30" s="64"/>
+      <c r="J30" s="64"/>
+      <c r="K30" s="64"/>
+      <c r="L30" s="64"/>
+      <c r="M30" s="64"/>
+      <c r="N30" s="64"/>
+    </row>
+    <row r="31" spans="1:27">
+      <c r="A31" s="84" t="s">
+        <v>271</v>
+      </c>
+      <c r="H31" s="87"/>
+      <c r="I31" s="64"/>
+      <c r="J31" s="64"/>
+      <c r="K31" s="64"/>
+      <c r="L31" s="64"/>
+      <c r="M31" s="64"/>
+      <c r="N31" s="64"/>
+    </row>
+    <row r="32" spans="1:27">
+      <c r="A32" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="H32" s="86" t="s">
         <v>97</v>
       </c>
-      <c r="I26" s="65"/>
-      <c r="J26" s="65"/>
-      <c r="K26" s="65"/>
-      <c r="L26" s="65"/>
-      <c r="M26" s="65"/>
-      <c r="N26" s="65"/>
-    </row>
-    <row r="27" spans="1:14">
-      <c r="A27" s="13" t="s">
-        <v>242</v>
-      </c>
-      <c r="H27" s="88"/>
-      <c r="I27" s="65"/>
-      <c r="J27" s="65"/>
-      <c r="K27" s="65"/>
-      <c r="L27" s="65"/>
-      <c r="M27" s="65"/>
-      <c r="N27" s="65"/>
-    </row>
-    <row r="28" spans="1:14">
-      <c r="A28" s="85" t="s">
-        <v>243</v>
-      </c>
-      <c r="H28" s="87" t="s">
+      <c r="I32" s="64"/>
+      <c r="J32" s="64"/>
+      <c r="K32" s="64"/>
+      <c r="L32" s="64"/>
+      <c r="M32" s="64"/>
+      <c r="N32" s="64"/>
+    </row>
+    <row r="33" spans="1:14">
+      <c r="A33" s="84" t="s">
+        <v>273</v>
+      </c>
+      <c r="H33" s="87"/>
+      <c r="I33" s="64"/>
+      <c r="J33" s="64"/>
+      <c r="K33" s="64"/>
+      <c r="L33" s="64"/>
+      <c r="M33" s="64"/>
+      <c r="N33" s="64"/>
+    </row>
+    <row r="34" spans="1:14">
+      <c r="A34" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="H34" s="86" t="s">
         <v>98</v>
       </c>
-      <c r="I28" s="65"/>
-      <c r="J28" s="65"/>
-      <c r="K28" s="65"/>
-      <c r="L28" s="65"/>
-      <c r="M28" s="65"/>
-      <c r="N28" s="65"/>
-    </row>
-    <row r="29" spans="1:14">
-      <c r="A29" s="13" t="s">
-        <v>244</v>
-      </c>
-      <c r="H29" s="88"/>
-      <c r="I29" s="65"/>
-      <c r="J29" s="65"/>
-      <c r="K29" s="65"/>
-      <c r="L29" s="65"/>
-      <c r="M29" s="65"/>
-      <c r="N29" s="65"/>
-    </row>
-    <row r="30" spans="1:14">
-      <c r="A30" s="85" t="s">
-        <v>245</v>
-      </c>
-      <c r="H30" s="87" t="s">
-        <v>99</v>
-      </c>
-      <c r="I30" s="65"/>
-      <c r="J30" s="65"/>
-      <c r="K30" s="65"/>
-      <c r="L30" s="65"/>
-      <c r="M30" s="65"/>
-      <c r="N30" s="65"/>
-    </row>
-    <row r="31" spans="1:14">
-      <c r="A31" s="85" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14">
-      <c r="A32" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="H32" s="23" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="85" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" s="13" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="85" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
+      <c r="I34" s="64"/>
+      <c r="J34" s="64"/>
+      <c r="K34" s="64"/>
+      <c r="L34" s="64"/>
+      <c r="M34" s="64"/>
+      <c r="N34" s="64"/>
+    </row>
+    <row r="35" spans="1:14">
+      <c r="A35" s="84" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
       <c r="A36" s="13" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" s="85" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
+        <v>276</v>
+      </c>
+      <c r="H36" s="23" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="A37" s="84" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
       <c r="A38" s="13" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="85" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="A39" s="84" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="85" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
+      <c r="A41" s="84" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="85" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
+      <c r="A43" s="84" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="85" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
+      <c r="A45" s="84" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
       <c r="A46" s="13" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" s="85" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
+      <c r="A47" s="84" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
       <c r="A48" s="13" t="s">
-        <v>263</v>
+        <v>288</v>
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="85" t="s">
-        <v>264</v>
+      <c r="A49" s="84" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="13" t="s">
-        <v>265</v>
+        <v>290</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="13" t="s">
-        <v>266</v>
+        <v>291</v>
       </c>
     </row>
   </sheetData>
@@ -4715,161 +4351,161 @@
   <sheetData>
     <row r="1" spans="1:19" ht="17.25" customHeight="1" thickBot="1">
       <c r="A1" s="1" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
     </row>
     <row r="2" spans="1:19">
       <c r="A2" s="12"/>
       <c r="B2" s="4"/>
-      <c r="E2" s="68" t="s">
+      <c r="E2" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-      <c r="M2" s="29"/>
-      <c r="N2" s="29"/>
-      <c r="O2" s="29"/>
-      <c r="P2" s="29"/>
-      <c r="Q2" s="29"/>
-      <c r="R2" s="29"/>
-      <c r="S2" s="30"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
+      <c r="P2" s="28"/>
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="29"/>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="12"/>
       <c r="B3" s="4"/>
-      <c r="E3" s="69" t="s">
-        <v>158</v>
-      </c>
-      <c r="S3" s="33"/>
+      <c r="E3" s="68" t="s">
+        <v>183</v>
+      </c>
+      <c r="S3" s="31"/>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
-      <c r="E4" s="70"/>
-      <c r="S4" s="33"/>
+      <c r="E4" s="69"/>
+      <c r="S4" s="31"/>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
-      <c r="E5" s="69" t="s">
-        <v>159</v>
-      </c>
-      <c r="S5" s="33"/>
+      <c r="E5" s="68" t="s">
+        <v>184</v>
+      </c>
+      <c r="S5" s="31"/>
     </row>
     <row r="6" spans="1:19">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
-      <c r="E6" s="70"/>
-      <c r="S6" s="33"/>
+      <c r="E6" s="69"/>
+      <c r="S6" s="31"/>
     </row>
     <row r="7" spans="1:19">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
-      <c r="E7" s="69" t="s">
-        <v>160</v>
-      </c>
-      <c r="S7" s="33"/>
+      <c r="E7" s="68" t="s">
+        <v>185</v>
+      </c>
+      <c r="S7" s="31"/>
     </row>
     <row r="8" spans="1:19">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
-      <c r="E8" s="69" t="s">
-        <v>161</v>
-      </c>
-      <c r="S8" s="33"/>
+      <c r="E8" s="68" t="s">
+        <v>186</v>
+      </c>
+      <c r="S8" s="31"/>
     </row>
     <row r="9" spans="1:19">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
-      <c r="E9" s="70" t="s">
-        <v>162</v>
-      </c>
-      <c r="S9" s="33"/>
+      <c r="E9" s="69" t="s">
+        <v>187</v>
+      </c>
+      <c r="S9" s="31"/>
     </row>
     <row r="10" spans="1:19">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
-      <c r="E10" s="70"/>
-      <c r="S10" s="33"/>
+      <c r="E10" s="69"/>
+      <c r="S10" s="31"/>
     </row>
     <row r="11" spans="1:19">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
-      <c r="E11" s="69" t="s">
-        <v>163</v>
-      </c>
-      <c r="S11" s="33"/>
+      <c r="E11" s="68" t="s">
+        <v>188</v>
+      </c>
+      <c r="S11" s="31"/>
     </row>
     <row r="12" spans="1:19">
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
-      <c r="E12" s="69" t="s">
-        <v>164</v>
-      </c>
-      <c r="S12" s="33"/>
+      <c r="E12" s="68" t="s">
+        <v>189</v>
+      </c>
+      <c r="S12" s="31"/>
     </row>
     <row r="13" spans="1:19">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
-      <c r="E13" s="69" t="s">
-        <v>165</v>
-      </c>
-      <c r="S13" s="33"/>
+      <c r="E13" s="68" t="s">
+        <v>190</v>
+      </c>
+      <c r="S13" s="31"/>
     </row>
     <row r="14" spans="1:19">
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
-      <c r="E14" s="70" t="s">
-        <v>166</v>
-      </c>
-      <c r="S14" s="33"/>
+      <c r="E14" s="69" t="s">
+        <v>191</v>
+      </c>
+      <c r="S14" s="31"/>
     </row>
     <row r="15" spans="1:19">
-      <c r="E15" s="70"/>
-      <c r="S15" s="33"/>
+      <c r="E15" s="69"/>
+      <c r="S15" s="31"/>
     </row>
     <row r="16" spans="1:19">
-      <c r="E16" s="70"/>
-      <c r="S16" s="33"/>
+      <c r="E16" s="69"/>
+      <c r="S16" s="31"/>
     </row>
     <row r="17" spans="5:19">
-      <c r="E17" s="69" t="s">
-        <v>167</v>
-      </c>
-      <c r="S17" s="33"/>
+      <c r="E17" s="68" t="s">
+        <v>192</v>
+      </c>
+      <c r="S17" s="31"/>
     </row>
     <row r="18" spans="5:19">
-      <c r="E18" s="69" t="s">
-        <v>168</v>
-      </c>
-      <c r="S18" s="33"/>
+      <c r="E18" s="68" t="s">
+        <v>193</v>
+      </c>
+      <c r="S18" s="31"/>
     </row>
     <row r="19" spans="5:19" ht="17.25" customHeight="1" thickBot="1">
-      <c r="E19" s="71" t="s">
-        <v>169</v>
-      </c>
-      <c r="F19" s="37"/>
-      <c r="G19" s="37"/>
-      <c r="H19" s="37"/>
-      <c r="I19" s="37"/>
-      <c r="J19" s="37"/>
-      <c r="K19" s="37"/>
-      <c r="L19" s="37"/>
-      <c r="M19" s="37"/>
-      <c r="N19" s="37"/>
-      <c r="O19" s="37"/>
-      <c r="P19" s="37"/>
-      <c r="Q19" s="37"/>
-      <c r="R19" s="37"/>
-      <c r="S19" s="38"/>
+      <c r="E19" s="70" t="s">
+        <v>194</v>
+      </c>
+      <c r="F19" s="35"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="35"/>
+      <c r="J19" s="35"/>
+      <c r="K19" s="35"/>
+      <c r="L19" s="35"/>
+      <c r="M19" s="35"/>
+      <c r="N19" s="35"/>
+      <c r="O19" s="35"/>
+      <c r="P19" s="35"/>
+      <c r="Q19" s="35"/>
+      <c r="R19" s="35"/>
+      <c r="S19" s="36"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -4890,17 +4526,17 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>170</v>
+        <v>195</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>172</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="85" t="str">
+      <c r="A2" s="84" t="str">
         <f>IF(Nurses!A2="","",Nurses!A2)</f>
         <v>간호사1</v>
       </c>
@@ -4911,18 +4547,18 @@
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="85" t="str">
+      <c r="A3" s="84" t="str">
         <f>IF(Nurses!A3="","",Nurses!A3)</f>
         <v>간호사2</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
       <c r="F3" s="11" t="s">
-        <v>173</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="85" t="str">
+      <c r="A4" s="84" t="str">
         <f>IF(Nurses!A4="","",Nurses!A4)</f>
         <v>간호사3</v>
       </c>
@@ -4930,7 +4566,7 @@
       <c r="C4" s="4"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="85" t="str">
+      <c r="A5" s="84" t="str">
         <f>IF(Nurses!A5="","",Nurses!A5)</f>
         <v>간호사4</v>
       </c>
@@ -4938,7 +4574,7 @@
       <c r="C5" s="4"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="85" t="str">
+      <c r="A6" s="84" t="str">
         <f>IF(Nurses!A6="","",Nurses!A6)</f>
         <v>간호사5</v>
       </c>
@@ -4946,7 +4582,7 @@
       <c r="C6" s="4"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="85" t="str">
+      <c r="A7" s="84" t="str">
         <f>IF(Nurses!A7="","",Nurses!A7)</f>
         <v>간호사6</v>
       </c>
@@ -4954,7 +4590,7 @@
       <c r="C7" s="4"/>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="85" t="str">
+      <c r="A8" s="84" t="str">
         <f>IF(Nurses!A8="","",Nurses!A8)</f>
         <v>간호사7</v>
       </c>
@@ -4962,7 +4598,7 @@
       <c r="C8" s="4"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="85" t="str">
+      <c r="A9" s="84" t="str">
         <f>IF(Nurses!A9="","",Nurses!A9)</f>
         <v>간호사8</v>
       </c>
@@ -4970,7 +4606,7 @@
       <c r="C9" s="4"/>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="85" t="str">
+      <c r="A10" s="84" t="str">
         <f>IF(Nurses!A10="","",Nurses!A10)</f>
         <v>간호사9</v>
       </c>
@@ -4978,7 +4614,7 @@
       <c r="C10" s="4"/>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="85" t="str">
+      <c r="A11" s="84" t="str">
         <f>IF(Nurses!A11="","",Nurses!A11)</f>
         <v>간호사10</v>
       </c>
@@ -4986,7 +4622,7 @@
       <c r="C11" s="4"/>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="85" t="str">
+      <c r="A12" s="84" t="str">
         <f>IF(Nurses!A12="","",Nurses!A12)</f>
         <v>간호사11</v>
       </c>
@@ -4994,7 +4630,7 @@
       <c r="C12" s="4"/>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="85" t="str">
+      <c r="A13" s="84" t="str">
         <f>IF(Nurses!A13="","",Nurses!A13)</f>
         <v>간호사12</v>
       </c>
@@ -5002,7 +4638,7 @@
       <c r="C13" s="4"/>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="85" t="str">
+      <c r="A14" s="84" t="str">
         <f>IF(Nurses!A14="","",Nurses!A14)</f>
         <v>간호사13</v>
       </c>
@@ -5010,7 +4646,7 @@
       <c r="C14" s="4"/>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="85" t="str">
+      <c r="A15" s="84" t="str">
         <f>IF(Nurses!A15="","",Nurses!A15)</f>
         <v>간호사14</v>
       </c>
@@ -5018,7 +4654,7 @@
       <c r="C15" s="4"/>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="85" t="str">
+      <c r="A16" s="84" t="str">
         <f>IF(Nurses!A16="","",Nurses!A16)</f>
         <v>간호사15</v>
       </c>
@@ -5026,7 +4662,7 @@
       <c r="C16" s="4"/>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="85" t="str">
+      <c r="A17" s="84" t="str">
         <f>IF(Nurses!A17="","",Nurses!A17)</f>
         <v>간호사16</v>
       </c>
@@ -5034,7 +4670,7 @@
       <c r="C17" s="4"/>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="85" t="str">
+      <c r="A18" s="84" t="str">
         <f>IF(Nurses!A18="","",Nurses!A18)</f>
         <v>간호사17</v>
       </c>
@@ -5042,7 +4678,7 @@
       <c r="C18" s="4"/>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="85" t="str">
+      <c r="A19" s="84" t="str">
         <f>IF(Nurses!A19="","",Nurses!A19)</f>
         <v>간호사18</v>
       </c>
@@ -5050,7 +4686,7 @@
       <c r="C19" s="4"/>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="85" t="str">
+      <c r="A20" s="84" t="str">
         <f>IF(Nurses!A20="","",Nurses!A20)</f>
         <v>간호사19</v>
       </c>
@@ -5058,7 +4694,7 @@
       <c r="C20" s="4"/>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="85" t="str">
+      <c r="A21" s="84" t="str">
         <f>IF(Nurses!A21="","",Nurses!A21)</f>
         <v>간호사20</v>
       </c>
@@ -5066,7 +4702,7 @@
       <c r="C21" s="4"/>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="85" t="str">
+      <c r="A22" s="84" t="str">
         <f>IF(Nurses!A22="","",Nurses!A22)</f>
         <v>간호사21</v>
       </c>
@@ -5074,7 +4710,7 @@
       <c r="C22" s="4"/>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="85" t="str">
+      <c r="A23" s="84" t="str">
         <f>IF(Nurses!A23="","",Nurses!A23)</f>
         <v>간호사22</v>
       </c>
@@ -5082,7 +4718,7 @@
       <c r="C23" s="4"/>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="85" t="str">
+      <c r="A24" s="84" t="str">
         <f>IF(Nurses!A24="","",Nurses!A24)</f>
         <v>간호사23</v>
       </c>
@@ -5090,7 +4726,7 @@
       <c r="C24" s="4"/>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="85" t="str">
+      <c r="A25" s="84" t="str">
         <f>IF(Nurses!A25="","",Nurses!A25)</f>
         <v>간호사24</v>
       </c>
@@ -5098,7 +4734,7 @@
       <c r="C25" s="4"/>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="85" t="str">
+      <c r="A26" s="84" t="str">
         <f>IF(Nurses!A26="","",Nurses!A26)</f>
         <v>간호사25</v>
       </c>
@@ -5106,7 +4742,7 @@
       <c r="C26" s="4"/>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="85" t="str">
+      <c r="A27" s="84" t="str">
         <f>IF(Nurses!A27="","",Nurses!A27)</f>
         <v>간호사26</v>
       </c>
@@ -5114,7 +4750,7 @@
       <c r="C27" s="4"/>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="85" t="str">
+      <c r="A28" s="84" t="str">
         <f>IF(Nurses!A28="","",Nurses!A28)</f>
         <v>간호사27</v>
       </c>
@@ -5122,7 +4758,7 @@
       <c r="C28" s="4"/>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="85" t="str">
+      <c r="A29" s="84" t="str">
         <f>IF(Nurses!A29="","",Nurses!A29)</f>
         <v>간호사28</v>
       </c>
@@ -5130,7 +4766,7 @@
       <c r="C29" s="4"/>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="85" t="str">
+      <c r="A30" s="84" t="str">
         <f>IF(Nurses!A30="","",Nurses!A30)</f>
         <v>간호사29</v>
       </c>
@@ -5138,7 +4774,7 @@
       <c r="C30" s="4"/>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="85" t="str">
+      <c r="A31" s="84" t="str">
         <f>IF(Nurses!A31="","",Nurses!A31)</f>
         <v>간호사30</v>
       </c>
@@ -5146,7 +4782,7 @@
       <c r="C31" s="4"/>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="85" t="str">
+      <c r="A32" s="84" t="str">
         <f>IF(Nurses!A32="","",Nurses!A32)</f>
         <v>간호사31</v>
       </c>
@@ -5154,7 +4790,7 @@
       <c r="C32" s="4"/>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="85" t="str">
+      <c r="A33" s="84" t="str">
         <f>IF(Nurses!A33="","",Nurses!A33)</f>
         <v>간호사32</v>
       </c>
@@ -5162,7 +4798,7 @@
       <c r="C33" s="4"/>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="85" t="str">
+      <c r="A34" s="84" t="str">
         <f>IF(Nurses!A34="","",Nurses!A34)</f>
         <v>간호사33</v>
       </c>
@@ -5170,7 +4806,7 @@
       <c r="C34" s="4"/>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="85" t="str">
+      <c r="A35" s="84" t="str">
         <f>IF(Nurses!A35="","",Nurses!A35)</f>
         <v>간호사34</v>
       </c>
@@ -5178,7 +4814,7 @@
       <c r="C35" s="4"/>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="85" t="str">
+      <c r="A36" s="84" t="str">
         <f>IF(Nurses!A36="","",Nurses!A36)</f>
         <v>간호사35</v>
       </c>
@@ -5186,7 +4822,7 @@
       <c r="C36" s="4"/>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="85" t="str">
+      <c r="A37" s="84" t="str">
         <f>IF(Nurses!A37="","",Nurses!A37)</f>
         <v>간호사36</v>
       </c>
@@ -5194,7 +4830,7 @@
       <c r="C37" s="4"/>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38" s="85" t="str">
+      <c r="A38" s="84" t="str">
         <f>IF(Nurses!A38="","",Nurses!A38)</f>
         <v>간호사37</v>
       </c>
@@ -5202,7 +4838,7 @@
       <c r="C38" s="4"/>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="85" t="str">
+      <c r="A39" s="84" t="str">
         <f>IF(Nurses!A39="","",Nurses!A39)</f>
         <v>간호사38</v>
       </c>
@@ -5210,7 +4846,7 @@
       <c r="C39" s="4"/>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="85" t="str">
+      <c r="A40" s="84" t="str">
         <f>IF(Nurses!A40="","",Nurses!A40)</f>
         <v>간호사39</v>
       </c>
@@ -5218,7 +4854,7 @@
       <c r="C40" s="4"/>
     </row>
     <row r="41" spans="1:3">
-      <c r="A41" s="85" t="str">
+      <c r="A41" s="84" t="str">
         <f>IF(Nurses!A41="","",Nurses!A41)</f>
         <v>간호사40</v>
       </c>
@@ -5226,7 +4862,7 @@
       <c r="C41" s="4"/>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="85" t="str">
+      <c r="A42" s="84" t="str">
         <f>IF(Nurses!A42="","",Nurses!A42)</f>
         <v>간호사41</v>
       </c>
@@ -5234,7 +4870,7 @@
       <c r="C42" s="4"/>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="85" t="str">
+      <c r="A43" s="84" t="str">
         <f>IF(Nurses!A43="","",Nurses!A43)</f>
         <v>간호사42</v>
       </c>
@@ -5242,7 +4878,7 @@
       <c r="C43" s="4"/>
     </row>
     <row r="44" spans="1:3">
-      <c r="A44" s="85" t="str">
+      <c r="A44" s="84" t="str">
         <f>IF(Nurses!A44="","",Nurses!A44)</f>
         <v>간호사43</v>
       </c>
@@ -5250,7 +4886,7 @@
       <c r="C44" s="4"/>
     </row>
     <row r="45" spans="1:3">
-      <c r="A45" s="85" t="str">
+      <c r="A45" s="84" t="str">
         <f>IF(Nurses!A45="","",Nurses!A45)</f>
         <v>간호사44</v>
       </c>
@@ -5258,7 +4894,7 @@
       <c r="C45" s="4"/>
     </row>
     <row r="46" spans="1:3">
-      <c r="A46" s="85" t="str">
+      <c r="A46" s="84" t="str">
         <f>IF(Nurses!A46="","",Nurses!A46)</f>
         <v>간호사45</v>
       </c>
@@ -5266,7 +4902,7 @@
       <c r="C46" s="4"/>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47" s="85" t="str">
+      <c r="A47" s="84" t="str">
         <f>IF(Nurses!A47="","",Nurses!A47)</f>
         <v>간호사46</v>
       </c>
@@ -5274,7 +4910,7 @@
       <c r="C47" s="4"/>
     </row>
     <row r="48" spans="1:3">
-      <c r="A48" s="85" t="str">
+      <c r="A48" s="84" t="str">
         <f>IF(Nurses!A48="","",Nurses!A48)</f>
         <v>간호사47</v>
       </c>
@@ -5282,7 +4918,7 @@
       <c r="C48" s="4"/>
     </row>
     <row r="49" spans="1:3">
-      <c r="A49" s="85" t="str">
+      <c r="A49" s="84" t="str">
         <f>IF(Nurses!A49="","",Nurses!A49)</f>
         <v>간호사48</v>
       </c>
@@ -5290,7 +4926,7 @@
       <c r="C49" s="4"/>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="85" t="str">
+      <c r="A50" s="84" t="str">
         <f>IF(Nurses!A50="","",Nurses!A50)</f>
         <v>간호사49</v>
       </c>
@@ -5298,7 +4934,7 @@
       <c r="C50" s="4"/>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" s="85" t="str">
+      <c r="A51" s="84" t="str">
         <f>IF(Nurses!A51="","",Nurses!A51)</f>
         <v>간호사50</v>
       </c>
@@ -5322,7 +4958,7 @@
   <sheetData>
     <row r="1" spans="1:45" ht="17.25" customHeight="1">
       <c r="A1" s="5" t="s">
-        <v>170</v>
+        <v>195</v>
       </c>
       <c r="B1" s="5">
         <v>1</v>
@@ -5418,12 +5054,12 @@
         <v>31</v>
       </c>
       <c r="AG1" s="6"/>
-      <c r="AH1" s="77" t="s">
+      <c r="AH1" s="75" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:45" ht="17.25" customHeight="1">
-      <c r="A2" s="85" t="str">
+      <c r="A2" s="84" t="str">
         <f>IF(Nurses!A2="","",Nurses!A2)</f>
         <v>간호사1</v>
       </c>
@@ -5459,23 +5095,23 @@
       <c r="AE2" s="7"/>
       <c r="AF2" s="7"/>
       <c r="AG2" s="6"/>
-      <c r="AH2" s="78" t="s">
-        <v>174</v>
-      </c>
-      <c r="AI2" s="76"/>
-      <c r="AJ2" s="76"/>
-      <c r="AK2" s="76"/>
-      <c r="AL2" s="76"/>
-      <c r="AM2" s="76"/>
-      <c r="AN2" s="76"/>
-      <c r="AO2" s="76"/>
-      <c r="AP2" s="76"/>
-      <c r="AQ2" s="76"/>
-      <c r="AR2" s="76"/>
-      <c r="AS2" s="76"/>
+      <c r="AH2" s="76" t="s">
+        <v>199</v>
+      </c>
+      <c r="AI2" s="74"/>
+      <c r="AJ2" s="74"/>
+      <c r="AK2" s="74"/>
+      <c r="AL2" s="74"/>
+      <c r="AM2" s="74"/>
+      <c r="AN2" s="74"/>
+      <c r="AO2" s="74"/>
+      <c r="AP2" s="74"/>
+      <c r="AQ2" s="74"/>
+      <c r="AR2" s="74"/>
+      <c r="AS2" s="74"/>
     </row>
     <row r="3" spans="1:45" ht="17.25" customHeight="1">
-      <c r="A3" s="85" t="str">
+      <c r="A3" s="84" t="str">
         <f>IF(Nurses!A3="","",Nurses!A3)</f>
         <v>간호사2</v>
       </c>
@@ -5511,23 +5147,23 @@
       <c r="AE3" s="7"/>
       <c r="AF3" s="7"/>
       <c r="AG3" s="6"/>
-      <c r="AH3" s="79" t="s">
-        <v>175</v>
-      </c>
-      <c r="AI3" s="76"/>
-      <c r="AJ3" s="76"/>
-      <c r="AK3" s="76"/>
-      <c r="AL3" s="76"/>
-      <c r="AM3" s="76"/>
-      <c r="AN3" s="76"/>
-      <c r="AO3" s="76"/>
-      <c r="AP3" s="76"/>
-      <c r="AQ3" s="76"/>
-      <c r="AR3" s="76"/>
-      <c r="AS3" s="76"/>
+      <c r="AH3" s="77" t="s">
+        <v>200</v>
+      </c>
+      <c r="AI3" s="74"/>
+      <c r="AJ3" s="74"/>
+      <c r="AK3" s="74"/>
+      <c r="AL3" s="74"/>
+      <c r="AM3" s="74"/>
+      <c r="AN3" s="74"/>
+      <c r="AO3" s="74"/>
+      <c r="AP3" s="74"/>
+      <c r="AQ3" s="74"/>
+      <c r="AR3" s="74"/>
+      <c r="AS3" s="74"/>
     </row>
     <row r="4" spans="1:45" ht="17.25" customHeight="1">
-      <c r="A4" s="85" t="str">
+      <c r="A4" s="84" t="str">
         <f>IF(Nurses!A4="","",Nurses!A4)</f>
         <v>간호사3</v>
       </c>
@@ -5563,23 +5199,23 @@
       <c r="AE4" s="7"/>
       <c r="AF4" s="7"/>
       <c r="AG4" s="6"/>
-      <c r="AH4" s="79" t="s">
-        <v>176</v>
-      </c>
-      <c r="AI4" s="76"/>
-      <c r="AJ4" s="76"/>
-      <c r="AK4" s="76"/>
-      <c r="AL4" s="76"/>
-      <c r="AM4" s="76"/>
-      <c r="AN4" s="76"/>
-      <c r="AO4" s="76"/>
-      <c r="AP4" s="76"/>
-      <c r="AQ4" s="76"/>
-      <c r="AR4" s="76"/>
-      <c r="AS4" s="76"/>
+      <c r="AH4" s="77" t="s">
+        <v>201</v>
+      </c>
+      <c r="AI4" s="74"/>
+      <c r="AJ4" s="74"/>
+      <c r="AK4" s="74"/>
+      <c r="AL4" s="74"/>
+      <c r="AM4" s="74"/>
+      <c r="AN4" s="74"/>
+      <c r="AO4" s="74"/>
+      <c r="AP4" s="74"/>
+      <c r="AQ4" s="74"/>
+      <c r="AR4" s="74"/>
+      <c r="AS4" s="74"/>
     </row>
     <row r="5" spans="1:45" ht="17.25" customHeight="1">
-      <c r="A5" s="85" t="str">
+      <c r="A5" s="84" t="str">
         <f>IF(Nurses!A5="","",Nurses!A5)</f>
         <v>간호사4</v>
       </c>
@@ -5615,21 +5251,21 @@
       <c r="AE5" s="7"/>
       <c r="AF5" s="7"/>
       <c r="AG5" s="6"/>
-      <c r="AH5" s="79"/>
-      <c r="AI5" s="76"/>
-      <c r="AJ5" s="76"/>
-      <c r="AK5" s="76"/>
-      <c r="AL5" s="76"/>
-      <c r="AM5" s="76"/>
-      <c r="AN5" s="76"/>
-      <c r="AO5" s="76"/>
-      <c r="AP5" s="76"/>
-      <c r="AQ5" s="76"/>
-      <c r="AR5" s="76"/>
-      <c r="AS5" s="76"/>
+      <c r="AH5" s="77"/>
+      <c r="AI5" s="74"/>
+      <c r="AJ5" s="74"/>
+      <c r="AK5" s="74"/>
+      <c r="AL5" s="74"/>
+      <c r="AM5" s="74"/>
+      <c r="AN5" s="74"/>
+      <c r="AO5" s="74"/>
+      <c r="AP5" s="74"/>
+      <c r="AQ5" s="74"/>
+      <c r="AR5" s="74"/>
+      <c r="AS5" s="74"/>
     </row>
     <row r="6" spans="1:45" ht="17.25" customHeight="1">
-      <c r="A6" s="85" t="str">
+      <c r="A6" s="84" t="str">
         <f>IF(Nurses!A6="","",Nurses!A6)</f>
         <v>간호사5</v>
       </c>
@@ -5665,23 +5301,23 @@
       <c r="AE6" s="7"/>
       <c r="AF6" s="7"/>
       <c r="AG6" s="6"/>
-      <c r="AH6" s="78" t="s">
-        <v>177</v>
-      </c>
-      <c r="AI6" s="76"/>
-      <c r="AJ6" s="76"/>
-      <c r="AK6" s="76"/>
-      <c r="AL6" s="76"/>
-      <c r="AM6" s="76"/>
-      <c r="AN6" s="76"/>
-      <c r="AO6" s="76"/>
-      <c r="AP6" s="76"/>
-      <c r="AQ6" s="76"/>
-      <c r="AR6" s="76"/>
-      <c r="AS6" s="76"/>
+      <c r="AH6" s="76" t="s">
+        <v>202</v>
+      </c>
+      <c r="AI6" s="74"/>
+      <c r="AJ6" s="74"/>
+      <c r="AK6" s="74"/>
+      <c r="AL6" s="74"/>
+      <c r="AM6" s="74"/>
+      <c r="AN6" s="74"/>
+      <c r="AO6" s="74"/>
+      <c r="AP6" s="74"/>
+      <c r="AQ6" s="74"/>
+      <c r="AR6" s="74"/>
+      <c r="AS6" s="74"/>
     </row>
     <row r="7" spans="1:45" ht="17.25" customHeight="1">
-      <c r="A7" s="85" t="str">
+      <c r="A7" s="84" t="str">
         <f>IF(Nurses!A7="","",Nurses!A7)</f>
         <v>간호사6</v>
       </c>
@@ -5717,23 +5353,23 @@
       <c r="AE7" s="7"/>
       <c r="AF7" s="7"/>
       <c r="AG7" s="6"/>
-      <c r="AH7" s="79" t="s">
-        <v>178</v>
-      </c>
-      <c r="AI7" s="76"/>
-      <c r="AJ7" s="76"/>
-      <c r="AK7" s="76"/>
-      <c r="AL7" s="76"/>
-      <c r="AM7" s="76"/>
-      <c r="AN7" s="76"/>
-      <c r="AO7" s="76"/>
-      <c r="AP7" s="76"/>
-      <c r="AQ7" s="76"/>
-      <c r="AR7" s="76"/>
-      <c r="AS7" s="76"/>
+      <c r="AH7" s="77" t="s">
+        <v>203</v>
+      </c>
+      <c r="AI7" s="74"/>
+      <c r="AJ7" s="74"/>
+      <c r="AK7" s="74"/>
+      <c r="AL7" s="74"/>
+      <c r="AM7" s="74"/>
+      <c r="AN7" s="74"/>
+      <c r="AO7" s="74"/>
+      <c r="AP7" s="74"/>
+      <c r="AQ7" s="74"/>
+      <c r="AR7" s="74"/>
+      <c r="AS7" s="74"/>
     </row>
     <row r="8" spans="1:45" ht="17.25" customHeight="1">
-      <c r="A8" s="85" t="str">
+      <c r="A8" s="84" t="str">
         <f>IF(Nurses!A8="","",Nurses!A8)</f>
         <v>간호사7</v>
       </c>
@@ -5769,21 +5405,21 @@
       <c r="AE8" s="7"/>
       <c r="AF8" s="7"/>
       <c r="AG8" s="6"/>
-      <c r="AH8" s="80"/>
-      <c r="AI8" s="76"/>
-      <c r="AJ8" s="76"/>
-      <c r="AK8" s="76"/>
-      <c r="AL8" s="76"/>
-      <c r="AM8" s="76"/>
-      <c r="AN8" s="76"/>
-      <c r="AO8" s="76"/>
-      <c r="AP8" s="76"/>
-      <c r="AQ8" s="76"/>
-      <c r="AR8" s="76"/>
-      <c r="AS8" s="76"/>
+      <c r="AH8" s="78"/>
+      <c r="AI8" s="74"/>
+      <c r="AJ8" s="74"/>
+      <c r="AK8" s="74"/>
+      <c r="AL8" s="74"/>
+      <c r="AM8" s="74"/>
+      <c r="AN8" s="74"/>
+      <c r="AO8" s="74"/>
+      <c r="AP8" s="74"/>
+      <c r="AQ8" s="74"/>
+      <c r="AR8" s="74"/>
+      <c r="AS8" s="74"/>
     </row>
     <row r="9" spans="1:45" ht="17.25" customHeight="1">
-      <c r="A9" s="85" t="str">
+      <c r="A9" s="84" t="str">
         <f>IF(Nurses!A9="","",Nurses!A9)</f>
         <v>간호사8</v>
       </c>
@@ -5819,23 +5455,23 @@
       <c r="AE9" s="7"/>
       <c r="AF9" s="7"/>
       <c r="AG9" s="6"/>
-      <c r="AH9" s="78" t="s">
-        <v>179</v>
-      </c>
-      <c r="AI9" s="76"/>
-      <c r="AJ9" s="76"/>
-      <c r="AK9" s="76"/>
-      <c r="AL9" s="76"/>
-      <c r="AM9" s="76"/>
-      <c r="AN9" s="76"/>
-      <c r="AO9" s="76"/>
-      <c r="AP9" s="76"/>
-      <c r="AQ9" s="76"/>
-      <c r="AR9" s="76"/>
-      <c r="AS9" s="76"/>
+      <c r="AH9" s="76" t="s">
+        <v>204</v>
+      </c>
+      <c r="AI9" s="74"/>
+      <c r="AJ9" s="74"/>
+      <c r="AK9" s="74"/>
+      <c r="AL9" s="74"/>
+      <c r="AM9" s="74"/>
+      <c r="AN9" s="74"/>
+      <c r="AO9" s="74"/>
+      <c r="AP9" s="74"/>
+      <c r="AQ9" s="74"/>
+      <c r="AR9" s="74"/>
+      <c r="AS9" s="74"/>
     </row>
     <row r="10" spans="1:45" ht="17.25" customHeight="1">
-      <c r="A10" s="85" t="str">
+      <c r="A10" s="84" t="str">
         <f>IF(Nurses!A10="","",Nurses!A10)</f>
         <v>간호사9</v>
       </c>
@@ -5871,23 +5507,23 @@
       <c r="AE10" s="7"/>
       <c r="AF10" s="7"/>
       <c r="AG10" s="6"/>
-      <c r="AH10" s="79" t="s">
-        <v>180</v>
-      </c>
-      <c r="AI10" s="76"/>
-      <c r="AJ10" s="76"/>
-      <c r="AK10" s="76"/>
-      <c r="AL10" s="76"/>
-      <c r="AM10" s="76"/>
-      <c r="AN10" s="76"/>
-      <c r="AO10" s="76"/>
-      <c r="AP10" s="76"/>
-      <c r="AQ10" s="76"/>
-      <c r="AR10" s="76"/>
-      <c r="AS10" s="76"/>
+      <c r="AH10" s="77" t="s">
+        <v>205</v>
+      </c>
+      <c r="AI10" s="74"/>
+      <c r="AJ10" s="74"/>
+      <c r="AK10" s="74"/>
+      <c r="AL10" s="74"/>
+      <c r="AM10" s="74"/>
+      <c r="AN10" s="74"/>
+      <c r="AO10" s="74"/>
+      <c r="AP10" s="74"/>
+      <c r="AQ10" s="74"/>
+      <c r="AR10" s="74"/>
+      <c r="AS10" s="74"/>
     </row>
     <row r="11" spans="1:45" ht="17.25" customHeight="1">
-      <c r="A11" s="85" t="str">
+      <c r="A11" s="84" t="str">
         <f>IF(Nurses!A11="","",Nurses!A11)</f>
         <v>간호사10</v>
       </c>
@@ -5923,21 +5559,21 @@
       <c r="AE11" s="7"/>
       <c r="AF11" s="7"/>
       <c r="AG11" s="6"/>
-      <c r="AH11" s="80"/>
-      <c r="AI11" s="76"/>
-      <c r="AJ11" s="76"/>
-      <c r="AK11" s="76"/>
-      <c r="AL11" s="76"/>
-      <c r="AM11" s="76"/>
-      <c r="AN11" s="76"/>
-      <c r="AO11" s="76"/>
-      <c r="AP11" s="76"/>
-      <c r="AQ11" s="76"/>
-      <c r="AR11" s="76"/>
-      <c r="AS11" s="76"/>
+      <c r="AH11" s="78"/>
+      <c r="AI11" s="74"/>
+      <c r="AJ11" s="74"/>
+      <c r="AK11" s="74"/>
+      <c r="AL11" s="74"/>
+      <c r="AM11" s="74"/>
+      <c r="AN11" s="74"/>
+      <c r="AO11" s="74"/>
+      <c r="AP11" s="74"/>
+      <c r="AQ11" s="74"/>
+      <c r="AR11" s="74"/>
+      <c r="AS11" s="74"/>
     </row>
     <row r="12" spans="1:45" ht="17.25" customHeight="1">
-      <c r="A12" s="85" t="str">
+      <c r="A12" s="84" t="str">
         <f>IF(Nurses!A12="","",Nurses!A12)</f>
         <v>간호사11</v>
       </c>
@@ -5973,23 +5609,23 @@
       <c r="AE12" s="7"/>
       <c r="AF12" s="7"/>
       <c r="AG12" s="6"/>
-      <c r="AH12" s="79" t="s">
-        <v>181</v>
-      </c>
-      <c r="AI12" s="76"/>
-      <c r="AJ12" s="76"/>
-      <c r="AK12" s="76"/>
-      <c r="AL12" s="76"/>
-      <c r="AM12" s="76"/>
-      <c r="AN12" s="76"/>
-      <c r="AO12" s="76"/>
-      <c r="AP12" s="76"/>
-      <c r="AQ12" s="76"/>
-      <c r="AR12" s="76"/>
-      <c r="AS12" s="76"/>
+      <c r="AH12" s="77" t="s">
+        <v>206</v>
+      </c>
+      <c r="AI12" s="74"/>
+      <c r="AJ12" s="74"/>
+      <c r="AK12" s="74"/>
+      <c r="AL12" s="74"/>
+      <c r="AM12" s="74"/>
+      <c r="AN12" s="74"/>
+      <c r="AO12" s="74"/>
+      <c r="AP12" s="74"/>
+      <c r="AQ12" s="74"/>
+      <c r="AR12" s="74"/>
+      <c r="AS12" s="74"/>
     </row>
     <row r="13" spans="1:45" ht="17.25" customHeight="1">
-      <c r="A13" s="85" t="str">
+      <c r="A13" s="84" t="str">
         <f>IF(Nurses!A13="","",Nurses!A13)</f>
         <v>간호사12</v>
       </c>
@@ -6025,23 +5661,23 @@
       <c r="AE13" s="7"/>
       <c r="AF13" s="7"/>
       <c r="AG13" s="6"/>
-      <c r="AH13" s="80" t="s">
-        <v>182</v>
-      </c>
-      <c r="AI13" s="76"/>
-      <c r="AJ13" s="76"/>
-      <c r="AK13" s="76"/>
-      <c r="AL13" s="76"/>
-      <c r="AM13" s="76"/>
-      <c r="AN13" s="76"/>
-      <c r="AO13" s="76"/>
-      <c r="AP13" s="76"/>
-      <c r="AQ13" s="76"/>
-      <c r="AR13" s="76"/>
-      <c r="AS13" s="76"/>
+      <c r="AH13" s="78" t="s">
+        <v>207</v>
+      </c>
+      <c r="AI13" s="74"/>
+      <c r="AJ13" s="74"/>
+      <c r="AK13" s="74"/>
+      <c r="AL13" s="74"/>
+      <c r="AM13" s="74"/>
+      <c r="AN13" s="74"/>
+      <c r="AO13" s="74"/>
+      <c r="AP13" s="74"/>
+      <c r="AQ13" s="74"/>
+      <c r="AR13" s="74"/>
+      <c r="AS13" s="74"/>
     </row>
     <row r="14" spans="1:45" ht="17.25" customHeight="1">
-      <c r="A14" s="85" t="str">
+      <c r="A14" s="84" t="str">
         <f>IF(Nurses!A14="","",Nurses!A14)</f>
         <v>간호사13</v>
       </c>
@@ -6076,23 +5712,23 @@
       <c r="AD14" s="7"/>
       <c r="AE14" s="7"/>
       <c r="AF14" s="7"/>
-      <c r="AH14" s="80" t="s">
-        <v>183</v>
-      </c>
-      <c r="AI14" s="76"/>
-      <c r="AJ14" s="76"/>
-      <c r="AK14" s="76"/>
-      <c r="AL14" s="76"/>
-      <c r="AM14" s="76"/>
-      <c r="AN14" s="76"/>
-      <c r="AO14" s="76"/>
-      <c r="AP14" s="76"/>
-      <c r="AQ14" s="76"/>
-      <c r="AR14" s="76"/>
-      <c r="AS14" s="76"/>
+      <c r="AH14" s="78" t="s">
+        <v>208</v>
+      </c>
+      <c r="AI14" s="74"/>
+      <c r="AJ14" s="74"/>
+      <c r="AK14" s="74"/>
+      <c r="AL14" s="74"/>
+      <c r="AM14" s="74"/>
+      <c r="AN14" s="74"/>
+      <c r="AO14" s="74"/>
+      <c r="AP14" s="74"/>
+      <c r="AQ14" s="74"/>
+      <c r="AR14" s="74"/>
+      <c r="AS14" s="74"/>
     </row>
     <row r="15" spans="1:45">
-      <c r="A15" s="85" t="str">
+      <c r="A15" s="84" t="str">
         <f>IF(Nurses!A15="","",Nurses!A15)</f>
         <v>간호사14</v>
       </c>
@@ -6129,7 +5765,7 @@
       <c r="AF15" s="7"/>
     </row>
     <row r="16" spans="1:45">
-      <c r="A16" s="85" t="str">
+      <c r="A16" s="84" t="str">
         <f>IF(Nurses!A16="","",Nurses!A16)</f>
         <v>간호사15</v>
       </c>
@@ -6166,7 +5802,7 @@
       <c r="AF16" s="7"/>
     </row>
     <row r="17" spans="1:34">
-      <c r="A17" s="85" t="str">
+      <c r="A17" s="84" t="str">
         <f>IF(Nurses!A17="","",Nurses!A17)</f>
         <v>간호사16</v>
       </c>
@@ -6203,7 +5839,7 @@
       <c r="AF17" s="7"/>
     </row>
     <row r="18" spans="1:34">
-      <c r="A18" s="85" t="str">
+      <c r="A18" s="84" t="str">
         <f>IF(Nurses!A18="","",Nurses!A18)</f>
         <v>간호사17</v>
       </c>
@@ -6241,7 +5877,7 @@
       <c r="AH18" s="19"/>
     </row>
     <row r="19" spans="1:34">
-      <c r="A19" s="85" t="str">
+      <c r="A19" s="84" t="str">
         <f>IF(Nurses!A19="","",Nurses!A19)</f>
         <v>간호사18</v>
       </c>
@@ -6278,7 +5914,7 @@
       <c r="AF19" s="7"/>
     </row>
     <row r="20" spans="1:34">
-      <c r="A20" s="85" t="str">
+      <c r="A20" s="84" t="str">
         <f>IF(Nurses!A20="","",Nurses!A20)</f>
         <v>간호사19</v>
       </c>
@@ -6316,7 +5952,7 @@
       <c r="AH20" s="16"/>
     </row>
     <row r="21" spans="1:34">
-      <c r="A21" s="85" t="str">
+      <c r="A21" s="84" t="str">
         <f>IF(Nurses!A21="","",Nurses!A21)</f>
         <v>간호사20</v>
       </c>
@@ -6353,7 +5989,7 @@
       <c r="AF21" s="7"/>
     </row>
     <row r="22" spans="1:34">
-      <c r="A22" s="85" t="str">
+      <c r="A22" s="84" t="str">
         <f>IF(Nurses!A22="","",Nurses!A22)</f>
         <v>간호사21</v>
       </c>
@@ -6390,7 +6026,7 @@
       <c r="AF22" s="7"/>
     </row>
     <row r="23" spans="1:34">
-      <c r="A23" s="85" t="str">
+      <c r="A23" s="84" t="str">
         <f>IF(Nurses!A23="","",Nurses!A23)</f>
         <v>간호사22</v>
       </c>
@@ -6427,7 +6063,7 @@
       <c r="AF23" s="7"/>
     </row>
     <row r="24" spans="1:34">
-      <c r="A24" s="85" t="str">
+      <c r="A24" s="84" t="str">
         <f>IF(Nurses!A24="","",Nurses!A24)</f>
         <v>간호사23</v>
       </c>
@@ -6464,7 +6100,7 @@
       <c r="AF24" s="7"/>
     </row>
     <row r="25" spans="1:34">
-      <c r="A25" s="85" t="str">
+      <c r="A25" s="84" t="str">
         <f>IF(Nurses!A25="","",Nurses!A25)</f>
         <v>간호사24</v>
       </c>
@@ -6502,7 +6138,7 @@
       <c r="AH25" s="19"/>
     </row>
     <row r="26" spans="1:34">
-      <c r="A26" s="85" t="str">
+      <c r="A26" s="84" t="str">
         <f>IF(Nurses!A26="","",Nurses!A26)</f>
         <v>간호사25</v>
       </c>
@@ -6540,7 +6176,7 @@
       <c r="AH26" s="19"/>
     </row>
     <row r="27" spans="1:34">
-      <c r="A27" s="85" t="str">
+      <c r="A27" s="84" t="str">
         <f>IF(Nurses!A27="","",Nurses!A27)</f>
         <v>간호사26</v>
       </c>
@@ -6577,7 +6213,7 @@
       <c r="AF27" s="7"/>
     </row>
     <row r="28" spans="1:34">
-      <c r="A28" s="85" t="str">
+      <c r="A28" s="84" t="str">
         <f>IF(Nurses!A28="","",Nurses!A28)</f>
         <v>간호사27</v>
       </c>
@@ -6614,7 +6250,7 @@
       <c r="AF28" s="7"/>
     </row>
     <row r="29" spans="1:34">
-      <c r="A29" s="85" t="str">
+      <c r="A29" s="84" t="str">
         <f>IF(Nurses!A29="","",Nurses!A29)</f>
         <v>간호사28</v>
       </c>
@@ -6651,7 +6287,7 @@
       <c r="AF29" s="7"/>
     </row>
     <row r="30" spans="1:34">
-      <c r="A30" s="85" t="str">
+      <c r="A30" s="84" t="str">
         <f>IF(Nurses!A30="","",Nurses!A30)</f>
         <v>간호사29</v>
       </c>
@@ -6688,7 +6324,7 @@
       <c r="AF30" s="7"/>
     </row>
     <row r="31" spans="1:34">
-      <c r="A31" s="85" t="str">
+      <c r="A31" s="84" t="str">
         <f>IF(Nurses!A31="","",Nurses!A31)</f>
         <v>간호사30</v>
       </c>
@@ -6725,7 +6361,7 @@
       <c r="AF31" s="7"/>
     </row>
     <row r="32" spans="1:34">
-      <c r="A32" s="85" t="str">
+      <c r="A32" s="84" t="str">
         <f>IF(Nurses!A32="","",Nurses!A32)</f>
         <v>간호사31</v>
       </c>
@@ -6762,7 +6398,7 @@
       <c r="AF32" s="7"/>
     </row>
     <row r="33" spans="1:32">
-      <c r="A33" s="85" t="str">
+      <c r="A33" s="84" t="str">
         <f>IF(Nurses!A33="","",Nurses!A33)</f>
         <v>간호사32</v>
       </c>
@@ -6799,7 +6435,7 @@
       <c r="AF33" s="7"/>
     </row>
     <row r="34" spans="1:32">
-      <c r="A34" s="85" t="str">
+      <c r="A34" s="84" t="str">
         <f>IF(Nurses!A34="","",Nurses!A34)</f>
         <v>간호사33</v>
       </c>
@@ -6836,7 +6472,7 @@
       <c r="AF34" s="7"/>
     </row>
     <row r="35" spans="1:32">
-      <c r="A35" s="85" t="str">
+      <c r="A35" s="84" t="str">
         <f>IF(Nurses!A35="","",Nurses!A35)</f>
         <v>간호사34</v>
       </c>
@@ -6873,7 +6509,7 @@
       <c r="AF35" s="7"/>
     </row>
     <row r="36" spans="1:32">
-      <c r="A36" s="85" t="str">
+      <c r="A36" s="84" t="str">
         <f>IF(Nurses!A36="","",Nurses!A36)</f>
         <v>간호사35</v>
       </c>
@@ -6910,7 +6546,7 @@
       <c r="AF36" s="7"/>
     </row>
     <row r="37" spans="1:32">
-      <c r="A37" s="85" t="str">
+      <c r="A37" s="84" t="str">
         <f>IF(Nurses!A37="","",Nurses!A37)</f>
         <v>간호사36</v>
       </c>
@@ -6947,7 +6583,7 @@
       <c r="AF37" s="7"/>
     </row>
     <row r="38" spans="1:32">
-      <c r="A38" s="85" t="str">
+      <c r="A38" s="84" t="str">
         <f>IF(Nurses!A38="","",Nurses!A38)</f>
         <v>간호사37</v>
       </c>
@@ -6984,7 +6620,7 @@
       <c r="AF38" s="7"/>
     </row>
     <row r="39" spans="1:32">
-      <c r="A39" s="85" t="str">
+      <c r="A39" s="84" t="str">
         <f>IF(Nurses!A39="","",Nurses!A39)</f>
         <v>간호사38</v>
       </c>
@@ -7021,7 +6657,7 @@
       <c r="AF39" s="7"/>
     </row>
     <row r="40" spans="1:32">
-      <c r="A40" s="85" t="str">
+      <c r="A40" s="84" t="str">
         <f>IF(Nurses!A40="","",Nurses!A40)</f>
         <v>간호사39</v>
       </c>
@@ -7058,7 +6694,7 @@
       <c r="AF40" s="7"/>
     </row>
     <row r="41" spans="1:32">
-      <c r="A41" s="85" t="str">
+      <c r="A41" s="84" t="str">
         <f>IF(Nurses!A41="","",Nurses!A41)</f>
         <v>간호사40</v>
       </c>
@@ -7095,7 +6731,7 @@
       <c r="AF41" s="7"/>
     </row>
     <row r="42" spans="1:32">
-      <c r="A42" s="85" t="str">
+      <c r="A42" s="84" t="str">
         <f>IF(Nurses!A42="","",Nurses!A42)</f>
         <v>간호사41</v>
       </c>
@@ -7132,7 +6768,7 @@
       <c r="AF42" s="7"/>
     </row>
     <row r="43" spans="1:32">
-      <c r="A43" s="85" t="str">
+      <c r="A43" s="84" t="str">
         <f>IF(Nurses!A43="","",Nurses!A43)</f>
         <v>간호사42</v>
       </c>
@@ -7169,7 +6805,7 @@
       <c r="AF43" s="7"/>
     </row>
     <row r="44" spans="1:32">
-      <c r="A44" s="85" t="str">
+      <c r="A44" s="84" t="str">
         <f>IF(Nurses!A44="","",Nurses!A44)</f>
         <v>간호사43</v>
       </c>
@@ -7206,7 +6842,7 @@
       <c r="AF44" s="7"/>
     </row>
     <row r="45" spans="1:32">
-      <c r="A45" s="85" t="str">
+      <c r="A45" s="84" t="str">
         <f>IF(Nurses!A45="","",Nurses!A45)</f>
         <v>간호사44</v>
       </c>
@@ -7243,7 +6879,7 @@
       <c r="AF45" s="7"/>
     </row>
     <row r="46" spans="1:32">
-      <c r="A46" s="85" t="str">
+      <c r="A46" s="84" t="str">
         <f>IF(Nurses!A46="","",Nurses!A46)</f>
         <v>간호사45</v>
       </c>
@@ -7280,7 +6916,7 @@
       <c r="AF46" s="7"/>
     </row>
     <row r="47" spans="1:32">
-      <c r="A47" s="85" t="str">
+      <c r="A47" s="84" t="str">
         <f>IF(Nurses!A47="","",Nurses!A47)</f>
         <v>간호사46</v>
       </c>
@@ -7317,7 +6953,7 @@
       <c r="AF47" s="7"/>
     </row>
     <row r="48" spans="1:32">
-      <c r="A48" s="85" t="str">
+      <c r="A48" s="84" t="str">
         <f>IF(Nurses!A48="","",Nurses!A48)</f>
         <v>간호사47</v>
       </c>
@@ -7354,7 +6990,7 @@
       <c r="AF48" s="7"/>
     </row>
     <row r="49" spans="1:32">
-      <c r="A49" s="85" t="str">
+      <c r="A49" s="84" t="str">
         <f>IF(Nurses!A49="","",Nurses!A49)</f>
         <v>간호사48</v>
       </c>
@@ -7391,7 +7027,7 @@
       <c r="AF49" s="7"/>
     </row>
     <row r="50" spans="1:32">
-      <c r="A50" s="85" t="str">
+      <c r="A50" s="84" t="str">
         <f>IF(Nurses!A50="","",Nurses!A50)</f>
         <v>간호사49</v>
       </c>
@@ -7428,7 +7064,7 @@
       <c r="AF50" s="7"/>
     </row>
     <row r="51" spans="1:32">
-      <c r="A51" s="85" t="str">
+      <c r="A51" s="84" t="str">
         <f>IF(Nurses!A51="","",Nurses!A51)</f>
         <v>간호사50</v>
       </c>
@@ -7481,7 +7117,7 @@
   <sheetData>
     <row r="1" spans="1:42">
       <c r="A1" s="5" t="s">
-        <v>170</v>
+        <v>195</v>
       </c>
       <c r="B1" s="5">
         <v>1</v>
@@ -7578,7 +7214,7 @@
       </c>
     </row>
     <row r="2" spans="1:42">
-      <c r="A2" s="85" t="str">
+      <c r="A2" s="84" t="str">
         <f>IF(Nurses!A2="","",Nurses!A2)</f>
         <v>간호사1</v>
       </c>
@@ -7615,7 +7251,7 @@
       <c r="AF2" s="7"/>
     </row>
     <row r="3" spans="1:42">
-      <c r="A3" s="85" t="str">
+      <c r="A3" s="84" t="str">
         <f>IF(Nurses!A3="","",Nurses!A3)</f>
         <v>간호사2</v>
       </c>
@@ -7651,12 +7287,12 @@
       <c r="AE3" s="7"/>
       <c r="AF3" s="7"/>
       <c r="AG3" s="6"/>
-      <c r="AH3" s="42" t="s">
+      <c r="AH3" s="40" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:42">
-      <c r="A4" s="85" t="str">
+      <c r="A4" s="84" t="str">
         <f>IF(Nurses!A4="","",Nurses!A4)</f>
         <v>간호사3</v>
       </c>
@@ -7692,20 +7328,20 @@
       <c r="AE4" s="7"/>
       <c r="AF4" s="7"/>
       <c r="AG4" s="6"/>
-      <c r="AH4" s="66" t="s">
-        <v>184</v>
-      </c>
-      <c r="AI4" s="82"/>
-      <c r="AJ4" s="82"/>
-      <c r="AK4" s="82"/>
-      <c r="AL4" s="82"/>
-      <c r="AM4" s="82"/>
-      <c r="AN4" s="82"/>
-      <c r="AO4" s="82"/>
-      <c r="AP4" s="82"/>
+      <c r="AH4" s="65" t="s">
+        <v>209</v>
+      </c>
+      <c r="AI4" s="80"/>
+      <c r="AJ4" s="80"/>
+      <c r="AK4" s="80"/>
+      <c r="AL4" s="80"/>
+      <c r="AM4" s="80"/>
+      <c r="AN4" s="80"/>
+      <c r="AO4" s="80"/>
+      <c r="AP4" s="80"/>
     </row>
     <row r="5" spans="1:42">
-      <c r="A5" s="85" t="str">
+      <c r="A5" s="84" t="str">
         <f>IF(Nurses!A5="","",Nurses!A5)</f>
         <v>간호사4</v>
       </c>
@@ -7741,18 +7377,18 @@
       <c r="AE5" s="7"/>
       <c r="AF5" s="7"/>
       <c r="AG5" s="6"/>
-      <c r="AH5" s="66"/>
-      <c r="AI5" s="82"/>
-      <c r="AJ5" s="82"/>
-      <c r="AK5" s="82"/>
-      <c r="AL5" s="82"/>
-      <c r="AM5" s="82"/>
-      <c r="AN5" s="82"/>
-      <c r="AO5" s="82"/>
-      <c r="AP5" s="82"/>
+      <c r="AH5" s="65"/>
+      <c r="AI5" s="80"/>
+      <c r="AJ5" s="80"/>
+      <c r="AK5" s="80"/>
+      <c r="AL5" s="80"/>
+      <c r="AM5" s="80"/>
+      <c r="AN5" s="80"/>
+      <c r="AO5" s="80"/>
+      <c r="AP5" s="80"/>
     </row>
     <row r="6" spans="1:42">
-      <c r="A6" s="85" t="str">
+      <c r="A6" s="84" t="str">
         <f>IF(Nurses!A6="","",Nurses!A6)</f>
         <v>간호사5</v>
       </c>
@@ -7788,20 +7424,20 @@
       <c r="AE6" s="7"/>
       <c r="AF6" s="7"/>
       <c r="AG6" s="6"/>
-      <c r="AH6" s="81" t="s">
-        <v>185</v>
-      </c>
-      <c r="AI6" s="82"/>
-      <c r="AJ6" s="82"/>
-      <c r="AK6" s="82"/>
-      <c r="AL6" s="82"/>
-      <c r="AM6" s="82"/>
-      <c r="AN6" s="82"/>
-      <c r="AO6" s="82"/>
-      <c r="AP6" s="82"/>
+      <c r="AH6" s="79" t="s">
+        <v>210</v>
+      </c>
+      <c r="AI6" s="80"/>
+      <c r="AJ6" s="80"/>
+      <c r="AK6" s="80"/>
+      <c r="AL6" s="80"/>
+      <c r="AM6" s="80"/>
+      <c r="AN6" s="80"/>
+      <c r="AO6" s="80"/>
+      <c r="AP6" s="80"/>
     </row>
     <row r="7" spans="1:42">
-      <c r="A7" s="85" t="str">
+      <c r="A7" s="84" t="str">
         <f>IF(Nurses!A7="","",Nurses!A7)</f>
         <v>간호사6</v>
       </c>
@@ -7837,18 +7473,18 @@
       <c r="AE7" s="7"/>
       <c r="AF7" s="7"/>
       <c r="AG7" s="6"/>
-      <c r="AH7" s="66"/>
-      <c r="AI7" s="82"/>
-      <c r="AJ7" s="82"/>
-      <c r="AK7" s="82"/>
-      <c r="AL7" s="82"/>
-      <c r="AM7" s="82"/>
-      <c r="AN7" s="82"/>
-      <c r="AO7" s="82"/>
-      <c r="AP7" s="82"/>
+      <c r="AH7" s="65"/>
+      <c r="AI7" s="80"/>
+      <c r="AJ7" s="80"/>
+      <c r="AK7" s="80"/>
+      <c r="AL7" s="80"/>
+      <c r="AM7" s="80"/>
+      <c r="AN7" s="80"/>
+      <c r="AO7" s="80"/>
+      <c r="AP7" s="80"/>
     </row>
     <row r="8" spans="1:42">
-      <c r="A8" s="85" t="str">
+      <c r="A8" s="84" t="str">
         <f>IF(Nurses!A8="","",Nurses!A8)</f>
         <v>간호사7</v>
       </c>
@@ -7884,20 +7520,20 @@
       <c r="AE8" s="7"/>
       <c r="AF8" s="7"/>
       <c r="AG8" s="6"/>
-      <c r="AH8" s="66" t="s">
-        <v>186</v>
-      </c>
-      <c r="AI8" s="82"/>
-      <c r="AJ8" s="82"/>
-      <c r="AK8" s="82"/>
-      <c r="AL8" s="82"/>
-      <c r="AM8" s="82"/>
-      <c r="AN8" s="82"/>
-      <c r="AO8" s="82"/>
-      <c r="AP8" s="82"/>
+      <c r="AH8" s="65" t="s">
+        <v>211</v>
+      </c>
+      <c r="AI8" s="80"/>
+      <c r="AJ8" s="80"/>
+      <c r="AK8" s="80"/>
+      <c r="AL8" s="80"/>
+      <c r="AM8" s="80"/>
+      <c r="AN8" s="80"/>
+      <c r="AO8" s="80"/>
+      <c r="AP8" s="80"/>
     </row>
     <row r="9" spans="1:42">
-      <c r="A9" s="85" t="str">
+      <c r="A9" s="84" t="str">
         <f>IF(Nurses!A9="","",Nurses!A9)</f>
         <v>간호사8</v>
       </c>
@@ -7933,18 +7569,18 @@
       <c r="AE9" s="7"/>
       <c r="AF9" s="7"/>
       <c r="AG9" s="6"/>
-      <c r="AH9" s="83"/>
-      <c r="AI9" s="82"/>
-      <c r="AJ9" s="82"/>
-      <c r="AK9" s="82"/>
-      <c r="AL9" s="82"/>
-      <c r="AM9" s="82"/>
-      <c r="AN9" s="82"/>
-      <c r="AO9" s="82"/>
-      <c r="AP9" s="82"/>
+      <c r="AH9" s="81"/>
+      <c r="AI9" s="80"/>
+      <c r="AJ9" s="80"/>
+      <c r="AK9" s="80"/>
+      <c r="AL9" s="80"/>
+      <c r="AM9" s="80"/>
+      <c r="AN9" s="80"/>
+      <c r="AO9" s="80"/>
+      <c r="AP9" s="80"/>
     </row>
     <row r="10" spans="1:42">
-      <c r="A10" s="85" t="str">
+      <c r="A10" s="84" t="str">
         <f>IF(Nurses!A10="","",Nurses!A10)</f>
         <v>간호사9</v>
       </c>
@@ -7980,20 +7616,20 @@
       <c r="AE10" s="7"/>
       <c r="AF10" s="7"/>
       <c r="AG10" s="6"/>
-      <c r="AH10" s="84" t="s">
-        <v>187</v>
-      </c>
-      <c r="AI10" s="82"/>
-      <c r="AJ10" s="82"/>
-      <c r="AK10" s="82"/>
-      <c r="AL10" s="82"/>
-      <c r="AM10" s="82"/>
-      <c r="AN10" s="82"/>
-      <c r="AO10" s="82"/>
-      <c r="AP10" s="82"/>
+      <c r="AH10" s="82" t="s">
+        <v>212</v>
+      </c>
+      <c r="AI10" s="80"/>
+      <c r="AJ10" s="80"/>
+      <c r="AK10" s="80"/>
+      <c r="AL10" s="80"/>
+      <c r="AM10" s="80"/>
+      <c r="AN10" s="80"/>
+      <c r="AO10" s="80"/>
+      <c r="AP10" s="80"/>
     </row>
     <row r="11" spans="1:42">
-      <c r="A11" s="85" t="str">
+      <c r="A11" s="84" t="str">
         <f>IF(Nurses!A11="","",Nurses!A11)</f>
         <v>간호사10</v>
       </c>
@@ -8031,7 +7667,7 @@
       <c r="AG11" s="6"/>
     </row>
     <row r="12" spans="1:42">
-      <c r="A12" s="85" t="str">
+      <c r="A12" s="84" t="str">
         <f>IF(Nurses!A12="","",Nurses!A12)</f>
         <v>간호사11</v>
       </c>
@@ -8069,7 +7705,7 @@
       <c r="AG12" s="6"/>
     </row>
     <row r="13" spans="1:42">
-      <c r="A13" s="85" t="str">
+      <c r="A13" s="84" t="str">
         <f>IF(Nurses!A13="","",Nurses!A13)</f>
         <v>간호사12</v>
       </c>
@@ -8107,7 +7743,7 @@
       <c r="AG13" s="6"/>
     </row>
     <row r="14" spans="1:42">
-      <c r="A14" s="85" t="str">
+      <c r="A14" s="84" t="str">
         <f>IF(Nurses!A14="","",Nurses!A14)</f>
         <v>간호사13</v>
       </c>
@@ -8144,7 +7780,7 @@
       <c r="AF14" s="7"/>
     </row>
     <row r="15" spans="1:42">
-      <c r="A15" s="85" t="str">
+      <c r="A15" s="84" t="str">
         <f>IF(Nurses!A15="","",Nurses!A15)</f>
         <v>간호사14</v>
       </c>
@@ -8181,7 +7817,7 @@
       <c r="AF15" s="7"/>
     </row>
     <row r="16" spans="1:42">
-      <c r="A16" s="85" t="str">
+      <c r="A16" s="84" t="str">
         <f>IF(Nurses!A16="","",Nurses!A16)</f>
         <v>간호사15</v>
       </c>
@@ -8218,7 +7854,7 @@
       <c r="AF16" s="7"/>
     </row>
     <row r="17" spans="1:32">
-      <c r="A17" s="85" t="str">
+      <c r="A17" s="84" t="str">
         <f>IF(Nurses!A17="","",Nurses!A17)</f>
         <v>간호사16</v>
       </c>
@@ -8255,7 +7891,7 @@
       <c r="AF17" s="7"/>
     </row>
     <row r="18" spans="1:32">
-      <c r="A18" s="85" t="str">
+      <c r="A18" s="84" t="str">
         <f>IF(Nurses!A18="","",Nurses!A18)</f>
         <v>간호사17</v>
       </c>
@@ -8292,7 +7928,7 @@
       <c r="AF18" s="7"/>
     </row>
     <row r="19" spans="1:32">
-      <c r="A19" s="85" t="str">
+      <c r="A19" s="84" t="str">
         <f>IF(Nurses!A19="","",Nurses!A19)</f>
         <v>간호사18</v>
       </c>
@@ -8329,7 +7965,7 @@
       <c r="AF19" s="7"/>
     </row>
     <row r="20" spans="1:32">
-      <c r="A20" s="85" t="str">
+      <c r="A20" s="84" t="str">
         <f>IF(Nurses!A20="","",Nurses!A20)</f>
         <v>간호사19</v>
       </c>
@@ -8366,7 +8002,7 @@
       <c r="AF20" s="7"/>
     </row>
     <row r="21" spans="1:32">
-      <c r="A21" s="85" t="str">
+      <c r="A21" s="84" t="str">
         <f>IF(Nurses!A21="","",Nurses!A21)</f>
         <v>간호사20</v>
       </c>
@@ -8403,7 +8039,7 @@
       <c r="AF21" s="7"/>
     </row>
     <row r="22" spans="1:32">
-      <c r="A22" s="85" t="str">
+      <c r="A22" s="84" t="str">
         <f>IF(Nurses!A22="","",Nurses!A22)</f>
         <v>간호사21</v>
       </c>
@@ -8440,7 +8076,7 @@
       <c r="AF22" s="7"/>
     </row>
     <row r="23" spans="1:32">
-      <c r="A23" s="85" t="str">
+      <c r="A23" s="84" t="str">
         <f>IF(Nurses!A23="","",Nurses!A23)</f>
         <v>간호사22</v>
       </c>
@@ -8477,7 +8113,7 @@
       <c r="AF23" s="7"/>
     </row>
     <row r="24" spans="1:32">
-      <c r="A24" s="85" t="str">
+      <c r="A24" s="84" t="str">
         <f>IF(Nurses!A24="","",Nurses!A24)</f>
         <v>간호사23</v>
       </c>
@@ -8514,7 +8150,7 @@
       <c r="AF24" s="7"/>
     </row>
     <row r="25" spans="1:32">
-      <c r="A25" s="85" t="str">
+      <c r="A25" s="84" t="str">
         <f>IF(Nurses!A25="","",Nurses!A25)</f>
         <v>간호사24</v>
       </c>
@@ -8551,7 +8187,7 @@
       <c r="AF25" s="7"/>
     </row>
     <row r="26" spans="1:32">
-      <c r="A26" s="85" t="str">
+      <c r="A26" s="84" t="str">
         <f>IF(Nurses!A26="","",Nurses!A26)</f>
         <v>간호사25</v>
       </c>
@@ -8588,7 +8224,7 @@
       <c r="AF26" s="7"/>
     </row>
     <row r="27" spans="1:32">
-      <c r="A27" s="85" t="str">
+      <c r="A27" s="84" t="str">
         <f>IF(Nurses!A27="","",Nurses!A27)</f>
         <v>간호사26</v>
       </c>
@@ -8625,7 +8261,7 @@
       <c r="AF27" s="7"/>
     </row>
     <row r="28" spans="1:32">
-      <c r="A28" s="85" t="str">
+      <c r="A28" s="84" t="str">
         <f>IF(Nurses!A28="","",Nurses!A28)</f>
         <v>간호사27</v>
       </c>
@@ -8662,7 +8298,7 @@
       <c r="AF28" s="7"/>
     </row>
     <row r="29" spans="1:32">
-      <c r="A29" s="85" t="str">
+      <c r="A29" s="84" t="str">
         <f>IF(Nurses!A29="","",Nurses!A29)</f>
         <v>간호사28</v>
       </c>
@@ -8699,7 +8335,7 @@
       <c r="AF29" s="7"/>
     </row>
     <row r="30" spans="1:32">
-      <c r="A30" s="85" t="str">
+      <c r="A30" s="84" t="str">
         <f>IF(Nurses!A30="","",Nurses!A30)</f>
         <v>간호사29</v>
       </c>
@@ -8736,7 +8372,7 @@
       <c r="AF30" s="7"/>
     </row>
     <row r="31" spans="1:32">
-      <c r="A31" s="85" t="str">
+      <c r="A31" s="84" t="str">
         <f>IF(Nurses!A31="","",Nurses!A31)</f>
         <v>간호사30</v>
       </c>
@@ -8773,7 +8409,7 @@
       <c r="AF31" s="7"/>
     </row>
     <row r="32" spans="1:32">
-      <c r="A32" s="85" t="str">
+      <c r="A32" s="84" t="str">
         <f>IF(Nurses!A32="","",Nurses!A32)</f>
         <v>간호사31</v>
       </c>
@@ -8810,7 +8446,7 @@
       <c r="AF32" s="7"/>
     </row>
     <row r="33" spans="1:32">
-      <c r="A33" s="85" t="str">
+      <c r="A33" s="84" t="str">
         <f>IF(Nurses!A33="","",Nurses!A33)</f>
         <v>간호사32</v>
       </c>
@@ -8847,7 +8483,7 @@
       <c r="AF33" s="7"/>
     </row>
     <row r="34" spans="1:32">
-      <c r="A34" s="85" t="str">
+      <c r="A34" s="84" t="str">
         <f>IF(Nurses!A34="","",Nurses!A34)</f>
         <v>간호사33</v>
       </c>
@@ -8884,7 +8520,7 @@
       <c r="AF34" s="7"/>
     </row>
     <row r="35" spans="1:32">
-      <c r="A35" s="85" t="str">
+      <c r="A35" s="84" t="str">
         <f>IF(Nurses!A35="","",Nurses!A35)</f>
         <v>간호사34</v>
       </c>
@@ -8921,7 +8557,7 @@
       <c r="AF35" s="7"/>
     </row>
     <row r="36" spans="1:32">
-      <c r="A36" s="85" t="str">
+      <c r="A36" s="84" t="str">
         <f>IF(Nurses!A36="","",Nurses!A36)</f>
         <v>간호사35</v>
       </c>
@@ -8958,7 +8594,7 @@
       <c r="AF36" s="7"/>
     </row>
     <row r="37" spans="1:32">
-      <c r="A37" s="85" t="str">
+      <c r="A37" s="84" t="str">
         <f>IF(Nurses!A37="","",Nurses!A37)</f>
         <v>간호사36</v>
       </c>
@@ -8995,7 +8631,7 @@
       <c r="AF37" s="7"/>
     </row>
     <row r="38" spans="1:32">
-      <c r="A38" s="85" t="str">
+      <c r="A38" s="84" t="str">
         <f>IF(Nurses!A38="","",Nurses!A38)</f>
         <v>간호사37</v>
       </c>
@@ -9032,7 +8668,7 @@
       <c r="AF38" s="7"/>
     </row>
     <row r="39" spans="1:32">
-      <c r="A39" s="85" t="str">
+      <c r="A39" s="84" t="str">
         <f>IF(Nurses!A39="","",Nurses!A39)</f>
         <v>간호사38</v>
       </c>
@@ -9069,7 +8705,7 @@
       <c r="AF39" s="7"/>
     </row>
     <row r="40" spans="1:32">
-      <c r="A40" s="85" t="str">
+      <c r="A40" s="84" t="str">
         <f>IF(Nurses!A40="","",Nurses!A40)</f>
         <v>간호사39</v>
       </c>
@@ -9106,7 +8742,7 @@
       <c r="AF40" s="7"/>
     </row>
     <row r="41" spans="1:32">
-      <c r="A41" s="85" t="str">
+      <c r="A41" s="84" t="str">
         <f>IF(Nurses!A41="","",Nurses!A41)</f>
         <v>간호사40</v>
       </c>
@@ -9143,7 +8779,7 @@
       <c r="AF41" s="7"/>
     </row>
     <row r="42" spans="1:32">
-      <c r="A42" s="85" t="str">
+      <c r="A42" s="84" t="str">
         <f>IF(Nurses!A42="","",Nurses!A42)</f>
         <v>간호사41</v>
       </c>
@@ -9180,7 +8816,7 @@
       <c r="AF42" s="7"/>
     </row>
     <row r="43" spans="1:32">
-      <c r="A43" s="85" t="str">
+      <c r="A43" s="84" t="str">
         <f>IF(Nurses!A43="","",Nurses!A43)</f>
         <v>간호사42</v>
       </c>
@@ -9217,7 +8853,7 @@
       <c r="AF43" s="7"/>
     </row>
     <row r="44" spans="1:32">
-      <c r="A44" s="85" t="str">
+      <c r="A44" s="84" t="str">
         <f>IF(Nurses!A44="","",Nurses!A44)</f>
         <v>간호사43</v>
       </c>
@@ -9254,7 +8890,7 @@
       <c r="AF44" s="7"/>
     </row>
     <row r="45" spans="1:32">
-      <c r="A45" s="85" t="str">
+      <c r="A45" s="84" t="str">
         <f>IF(Nurses!A45="","",Nurses!A45)</f>
         <v>간호사44</v>
       </c>
@@ -9291,7 +8927,7 @@
       <c r="AF45" s="7"/>
     </row>
     <row r="46" spans="1:32">
-      <c r="A46" s="85" t="str">
+      <c r="A46" s="84" t="str">
         <f>IF(Nurses!A46="","",Nurses!A46)</f>
         <v>간호사45</v>
       </c>
@@ -9328,7 +8964,7 @@
       <c r="AF46" s="7"/>
     </row>
     <row r="47" spans="1:32">
-      <c r="A47" s="85" t="str">
+      <c r="A47" s="84" t="str">
         <f>IF(Nurses!A47="","",Nurses!A47)</f>
         <v>간호사46</v>
       </c>
@@ -9365,7 +9001,7 @@
       <c r="AF47" s="7"/>
     </row>
     <row r="48" spans="1:32">
-      <c r="A48" s="85" t="str">
+      <c r="A48" s="84" t="str">
         <f>IF(Nurses!A48="","",Nurses!A48)</f>
         <v>간호사47</v>
       </c>
@@ -9402,7 +9038,7 @@
       <c r="AF48" s="7"/>
     </row>
     <row r="49" spans="1:32">
-      <c r="A49" s="85" t="str">
+      <c r="A49" s="84" t="str">
         <f>IF(Nurses!A49="","",Nurses!A49)</f>
         <v>간호사48</v>
       </c>
@@ -9439,7 +9075,7 @@
       <c r="AF49" s="7"/>
     </row>
     <row r="50" spans="1:32">
-      <c r="A50" s="85" t="str">
+      <c r="A50" s="84" t="str">
         <f>IF(Nurses!A50="","",Nurses!A50)</f>
         <v>간호사49</v>
       </c>
@@ -9476,7 +9112,7 @@
       <c r="AF50" s="7"/>
     </row>
     <row r="51" spans="1:32">
-      <c r="A51" s="85" t="str">
+      <c r="A51" s="84" t="str">
         <f>IF(Nurses!A51="","",Nurses!A51)</f>
         <v>간호사50</v>
       </c>
@@ -9529,26 +9165,26 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="14" t="s">
-        <v>128</v>
+        <v>153</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>188</v>
+        <v>213</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>189</v>
+        <v>214</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>190</v>
+        <v>215</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>191</v>
+        <v>216</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>192</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2" spans="1:17">
-      <c r="A2" s="85" t="str">
+      <c r="A2" s="84" t="str">
         <f>IF(Nurses!A2="","",Nurses!A2)</f>
         <v>간호사1</v>
       </c>
@@ -9564,12 +9200,12 @@
       <c r="Q2" s="11"/>
     </row>
     <row r="3" spans="1:17">
-      <c r="A3" s="85" t="str">
+      <c r="A3" s="84" t="str">
         <f>IF(Nurses!A3="","",Nurses!A3)</f>
         <v>간호사2</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="K3" s="11"/>
       <c r="L3" s="11"/>
@@ -9580,292 +9216,292 @@
       <c r="Q3" s="11"/>
     </row>
     <row r="4" spans="1:17">
-      <c r="A4" s="85" t="str">
+      <c r="A4" s="84" t="str">
         <f>IF(Nurses!A4="","",Nurses!A4)</f>
         <v>간호사3</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>194</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5" spans="1:17">
-      <c r="A5" s="85" t="str">
+      <c r="A5" s="84" t="str">
         <f>IF(Nurses!A5="","",Nurses!A5)</f>
         <v>간호사4</v>
       </c>
     </row>
     <row r="6" spans="1:17">
-      <c r="A6" s="85" t="str">
+      <c r="A6" s="84" t="str">
         <f>IF(Nurses!A6="","",Nurses!A6)</f>
         <v>간호사5</v>
       </c>
     </row>
     <row r="7" spans="1:17">
-      <c r="A7" s="85" t="str">
+      <c r="A7" s="84" t="str">
         <f>IF(Nurses!A7="","",Nurses!A7)</f>
         <v>간호사6</v>
       </c>
     </row>
     <row r="8" spans="1:17">
-      <c r="A8" s="85" t="str">
+      <c r="A8" s="84" t="str">
         <f>IF(Nurses!A8="","",Nurses!A8)</f>
         <v>간호사7</v>
       </c>
     </row>
     <row r="9" spans="1:17">
-      <c r="A9" s="85" t="str">
+      <c r="A9" s="84" t="str">
         <f>IF(Nurses!A9="","",Nurses!A9)</f>
         <v>간호사8</v>
       </c>
     </row>
     <row r="10" spans="1:17">
-      <c r="A10" s="85" t="str">
+      <c r="A10" s="84" t="str">
         <f>IF(Nurses!A10="","",Nurses!A10)</f>
         <v>간호사9</v>
       </c>
     </row>
     <row r="11" spans="1:17">
-      <c r="A11" s="85" t="str">
+      <c r="A11" s="84" t="str">
         <f>IF(Nurses!A11="","",Nurses!A11)</f>
         <v>간호사10</v>
       </c>
     </row>
     <row r="12" spans="1:17">
-      <c r="A12" s="85" t="str">
+      <c r="A12" s="84" t="str">
         <f>IF(Nurses!A12="","",Nurses!A12)</f>
         <v>간호사11</v>
       </c>
     </row>
     <row r="13" spans="1:17">
-      <c r="A13" s="85" t="str">
+      <c r="A13" s="84" t="str">
         <f>IF(Nurses!A13="","",Nurses!A13)</f>
         <v>간호사12</v>
       </c>
     </row>
     <row r="14" spans="1:17">
-      <c r="A14" s="85" t="str">
+      <c r="A14" s="84" t="str">
         <f>IF(Nurses!A14="","",Nurses!A14)</f>
         <v>간호사13</v>
       </c>
     </row>
     <row r="15" spans="1:17">
-      <c r="A15" s="85" t="str">
+      <c r="A15" s="84" t="str">
         <f>IF(Nurses!A15="","",Nurses!A15)</f>
         <v>간호사14</v>
       </c>
     </row>
     <row r="16" spans="1:17">
-      <c r="A16" s="85" t="str">
+      <c r="A16" s="84" t="str">
         <f>IF(Nurses!A16="","",Nurses!A16)</f>
         <v>간호사15</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="85" t="str">
+      <c r="A17" s="84" t="str">
         <f>IF(Nurses!A17="","",Nurses!A17)</f>
         <v>간호사16</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="85" t="str">
+      <c r="A18" s="84" t="str">
         <f>IF(Nurses!A18="","",Nurses!A18)</f>
         <v>간호사17</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="85" t="str">
+      <c r="A19" s="84" t="str">
         <f>IF(Nurses!A19="","",Nurses!A19)</f>
         <v>간호사18</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="85" t="str">
+      <c r="A20" s="84" t="str">
         <f>IF(Nurses!A20="","",Nurses!A20)</f>
         <v>간호사19</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="85" t="str">
+      <c r="A21" s="84" t="str">
         <f>IF(Nurses!A21="","",Nurses!A21)</f>
         <v>간호사20</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="85" t="str">
+      <c r="A22" s="84" t="str">
         <f>IF(Nurses!A22="","",Nurses!A22)</f>
         <v>간호사21</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="85" t="str">
+      <c r="A23" s="84" t="str">
         <f>IF(Nurses!A23="","",Nurses!A23)</f>
         <v>간호사22</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="85" t="str">
+      <c r="A24" s="84" t="str">
         <f>IF(Nurses!A24="","",Nurses!A24)</f>
         <v>간호사23</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="85" t="str">
+      <c r="A25" s="84" t="str">
         <f>IF(Nurses!A25="","",Nurses!A25)</f>
         <v>간호사24</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="85" t="str">
+      <c r="A26" s="84" t="str">
         <f>IF(Nurses!A26="","",Nurses!A26)</f>
         <v>간호사25</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="85" t="str">
+      <c r="A27" s="84" t="str">
         <f>IF(Nurses!A27="","",Nurses!A27)</f>
         <v>간호사26</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="85" t="str">
+      <c r="A28" s="84" t="str">
         <f>IF(Nurses!A28="","",Nurses!A28)</f>
         <v>간호사27</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="85" t="str">
+      <c r="A29" s="84" t="str">
         <f>IF(Nurses!A29="","",Nurses!A29)</f>
         <v>간호사28</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="85" t="str">
+      <c r="A30" s="84" t="str">
         <f>IF(Nurses!A30="","",Nurses!A30)</f>
         <v>간호사29</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="85" t="str">
+      <c r="A31" s="84" t="str">
         <f>IF(Nurses!A31="","",Nurses!A31)</f>
         <v>간호사30</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="85" t="str">
+      <c r="A32" s="84" t="str">
         <f>IF(Nurses!A32="","",Nurses!A32)</f>
         <v>간호사31</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="85" t="str">
+      <c r="A33" s="84" t="str">
         <f>IF(Nurses!A33="","",Nurses!A33)</f>
         <v>간호사32</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="85" t="str">
+      <c r="A34" s="84" t="str">
         <f>IF(Nurses!A34="","",Nurses!A34)</f>
         <v>간호사33</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="85" t="str">
+      <c r="A35" s="84" t="str">
         <f>IF(Nurses!A35="","",Nurses!A35)</f>
         <v>간호사34</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="85" t="str">
+      <c r="A36" s="84" t="str">
         <f>IF(Nurses!A36="","",Nurses!A36)</f>
         <v>간호사35</v>
       </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="85" t="str">
+      <c r="A37" s="84" t="str">
         <f>IF(Nurses!A37="","",Nurses!A37)</f>
         <v>간호사36</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="85" t="str">
+      <c r="A38" s="84" t="str">
         <f>IF(Nurses!A38="","",Nurses!A38)</f>
         <v>간호사37</v>
       </c>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="85" t="str">
+      <c r="A39" s="84" t="str">
         <f>IF(Nurses!A39="","",Nurses!A39)</f>
         <v>간호사38</v>
       </c>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="85" t="str">
+      <c r="A40" s="84" t="str">
         <f>IF(Nurses!A40="","",Nurses!A40)</f>
         <v>간호사39</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="85" t="str">
+      <c r="A41" s="84" t="str">
         <f>IF(Nurses!A41="","",Nurses!A41)</f>
         <v>간호사40</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="85" t="str">
+      <c r="A42" s="84" t="str">
         <f>IF(Nurses!A42="","",Nurses!A42)</f>
         <v>간호사41</v>
       </c>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="85" t="str">
+      <c r="A43" s="84" t="str">
         <f>IF(Nurses!A43="","",Nurses!A43)</f>
         <v>간호사42</v>
       </c>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" s="85" t="str">
+      <c r="A44" s="84" t="str">
         <f>IF(Nurses!A44="","",Nurses!A44)</f>
         <v>간호사43</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="85" t="str">
+      <c r="A45" s="84" t="str">
         <f>IF(Nurses!A45="","",Nurses!A45)</f>
         <v>간호사44</v>
       </c>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" s="85" t="str">
+      <c r="A46" s="84" t="str">
         <f>IF(Nurses!A46="","",Nurses!A46)</f>
         <v>간호사45</v>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="85" t="str">
+      <c r="A47" s="84" t="str">
         <f>IF(Nurses!A47="","",Nurses!A47)</f>
         <v>간호사46</v>
       </c>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" s="85" t="str">
+      <c r="A48" s="84" t="str">
         <f>IF(Nurses!A48="","",Nurses!A48)</f>
         <v>간호사47</v>
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="85" t="str">
+      <c r="A49" s="84" t="str">
         <f>IF(Nurses!A49="","",Nurses!A49)</f>
         <v>간호사48</v>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="85" t="str">
+      <c r="A50" s="84" t="str">
         <f>IF(Nurses!A50="","",Nurses!A50)</f>
         <v>간호사49</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="85" t="str">
+      <c r="A51" s="84" t="str">
         <f>IF(Nurses!A51="","",Nurses!A51)</f>
         <v>간호사50</v>
       </c>
@@ -9887,147 +9523,147 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42">
-      <c r="A1" s="96" t="s">
-        <v>195</v>
-      </c>
-      <c r="B1" s="95"/>
-      <c r="C1" s="95"/>
-      <c r="D1" s="95"/>
-      <c r="E1" s="95"/>
-      <c r="F1" s="95"/>
-      <c r="G1" s="95"/>
-      <c r="H1" s="95"/>
-      <c r="I1" s="95"/>
-      <c r="J1" s="95"/>
-      <c r="K1" s="95"/>
-      <c r="L1" s="95"/>
-      <c r="M1" s="95"/>
-      <c r="N1" s="95"/>
-      <c r="O1" s="95"/>
-      <c r="P1" s="95"/>
-      <c r="Q1" s="95"/>
-      <c r="R1" s="95"/>
-      <c r="S1" s="95"/>
-      <c r="T1" s="95"/>
-      <c r="U1" s="95"/>
-      <c r="V1" s="95"/>
-      <c r="W1" s="95"/>
-      <c r="X1" s="95"/>
-      <c r="Y1" s="95"/>
-      <c r="Z1" s="95"/>
-      <c r="AA1" s="95"/>
-      <c r="AB1" s="95"/>
-      <c r="AC1" s="95"/>
-      <c r="AD1" s="95"/>
-      <c r="AE1" s="95"/>
-      <c r="AF1" s="95"/>
-      <c r="AG1" s="95"/>
-      <c r="AH1" s="95"/>
-      <c r="AI1" s="95"/>
-      <c r="AJ1" s="95"/>
-      <c r="AK1" s="95"/>
-      <c r="AL1" s="95"/>
-      <c r="AM1" s="95"/>
-      <c r="AN1" s="95"/>
-      <c r="AO1" s="95"/>
-      <c r="AP1" s="95"/>
+      <c r="A1" s="97" t="s">
+        <v>220</v>
+      </c>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="96"/>
+      <c r="H1" s="96"/>
+      <c r="I1" s="96"/>
+      <c r="J1" s="96"/>
+      <c r="K1" s="96"/>
+      <c r="L1" s="96"/>
+      <c r="M1" s="96"/>
+      <c r="N1" s="96"/>
+      <c r="O1" s="96"/>
+      <c r="P1" s="96"/>
+      <c r="Q1" s="96"/>
+      <c r="R1" s="96"/>
+      <c r="S1" s="96"/>
+      <c r="T1" s="96"/>
+      <c r="U1" s="96"/>
+      <c r="V1" s="96"/>
+      <c r="W1" s="96"/>
+      <c r="X1" s="96"/>
+      <c r="Y1" s="96"/>
+      <c r="Z1" s="96"/>
+      <c r="AA1" s="96"/>
+      <c r="AB1" s="96"/>
+      <c r="AC1" s="96"/>
+      <c r="AD1" s="96"/>
+      <c r="AE1" s="96"/>
+      <c r="AF1" s="96"/>
+      <c r="AG1" s="96"/>
+      <c r="AH1" s="96"/>
+      <c r="AI1" s="96"/>
+      <c r="AJ1" s="96"/>
+      <c r="AK1" s="96"/>
+      <c r="AL1" s="96"/>
+      <c r="AM1" s="96"/>
+      <c r="AN1" s="96"/>
+      <c r="AO1" s="96"/>
+      <c r="AP1" s="96"/>
     </row>
     <row r="2" spans="1:42">
       <c r="A2" s="8" t="s">
-        <v>196</v>
+        <v>221</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="S2" s="6" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="T2" s="6" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="U2" s="6" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="V2" s="6" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="W2" s="6" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="X2" s="6" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="Y2" s="6" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="Z2" s="6" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="AA2" s="6" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="AB2" s="6" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="AC2" s="6" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="AD2" s="6" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="AE2" s="6" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="AF2" s="6" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="AG2" s="6"/>
       <c r="AH2" s="6"/>
@@ -10042,7 +9678,7 @@
     </row>
     <row r="3" spans="1:42">
       <c r="A3" s="5" t="s">
-        <v>170</v>
+        <v>195</v>
       </c>
       <c r="B3" s="5">
         <v>1</v>
@@ -10138,169 +9774,169 @@
         <v>31</v>
       </c>
       <c r="AG3" s="5" t="s">
-        <v>199</v>
+        <v>224</v>
       </c>
       <c r="AH3" s="5" t="s">
-        <v>200</v>
+        <v>225</v>
       </c>
       <c r="AI3" s="5" t="s">
-        <v>201</v>
+        <v>226</v>
       </c>
       <c r="AJ3" s="5" t="s">
-        <v>202</v>
+        <v>227</v>
       </c>
       <c r="AK3" s="5" t="s">
-        <v>203</v>
+        <v>228</v>
       </c>
       <c r="AL3" s="5" t="s">
-        <v>204</v>
+        <v>229</v>
       </c>
       <c r="AM3" s="5" t="s">
-        <v>205</v>
+        <v>230</v>
       </c>
       <c r="AN3" s="5" t="s">
-        <v>206</v>
+        <v>231</v>
       </c>
       <c r="AO3" s="5" t="s">
-        <v>207</v>
+        <v>232</v>
       </c>
       <c r="AP3" s="5" t="s">
-        <v>208</v>
+        <v>233</v>
       </c>
     </row>
     <row r="4" spans="1:42">
       <c r="A4" t="s">
-        <v>133</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:42">
       <c r="A5" t="s">
-        <v>134</v>
+        <v>159</v>
       </c>
     </row>
     <row r="6" spans="1:42">
       <c r="A6" t="s">
-        <v>136</v>
+        <v>161</v>
       </c>
     </row>
     <row r="7" spans="1:42">
       <c r="A7" t="s">
-        <v>138</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8" spans="1:42">
       <c r="A8" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
     </row>
     <row r="9" spans="1:42">
       <c r="A9" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" spans="1:42">
       <c r="A10" t="s">
-        <v>143</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11" spans="1:42">
       <c r="A11" t="s">
-        <v>145</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12" spans="1:42">
       <c r="A12" t="s">
-        <v>147</v>
+        <v>172</v>
       </c>
     </row>
     <row r="13" spans="1:42">
       <c r="A13" t="s">
-        <v>148</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14" spans="1:42">
       <c r="A14" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15" spans="1:42">
       <c r="A15" t="s">
-        <v>151</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16" spans="1:42">
       <c r="A16" t="s">
-        <v>229</v>
+        <v>254</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>230</v>
+        <v>255</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>231</v>
+        <v>256</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>232</v>
+        <v>257</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>233</v>
+        <v>258</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>234</v>
+        <v>259</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>235</v>
+        <v>260</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>236</v>
+        <v>261</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>237</v>
+        <v>262</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>238</v>
+        <v>263</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>239</v>
+        <v>264</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>240</v>
+        <v>265</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>241</v>
+        <v>266</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>242</v>
+        <v>267</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>243</v>
+        <v>268</v>
       </c>
     </row>
   </sheetData>

--- a/nurse_scheduler_complete.xlsx
+++ b/nurse_scheduler_complete.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\송민영\Desktop\근무표 프로그램\완전판\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B5250F5-1CD9-4DA5-9A4D-534A8BFDE805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{988B63CA-DCF1-45ED-B373-E8489EFFC8DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="설명서" sheetId="1" r:id="rId1"/>
@@ -208,9 +208,6 @@
     <t>Preference miss penalty (선호 근무 무시 벌점): 선생님들이 신청한 듀티(E or D 등)를 안 들어줬을 때 컴퓨터가 받는 벌점입니다. 이 숫자를 높게 바꿀수록 컴퓨터는 신청 듀티를 무조건 100% 들어주려고 노력하게 됩니다.</t>
   </si>
   <si>
-    <t>Fairness weight (공평성 가중치): 간호사들끼리 특정 듀티의 개수가 차이 날 때마다 컴퓨터가 받는 벌점입니다. 이 숫자가 클수록 컴퓨터가 간호사들 간의 개수를 아주 칼같이 똑맞추려고 노력합니다.</t>
-  </si>
-  <si>
     <t xml:space="preserve">total work: 총 출근 일수를 똑같이 맞추려는 노력 점수 </t>
   </si>
   <si>
@@ -936,6 +933,10 @@
   </si>
   <si>
     <t>막내 여부: 막내 여부를 두 명 이상 Y 체크하면 막내끼리는 같은 듀티에 가급적 배치하지 않습니다</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fairness weight (공평성 가중치): 간호사들끼리 특정 듀티의 개수가 차이 날 때마다 컴퓨터가 받는 벌점입니다. 이 숫자가 클수록 컴퓨터가 간호사들 간의 개수를 아주 칼같이 똑맞추려고 노력합니다. 10000점이 기본설정</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1388,7 +1389,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1600,16 +1601,15 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1923,14 +1923,14 @@
   <sheetData>
     <row r="1" spans="1:24" ht="38.25" customHeight="1">
       <c r="A1" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="K1" s="26" t="s">
         <v>60</v>
-      </c>
-      <c r="K1" s="26" t="s">
-        <v>61</v>
       </c>
       <c r="L1" s="27"/>
       <c r="M1" s="94" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S1" s="28"/>
       <c r="T1" s="28"/>
@@ -1944,7 +1944,7 @@
       <c r="K2" s="30"/>
       <c r="L2" s="25"/>
       <c r="M2" s="94" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="X2" s="31"/>
     </row>
@@ -1956,7 +1956,7 @@
       <c r="H3" s="25"/>
       <c r="I3" s="24"/>
       <c r="K3" s="32" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="X3" s="31"/>
     </row>
@@ -1968,7 +1968,7 @@
       <c r="H4" s="25"/>
       <c r="I4" s="24"/>
       <c r="K4" s="33" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L4" s="34"/>
       <c r="M4" s="35"/>
@@ -1986,22 +1986,22 @@
     </row>
     <row r="6" spans="1:24" ht="15.75" customHeight="1">
       <c r="A6" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:24" ht="26.25" customHeight="1">
       <c r="A8" s="22" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:24">
       <c r="A10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:24">
       <c r="A12" s="23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:24">
@@ -2009,7 +2009,7 @@
     </row>
     <row r="14" spans="1:24">
       <c r="A14" s="17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:24">
@@ -2017,7 +2017,7 @@
     </row>
     <row r="16" spans="1:24">
       <c r="A16" s="17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:1">
@@ -2025,7 +2025,7 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:1">
@@ -2033,7 +2033,7 @@
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -2041,12 +2041,12 @@
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="23" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" spans="1:1">
@@ -2054,12 +2054,12 @@
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" spans="1:1">
@@ -2067,7 +2067,7 @@
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" spans="1:1">
@@ -2075,7 +2075,7 @@
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33" spans="1:1">
@@ -2083,12 +2083,12 @@
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="23" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="37" spans="1:1">
@@ -2096,22 +2096,22 @@
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:1" ht="26.25" customHeight="1">
       <c r="A42" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="46" spans="1:1" ht="21.75" customHeight="1">
       <c r="A46" s="18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="47" spans="1:1">
@@ -2119,7 +2119,7 @@
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="49" spans="1:1">
@@ -2127,7 +2127,7 @@
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="51" spans="1:1">
@@ -2135,7 +2135,7 @@
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="53" spans="1:1">
@@ -2143,7 +2143,7 @@
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="55" spans="1:1">
@@ -2151,7 +2151,7 @@
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="57" spans="1:1">
@@ -2159,12 +2159,12 @@
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="60" spans="1:1" ht="21.75" customHeight="1">
       <c r="A60" s="18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="61" spans="1:1">
@@ -2172,7 +2172,7 @@
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="63" spans="1:1">
@@ -2180,7 +2180,7 @@
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="65" spans="1:1">
@@ -2188,7 +2188,7 @@
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="67" spans="1:1">
@@ -2196,7 +2196,7 @@
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="20" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="69" spans="1:1">
@@ -2204,7 +2204,7 @@
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="20" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="71" spans="1:1">
@@ -2212,7 +2212,7 @@
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="20" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="73" spans="1:1">
@@ -2220,7 +2220,7 @@
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="20" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="75" spans="1:1">
@@ -2228,7 +2228,7 @@
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="77" spans="1:1">
@@ -2236,7 +2236,7 @@
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="79" spans="1:1">
@@ -2244,7 +2244,7 @@
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="81" spans="1:1">
@@ -2252,12 +2252,12 @@
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="17" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="19" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="84" spans="1:1">
@@ -2265,7 +2265,7 @@
     </row>
     <row r="86" spans="1:1" ht="21.75" customHeight="1">
       <c r="A86" s="18" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="87" spans="1:1">
@@ -2273,7 +2273,7 @@
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="17" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="89" spans="1:1">
@@ -2281,7 +2281,7 @@
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="91" spans="1:1">
@@ -2289,7 +2289,7 @@
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="19" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="93" spans="1:1">
@@ -2297,7 +2297,7 @@
     </row>
     <row r="94" spans="1:1">
       <c r="A94" s="20" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="95" spans="1:1">
@@ -2305,7 +2305,7 @@
     </row>
     <row r="96" spans="1:1">
       <c r="A96" s="20" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="97" spans="1:10">
@@ -2313,7 +2313,7 @@
     </row>
     <row r="98" spans="1:10">
       <c r="A98" s="20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="99" spans="1:10">
@@ -2321,12 +2321,12 @@
     </row>
     <row r="100" spans="1:10">
       <c r="A100" s="19" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="102" spans="1:10" ht="21.75" customHeight="1">
       <c r="A102" s="18" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="103" spans="1:10">
@@ -2334,7 +2334,7 @@
     </row>
     <row r="104" spans="1:10">
       <c r="A104" s="41" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B104" s="42"/>
       <c r="C104" s="42"/>
@@ -2360,7 +2360,7 @@
     </row>
     <row r="106" spans="1:10">
       <c r="A106" s="79" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B106" s="42"/>
       <c r="C106" s="42"/>
@@ -2386,7 +2386,7 @@
     </row>
     <row r="108" spans="1:10">
       <c r="A108" s="41" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B108" s="42"/>
       <c r="C108" s="42"/>
@@ -2400,7 +2400,7 @@
     </row>
     <row r="110" spans="1:10" ht="21.75" customHeight="1">
       <c r="A110" s="18" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="111" spans="1:10">
@@ -2408,7 +2408,7 @@
     </row>
     <row r="112" spans="1:10">
       <c r="A112" s="17" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="113" spans="1:1">
@@ -2416,7 +2416,7 @@
     </row>
     <row r="114" spans="1:1">
       <c r="A114" s="17" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="115" spans="1:1">
@@ -2424,12 +2424,12 @@
     </row>
     <row r="116" spans="1:1">
       <c r="A116" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="119" spans="1:1">
@@ -2437,7 +2437,7 @@
     </row>
     <row r="120" spans="1:1">
       <c r="A120" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="121" spans="1:1">
@@ -2445,7 +2445,7 @@
     </row>
     <row r="122" spans="1:1" ht="26.25" customHeight="1">
       <c r="A122" s="38" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="123" spans="1:1">
@@ -2453,7 +2453,7 @@
     </row>
     <row r="124" spans="1:1">
       <c r="A124" s="43" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="125" spans="1:1">
@@ -2461,12 +2461,12 @@
     </row>
     <row r="126" spans="1:1">
       <c r="A126" s="43" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="127" spans="1:1">
       <c r="A127" s="45" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="128" spans="1:1">
@@ -2474,12 +2474,12 @@
     </row>
     <row r="129" spans="1:1">
       <c r="A129" s="43" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" s="39" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="131" spans="1:1">
@@ -2487,37 +2487,37 @@
     </row>
     <row r="132" spans="1:1">
       <c r="A132" s="43" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="134" spans="1:1" ht="26.25" customHeight="1">
       <c r="A134" s="83" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="135" spans="1:1" ht="26.25" customHeight="1">
       <c r="A135" s="88" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="138" spans="1:1" ht="20.25" customHeight="1">
       <c r="A138" s="92" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="141" spans="1:1" ht="21.75" customHeight="1">
       <c r="A141" s="18" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="143" spans="1:1">
       <c r="A143" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="144" spans="1:1">
@@ -2525,17 +2525,17 @@
     </row>
     <row r="145" spans="1:1">
       <c r="A145" s="89" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="146" spans="1:1">
       <c r="A146" s="90" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="147" spans="1:1">
       <c r="A147" s="90" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="148" spans="1:1">
@@ -2543,17 +2543,17 @@
     </row>
     <row r="149" spans="1:1">
       <c r="A149" s="89" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="150" spans="1:1">
       <c r="A150" s="90" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="151" spans="1:1">
       <c r="A151" s="90" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="152" spans="1:1">
@@ -2561,17 +2561,17 @@
     </row>
     <row r="153" spans="1:1">
       <c r="A153" s="89" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="154" spans="1:1">
       <c r="A154" s="90" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="155" spans="1:1">
       <c r="A155" s="90" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="156" spans="1:1">
@@ -2579,22 +2579,22 @@
     </row>
     <row r="157" spans="1:1">
       <c r="A157" s="89" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="158" spans="1:1">
       <c r="A158" s="90" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="159" spans="1:1">
       <c r="A159" s="90" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="161" spans="1:1" ht="21.75" customHeight="1">
       <c r="A161" s="18" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="162" spans="1:1">
@@ -2602,37 +2602,37 @@
     </row>
     <row r="163" spans="1:1">
       <c r="A163" s="17" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="164" spans="1:1">
       <c r="A164" s="17" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="166" spans="1:1">
       <c r="A166" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="167" spans="1:1">
       <c r="A167" s="90" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="168" spans="1:1">
       <c r="A168" s="91" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="169" spans="1:1">
       <c r="A169" s="91" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="170" spans="1:1">
       <c r="A170" s="91" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -2655,22 +2655,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>236</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -2694,31 +2694,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>244</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2774,31 +2774,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>251</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2912,12 +2912,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="96" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
@@ -3348,7 +3348,7 @@
     </row>
     <row r="37" spans="1:17" ht="17.25" customHeight="1">
       <c r="A37" s="54" t="s">
-        <v>54</v>
+        <v>295</v>
       </c>
       <c r="B37" s="55"/>
       <c r="C37" s="55"/>
@@ -3388,7 +3388,7 @@
     </row>
     <row r="39" spans="1:17" ht="17.25" customHeight="1">
       <c r="A39" s="59" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B39" s="55"/>
       <c r="C39" s="55"/>
@@ -3428,7 +3428,7 @@
     </row>
     <row r="41" spans="1:17" ht="17.25" customHeight="1">
       <c r="A41" s="59" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B41" s="55"/>
       <c r="C41" s="55"/>
@@ -3468,7 +3468,7 @@
     </row>
     <row r="43" spans="1:17" ht="17.25" customHeight="1">
       <c r="A43" s="59" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B43" s="55"/>
       <c r="C43" s="55"/>
@@ -3508,7 +3508,7 @@
     </row>
     <row r="45" spans="1:17" ht="17.25" customHeight="1">
       <c r="A45" s="59" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B45" s="55"/>
       <c r="C45" s="55"/>
@@ -3548,7 +3548,7 @@
     </row>
     <row r="47" spans="1:17" ht="18" customHeight="1" thickBot="1">
       <c r="A47" s="60" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B47" s="61"/>
       <c r="C47" s="61"/>
@@ -3591,27 +3591,27 @@
   <sheetData>
     <row r="1" spans="1:27" ht="17.25" customHeight="1" thickBot="1">
       <c r="A1" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B1" s="66" t="s">
         <v>153</v>
       </c>
-      <c r="B1" s="66" t="s">
+      <c r="C1" s="66" t="s">
         <v>154</v>
       </c>
-      <c r="C1" s="66" t="s">
+      <c r="D1" s="66" t="s">
         <v>155</v>
       </c>
-      <c r="D1" s="66" t="s">
+      <c r="E1" s="66" t="s">
         <v>156</v>
       </c>
-      <c r="E1" s="66" t="s">
-        <v>157</v>
-      </c>
       <c r="F1" s="66" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="2" spans="1:27">
       <c r="A2" s="84" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H2" s="67" t="s">
         <v>51</v>
@@ -3638,407 +3638,137 @@
     </row>
     <row r="3" spans="1:27">
       <c r="A3" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="H3" s="51" t="s">
         <v>159</v>
       </c>
-      <c r="H3" s="51" t="s">
-        <v>160</v>
-      </c>
-      <c r="I3" s="98"/>
-      <c r="J3" s="98"/>
-      <c r="K3" s="98"/>
-      <c r="L3" s="98"/>
-      <c r="M3" s="98"/>
-      <c r="N3" s="98"/>
-      <c r="O3" s="98"/>
-      <c r="P3" s="98"/>
-      <c r="Q3" s="98"/>
-      <c r="R3" s="98"/>
-      <c r="S3" s="98"/>
-      <c r="T3" s="98"/>
-      <c r="U3" s="98"/>
-      <c r="V3" s="98"/>
-      <c r="W3" s="98"/>
-      <c r="X3" s="98"/>
-      <c r="Y3" s="98"/>
-      <c r="Z3" s="98"/>
       <c r="AA3" s="31"/>
     </row>
     <row r="4" spans="1:27">
       <c r="A4" s="84" t="s">
+        <v>160</v>
+      </c>
+      <c r="H4" s="51" t="s">
         <v>161</v>
       </c>
-      <c r="H4" s="51" t="s">
-        <v>162</v>
-      </c>
-      <c r="I4" s="98"/>
-      <c r="J4" s="98"/>
-      <c r="K4" s="98"/>
-      <c r="L4" s="98"/>
-      <c r="M4" s="98"/>
-      <c r="N4" s="98"/>
-      <c r="O4" s="98"/>
-      <c r="P4" s="98"/>
-      <c r="Q4" s="98"/>
-      <c r="R4" s="98"/>
-      <c r="S4" s="98"/>
-      <c r="T4" s="98"/>
-      <c r="U4" s="98"/>
-      <c r="V4" s="98"/>
-      <c r="W4" s="98"/>
-      <c r="X4" s="98"/>
-      <c r="Y4" s="98"/>
-      <c r="Z4" s="98"/>
       <c r="AA4" s="31"/>
     </row>
     <row r="5" spans="1:27">
       <c r="A5" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="H5" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="H5" s="51" t="s">
-        <v>164</v>
-      </c>
-      <c r="I5" s="98"/>
-      <c r="J5" s="98"/>
-      <c r="K5" s="98"/>
-      <c r="L5" s="98"/>
-      <c r="M5" s="98"/>
-      <c r="N5" s="98"/>
-      <c r="O5" s="98"/>
-      <c r="P5" s="98"/>
-      <c r="Q5" s="98"/>
-      <c r="R5" s="98"/>
-      <c r="S5" s="98"/>
-      <c r="T5" s="98"/>
-      <c r="U5" s="98"/>
-      <c r="V5" s="98"/>
-      <c r="W5" s="98"/>
-      <c r="X5" s="98"/>
-      <c r="Y5" s="98"/>
-      <c r="Z5" s="98"/>
       <c r="AA5" s="31"/>
     </row>
     <row r="6" spans="1:27">
       <c r="A6" s="84" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H6" s="71"/>
-      <c r="I6" s="98"/>
-      <c r="J6" s="98"/>
-      <c r="K6" s="98"/>
-      <c r="L6" s="98"/>
-      <c r="M6" s="98"/>
-      <c r="N6" s="98"/>
-      <c r="O6" s="98"/>
-      <c r="P6" s="98"/>
-      <c r="Q6" s="98"/>
-      <c r="R6" s="98"/>
-      <c r="S6" s="98"/>
-      <c r="T6" s="98"/>
-      <c r="U6" s="98"/>
-      <c r="V6" s="98"/>
-      <c r="W6" s="98"/>
-      <c r="X6" s="98"/>
-      <c r="Y6" s="98"/>
-      <c r="Z6" s="98"/>
       <c r="AA6" s="31"/>
     </row>
     <row r="7" spans="1:27">
       <c r="A7" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="H7" s="71" t="s">
         <v>166</v>
       </c>
-      <c r="H7" s="71" t="s">
-        <v>167</v>
-      </c>
-      <c r="I7" s="98"/>
-      <c r="J7" s="98"/>
-      <c r="K7" s="98"/>
-      <c r="L7" s="98"/>
-      <c r="M7" s="98"/>
-      <c r="N7" s="98"/>
-      <c r="O7" s="98"/>
-      <c r="P7" s="98"/>
-      <c r="Q7" s="98"/>
-      <c r="R7" s="98"/>
-      <c r="S7" s="98"/>
-      <c r="T7" s="98"/>
-      <c r="U7" s="98"/>
-      <c r="V7" s="98"/>
-      <c r="W7" s="98"/>
-      <c r="X7" s="98"/>
-      <c r="Y7" s="98"/>
-      <c r="Z7" s="98"/>
       <c r="AA7" s="31"/>
     </row>
     <row r="8" spans="1:27">
       <c r="A8" s="84" t="s">
+        <v>167</v>
+      </c>
+      <c r="H8" s="71" t="s">
         <v>168</v>
       </c>
-      <c r="H8" s="71" t="s">
-        <v>169</v>
-      </c>
-      <c r="I8" s="98"/>
-      <c r="J8" s="98"/>
-      <c r="K8" s="98"/>
-      <c r="L8" s="98"/>
-      <c r="M8" s="98"/>
-      <c r="N8" s="98"/>
-      <c r="O8" s="98"/>
-      <c r="P8" s="98"/>
-      <c r="Q8" s="98"/>
-      <c r="R8" s="98"/>
-      <c r="S8" s="98"/>
-      <c r="T8" s="98"/>
-      <c r="U8" s="98"/>
-      <c r="V8" s="98"/>
-      <c r="W8" s="98"/>
-      <c r="X8" s="98"/>
-      <c r="Y8" s="98"/>
-      <c r="Z8" s="98"/>
       <c r="AA8" s="31"/>
     </row>
     <row r="9" spans="1:27">
       <c r="A9" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="H9" s="71" t="s">
         <v>170</v>
       </c>
-      <c r="H9" s="71" t="s">
-        <v>171</v>
-      </c>
-      <c r="I9" s="98"/>
-      <c r="J9" s="98"/>
-      <c r="K9" s="98"/>
-      <c r="L9" s="98"/>
-      <c r="M9" s="98"/>
-      <c r="N9" s="98"/>
-      <c r="O9" s="98"/>
-      <c r="P9" s="98"/>
-      <c r="Q9" s="98"/>
-      <c r="R9" s="98"/>
-      <c r="S9" s="98"/>
-      <c r="T9" s="98"/>
-      <c r="U9" s="98"/>
-      <c r="V9" s="98"/>
-      <c r="W9" s="98"/>
-      <c r="X9" s="98"/>
-      <c r="Y9" s="98"/>
-      <c r="Z9" s="98"/>
       <c r="AA9" s="31"/>
     </row>
     <row r="10" spans="1:27">
       <c r="A10" s="84" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H10" s="71"/>
-      <c r="I10" s="98"/>
-      <c r="J10" s="98"/>
-      <c r="K10" s="98"/>
-      <c r="L10" s="98"/>
-      <c r="M10" s="98"/>
-      <c r="N10" s="98"/>
-      <c r="O10" s="98"/>
-      <c r="P10" s="98"/>
-      <c r="Q10" s="98"/>
-      <c r="R10" s="98"/>
-      <c r="S10" s="98"/>
-      <c r="T10" s="98"/>
-      <c r="U10" s="98"/>
-      <c r="V10" s="98"/>
-      <c r="W10" s="98"/>
-      <c r="X10" s="98"/>
-      <c r="Y10" s="98"/>
-      <c r="Z10" s="98"/>
       <c r="AA10" s="31"/>
     </row>
     <row r="11" spans="1:27">
       <c r="A11" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="H11" s="71" t="s">
         <v>173</v>
       </c>
-      <c r="H11" s="71" t="s">
-        <v>174</v>
-      </c>
-      <c r="I11" s="98"/>
-      <c r="J11" s="98"/>
-      <c r="K11" s="98"/>
-      <c r="L11" s="98"/>
-      <c r="M11" s="98"/>
-      <c r="N11" s="98"/>
-      <c r="O11" s="98"/>
-      <c r="P11" s="98"/>
-      <c r="Q11" s="98"/>
-      <c r="R11" s="98"/>
-      <c r="S11" s="98"/>
-      <c r="T11" s="98"/>
-      <c r="U11" s="98"/>
-      <c r="V11" s="98"/>
-      <c r="W11" s="98"/>
-      <c r="X11" s="98"/>
-      <c r="Y11" s="98"/>
-      <c r="Z11" s="98"/>
       <c r="AA11" s="31"/>
     </row>
     <row r="12" spans="1:27">
       <c r="A12" s="84" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H12" s="71"/>
-      <c r="I12" s="98"/>
-      <c r="J12" s="98"/>
-      <c r="K12" s="98"/>
-      <c r="L12" s="98"/>
-      <c r="M12" s="98"/>
-      <c r="N12" s="98"/>
-      <c r="O12" s="98"/>
-      <c r="P12" s="98"/>
-      <c r="Q12" s="98"/>
-      <c r="R12" s="98"/>
-      <c r="S12" s="98"/>
-      <c r="T12" s="98"/>
-      <c r="U12" s="98"/>
-      <c r="V12" s="98"/>
-      <c r="W12" s="98"/>
-      <c r="X12" s="98"/>
-      <c r="Y12" s="98"/>
-      <c r="Z12" s="98"/>
       <c r="AA12" s="31"/>
     </row>
     <row r="13" spans="1:27">
       <c r="A13" s="13" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H13" s="72" t="s">
-        <v>157</v>
-      </c>
-      <c r="I13" s="98"/>
-      <c r="J13" s="98"/>
-      <c r="K13" s="98"/>
-      <c r="L13" s="98"/>
-      <c r="M13" s="98"/>
-      <c r="N13" s="98"/>
-      <c r="O13" s="98"/>
-      <c r="P13" s="98"/>
-      <c r="Q13" s="98"/>
-      <c r="R13" s="98"/>
-      <c r="S13" s="98"/>
-      <c r="T13" s="98"/>
-      <c r="U13" s="98"/>
-      <c r="V13" s="98"/>
-      <c r="W13" s="98"/>
-      <c r="X13" s="98"/>
-      <c r="Y13" s="98"/>
-      <c r="Z13" s="98"/>
+        <v>156</v>
+      </c>
       <c r="AA13" s="31"/>
     </row>
     <row r="14" spans="1:27">
       <c r="A14" s="84" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H14" s="72" t="s">
-        <v>177</v>
-      </c>
-      <c r="I14" s="98"/>
-      <c r="J14" s="98"/>
-      <c r="K14" s="98"/>
-      <c r="L14" s="98"/>
-      <c r="M14" s="98"/>
-      <c r="N14" s="98"/>
-      <c r="O14" s="98"/>
-      <c r="P14" s="98"/>
-      <c r="Q14" s="98"/>
-      <c r="R14" s="98"/>
-      <c r="S14" s="98"/>
-      <c r="T14" s="98"/>
-      <c r="U14" s="98"/>
-      <c r="V14" s="98"/>
-      <c r="W14" s="98"/>
-      <c r="X14" s="98"/>
-      <c r="Y14" s="98"/>
-      <c r="Z14" s="98"/>
+        <v>176</v>
+      </c>
       <c r="AA14" s="31"/>
     </row>
     <row r="15" spans="1:27">
       <c r="A15" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H15" s="73" t="s">
-        <v>178</v>
-      </c>
-      <c r="I15" s="98"/>
-      <c r="J15" s="98"/>
-      <c r="K15" s="98"/>
-      <c r="L15" s="98"/>
-      <c r="M15" s="98"/>
-      <c r="N15" s="98"/>
-      <c r="O15" s="98"/>
-      <c r="P15" s="98"/>
-      <c r="Q15" s="98"/>
-      <c r="R15" s="98"/>
-      <c r="S15" s="98"/>
-      <c r="T15" s="98"/>
-      <c r="U15" s="98"/>
-      <c r="V15" s="98"/>
-      <c r="W15" s="98"/>
-      <c r="X15" s="98"/>
-      <c r="Y15" s="98"/>
-      <c r="Z15" s="98"/>
+        <v>177</v>
+      </c>
       <c r="AA15" s="31"/>
     </row>
     <row r="16" spans="1:27" ht="17.25" customHeight="1">
       <c r="A16" s="84" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H16" s="73" t="s">
-        <v>179</v>
-      </c>
-      <c r="I16" s="98"/>
-      <c r="J16" s="98"/>
-      <c r="K16" s="98"/>
-      <c r="L16" s="98"/>
-      <c r="M16" s="98"/>
-      <c r="N16" s="98"/>
-      <c r="O16" s="98"/>
-      <c r="P16" s="98"/>
-      <c r="Q16" s="98"/>
-      <c r="R16" s="98"/>
-      <c r="S16" s="98"/>
-      <c r="T16" s="98"/>
-      <c r="U16" s="98"/>
-      <c r="V16" s="98"/>
-      <c r="W16" s="98"/>
-      <c r="X16" s="98"/>
-      <c r="Y16" s="98"/>
-      <c r="Z16" s="98"/>
+        <v>178</v>
+      </c>
       <c r="AA16" s="31"/>
     </row>
     <row r="17" spans="1:27">
       <c r="A17" s="13" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H17" s="73"/>
-      <c r="I17" s="98"/>
-      <c r="J17" s="98"/>
-      <c r="K17" s="98"/>
-      <c r="L17" s="98"/>
-      <c r="M17" s="98"/>
-      <c r="N17" s="98"/>
-      <c r="O17" s="98"/>
-      <c r="P17" s="98"/>
-      <c r="Q17" s="98"/>
-      <c r="R17" s="98"/>
-      <c r="S17" s="98"/>
-      <c r="T17" s="98"/>
-      <c r="U17" s="98"/>
-      <c r="V17" s="98"/>
-      <c r="W17" s="98"/>
-      <c r="X17" s="98"/>
-      <c r="Y17" s="98"/>
-      <c r="Z17" s="98"/>
       <c r="AA17" s="31"/>
     </row>
     <row r="18" spans="1:27" ht="17.25" thickBot="1">
       <c r="A18" s="84" t="s">
-        <v>258</v>
-      </c>
-      <c r="H18" s="99" t="s">
-        <v>295</v>
+        <v>257</v>
+      </c>
+      <c r="H18" s="95" t="s">
+        <v>294</v>
       </c>
       <c r="I18" s="35"/>
       <c r="J18" s="35"/>
@@ -4062,25 +3792,25 @@
     </row>
     <row r="19" spans="1:27">
       <c r="A19" s="13" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="1:27">
       <c r="A20" s="84" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="1:27">
       <c r="A21" s="13" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="1:27">
       <c r="A22" s="84" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H22" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I22" s="64"/>
       <c r="J22" s="64"/>
@@ -4091,7 +3821,7 @@
     </row>
     <row r="23" spans="1:27">
       <c r="A23" s="13" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H23" s="85"/>
       <c r="I23" s="64"/>
@@ -4103,10 +3833,10 @@
     </row>
     <row r="24" spans="1:27">
       <c r="A24" s="84" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H24" s="86" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I24" s="64"/>
       <c r="J24" s="64"/>
@@ -4117,7 +3847,7 @@
     </row>
     <row r="25" spans="1:27">
       <c r="A25" s="13" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H25" s="87"/>
       <c r="I25" s="64"/>
@@ -4129,10 +3859,10 @@
     </row>
     <row r="26" spans="1:27">
       <c r="A26" s="84" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H26" s="86" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I26" s="64"/>
       <c r="J26" s="64"/>
@@ -4143,7 +3873,7 @@
     </row>
     <row r="27" spans="1:27">
       <c r="A27" s="13" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H27" s="87"/>
       <c r="I27" s="64"/>
@@ -4155,10 +3885,10 @@
     </row>
     <row r="28" spans="1:27">
       <c r="A28" s="84" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H28" s="86" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I28" s="64"/>
       <c r="J28" s="64"/>
@@ -4169,7 +3899,7 @@
     </row>
     <row r="29" spans="1:27">
       <c r="A29" s="13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H29" s="87"/>
       <c r="I29" s="64"/>
@@ -4181,10 +3911,10 @@
     </row>
     <row r="30" spans="1:27">
       <c r="A30" s="84" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H30" s="86" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I30" s="64"/>
       <c r="J30" s="64"/>
@@ -4195,7 +3925,7 @@
     </row>
     <row r="31" spans="1:27">
       <c r="A31" s="84" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H31" s="87"/>
       <c r="I31" s="64"/>
@@ -4207,10 +3937,10 @@
     </row>
     <row r="32" spans="1:27">
       <c r="A32" s="13" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H32" s="86" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I32" s="64"/>
       <c r="J32" s="64"/>
@@ -4221,7 +3951,7 @@
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="84" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H33" s="87"/>
       <c r="I33" s="64"/>
@@ -4233,10 +3963,10 @@
     </row>
     <row r="34" spans="1:14">
       <c r="A34" s="13" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H34" s="86" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I34" s="64"/>
       <c r="J34" s="64"/>
@@ -4247,90 +3977,90 @@
     </row>
     <row r="35" spans="1:14">
       <c r="A35" s="84" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" s="13" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H36" s="23" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" s="84" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" s="13" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="39" spans="1:14">
       <c r="A39" s="84" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="84" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="84" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="84" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="13" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="84" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="13" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="84" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="13" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="13" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
   </sheetData>
@@ -4351,10 +4081,10 @@
   <sheetData>
     <row r="1" spans="1:19" ht="17.25" customHeight="1" thickBot="1">
       <c r="A1" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>181</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="2" spans="1:19">
@@ -4382,7 +4112,7 @@
       <c r="A3" s="12"/>
       <c r="B3" s="4"/>
       <c r="E3" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="S3" s="31"/>
     </row>
@@ -4396,7 +4126,7 @@
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="E5" s="68" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S5" s="31"/>
     </row>
@@ -4410,7 +4140,7 @@
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="E7" s="68" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="S7" s="31"/>
     </row>
@@ -4418,7 +4148,7 @@
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="E8" s="68" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="S8" s="31"/>
     </row>
@@ -4426,7 +4156,7 @@
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="E9" s="69" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="S9" s="31"/>
     </row>
@@ -4440,7 +4170,7 @@
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="E11" s="68" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="S11" s="31"/>
     </row>
@@ -4448,7 +4178,7 @@
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="E12" s="68" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="S12" s="31"/>
     </row>
@@ -4456,7 +4186,7 @@
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="E13" s="68" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="S13" s="31"/>
     </row>
@@ -4464,7 +4194,7 @@
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="E14" s="69" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="S14" s="31"/>
     </row>
@@ -4478,19 +4208,19 @@
     </row>
     <row r="17" spans="5:19">
       <c r="E17" s="68" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="S17" s="31"/>
     </row>
     <row r="18" spans="5:19">
       <c r="E18" s="68" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="S18" s="31"/>
     </row>
     <row r="19" spans="5:19" ht="17.25" customHeight="1" thickBot="1">
       <c r="E19" s="70" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F19" s="35"/>
       <c r="G19" s="35"/>
@@ -4526,13 +4256,13 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>196</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -4554,7 +4284,7 @@
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
       <c r="F3" s="11" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4958,7 +4688,7 @@
   <sheetData>
     <row r="1" spans="1:45" ht="17.25" customHeight="1">
       <c r="A1" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B1" s="5">
         <v>1</v>
@@ -5096,7 +4826,7 @@
       <c r="AF2" s="7"/>
       <c r="AG2" s="6"/>
       <c r="AH2" s="76" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AI2" s="74"/>
       <c r="AJ2" s="74"/>
@@ -5148,7 +4878,7 @@
       <c r="AF3" s="7"/>
       <c r="AG3" s="6"/>
       <c r="AH3" s="77" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AI3" s="74"/>
       <c r="AJ3" s="74"/>
@@ -5200,7 +4930,7 @@
       <c r="AF4" s="7"/>
       <c r="AG4" s="6"/>
       <c r="AH4" s="77" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AI4" s="74"/>
       <c r="AJ4" s="74"/>
@@ -5302,7 +5032,7 @@
       <c r="AF6" s="7"/>
       <c r="AG6" s="6"/>
       <c r="AH6" s="76" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AI6" s="74"/>
       <c r="AJ6" s="74"/>
@@ -5354,7 +5084,7 @@
       <c r="AF7" s="7"/>
       <c r="AG7" s="6"/>
       <c r="AH7" s="77" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AI7" s="74"/>
       <c r="AJ7" s="74"/>
@@ -5456,7 +5186,7 @@
       <c r="AF9" s="7"/>
       <c r="AG9" s="6"/>
       <c r="AH9" s="76" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AI9" s="74"/>
       <c r="AJ9" s="74"/>
@@ -5508,7 +5238,7 @@
       <c r="AF10" s="7"/>
       <c r="AG10" s="6"/>
       <c r="AH10" s="77" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AI10" s="74"/>
       <c r="AJ10" s="74"/>
@@ -5610,7 +5340,7 @@
       <c r="AF12" s="7"/>
       <c r="AG12" s="6"/>
       <c r="AH12" s="77" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AI12" s="74"/>
       <c r="AJ12" s="74"/>
@@ -5662,7 +5392,7 @@
       <c r="AF13" s="7"/>
       <c r="AG13" s="6"/>
       <c r="AH13" s="78" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AI13" s="74"/>
       <c r="AJ13" s="74"/>
@@ -5713,7 +5443,7 @@
       <c r="AE14" s="7"/>
       <c r="AF14" s="7"/>
       <c r="AH14" s="78" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AI14" s="74"/>
       <c r="AJ14" s="74"/>
@@ -7117,7 +6847,7 @@
   <sheetData>
     <row r="1" spans="1:42">
       <c r="A1" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B1" s="5">
         <v>1</v>
@@ -7329,7 +7059,7 @@
       <c r="AF4" s="7"/>
       <c r="AG4" s="6"/>
       <c r="AH4" s="65" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AI4" s="80"/>
       <c r="AJ4" s="80"/>
@@ -7425,7 +7155,7 @@
       <c r="AF6" s="7"/>
       <c r="AG6" s="6"/>
       <c r="AH6" s="79" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AI6" s="80"/>
       <c r="AJ6" s="80"/>
@@ -7521,7 +7251,7 @@
       <c r="AF8" s="7"/>
       <c r="AG8" s="6"/>
       <c r="AH8" s="65" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AI8" s="80"/>
       <c r="AJ8" s="80"/>
@@ -7617,7 +7347,7 @@
       <c r="AF10" s="7"/>
       <c r="AG10" s="6"/>
       <c r="AH10" s="82" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AI10" s="80"/>
       <c r="AJ10" s="80"/>
@@ -9165,22 +8895,22 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B1" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="C1" s="14" t="s">
         <v>213</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="D1" s="14" t="s">
         <v>214</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="E1" s="14" t="s">
         <v>215</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="F1" s="14" t="s">
         <v>216</v>
-      </c>
-      <c r="F1" s="14" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="2" spans="1:17">
@@ -9205,7 +8935,7 @@
         <v>간호사2</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K3" s="11"/>
       <c r="L3" s="11"/>
@@ -9221,7 +8951,7 @@
         <v>간호사3</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -9523,147 +9253,147 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42">
-      <c r="A1" s="97" t="s">
-        <v>220</v>
-      </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
-      <c r="G1" s="96"/>
-      <c r="H1" s="96"/>
-      <c r="I1" s="96"/>
-      <c r="J1" s="96"/>
-      <c r="K1" s="96"/>
-      <c r="L1" s="96"/>
-      <c r="M1" s="96"/>
-      <c r="N1" s="96"/>
-      <c r="O1" s="96"/>
-      <c r="P1" s="96"/>
-      <c r="Q1" s="96"/>
-      <c r="R1" s="96"/>
-      <c r="S1" s="96"/>
-      <c r="T1" s="96"/>
-      <c r="U1" s="96"/>
-      <c r="V1" s="96"/>
-      <c r="W1" s="96"/>
-      <c r="X1" s="96"/>
-      <c r="Y1" s="96"/>
-      <c r="Z1" s="96"/>
-      <c r="AA1" s="96"/>
-      <c r="AB1" s="96"/>
-      <c r="AC1" s="96"/>
-      <c r="AD1" s="96"/>
-      <c r="AE1" s="96"/>
-      <c r="AF1" s="96"/>
-      <c r="AG1" s="96"/>
-      <c r="AH1" s="96"/>
-      <c r="AI1" s="96"/>
-      <c r="AJ1" s="96"/>
-      <c r="AK1" s="96"/>
-      <c r="AL1" s="96"/>
-      <c r="AM1" s="96"/>
-      <c r="AN1" s="96"/>
-      <c r="AO1" s="96"/>
-      <c r="AP1" s="96"/>
+      <c r="A1" s="98" t="s">
+        <v>219</v>
+      </c>
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
+      <c r="G1" s="97"/>
+      <c r="H1" s="97"/>
+      <c r="I1" s="97"/>
+      <c r="J1" s="97"/>
+      <c r="K1" s="97"/>
+      <c r="L1" s="97"/>
+      <c r="M1" s="97"/>
+      <c r="N1" s="97"/>
+      <c r="O1" s="97"/>
+      <c r="P1" s="97"/>
+      <c r="Q1" s="97"/>
+      <c r="R1" s="97"/>
+      <c r="S1" s="97"/>
+      <c r="T1" s="97"/>
+      <c r="U1" s="97"/>
+      <c r="V1" s="97"/>
+      <c r="W1" s="97"/>
+      <c r="X1" s="97"/>
+      <c r="Y1" s="97"/>
+      <c r="Z1" s="97"/>
+      <c r="AA1" s="97"/>
+      <c r="AB1" s="97"/>
+      <c r="AC1" s="97"/>
+      <c r="AD1" s="97"/>
+      <c r="AE1" s="97"/>
+      <c r="AF1" s="97"/>
+      <c r="AG1" s="97"/>
+      <c r="AH1" s="97"/>
+      <c r="AI1" s="97"/>
+      <c r="AJ1" s="97"/>
+      <c r="AK1" s="97"/>
+      <c r="AL1" s="97"/>
+      <c r="AM1" s="97"/>
+      <c r="AN1" s="97"/>
+      <c r="AO1" s="97"/>
+      <c r="AP1" s="97"/>
     </row>
     <row r="2" spans="1:42">
       <c r="A2" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="C2" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>223</v>
-      </c>
       <c r="D2" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H2" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="J2" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="K2" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="J2" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>223</v>
-      </c>
       <c r="L2" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="O2" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q2" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="P2" s="6" t="s">
+      <c r="R2" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="Q2" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="R2" s="6" t="s">
-        <v>223</v>
-      </c>
       <c r="S2" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="T2" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="U2" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="V2" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="W2" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="X2" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="W2" s="6" t="s">
+      <c r="Y2" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="X2" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="Y2" s="6" t="s">
-        <v>223</v>
-      </c>
       <c r="Z2" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AA2" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AB2" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AC2" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="AD2" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="AE2" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="AD2" s="6" t="s">
+      <c r="AF2" s="6" t="s">
         <v>222</v>
-      </c>
-      <c r="AE2" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="AF2" s="6" t="s">
-        <v>223</v>
       </c>
       <c r="AG2" s="6"/>
       <c r="AH2" s="6"/>
@@ -9678,7 +9408,7 @@
     </row>
     <row r="3" spans="1:42">
       <c r="A3" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B3" s="5">
         <v>1</v>
@@ -9774,169 +9504,169 @@
         <v>31</v>
       </c>
       <c r="AG3" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="AH3" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="AH3" s="5" t="s">
+      <c r="AI3" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="AI3" s="5" t="s">
+      <c r="AJ3" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="AJ3" s="5" t="s">
+      <c r="AK3" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="AK3" s="5" t="s">
+      <c r="AL3" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="AL3" s="5" t="s">
+      <c r="AM3" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="AM3" s="5" t="s">
+      <c r="AN3" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="AN3" s="5" t="s">
+      <c r="AO3" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="AO3" s="5" t="s">
+      <c r="AP3" s="5" t="s">
         <v>232</v>
-      </c>
-      <c r="AP3" s="5" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="4" spans="1:42">
       <c r="A4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:42">
       <c r="A5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" spans="1:42">
       <c r="A6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="7" spans="1:42">
       <c r="A7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8" spans="1:42">
       <c r="A8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" spans="1:42">
       <c r="A9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10" spans="1:42">
       <c r="A10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11" spans="1:42">
       <c r="A11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" spans="1:42">
       <c r="A12" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13" spans="1:42">
       <c r="A13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14" spans="1:42">
       <c r="A14" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="15" spans="1:42">
       <c r="A15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="16" spans="1:42">
       <c r="A16" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
   </sheetData>

--- a/nurse_scheduler_complete.xlsx
+++ b/nurse_scheduler_complete.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\송민영\Desktop\근무표 프로그램\완전판\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{988B63CA-DCF1-45ED-B373-E8489EFFC8DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A23F60A1-C94D-4FC1-BFE8-53499D4C5E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3154,7 +3154,7 @@
         <v>37</v>
       </c>
       <c r="B23" s="47">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="C23" s="46" t="s">
         <v>38</v>
@@ -3166,7 +3166,7 @@
         <v>39</v>
       </c>
       <c r="B24" s="47">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>40</v>
@@ -3178,7 +3178,7 @@
         <v>41</v>
       </c>
       <c r="B25" s="47">
-        <v>10</v>
+        <v>10000</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>42</v>
@@ -3190,7 +3190,7 @@
         <v>43</v>
       </c>
       <c r="B26" s="47">
-        <v>10</v>
+        <v>8000</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>44</v>
@@ -3202,7 +3202,7 @@
         <v>45</v>
       </c>
       <c r="B27" s="49">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="C27" s="10" t="s">
         <v>46</v>
@@ -3214,7 +3214,7 @@
         <v>47</v>
       </c>
       <c r="B28" s="49">
-        <v>10</v>
+        <v>8000</v>
       </c>
       <c r="C28" s="10" t="s">
         <v>48</v>
@@ -3226,7 +3226,7 @@
         <v>49</v>
       </c>
       <c r="B29" s="47">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>50</v>

--- a/nurse_scheduler_complete.xlsx
+++ b/nurse_scheduler_complete.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\송민영\Desktop\근무표 프로그램\완전판\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\송민영\Desktop\근무표 프로그램\완전판 파이썬 필요없음\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A23F60A1-C94D-4FC1-BFE8-53499D4C5E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D68814B6-DE7F-47A7-87C6-567887E65226}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="설명서" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,322 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="294">
+  <si>
+    <t>Nurse Name</t>
+  </si>
+  <si>
+    <t>D-5</t>
+  </si>
+  <si>
+    <t>D-4</t>
+  </si>
+  <si>
+    <t>D-3</t>
+  </si>
+  <si>
+    <t>D-2</t>
+  </si>
+  <si>
+    <t>D-1</t>
+  </si>
+  <si>
+    <t>설명</t>
+  </si>
+  <si>
+    <t>전 달 마지막 5일의 듀티를 작성합니다. 프로그램이 전 달 마지막 근무 5일을 규칙에 반영합니다</t>
+  </si>
+  <si>
+    <t>D, E, N, M, O 중 하나를 적습니다. (칸을 비워두시면 무조건 오프(O)로 간주합니다.)</t>
+  </si>
+  <si>
+    <t>🏥 [근무표 자동화 스케줄러 사용 설명서]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">만든사람: </t>
+  </si>
+  <si>
+    <t>동남보건대 간호학과 21학번 송민영</t>
+  </si>
+  <si>
+    <t>성균관대 기계공학부 20학번 김정진</t>
+  </si>
+  <si>
+    <t>간호관리학 실습 중 급하게 제작한 프로그램입니다. 부족한 점이 많습니다 (마지막 수정 2026/03/30)</t>
+  </si>
+  <si>
+    <t>마음껏 사용해주시고 피드백, 원하는 기능, 수정해야할 점, 오류 등 알려주시면 감사하겠습니다. (alex0840@naver.com)</t>
+  </si>
+  <si>
+    <t>본 프로그램은 간호사들의 수면권 보장, 공평한 근무 배분, 그리고 병동의 안전한 운영을 위해 AI(구글 최적화 알고리즘)가 수백만 번의 계산을 거쳐 최적의 근무표를 짜주는 스마트 스케줄러입니다.</t>
+  </si>
+  <si>
+    <t>🚫 제 1장. 절대 불변의 기본 규칙 (자동 적용)</t>
+  </si>
+  <si>
+    <t>이 규칙들은 간호사의 건강과 병동 안전을 위해 컴퓨터가 절대적으로 지키도록 설계된 '수정 불가능한' 뼈대 규칙입니다.</t>
+  </si>
+  <si>
+    <t>1. 수면권 및 바이오리듬 보장 (최악의 듀티 차단)</t>
+  </si>
+  <si>
+    <t>E ➔ D 금지: 이브닝 후 데이 출근 절대 금지</t>
+  </si>
+  <si>
+    <t>M ➔ D, E ➔ M 금지: 미들(M) 근무 전후의 무리한 교대 금지</t>
+  </si>
+  <si>
+    <t>N ➔ O ➔ D 금지: 나이트 후 하루 쉬고 데이 출근 절대 금지</t>
+  </si>
+  <si>
+    <t>N ➔ O ➔ N 억제: 나이트 후 하루(또는 며칠) 쉬고 완충 듀티 없이 다시 나이트 출근 억제 (월초/월말 나이트 몰림 방지)</t>
+  </si>
+  <si>
+    <t>O ➔ W ➔ O (퐁당퐁당) 금지: 오프 후 하루만 일하고 다시 오프를 부여하는 징검다리 근무 원천 차단</t>
+  </si>
+  <si>
+    <t>2. 환자 안전 및 병동 운영 보장</t>
+  </si>
+  <si>
+    <t>듀티별 필수 경력자(Charge) 배치: 모든 날짜의 D, E, N, M 근무에는 반드시 '차지 권한'이 있는 경력 간호사가 최소 1명 이상 배치됨. (신규들로만 구성된 듀티 발생 불가)</t>
+  </si>
+  <si>
+    <t>3. 나이트 전담(Night Keep) 특수 보호</t>
+  </si>
+  <si>
+    <t>데이(D), 이브닝(E), 미들(M) 근무 절대 배정 안 됨.</t>
+  </si>
+  <si>
+    <t>한 달에 정확히 15개의 나이트(N)만 배정되며 나머지는 올 오프(O).</t>
+  </si>
+  <si>
+    <t>단, 연속 나이트 횟수나 휴식일은 일반 간호사와 똑같이 엑셀(Setup) 규칙을 따름.</t>
+  </si>
+  <si>
+    <t>4. 스마트 공평성 유지</t>
+  </si>
+  <si>
+    <t>경력자는 경력자끼리, 일반/신규는 일반/신규끼리 총 근무 수, 나이트 수, 데이/이브닝 수, 주말 근무 수가 최대한 똑같아지도록 컴퓨터가 알아서 분배함.</t>
+  </si>
+  <si>
+    <t>✏️ 제 2장. 스케줄 세팅 방법 (엑셀 입력란)</t>
+  </si>
+  <si>
+    <t>엑셀의 각 시트(Sheet)에 정보를 입력하여 병동 상황에 맞게 스케줄을 조종할 수 있습니다.</t>
+  </si>
+  <si>
+    <t>1️⃣ [Setup] 시트 (기본 설정)</t>
+  </si>
+  <si>
+    <t>Year / Month: 근무표를 짤 연도와 월</t>
+  </si>
+  <si>
+    <t>이번 달 기본 오프: 이번 달 공휴일을 포함한 기본 오프 개수 (이 개수를 넘어서 쉬는 날은 스케줄표에 S로 표시됨)</t>
+  </si>
+  <si>
+    <t>Weekday / Weekend Req: 평일 및 주말/공휴일의 듀티별(D, E, N, M) 필요 인원수</t>
+  </si>
+  <si>
+    <t>Max consecutive ~ : 최대 연속 출근 일수, 최대 연속 D/E 일수</t>
+  </si>
+  <si>
+    <t>Max / Min consecutive night days: 나이트 최대 / 최소 연속 일수</t>
+  </si>
+  <si>
+    <t>Off days after a night block: 나이트 근무가 끝난 뒤 반드시 며칠을 쉬게 할 것인지 설정 (통상 2일)</t>
+  </si>
+  <si>
+    <t>2️⃣ [Nurses] 시트 (간호사 명단 및 권한) ★가장 중요★</t>
+  </si>
+  <si>
+    <t>Nurse Name: 간호사 이름 (모든 시트의 이름 순서는 동일해야 함)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">경력(Y/N) [차지 권한 부여]: 원하는 듀티에만 차지를 부여할 수 있습니다. </t>
+  </si>
+  <si>
+    <t>D차지 ➔ 데이 때만 경력직으로 인정</t>
+  </si>
+  <si>
+    <t>E차지 ➔ 이브닝 때만 경력직으로 인정</t>
+  </si>
+  <si>
+    <t>N차지 ➔ 나이트 때만 경력직으로 인정 (데이/이브 때는 일반 간호사 취급)</t>
+  </si>
+  <si>
+    <t>D, E 차지 또는 D/E차지 ➔ 데이와 이브닝 둘 다 경력직 인정</t>
+  </si>
+  <si>
+    <t>데이, 이브닝 차지 ➔ 한글로 적어도 알파벳과 똑같이 알아듣습니다!</t>
+  </si>
+  <si>
+    <t>Y ➔ 모든 듀티에서 경력직으로 완전 인정</t>
+  </si>
+  <si>
+    <t>최대 오프 개수: 각 간호사의 남은 연차 등을 고려해 이번 달 최대 쉴 수 있는 개수 기입 (비워두면 무제한 허용)</t>
+  </si>
+  <si>
+    <t>나이트전담(Y/N): 나이트 전담 선생님만 Y 기입</t>
+  </si>
+  <si>
+    <t>비고 (E열): 신규 간호사 프리셉터 매칭 기능</t>
+  </si>
+  <si>
+    <t>신규 선생님의 E열에 프리셉터 선생님 이름(예: 이선희)을 적으면, 프리셉터가 출근하는 날짜와 듀티에만 신규 간호사가 똑같이 출근하게 됩니다.</t>
+  </si>
+  <si>
+    <t>3️⃣ [Holidays] 시트 (휴일 및 특수 인원 추가)</t>
+  </si>
+  <si>
+    <t>날짜 지정: 주말 외에 달력상 빨간 날을 지정합니다.</t>
+  </si>
+  <si>
+    <t>Optional Note [특정 날짜 인원 마음대로 추가하기]:</t>
+  </si>
+  <si>
+    <t>명절이나 유독 바쁜 평일에 인원을 임시로 더 넣고 싶을 때 사용합니다.</t>
+  </si>
+  <si>
+    <t>D2 ➔ 데이 2명 추가 배치</t>
+  </si>
+  <si>
+    <t>D1, E1 ➔ 데이 1명, 이브닝 1명 추가 배치</t>
+  </si>
+  <si>
+    <t>M ➔ 미들 1명 추가 배치</t>
+  </si>
+  <si>
+    <t>숫자 없이 알파벳만 쓰면 자동으로 1명 추가로 인식합니다.</t>
+  </si>
+  <si>
+    <t>4️⃣ [ShiftPreferences] 시트 (선호 듀티 신청)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  선생님들이 원하는 근무를 신청하는 곳입니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  다중 선택 기능: "데이나 이브닝 아무거나 줘!"가 가능합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  엑셀 칸에 E or D, E, D, E/D 라고 자유롭게 적으면, 컴퓨터가 알아서 둘 중 하나를 찰떡같이 배정해 줍니다.</t>
+  </si>
+  <si>
+    <t>5️⃣ 기타 시트</t>
+  </si>
+  <si>
+    <t>[OffRequests]: 무조건 쉬어야 하는 날(신청 오프). O, OFF, 1 등으로 표시.</t>
+  </si>
+  <si>
+    <t>[Restrictions]: 이번 달에 나이트를 아예 하면 안 되는 선생님(임산부, 진단서 등)은 Y로 체크.</t>
+  </si>
+  <si>
+    <t>[PrevMonth] (전월 근무 이월): 지난달 마지막 5일의 듀티를 적어두면, 연속 근무 횟수와 나이트 휴식 조건이 이번 달 1일로 완벽하게 이월되어 계산됩니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   [Validation, DailyCoverage] : 프로그램이 규칙에 맞게 듀티가 배분되었는지 자동 확인하는 시트입니다. 신경 안써도 됩니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  [RequestsSummary]: 신청 듀티, 신청 오프가 반려 되었을때의 내용이 자동으로 적힙니다.</t>
+  </si>
+  <si>
+    <t>🚨 제 3장. 에러 방지 주의사항 (필독!)</t>
+  </si>
+  <si>
+    <t>1. 날짜 띄어쓰기 절대 금지 (Holidays 시트): * A열의 날짜칸(YYYY-MM-DD)에 스페이스바(빈칸)가 들어가면 컴퓨터가 날짜로 인식하지 못해 에러가 납니다.</t>
+  </si>
+  <si>
+    <t>2. 이름(오타) 통일:</t>
+  </si>
+  <si>
+    <t>Nurses 시트에 적힌 이름과 OffRequests, ShiftPreferences 등 간호사 이름이 들어간 모든 시트의 이름과 순서가 반드시 일치해야 합니다. (간호사 퇴사/입사로 인원을 수정할 때는 세 시트 모두 똑같이 수정해 주세요. 자동 반영 되는데 간호사 순서 밀림에 주의해주세요)</t>
+  </si>
+  <si>
+    <t>3. 불가능한 조건 조심:</t>
+  </si>
+  <si>
+    <t>"모두가 1일에 오프를 원한다"거나, "필요 인원은 10명인데 5명이 휴가를 갔다"는 등 수학적으로 도저히 불가능한 상황에서는 컴퓨터가 INFEASIBLE(충돌) 에러를 띄웁니다. 이때는 인원수나 오프 신청을 살짝 조율해 주셔야 합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4. 시트의 이름, 입력란 외 이름, 입력란의 행과 열을 바꾸면 프로그램이 인식하지 못합니다!</t>
+  </si>
+  <si>
+    <t>(스케줄 작성 완료 후 엑셀을 저장 후 종료한 뒤에 .exe 파일을 더블클릭하시면 됩니다!)</t>
+  </si>
+  <si>
+    <t>액셀 파일과 실행 exe 파일을 한 폴더안에 넣어야 작동이 됩니다! 엑셀과 프로그램 파일 이름을 바꾸지 마세요!</t>
+  </si>
+  <si>
+    <t>프로그램창 (CMD) 해석</t>
+  </si>
+  <si>
+    <t>근무표 작성이 완료되면 까만 창 맨 아래에 두 줄의 영어 메시지가 뜹니다. 이것은 AI(인공지능)가 스케줄을 짜면서 겪은 과정과 결과물의 점수를 알려주는 보고서입니다.</t>
+  </si>
+  <si>
+    <t>1️⃣ Solver status (컴퓨터의 최종 상태 보고)</t>
+  </si>
+  <si>
+    <t>컴퓨터가 근무표를 성공적으로 완성했는지, 아니면 규칙이 너무 빡빡해서 실패했는지를 알려줍니다.</t>
+  </si>
+  <si>
+    <t>OPTIMAL (가장 이상적!)</t>
+  </si>
+  <si>
+    <t>의미: 주어진 조건 안에서 수학적으로 가장 완벽하고 공평한 1등 스케줄을 찾아냈습니다</t>
+  </si>
+  <si>
+    <t>상태: 안심하고 엑셀 근무표를 확인하시면 됩니다.</t>
+  </si>
+  <si>
+    <t>FEASIBLE (쓸만한 스케줄 완성)</t>
+  </si>
+  <si>
+    <t>의미: 100점짜리 정답인지는 확신할 수 없지만, 모든 절대 규칙(Hard)을 완벽하게 지킨 스케줄을 일단 완성했습니다</t>
+  </si>
+  <si>
+    <t>상태: 엑셀 근무표를 그대로 사용하셔도 무방합니다. (더 완벽한 결과를 원하시면 Setup 시트의 시간을 늘리고 다시 돌려보세요.)</t>
+  </si>
+  <si>
+    <t>INFEASIBLE (작성 실패 - 규칙 충돌) 🚨</t>
+  </si>
+  <si>
+    <t>의미: 스케줄을 짤 수가 없습니다! 조건들이 서로 모순됩니다</t>
+  </si>
+  <si>
+    <t>상태: 근무표 작성에 실패하여 엑셀이 업데이트되지 않습니다. (주로 1순위 오프가 너무 많거나, 출근할 인원이 부족할 때 발생합니다. 인원이나 오프를 수정하고 다시 돌려주세요.)</t>
+  </si>
+  <si>
+    <t>UNKNOWN (작성 실패 - 시간 초과) 🚨</t>
+  </si>
+  <si>
+    <t>의미: 규칙이 너무 복잡해서 제한 시간 안에 단 한 개의 스케줄도 완성하지 못했습니다.</t>
+  </si>
+  <si>
+    <t>상태: Setup 시트의 Solver time limit (sec) 시간을 600초 이상으로 넉넉히 늘리거나, 연속 근무 제한을 살짝 풀어주세요.</t>
+  </si>
+  <si>
+    <t>2️⃣ Objective value (AI의 스케줄 채점표 / 벌점)</t>
+  </si>
+  <si>
+    <t>의미: 이 숫자는 인공지능이 스케줄을 짜면서 받은 벌점(Penalty)의 총합입니다.</t>
+  </si>
+  <si>
+    <t>해석 방법: "숫자가 낮을수록(0에 가까울수록) 훌륭한 근무표입니다!"</t>
+  </si>
+  <si>
+    <t>컴퓨터는 무조건 이 벌점을 낮추기 위해 수백만 번의 경우의 수를 계산합니다.</t>
+  </si>
+  <si>
+    <t>벌점이 올라가는(숫자가 커지는) 이유:</t>
+  </si>
+  <si>
+    <t>1. 선생님들이 신청한 듀티(E or D 등)를 어쩔 수 없이 못 들어줬을 때</t>
+  </si>
+  <si>
+    <t>2. 2순위, 3순위 오프 신청을 반려하고 출근시켰을 때</t>
+  </si>
+  <si>
+    <t>3. 간호사들 간의 총 근무 일수나 나이트 개수가 공평하게 딱 떨어지지 않았을 때</t>
+  </si>
   <si>
     <t>Scheduler Controls</t>
   </si>
@@ -199,15 +514,15 @@
     <t>Balances weekend/holiday work</t>
   </si>
   <si>
-    <t>설명</t>
-  </si>
-  <si>
     <t>Solver time limit (sec) (최대 계산 시간): 컴퓨터가 정답을 찾기 위해 고민할 수 있는 시간(초 단위)입니다.  조건이 많거나 에러(시간 초과)가 난다면 이 숫자를 600 정도로 넉넉하게 늘려주세요.</t>
   </si>
   <si>
     <t>Preference miss penalty (선호 근무 무시 벌점): 선생님들이 신청한 듀티(E or D 등)를 안 들어줬을 때 컴퓨터가 받는 벌점입니다. 이 숫자를 높게 바꿀수록 컴퓨터는 신청 듀티를 무조건 100% 들어주려고 노력하게 됩니다.</t>
   </si>
   <si>
+    <t>Fairness weight (공평성 가중치): 간호사들끼리 특정 듀티의 개수가 차이 날 때마다 컴퓨터가 받는 벌점입니다. 이 숫자가 클수록 컴퓨터가 간호사들 간의 개수를 아주 칼같이 똑맞추려고 노력합니다. 10000점이 기본설정</t>
+  </si>
+  <si>
     <t xml:space="preserve">total work: 총 출근 일수를 똑같이 맞추려는 노력 점수 </t>
   </si>
   <si>
@@ -223,288 +538,6 @@
     <t>절대규칙 : 만약 스케줄이 꼬여서 이 규칙을 어겨야만 근무표가 완성되는 상황이 오면, 컴퓨터는 규칙을 어기는 대신 차라리 "스케줄을 짤 수 없습니다!" 하고 에러를 내며 작동을 멈춥니다.</t>
   </si>
   <si>
-    <t>🏥 [근무표 자동화 스케줄러 사용 설명서]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">만든사람: </t>
-  </si>
-  <si>
-    <t>동남보건대 간호학과 21학번 송민영</t>
-  </si>
-  <si>
-    <t>마음껏 사용해주시고 피드백, 원하는 기능, 수정해야할 점, 오류 등 알려주시면 감사하겠습니다. (alex0840@naver.com)</t>
-  </si>
-  <si>
-    <t>본 프로그램은 간호사들의 수면권 보장, 공평한 근무 배분, 그리고 병동의 안전한 운영을 위해 AI(구글 최적화 알고리즘)가 수백만 번의 계산을 거쳐 최적의 근무표를 짜주는 스마트 스케줄러입니다.</t>
-  </si>
-  <si>
-    <t>🚫 제 1장. 절대 불변의 기본 규칙 (자동 적용)</t>
-  </si>
-  <si>
-    <t>이 규칙들은 간호사의 건강과 병동 안전을 위해 컴퓨터가 절대적으로 지키도록 설계된 '수정 불가능한' 뼈대 규칙입니다.</t>
-  </si>
-  <si>
-    <t>1. 수면권 및 바이오리듬 보장 (최악의 듀티 차단)</t>
-  </si>
-  <si>
-    <t>E ➔ D 금지: 이브닝 후 데이 출근 절대 금지</t>
-  </si>
-  <si>
-    <t>M ➔ D, E ➔ M 금지: 미들(M) 근무 전후의 무리한 교대 금지</t>
-  </si>
-  <si>
-    <t>N ➔ O ➔ D 금지: 나이트 후 하루 쉬고 데이 출근 절대 금지</t>
-  </si>
-  <si>
-    <t>N ➔ O ➔ N 억제: 나이트 후 하루(또는 며칠) 쉬고 완충 듀티 없이 다시 나이트 출근 억제 (월초/월말 나이트 몰림 방지)</t>
-  </si>
-  <si>
-    <t>O ➔ W ➔ O (퐁당퐁당) 금지: 오프 후 하루만 일하고 다시 오프를 부여하는 징검다리 근무 원천 차단</t>
-  </si>
-  <si>
-    <t>2. 환자 안전 및 병동 운영 보장</t>
-  </si>
-  <si>
-    <t>듀티별 필수 경력자(Charge) 배치: 모든 날짜의 D, E, N, M 근무에는 반드시 '차지 권한'이 있는 경력 간호사가 최소 1명 이상 배치됨. (신규들로만 구성된 듀티 발생 불가)</t>
-  </si>
-  <si>
-    <t>3. 나이트 전담(Night Keep) 특수 보호</t>
-  </si>
-  <si>
-    <t>데이(D), 이브닝(E), 미들(M) 근무 절대 배정 안 됨.</t>
-  </si>
-  <si>
-    <t>한 달에 정확히 15개의 나이트(N)만 배정되며 나머지는 올 오프(O).</t>
-  </si>
-  <si>
-    <t>단, 연속 나이트 횟수나 휴식일은 일반 간호사와 똑같이 엑셀(Setup) 규칙을 따름.</t>
-  </si>
-  <si>
-    <t>4. 스마트 공평성 유지</t>
-  </si>
-  <si>
-    <t>경력자는 경력자끼리, 일반/신규는 일반/신규끼리 총 근무 수, 나이트 수, 데이/이브닝 수, 주말 근무 수가 최대한 똑같아지도록 컴퓨터가 알아서 분배함.</t>
-  </si>
-  <si>
-    <t>✏️ 제 2장. 스케줄 세팅 방법 (엑셀 입력란)</t>
-  </si>
-  <si>
-    <t>엑셀의 각 시트(Sheet)에 정보를 입력하여 병동 상황에 맞게 스케줄을 조종할 수 있습니다.</t>
-  </si>
-  <si>
-    <t>1️⃣ [Setup] 시트 (기본 설정)</t>
-  </si>
-  <si>
-    <t>Year / Month: 근무표를 짤 연도와 월</t>
-  </si>
-  <si>
-    <t>이번 달 기본 오프: 이번 달 공휴일을 포함한 기본 오프 개수 (이 개수를 넘어서 쉬는 날은 스케줄표에 S로 표시됨)</t>
-  </si>
-  <si>
-    <t>Weekday / Weekend Req: 평일 및 주말/공휴일의 듀티별(D, E, N, M) 필요 인원수</t>
-  </si>
-  <si>
-    <t>Max consecutive ~ : 최대 연속 출근 일수, 최대 연속 D/E 일수</t>
-  </si>
-  <si>
-    <t>Max / Min consecutive night days: 나이트 최대 / 최소 연속 일수</t>
-  </si>
-  <si>
-    <t>Off days after a night block: 나이트 근무가 끝난 뒤 반드시 며칠을 쉬게 할 것인지 설정 (통상 2일)</t>
-  </si>
-  <si>
-    <t>2️⃣ [Nurses] 시트 (간호사 명단 및 권한) ★가장 중요★</t>
-  </si>
-  <si>
-    <t>Nurse Name: 간호사 이름 (모든 시트의 이름 순서는 동일해야 함)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">경력(Y/N) [차지 권한 부여]: 원하는 듀티에만 차지를 부여할 수 있습니다. </t>
-  </si>
-  <si>
-    <t>D차지 ➔ 데이 때만 경력직으로 인정</t>
-  </si>
-  <si>
-    <t>E차지 ➔ 이브닝 때만 경력직으로 인정</t>
-  </si>
-  <si>
-    <t>N차지 ➔ 나이트 때만 경력직으로 인정 (데이/이브 때는 일반 간호사 취급)</t>
-  </si>
-  <si>
-    <t>D, E 차지 또는 D/E차지 ➔ 데이와 이브닝 둘 다 경력직 인정</t>
-  </si>
-  <si>
-    <t>데이, 이브닝 차지 ➔ 한글로 적어도 알파벳과 똑같이 알아듣습니다!</t>
-  </si>
-  <si>
-    <t>Y ➔ 모든 듀티에서 경력직으로 완전 인정</t>
-  </si>
-  <si>
-    <t>최대 오프 개수: 각 간호사의 남은 연차 등을 고려해 이번 달 최대 쉴 수 있는 개수 기입 (비워두면 무제한 허용)</t>
-  </si>
-  <si>
-    <t>나이트전담(Y/N): 나이트 전담 선생님만 Y 기입</t>
-  </si>
-  <si>
-    <t>비고 (E열): 신규 간호사 프리셉터 매칭 기능</t>
-  </si>
-  <si>
-    <t>신규 선생님의 E열에 프리셉터 선생님 이름(예: 이선희)을 적으면, 프리셉터가 출근하는 날짜와 듀티에만 신규 간호사가 똑같이 출근하게 됩니다.</t>
-  </si>
-  <si>
-    <t>3️⃣ [Holidays] 시트 (휴일 및 특수 인원 추가)</t>
-  </si>
-  <si>
-    <t>날짜 지정: 주말 외에 달력상 빨간 날을 지정합니다.</t>
-  </si>
-  <si>
-    <t>Optional Note [특정 날짜 인원 마음대로 추가하기]:</t>
-  </si>
-  <si>
-    <t>명절이나 유독 바쁜 평일에 인원을 임시로 더 넣고 싶을 때 사용합니다.</t>
-  </si>
-  <si>
-    <t>D2 ➔ 데이 2명 추가 배치</t>
-  </si>
-  <si>
-    <t>D1, E1 ➔ 데이 1명, 이브닝 1명 추가 배치</t>
-  </si>
-  <si>
-    <t>M ➔ 미들 1명 추가 배치</t>
-  </si>
-  <si>
-    <t>숫자 없이 알파벳만 쓰면 자동으로 1명 추가로 인식합니다.</t>
-  </si>
-  <si>
-    <t>4️⃣ [ShiftPreferences] 시트 (선호 듀티 신청)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  선생님들이 원하는 근무를 신청하는 곳입니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  다중 선택 기능: "데이나 이브닝 아무거나 줘!"가 가능합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  엑셀 칸에 E or D, E, D, E/D 라고 자유롭게 적으면, 컴퓨터가 알아서 둘 중 하나를 찰떡같이 배정해 줍니다.</t>
-  </si>
-  <si>
-    <t>5️⃣ 기타 시트</t>
-  </si>
-  <si>
-    <t>[OffRequests]: 무조건 쉬어야 하는 날(신청 오프). O, OFF, 1 등으로 표시.</t>
-  </si>
-  <si>
-    <t>[Restrictions]: 이번 달에 나이트를 아예 하면 안 되는 선생님(임산부, 진단서 등)은 Y로 체크.</t>
-  </si>
-  <si>
-    <t>[PrevMonth] (전월 근무 이월): 지난달 마지막 5일의 듀티를 적어두면, 연속 근무 횟수와 나이트 휴식 조건이 이번 달 1일로 완벽하게 이월되어 계산됩니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   [Validation, DailyCoverage] : 프로그램이 규칙에 맞게 듀티가 배분되었는지 자동 확인하는 시트입니다. 신경 안써도 됩니다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  [RequestsSummary]: 신청 듀티, 신청 오프가 반려 되었을때의 내용이 자동으로 적힙니다.</t>
-  </si>
-  <si>
-    <t>🚨 제 3장. 에러 방지 주의사항 (필독!)</t>
-  </si>
-  <si>
-    <t>1. 날짜 띄어쓰기 절대 금지 (Holidays 시트): * A열의 날짜칸(YYYY-MM-DD)에 스페이스바(빈칸)가 들어가면 컴퓨터가 날짜로 인식하지 못해 에러가 납니다.</t>
-  </si>
-  <si>
-    <t>2. 이름(오타) 통일:</t>
-  </si>
-  <si>
-    <t>3. 불가능한 조건 조심:</t>
-  </si>
-  <si>
-    <t>"모두가 1일에 오프를 원한다"거나, "필요 인원은 10명인데 5명이 휴가를 갔다"는 등 수학적으로 도저히 불가능한 상황에서는 컴퓨터가 INFEASIBLE(충돌) 에러를 띄웁니다. 이때는 인원수나 오프 신청을 살짝 조율해 주셔야 합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 4. 시트의 이름, 입력란 외 이름, 입력란의 행과 열을 바꾸면 프로그램이 인식하지 못합니다!</t>
-  </si>
-  <si>
-    <t>(스케줄 작성 완료 후 엑셀을 저장 후 종료한 뒤에 .exe 파일을 더블클릭하시면 됩니다!)</t>
-  </si>
-  <si>
-    <t>액셀 파일과 실행 exe 파일을 한 폴더안에 넣어야 작동이 됩니다! 엑셀과 프로그램 파일 이름을 바꾸지 마세요!</t>
-  </si>
-  <si>
-    <t>프로그램창 (CMD) 해석</t>
-  </si>
-  <si>
-    <t>근무표 작성이 완료되면 까만 창 맨 아래에 두 줄의 영어 메시지가 뜹니다. 이것은 AI(인공지능)가 스케줄을 짜면서 겪은 과정과 결과물의 점수를 알려주는 보고서입니다.</t>
-  </si>
-  <si>
-    <t>1️⃣ Solver status (컴퓨터의 최종 상태 보고)</t>
-  </si>
-  <si>
-    <t>컴퓨터가 근무표를 성공적으로 완성했는지, 아니면 규칙이 너무 빡빡해서 실패했는지를 알려줍니다.</t>
-  </si>
-  <si>
-    <t>OPTIMAL (가장 이상적!)</t>
-  </si>
-  <si>
-    <t>의미: 주어진 조건 안에서 수학적으로 가장 완벽하고 공평한 1등 스케줄을 찾아냈습니다</t>
-  </si>
-  <si>
-    <t>상태: 안심하고 엑셀 근무표를 확인하시면 됩니다.</t>
-  </si>
-  <si>
-    <t>FEASIBLE (쓸만한 스케줄 완성)</t>
-  </si>
-  <si>
-    <t>의미: 100점짜리 정답인지는 확신할 수 없지만, 모든 절대 규칙(Hard)을 완벽하게 지킨 스케줄을 일단 완성했습니다</t>
-  </si>
-  <si>
-    <t>상태: 엑셀 근무표를 그대로 사용하셔도 무방합니다. (더 완벽한 결과를 원하시면 Setup 시트의 시간을 늘리고 다시 돌려보세요.)</t>
-  </si>
-  <si>
-    <t>INFEASIBLE (작성 실패 - 규칙 충돌) 🚨</t>
-  </si>
-  <si>
-    <t>의미: 스케줄을 짤 수가 없습니다! 조건들이 서로 모순됩니다</t>
-  </si>
-  <si>
-    <t>상태: 근무표 작성에 실패하여 엑셀이 업데이트되지 않습니다. (주로 1순위 오프가 너무 많거나, 출근할 인원이 부족할 때 발생합니다. 인원이나 오프를 수정하고 다시 돌려주세요.)</t>
-  </si>
-  <si>
-    <t>UNKNOWN (작성 실패 - 시간 초과) 🚨</t>
-  </si>
-  <si>
-    <t>의미: 규칙이 너무 복잡해서 제한 시간 안에 단 한 개의 스케줄도 완성하지 못했습니다.</t>
-  </si>
-  <si>
-    <t>상태: Setup 시트의 Solver time limit (sec) 시간을 600초 이상으로 넉넉히 늘리거나, 연속 근무 제한을 살짝 풀어주세요.</t>
-  </si>
-  <si>
-    <t>2️⃣ Objective value (AI의 스케줄 채점표 / 벌점)</t>
-  </si>
-  <si>
-    <t>의미: 이 숫자는 인공지능이 스케줄을 짜면서 받은 벌점(Penalty)의 총합입니다.</t>
-  </si>
-  <si>
-    <t>해석 방법: "숫자가 낮을수록(0에 가까울수록) 훌륭한 근무표입니다!"</t>
-  </si>
-  <si>
-    <t>컴퓨터는 무조건 이 벌점을 낮추기 위해 수백만 번의 경우의 수를 계산합니다.</t>
-  </si>
-  <si>
-    <t>벌점이 올라가는(숫자가 커지는) 이유:</t>
-  </si>
-  <si>
-    <t>1. 선생님들이 신청한 듀티(E or D 등)를 어쩔 수 없이 못 들어줬을 때</t>
-  </si>
-  <si>
-    <t>2. 2순위, 3순위 오프 신청을 반려하고 출근시켰을 때</t>
-  </si>
-  <si>
-    <t>3. 간호사들 간의 총 근무 일수나 나이트 개수가 공평하게 딱 떨어지지 않았을 때</t>
-  </si>
-  <si>
-    <t>Nurse Name</t>
-  </si>
-  <si>
     <t>경력(Y/N)</t>
   </si>
   <si>
@@ -517,9 +550,15 @@
     <t>프리셉터</t>
   </si>
   <si>
+    <t>막내 여부(Y)</t>
+  </si>
+  <si>
     <t>간호사1</t>
   </si>
   <si>
+    <t>y</t>
+  </si>
+  <si>
     <t>간호사2</t>
   </si>
   <si>
@@ -583,6 +622,9 @@
     <t>홍길동 (no duty) ➔ (완전 신입) 프리셉터 듀티를 따라가지만, 투명인간 취급되어 병동 인원 카운트에서 제외됩니다. (※ 대소문자나 띄어쓰기는 상관없습니다. (NO DUTY), no duty 등 편하게 적으시면 됩니다!)</t>
   </si>
   <si>
+    <t>막내 여부: 막내 여부를 두 명 이상 Y 체크하면 막내끼리는 같은 듀티에 가급적 배치하지 않습니다</t>
+  </si>
+  <si>
     <t>tip: 최대 오프 개수가 너무 적어서 모든 칸을 채울 수 없는 경우 에러가 납니다. 연차를 사용하거나 m 근무 추가, 하루 듀티 최대 수를 늘려주세요</t>
   </si>
   <si>
@@ -682,39 +724,18 @@
     <t>Allowed markers: D, E, N, M 입력가능</t>
   </si>
   <si>
-    <t>D-5</t>
-  </si>
-  <si>
-    <t>D-4</t>
-  </si>
-  <si>
-    <t>D-3</t>
-  </si>
-  <si>
-    <t>D-2</t>
-  </si>
-  <si>
-    <t>D-1</t>
-  </si>
-  <si>
-    <t>전 달 마지막 5일의 듀티를 작성합니다. 프로그램이 전 달 마지막 근무 5일을 규칙에 반영합니다</t>
-  </si>
-  <si>
-    <t>D, E, N, M, O 중 하나를 적습니다. (칸을 비워두시면 무조건 오프(O)로 간주합니다.)</t>
-  </si>
-  <si>
     <t>Final Schedule</t>
   </si>
   <si>
     <t>Type</t>
   </si>
   <si>
+    <t>WD</t>
+  </si>
+  <si>
     <t>WH</t>
   </si>
   <si>
-    <t>WD</t>
-  </si>
-  <si>
     <t>TotalWork</t>
   </si>
   <si>
@@ -745,6 +766,12 @@
     <t>PrefMiss</t>
   </si>
   <si>
+    <t>O</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
@@ -781,6 +808,9 @@
     <t>Overall</t>
   </si>
   <si>
+    <t>OK</t>
+  </si>
+  <si>
     <t>ReqD</t>
   </si>
   <si>
@@ -802,154 +832,120 @@
     <t>OK?</t>
   </si>
   <si>
-    <t>간호관리학 실습 중 급하게 제작한 프로그램입니다. 부족한 점이 많습니다 (마지막 수정 2026/03/30)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>간호사13</t>
-  </si>
-  <si>
-    <t>간호사14</t>
-  </si>
-  <si>
-    <t>간호사15</t>
-  </si>
-  <si>
-    <t>간호사16</t>
-  </si>
-  <si>
-    <t>간호사17</t>
-  </si>
-  <si>
-    <t>간호사18</t>
-  </si>
-  <si>
-    <t>간호사19</t>
-  </si>
-  <si>
-    <t>간호사20</t>
-  </si>
-  <si>
-    <t>간호사21</t>
-  </si>
-  <si>
-    <t>간호사22</t>
-  </si>
-  <si>
-    <t>간호사23</t>
-  </si>
-  <si>
-    <t>간호사24</t>
-  </si>
-  <si>
-    <t>간호사25</t>
-  </si>
-  <si>
-    <t>간호사26</t>
-  </si>
-  <si>
-    <t>간호사27</t>
-  </si>
-  <si>
-    <t>간호사28</t>
-  </si>
-  <si>
-    <t>간호사29</t>
-  </si>
-  <si>
-    <t>간호사30</t>
-  </si>
-  <si>
-    <t>간호사31</t>
-  </si>
-  <si>
-    <t>간호사32</t>
-  </si>
-  <si>
-    <t>간호사33</t>
-  </si>
-  <si>
-    <t>간호사34</t>
-  </si>
-  <si>
-    <t>간호사35</t>
-  </si>
-  <si>
-    <t>간호사36</t>
-  </si>
-  <si>
-    <t>간호사37</t>
-  </si>
-  <si>
-    <t>간호사38</t>
-  </si>
-  <si>
-    <t>간호사39</t>
-  </si>
-  <si>
-    <t>간호사40</t>
-  </si>
-  <si>
-    <t>간호사41</t>
-  </si>
-  <si>
-    <t>간호사42</t>
-  </si>
-  <si>
-    <t>간호사43</t>
-  </si>
-  <si>
-    <t>간호사44</t>
-  </si>
-  <si>
-    <t>간호사45</t>
-  </si>
-  <si>
-    <t>간호사46</t>
-  </si>
-  <si>
-    <t>간호사47</t>
-  </si>
-  <si>
-    <t>간호사48</t>
-  </si>
-  <si>
-    <t>간호사49</t>
-  </si>
-  <si>
-    <t>간호사50</t>
-  </si>
-  <si>
-    <t>Nurses 시트에 적힌 이름과 OffRequests, ShiftPreferences 등 간호사 이름이 들어간 모든 시트의 이름과 순서가 반드시 일치해야 합니다. (간호사 퇴사/입사로 인원을 수정할 때는 세 시트 모두 똑같이 수정해 주세요. 자동 반영 되는데 간호사 순서 밀림에 주의해주세요)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>성균관대 기계공학부 20학번 김정진</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>막내 여부(Y)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>막내 여부: 막내 여부를 두 명 이상 Y 체크하면 막내끼리는 같은 듀티에 가급적 배치하지 않습니다</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Fairness weight (공평성 가중치): 간호사들끼리 특정 듀티의 개수가 차이 날 때마다 컴퓨터가 받는 벌점입니다. 이 숫자가 클수록 컴퓨터가 간호사들 간의 개수를 아주 칼같이 똑맞추려고 노력합니다. 10000점이 기본설정</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <t>2026-04-01</t>
+  </si>
+  <si>
+    <t>Weekday</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>2026-04-04</t>
+  </si>
+  <si>
+    <t>Weekend/Holiday</t>
+  </si>
+  <si>
+    <t>2026-04-05</t>
+  </si>
+  <si>
+    <t>2026-04-06</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-04-08</t>
+  </si>
+  <si>
+    <t>2026-04-09</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>2026-04-11</t>
+  </si>
+  <si>
+    <t>2026-04-12</t>
+  </si>
+  <si>
+    <t>2026-04-13</t>
+  </si>
+  <si>
+    <t>2026-04-14</t>
+  </si>
+  <si>
+    <t>2026-04-15</t>
+  </si>
+  <si>
+    <t>2026-04-16</t>
+  </si>
+  <si>
+    <t>2026-04-17</t>
+  </si>
+  <si>
+    <t>2026-04-18</t>
+  </si>
+  <si>
+    <t>2026-04-19</t>
+  </si>
+  <si>
+    <t>2026-04-20</t>
+  </si>
+  <si>
+    <t>2026-04-21</t>
+  </si>
+  <si>
+    <t>2026-04-22</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>2026-04-25</t>
+  </si>
+  <si>
+    <t>2026-04-26</t>
+  </si>
+  <si>
+    <t>2026-04-27</t>
+  </si>
+  <si>
+    <t>2026-04-28</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="34">
+  <fonts count="35">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1219,7 +1215,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1250,6 +1246,16 @@
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -1382,28 +1388,28 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1415,68 +1421,68 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1485,16 +1491,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1509,106 +1515,109 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1923,14 +1932,14 @@
   <sheetData>
     <row r="1" spans="1:24" ht="38.25" customHeight="1">
       <c r="A1" s="21" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="K1" s="26" t="s">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="L1" s="27"/>
-      <c r="M1" s="94" t="s">
-        <v>61</v>
+      <c r="M1" s="93" t="s">
+        <v>11</v>
       </c>
       <c r="S1" s="28"/>
       <c r="T1" s="28"/>
@@ -1943,8 +1952,8 @@
       <c r="A2" s="21"/>
       <c r="K2" s="30"/>
       <c r="L2" s="25"/>
-      <c r="M2" s="94" t="s">
-        <v>292</v>
+      <c r="M2" s="93" t="s">
+        <v>12</v>
       </c>
       <c r="X2" s="31"/>
     </row>
@@ -1956,7 +1965,7 @@
       <c r="H3" s="25"/>
       <c r="I3" s="24"/>
       <c r="K3" s="32" t="s">
-        <v>252</v>
+        <v>13</v>
       </c>
       <c r="X3" s="31"/>
     </row>
@@ -1968,7 +1977,7 @@
       <c r="H4" s="25"/>
       <c r="I4" s="24"/>
       <c r="K4" s="33" t="s">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="L4" s="34"/>
       <c r="M4" s="35"/>
@@ -1986,22 +1995,22 @@
     </row>
     <row r="6" spans="1:24" ht="15.75" customHeight="1">
       <c r="A6" s="11" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:24" ht="26.25" customHeight="1">
       <c r="A8" s="22" t="s">
-        <v>64</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:24">
       <c r="A10" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:24">
       <c r="A12" s="23" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:24">
@@ -2009,7 +2018,7 @@
     </row>
     <row r="14" spans="1:24">
       <c r="A14" s="17" t="s">
-        <v>67</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:24">
@@ -2017,7 +2026,7 @@
     </row>
     <row r="16" spans="1:24">
       <c r="A16" s="17" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:1">
@@ -2025,7 +2034,7 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="17" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:1">
@@ -2033,7 +2042,7 @@
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="17" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -2041,12 +2050,12 @@
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="17" t="s">
-        <v>71</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="23" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:1">
@@ -2054,12 +2063,12 @@
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="17" t="s">
-        <v>73</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="23" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:1">
@@ -2067,7 +2076,7 @@
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="16" t="s">
-        <v>75</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31" spans="1:1">
@@ -2075,7 +2084,7 @@
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="16" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" spans="1:1">
@@ -2083,12 +2092,12 @@
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="16" t="s">
-        <v>77</v>
+        <v>29</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="23" t="s">
-        <v>78</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37" spans="1:1">
@@ -2096,22 +2105,22 @@
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="16" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
     </row>
     <row r="42" spans="1:1" ht="26.25" customHeight="1">
       <c r="A42" s="15" t="s">
-        <v>80</v>
+        <v>32</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>81</v>
+        <v>33</v>
       </c>
     </row>
     <row r="46" spans="1:1" ht="21.75" customHeight="1">
       <c r="A46" s="18" t="s">
-        <v>82</v>
+        <v>34</v>
       </c>
     </row>
     <row r="47" spans="1:1">
@@ -2119,7 +2128,7 @@
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="17" t="s">
-        <v>83</v>
+        <v>35</v>
       </c>
     </row>
     <row r="49" spans="1:1">
@@ -2127,7 +2136,7 @@
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="17" t="s">
-        <v>84</v>
+        <v>36</v>
       </c>
     </row>
     <row r="51" spans="1:1">
@@ -2135,7 +2144,7 @@
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="17" t="s">
-        <v>85</v>
+        <v>37</v>
       </c>
     </row>
     <row r="53" spans="1:1">
@@ -2143,7 +2152,7 @@
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="17" t="s">
-        <v>86</v>
+        <v>38</v>
       </c>
     </row>
     <row r="55" spans="1:1">
@@ -2151,7 +2160,7 @@
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="17" t="s">
-        <v>87</v>
+        <v>39</v>
       </c>
     </row>
     <row r="57" spans="1:1">
@@ -2159,12 +2168,12 @@
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="17" t="s">
-        <v>88</v>
+        <v>40</v>
       </c>
     </row>
     <row r="60" spans="1:1" ht="21.75" customHeight="1">
       <c r="A60" s="18" t="s">
-        <v>89</v>
+        <v>41</v>
       </c>
     </row>
     <row r="61" spans="1:1">
@@ -2172,7 +2181,7 @@
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="17" t="s">
-        <v>90</v>
+        <v>42</v>
       </c>
     </row>
     <row r="63" spans="1:1">
@@ -2180,7 +2189,7 @@
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="17" t="s">
-        <v>91</v>
+        <v>43</v>
       </c>
     </row>
     <row r="65" spans="1:1">
@@ -2188,7 +2197,7 @@
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="20" t="s">
-        <v>92</v>
+        <v>44</v>
       </c>
     </row>
     <row r="67" spans="1:1">
@@ -2196,7 +2205,7 @@
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="20" t="s">
-        <v>93</v>
+        <v>45</v>
       </c>
     </row>
     <row r="69" spans="1:1">
@@ -2204,7 +2213,7 @@
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="20" t="s">
-        <v>94</v>
+        <v>46</v>
       </c>
     </row>
     <row r="71" spans="1:1">
@@ -2212,7 +2221,7 @@
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="20" t="s">
-        <v>95</v>
+        <v>47</v>
       </c>
     </row>
     <row r="73" spans="1:1">
@@ -2220,7 +2229,7 @@
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="20" t="s">
-        <v>96</v>
+        <v>48</v>
       </c>
     </row>
     <row r="75" spans="1:1">
@@ -2228,7 +2237,7 @@
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="20" t="s">
-        <v>97</v>
+        <v>49</v>
       </c>
     </row>
     <row r="77" spans="1:1">
@@ -2236,7 +2245,7 @@
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="17" t="s">
-        <v>98</v>
+        <v>50</v>
       </c>
     </row>
     <row r="79" spans="1:1">
@@ -2244,7 +2253,7 @@
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="17" t="s">
-        <v>99</v>
+        <v>51</v>
       </c>
     </row>
     <row r="81" spans="1:1">
@@ -2252,12 +2261,12 @@
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="17" t="s">
-        <v>100</v>
+        <v>52</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="19" t="s">
-        <v>101</v>
+        <v>53</v>
       </c>
     </row>
     <row r="84" spans="1:1">
@@ -2265,7 +2274,7 @@
     </row>
     <row r="86" spans="1:1" ht="21.75" customHeight="1">
       <c r="A86" s="18" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
     </row>
     <row r="87" spans="1:1">
@@ -2273,7 +2282,7 @@
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="17" t="s">
-        <v>103</v>
+        <v>55</v>
       </c>
     </row>
     <row r="89" spans="1:1">
@@ -2281,7 +2290,7 @@
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="17" t="s">
-        <v>104</v>
+        <v>56</v>
       </c>
     </row>
     <row r="91" spans="1:1">
@@ -2289,7 +2298,7 @@
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="19" t="s">
-        <v>105</v>
+        <v>57</v>
       </c>
     </row>
     <row r="93" spans="1:1">
@@ -2297,7 +2306,7 @@
     </row>
     <row r="94" spans="1:1">
       <c r="A94" s="20" t="s">
-        <v>106</v>
+        <v>58</v>
       </c>
     </row>
     <row r="95" spans="1:1">
@@ -2305,7 +2314,7 @@
     </row>
     <row r="96" spans="1:1">
       <c r="A96" s="20" t="s">
-        <v>107</v>
+        <v>59</v>
       </c>
     </row>
     <row r="97" spans="1:10">
@@ -2313,7 +2322,7 @@
     </row>
     <row r="98" spans="1:10">
       <c r="A98" s="20" t="s">
-        <v>108</v>
+        <v>60</v>
       </c>
     </row>
     <row r="99" spans="1:10">
@@ -2321,12 +2330,12 @@
     </row>
     <row r="100" spans="1:10">
       <c r="A100" s="19" t="s">
-        <v>109</v>
+        <v>61</v>
       </c>
     </row>
     <row r="102" spans="1:10" ht="21.75" customHeight="1">
       <c r="A102" s="18" t="s">
-        <v>110</v>
+        <v>62</v>
       </c>
     </row>
     <row r="103" spans="1:10">
@@ -2334,7 +2343,7 @@
     </row>
     <row r="104" spans="1:10">
       <c r="A104" s="41" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="B104" s="42"/>
       <c r="C104" s="42"/>
@@ -2360,7 +2369,7 @@
     </row>
     <row r="106" spans="1:10">
       <c r="A106" s="79" t="s">
-        <v>112</v>
+        <v>64</v>
       </c>
       <c r="B106" s="42"/>
       <c r="C106" s="42"/>
@@ -2386,7 +2395,7 @@
     </row>
     <row r="108" spans="1:10">
       <c r="A108" s="41" t="s">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="B108" s="42"/>
       <c r="C108" s="42"/>
@@ -2400,7 +2409,7 @@
     </row>
     <row r="110" spans="1:10" ht="21.75" customHeight="1">
       <c r="A110" s="18" t="s">
-        <v>114</v>
+        <v>66</v>
       </c>
     </row>
     <row r="111" spans="1:10">
@@ -2408,7 +2417,7 @@
     </row>
     <row r="112" spans="1:10">
       <c r="A112" s="17" t="s">
-        <v>115</v>
+        <v>67</v>
       </c>
     </row>
     <row r="113" spans="1:1">
@@ -2416,7 +2425,7 @@
     </row>
     <row r="114" spans="1:1">
       <c r="A114" s="17" t="s">
-        <v>116</v>
+        <v>68</v>
       </c>
     </row>
     <row r="115" spans="1:1">
@@ -2424,12 +2433,12 @@
     </row>
     <row r="116" spans="1:1">
       <c r="A116" s="17" t="s">
-        <v>117</v>
+        <v>69</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" s="11" t="s">
-        <v>118</v>
+        <v>70</v>
       </c>
     </row>
     <row r="119" spans="1:1">
@@ -2437,7 +2446,7 @@
     </row>
     <row r="120" spans="1:1">
       <c r="A120" s="11" t="s">
-        <v>119</v>
+        <v>71</v>
       </c>
     </row>
     <row r="121" spans="1:1">
@@ -2445,7 +2454,7 @@
     </row>
     <row r="122" spans="1:1" ht="26.25" customHeight="1">
       <c r="A122" s="38" t="s">
-        <v>120</v>
+        <v>72</v>
       </c>
     </row>
     <row r="123" spans="1:1">
@@ -2453,7 +2462,7 @@
     </row>
     <row r="124" spans="1:1">
       <c r="A124" s="43" t="s">
-        <v>121</v>
+        <v>73</v>
       </c>
     </row>
     <row r="125" spans="1:1">
@@ -2461,12 +2470,12 @@
     </row>
     <row r="126" spans="1:1">
       <c r="A126" s="43" t="s">
-        <v>122</v>
+        <v>74</v>
       </c>
     </row>
     <row r="127" spans="1:1">
       <c r="A127" s="45" t="s">
-        <v>291</v>
+        <v>75</v>
       </c>
     </row>
     <row r="128" spans="1:1">
@@ -2474,12 +2483,12 @@
     </row>
     <row r="129" spans="1:1">
       <c r="A129" s="43" t="s">
-        <v>123</v>
+        <v>76</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" s="39" t="s">
-        <v>124</v>
+        <v>77</v>
       </c>
     </row>
     <row r="131" spans="1:1">
@@ -2487,37 +2496,37 @@
     </row>
     <row r="132" spans="1:1">
       <c r="A132" s="43" t="s">
-        <v>125</v>
+        <v>78</v>
       </c>
     </row>
     <row r="134" spans="1:1" ht="26.25" customHeight="1">
       <c r="A134" s="83" t="s">
-        <v>126</v>
+        <v>79</v>
       </c>
     </row>
     <row r="135" spans="1:1" ht="26.25" customHeight="1">
       <c r="A135" s="88" t="s">
-        <v>127</v>
+        <v>80</v>
       </c>
     </row>
     <row r="138" spans="1:1" ht="20.25" customHeight="1">
       <c r="A138" s="92" t="s">
-        <v>128</v>
+        <v>81</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139" t="s">
-        <v>129</v>
+        <v>82</v>
       </c>
     </row>
     <row r="141" spans="1:1" ht="21.75" customHeight="1">
       <c r="A141" s="18" t="s">
-        <v>130</v>
+        <v>83</v>
       </c>
     </row>
     <row r="143" spans="1:1">
       <c r="A143" t="s">
-        <v>131</v>
+        <v>84</v>
       </c>
     </row>
     <row r="144" spans="1:1">
@@ -2525,17 +2534,17 @@
     </row>
     <row r="145" spans="1:1">
       <c r="A145" s="89" t="s">
-        <v>132</v>
+        <v>85</v>
       </c>
     </row>
     <row r="146" spans="1:1">
       <c r="A146" s="90" t="s">
-        <v>133</v>
+        <v>86</v>
       </c>
     </row>
     <row r="147" spans="1:1">
       <c r="A147" s="90" t="s">
-        <v>134</v>
+        <v>87</v>
       </c>
     </row>
     <row r="148" spans="1:1">
@@ -2543,17 +2552,17 @@
     </row>
     <row r="149" spans="1:1">
       <c r="A149" s="89" t="s">
-        <v>135</v>
+        <v>88</v>
       </c>
     </row>
     <row r="150" spans="1:1">
       <c r="A150" s="90" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
     </row>
     <row r="151" spans="1:1">
       <c r="A151" s="90" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
     </row>
     <row r="152" spans="1:1">
@@ -2561,17 +2570,17 @@
     </row>
     <row r="153" spans="1:1">
       <c r="A153" s="89" t="s">
-        <v>138</v>
+        <v>91</v>
       </c>
     </row>
     <row r="154" spans="1:1">
       <c r="A154" s="90" t="s">
-        <v>139</v>
+        <v>92</v>
       </c>
     </row>
     <row r="155" spans="1:1">
       <c r="A155" s="90" t="s">
-        <v>140</v>
+        <v>93</v>
       </c>
     </row>
     <row r="156" spans="1:1">
@@ -2579,22 +2588,22 @@
     </row>
     <row r="157" spans="1:1">
       <c r="A157" s="89" t="s">
-        <v>141</v>
+        <v>94</v>
       </c>
     </row>
     <row r="158" spans="1:1">
       <c r="A158" s="90" t="s">
-        <v>142</v>
+        <v>95</v>
       </c>
     </row>
     <row r="159" spans="1:1">
       <c r="A159" s="90" t="s">
-        <v>143</v>
+        <v>96</v>
       </c>
     </row>
     <row r="161" spans="1:1" ht="21.75" customHeight="1">
       <c r="A161" s="18" t="s">
-        <v>144</v>
+        <v>97</v>
       </c>
     </row>
     <row r="162" spans="1:1">
@@ -2602,41 +2611,41 @@
     </row>
     <row r="163" spans="1:1">
       <c r="A163" s="17" t="s">
-        <v>145</v>
+        <v>98</v>
       </c>
     </row>
     <row r="164" spans="1:1">
       <c r="A164" s="17" t="s">
-        <v>146</v>
+        <v>99</v>
       </c>
     </row>
     <row r="166" spans="1:1">
       <c r="A166" s="19" t="s">
-        <v>147</v>
+        <v>100</v>
       </c>
     </row>
     <row r="167" spans="1:1">
       <c r="A167" s="90" t="s">
-        <v>148</v>
+        <v>101</v>
       </c>
     </row>
     <row r="168" spans="1:1">
       <c r="A168" s="91" t="s">
-        <v>149</v>
+        <v>102</v>
       </c>
     </row>
     <row r="169" spans="1:1">
       <c r="A169" s="91" t="s">
-        <v>150</v>
+        <v>103</v>
       </c>
     </row>
     <row r="170" spans="1:1">
       <c r="A170" s="91" t="s">
-        <v>151</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2655,26 +2664,26 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2694,78 +2703,390 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="5" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="I2" s="93"/>
+      <c r="A2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2" s="98" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="I3" s="93"/>
+      <c r="A3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3" s="98" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="I4" s="93"/>
+      <c r="A4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4" s="98" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="I5" s="93"/>
+      <c r="A5" t="s">
+        <v>175</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="98" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="I6" s="93"/>
+      <c r="A6" t="s">
+        <v>177</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6" s="98" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="I7" s="93"/>
+      <c r="A7" t="s">
+        <v>178</v>
+      </c>
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7" s="98" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="I8" s="93"/>
+      <c r="A8" t="s">
+        <v>180</v>
+      </c>
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8" s="98" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="I9" s="93"/>
+      <c r="A9" t="s">
+        <v>182</v>
+      </c>
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9" s="98" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="I10" s="93"/>
+      <c r="A10" t="s">
+        <v>184</v>
+      </c>
+      <c r="B10">
+        <v>4</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10" s="98" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="I11" s="93"/>
+      <c r="A11" t="s">
+        <v>185</v>
+      </c>
+      <c r="B11">
+        <v>4</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11" s="98" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="I12" s="93"/>
+      <c r="A12" t="s">
+        <v>187</v>
+      </c>
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12" s="98" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="I13" s="93"/>
+      <c r="A13" t="s">
+        <v>188</v>
+      </c>
+      <c r="B13">
+        <v>3</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13" s="98" t="s">
+        <v>254</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
@@ -2774,128 +3095,905 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="5" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="I2" s="93"/>
+      <c r="A2" t="s">
+        <v>262</v>
+      </c>
+      <c r="B2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2" s="98" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="I3" s="93"/>
+      <c r="A3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3" s="98" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="I4" s="93"/>
+      <c r="A4" t="s">
+        <v>265</v>
+      </c>
+      <c r="B4" t="s">
+        <v>263</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="I4" s="98" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="I5" s="93"/>
+      <c r="A5" t="s">
+        <v>266</v>
+      </c>
+      <c r="B5" t="s">
+        <v>267</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5" s="98" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="I6" s="93"/>
+      <c r="A6" t="s">
+        <v>268</v>
+      </c>
+      <c r="B6" t="s">
+        <v>267</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="I6" s="98" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="I7" s="93"/>
+      <c r="A7" t="s">
+        <v>269</v>
+      </c>
+      <c r="B7" t="s">
+        <v>263</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7" s="98" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="I8" s="93"/>
+      <c r="A8" t="s">
+        <v>270</v>
+      </c>
+      <c r="B8" t="s">
+        <v>263</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+      <c r="H8">
+        <v>2</v>
+      </c>
+      <c r="I8" s="98" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="I9" s="93"/>
+      <c r="A9" t="s">
+        <v>271</v>
+      </c>
+      <c r="B9" t="s">
+        <v>263</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+      <c r="H9">
+        <v>2</v>
+      </c>
+      <c r="I9" s="98" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="I10" s="93"/>
+      <c r="A10" t="s">
+        <v>272</v>
+      </c>
+      <c r="B10" t="s">
+        <v>263</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10">
+        <v>2</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+      <c r="H10">
+        <v>2</v>
+      </c>
+      <c r="I10" s="98" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="I11" s="93"/>
+      <c r="A11" t="s">
+        <v>273</v>
+      </c>
+      <c r="B11" t="s">
+        <v>263</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+      <c r="H11">
+        <v>2</v>
+      </c>
+      <c r="I11" s="98" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="I12" s="93"/>
+      <c r="A12" t="s">
+        <v>274</v>
+      </c>
+      <c r="B12" t="s">
+        <v>267</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12">
+        <v>2</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+      <c r="H12">
+        <v>2</v>
+      </c>
+      <c r="I12" s="98" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="I13" s="93"/>
+      <c r="A13" t="s">
+        <v>275</v>
+      </c>
+      <c r="B13" t="s">
+        <v>267</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13">
+        <v>2</v>
+      </c>
+      <c r="E13">
+        <v>2</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+      <c r="H13">
+        <v>2</v>
+      </c>
+      <c r="I13" s="98" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="I14" s="93"/>
+      <c r="A14" t="s">
+        <v>276</v>
+      </c>
+      <c r="B14" t="s">
+        <v>263</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14">
+        <v>2</v>
+      </c>
+      <c r="E14">
+        <v>2</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+      <c r="H14">
+        <v>2</v>
+      </c>
+      <c r="I14" s="98" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="I15" s="93"/>
+      <c r="A15" t="s">
+        <v>277</v>
+      </c>
+      <c r="B15" t="s">
+        <v>263</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="D15">
+        <v>2</v>
+      </c>
+      <c r="E15">
+        <v>2</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="G15">
+        <v>2</v>
+      </c>
+      <c r="H15">
+        <v>2</v>
+      </c>
+      <c r="I15" s="98" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="I16" s="93"/>
-    </row>
-    <row r="17" spans="9:9">
-      <c r="I17" s="93"/>
-    </row>
-    <row r="18" spans="9:9">
-      <c r="I18" s="93"/>
-    </row>
-    <row r="19" spans="9:9">
-      <c r="I19" s="93"/>
-    </row>
-    <row r="20" spans="9:9">
-      <c r="I20" s="93"/>
-    </row>
-    <row r="21" spans="9:9">
-      <c r="I21" s="93"/>
-    </row>
-    <row r="22" spans="9:9">
-      <c r="I22" s="93"/>
-    </row>
-    <row r="23" spans="9:9">
-      <c r="I23" s="93"/>
-    </row>
-    <row r="24" spans="9:9">
-      <c r="I24" s="93"/>
-    </row>
-    <row r="25" spans="9:9">
-      <c r="I25" s="93"/>
-    </row>
-    <row r="26" spans="9:9">
-      <c r="I26" s="93"/>
-    </row>
-    <row r="27" spans="9:9">
-      <c r="I27" s="93"/>
-    </row>
-    <row r="28" spans="9:9">
-      <c r="I28" s="93"/>
-    </row>
-    <row r="29" spans="9:9">
-      <c r="I29" s="93"/>
-    </row>
-    <row r="30" spans="9:9">
-      <c r="I30" s="93"/>
-    </row>
-    <row r="31" spans="9:9">
-      <c r="I31" s="93"/>
-    </row>
-    <row r="32" spans="9:9">
-      <c r="I32" s="93"/>
+      <c r="A16" t="s">
+        <v>278</v>
+      </c>
+      <c r="B16" t="s">
+        <v>263</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16">
+        <v>2</v>
+      </c>
+      <c r="E16">
+        <v>2</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="G16">
+        <v>2</v>
+      </c>
+      <c r="H16">
+        <v>2</v>
+      </c>
+      <c r="I16" s="98" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" t="s">
+        <v>279</v>
+      </c>
+      <c r="B17" t="s">
+        <v>263</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
+      <c r="D17">
+        <v>2</v>
+      </c>
+      <c r="E17">
+        <v>2</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17">
+        <v>2</v>
+      </c>
+      <c r="H17">
+        <v>2</v>
+      </c>
+      <c r="I17" s="98" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
+        <v>280</v>
+      </c>
+      <c r="B18" t="s">
+        <v>263</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18">
+        <v>2</v>
+      </c>
+      <c r="E18">
+        <v>2</v>
+      </c>
+      <c r="F18">
+        <v>2</v>
+      </c>
+      <c r="G18">
+        <v>2</v>
+      </c>
+      <c r="H18">
+        <v>2</v>
+      </c>
+      <c r="I18" s="98" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" t="s">
+        <v>281</v>
+      </c>
+      <c r="B19" t="s">
+        <v>267</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19">
+        <v>2</v>
+      </c>
+      <c r="E19">
+        <v>2</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+      <c r="G19">
+        <v>2</v>
+      </c>
+      <c r="H19">
+        <v>2</v>
+      </c>
+      <c r="I19" s="98" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" t="s">
+        <v>282</v>
+      </c>
+      <c r="B20" t="s">
+        <v>267</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="D20">
+        <v>2</v>
+      </c>
+      <c r="E20">
+        <v>2</v>
+      </c>
+      <c r="F20">
+        <v>2</v>
+      </c>
+      <c r="G20">
+        <v>2</v>
+      </c>
+      <c r="H20">
+        <v>2</v>
+      </c>
+      <c r="I20" s="98" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" t="s">
+        <v>283</v>
+      </c>
+      <c r="B21" t="s">
+        <v>263</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21">
+        <v>2</v>
+      </c>
+      <c r="E21">
+        <v>2</v>
+      </c>
+      <c r="F21">
+        <v>2</v>
+      </c>
+      <c r="G21">
+        <v>2</v>
+      </c>
+      <c r="H21">
+        <v>2</v>
+      </c>
+      <c r="I21" s="98" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" t="s">
+        <v>284</v>
+      </c>
+      <c r="B22" t="s">
+        <v>263</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="D22">
+        <v>2</v>
+      </c>
+      <c r="E22">
+        <v>2</v>
+      </c>
+      <c r="F22">
+        <v>2</v>
+      </c>
+      <c r="G22">
+        <v>2</v>
+      </c>
+      <c r="H22">
+        <v>2</v>
+      </c>
+      <c r="I22" s="98" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" t="s">
+        <v>285</v>
+      </c>
+      <c r="B23" t="s">
+        <v>263</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+      <c r="D23">
+        <v>2</v>
+      </c>
+      <c r="E23">
+        <v>2</v>
+      </c>
+      <c r="F23">
+        <v>2</v>
+      </c>
+      <c r="G23">
+        <v>2</v>
+      </c>
+      <c r="H23">
+        <v>2</v>
+      </c>
+      <c r="I23" s="98" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" t="s">
+        <v>286</v>
+      </c>
+      <c r="B24" t="s">
+        <v>263</v>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+      <c r="D24">
+        <v>2</v>
+      </c>
+      <c r="E24">
+        <v>2</v>
+      </c>
+      <c r="F24">
+        <v>2</v>
+      </c>
+      <c r="G24">
+        <v>2</v>
+      </c>
+      <c r="H24">
+        <v>2</v>
+      </c>
+      <c r="I24" s="98" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" t="s">
+        <v>287</v>
+      </c>
+      <c r="B25" t="s">
+        <v>263</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+      <c r="D25">
+        <v>2</v>
+      </c>
+      <c r="E25">
+        <v>2</v>
+      </c>
+      <c r="F25">
+        <v>2</v>
+      </c>
+      <c r="G25">
+        <v>2</v>
+      </c>
+      <c r="H25">
+        <v>2</v>
+      </c>
+      <c r="I25" s="98" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" t="s">
+        <v>288</v>
+      </c>
+      <c r="B26" t="s">
+        <v>267</v>
+      </c>
+      <c r="C26">
+        <v>2</v>
+      </c>
+      <c r="D26">
+        <v>2</v>
+      </c>
+      <c r="E26">
+        <v>2</v>
+      </c>
+      <c r="F26">
+        <v>2</v>
+      </c>
+      <c r="G26">
+        <v>2</v>
+      </c>
+      <c r="H26">
+        <v>2</v>
+      </c>
+      <c r="I26" s="98" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" t="s">
+        <v>289</v>
+      </c>
+      <c r="B27" t="s">
+        <v>267</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+      <c r="D27">
+        <v>2</v>
+      </c>
+      <c r="E27">
+        <v>2</v>
+      </c>
+      <c r="F27">
+        <v>2</v>
+      </c>
+      <c r="G27">
+        <v>2</v>
+      </c>
+      <c r="H27">
+        <v>2</v>
+      </c>
+      <c r="I27" s="98" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" t="s">
+        <v>290</v>
+      </c>
+      <c r="B28" t="s">
+        <v>263</v>
+      </c>
+      <c r="C28">
+        <v>2</v>
+      </c>
+      <c r="D28">
+        <v>2</v>
+      </c>
+      <c r="E28">
+        <v>2</v>
+      </c>
+      <c r="F28">
+        <v>2</v>
+      </c>
+      <c r="G28">
+        <v>2</v>
+      </c>
+      <c r="H28">
+        <v>2</v>
+      </c>
+      <c r="I28" s="98" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" t="s">
+        <v>291</v>
+      </c>
+      <c r="B29" t="s">
+        <v>263</v>
+      </c>
+      <c r="C29">
+        <v>2</v>
+      </c>
+      <c r="D29">
+        <v>2</v>
+      </c>
+      <c r="E29">
+        <v>2</v>
+      </c>
+      <c r="F29">
+        <v>2</v>
+      </c>
+      <c r="G29">
+        <v>2</v>
+      </c>
+      <c r="H29">
+        <v>2</v>
+      </c>
+      <c r="I29" s="98" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" t="s">
+        <v>292</v>
+      </c>
+      <c r="B30" t="s">
+        <v>263</v>
+      </c>
+      <c r="C30">
+        <v>2</v>
+      </c>
+      <c r="D30">
+        <v>2</v>
+      </c>
+      <c r="E30">
+        <v>2</v>
+      </c>
+      <c r="F30">
+        <v>2</v>
+      </c>
+      <c r="G30">
+        <v>2</v>
+      </c>
+      <c r="H30">
+        <v>2</v>
+      </c>
+      <c r="I30" s="98" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" t="s">
+        <v>293</v>
+      </c>
+      <c r="B31" t="s">
+        <v>263</v>
+      </c>
+      <c r="C31">
+        <v>2</v>
+      </c>
+      <c r="D31">
+        <v>2</v>
+      </c>
+      <c r="E31">
+        <v>2</v>
+      </c>
+      <c r="F31">
+        <v>2</v>
+      </c>
+      <c r="G31">
+        <v>2</v>
+      </c>
+      <c r="H31">
+        <v>2</v>
+      </c>
+      <c r="I31" s="98" t="s">
+        <v>254</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2912,50 +4010,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="96" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
+      <c r="A1" s="99" t="s">
+        <v>105</v>
+      </c>
+      <c r="B1" s="100"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="100"/>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>1</v>
+        <v>106</v>
       </c>
       <c r="B2" s="47">
         <v>2026</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>2</v>
+        <v>107</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>3</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B3" s="47">
         <v>4</v>
       </c>
-      <c r="B3" s="47">
-        <v>3</v>
-      </c>
       <c r="C3" s="2" t="s">
-        <v>5</v>
+        <v>110</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>6</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="11" t="s">
-        <v>7</v>
+        <v>112</v>
       </c>
       <c r="B4" s="47">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>113</v>
       </c>
       <c r="D4" s="2"/>
     </row>
@@ -2965,49 +4063,49 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="3" t="s">
-        <v>9</v>
+        <v>114</v>
       </c>
       <c r="B6" s="47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>115</v>
       </c>
       <c r="D6" s="2"/>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="3" t="s">
-        <v>11</v>
+        <v>116</v>
       </c>
       <c r="B7" s="47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>12</v>
+        <v>117</v>
       </c>
       <c r="D7" s="2"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="3" t="s">
-        <v>13</v>
+        <v>118</v>
       </c>
       <c r="B8" s="47">
         <v>2</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>14</v>
+        <v>119</v>
       </c>
       <c r="D8" s="2"/>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="9" t="s">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="B9" s="49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>16</v>
+        <v>121</v>
       </c>
       <c r="D9" s="10"/>
     </row>
@@ -3019,49 +4117,49 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="3" t="s">
-        <v>17</v>
+        <v>122</v>
       </c>
       <c r="B11" s="47">
         <v>2</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>18</v>
+        <v>123</v>
       </c>
       <c r="D11" s="2"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="3" t="s">
-        <v>19</v>
+        <v>124</v>
       </c>
       <c r="B12" s="47">
         <v>2</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>20</v>
+        <v>125</v>
       </c>
       <c r="D12" s="2"/>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="3" t="s">
-        <v>21</v>
+        <v>126</v>
       </c>
       <c r="B13" s="47">
         <v>2</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>22</v>
+        <v>127</v>
       </c>
       <c r="D13" s="2"/>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="9" t="s">
-        <v>23</v>
+        <v>128</v>
       </c>
       <c r="B14" s="49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>24</v>
+        <v>129</v>
       </c>
       <c r="D14" s="10"/>
     </row>
@@ -3073,73 +4171,73 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="3" t="s">
-        <v>25</v>
+        <v>130</v>
       </c>
       <c r="B16" s="47">
         <v>5</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>26</v>
+        <v>131</v>
       </c>
       <c r="D16" s="2"/>
     </row>
     <row r="17" spans="1:17">
       <c r="A17" s="9" t="s">
-        <v>27</v>
+        <v>132</v>
       </c>
       <c r="B17" s="49">
         <v>4</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>28</v>
+        <v>133</v>
       </c>
       <c r="D17" s="10"/>
     </row>
     <row r="18" spans="1:17">
       <c r="A18" s="9" t="s">
-        <v>29</v>
+        <v>134</v>
       </c>
       <c r="B18" s="49">
         <v>4</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>30</v>
+        <v>135</v>
       </c>
       <c r="D18" s="10"/>
     </row>
     <row r="19" spans="1:17">
       <c r="A19" s="3" t="s">
-        <v>31</v>
+        <v>136</v>
       </c>
       <c r="B19" s="47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>32</v>
+        <v>137</v>
       </c>
       <c r="D19" s="2"/>
     </row>
     <row r="20" spans="1:17">
       <c r="A20" s="9" t="s">
-        <v>33</v>
+        <v>138</v>
       </c>
       <c r="B20" s="49">
         <v>2</v>
       </c>
       <c r="C20" t="s">
-        <v>34</v>
+        <v>139</v>
       </c>
       <c r="D20" s="10"/>
     </row>
     <row r="21" spans="1:17">
       <c r="A21" s="3" t="s">
-        <v>35</v>
+        <v>140</v>
       </c>
       <c r="B21" s="47">
         <v>2</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>36</v>
+        <v>141</v>
       </c>
       <c r="D21" s="2"/>
     </row>
@@ -3151,85 +4249,85 @@
     </row>
     <row r="23" spans="1:17">
       <c r="A23" s="3" t="s">
-        <v>37</v>
+        <v>142</v>
       </c>
       <c r="B23" s="47">
         <v>120</v>
       </c>
       <c r="C23" s="46" t="s">
-        <v>38</v>
+        <v>143</v>
       </c>
       <c r="D23" s="2"/>
     </row>
     <row r="24" spans="1:17">
       <c r="A24" s="3" t="s">
-        <v>39</v>
+        <v>144</v>
       </c>
       <c r="B24" s="47">
         <v>1000</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>40</v>
+        <v>145</v>
       </c>
       <c r="D24" s="2"/>
     </row>
     <row r="25" spans="1:17">
       <c r="A25" s="3" t="s">
-        <v>41</v>
+        <v>146</v>
       </c>
       <c r="B25" s="47">
         <v>10000</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>42</v>
+        <v>147</v>
       </c>
       <c r="D25" s="2"/>
     </row>
     <row r="26" spans="1:17">
       <c r="A26" s="3" t="s">
-        <v>43</v>
+        <v>148</v>
       </c>
       <c r="B26" s="47">
         <v>8000</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>44</v>
+        <v>149</v>
       </c>
       <c r="D26" s="2"/>
     </row>
     <row r="27" spans="1:17">
       <c r="A27" s="9" t="s">
-        <v>45</v>
+        <v>150</v>
       </c>
       <c r="B27" s="49">
         <v>100</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>46</v>
+        <v>151</v>
       </c>
       <c r="D27" s="10"/>
     </row>
     <row r="28" spans="1:17">
       <c r="A28" s="9" t="s">
-        <v>47</v>
+        <v>152</v>
       </c>
       <c r="B28" s="49">
         <v>8000</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>48</v>
+        <v>153</v>
       </c>
       <c r="D28" s="10"/>
     </row>
     <row r="29" spans="1:17">
       <c r="A29" s="3" t="s">
-        <v>49</v>
+        <v>154</v>
       </c>
       <c r="B29" s="47">
         <v>100</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>50</v>
+        <v>155</v>
       </c>
       <c r="D29" s="2"/>
     </row>
@@ -3247,7 +4345,7 @@
     </row>
     <row r="32" spans="1:17" ht="17.25" customHeight="1">
       <c r="A32" s="63" t="s">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="B32" s="52"/>
       <c r="C32" s="52"/>
@@ -3268,7 +4366,7 @@
     </row>
     <row r="33" spans="1:17" ht="17.25" customHeight="1">
       <c r="A33" s="54" t="s">
-        <v>52</v>
+        <v>156</v>
       </c>
       <c r="B33" s="55"/>
       <c r="C33" s="55"/>
@@ -3308,7 +4406,7 @@
     </row>
     <row r="35" spans="1:17" ht="17.25" customHeight="1">
       <c r="A35" s="54" t="s">
-        <v>53</v>
+        <v>157</v>
       </c>
       <c r="B35" s="55"/>
       <c r="C35" s="55"/>
@@ -3348,7 +4446,7 @@
     </row>
     <row r="37" spans="1:17" ht="17.25" customHeight="1">
       <c r="A37" s="54" t="s">
-        <v>295</v>
+        <v>158</v>
       </c>
       <c r="B37" s="55"/>
       <c r="C37" s="55"/>
@@ -3388,7 +4486,7 @@
     </row>
     <row r="39" spans="1:17" ht="17.25" customHeight="1">
       <c r="A39" s="59" t="s">
-        <v>54</v>
+        <v>159</v>
       </c>
       <c r="B39" s="55"/>
       <c r="C39" s="55"/>
@@ -3428,7 +4526,7 @@
     </row>
     <row r="41" spans="1:17" ht="17.25" customHeight="1">
       <c r="A41" s="59" t="s">
-        <v>55</v>
+        <v>160</v>
       </c>
       <c r="B41" s="55"/>
       <c r="C41" s="55"/>
@@ -3468,7 +4566,7 @@
     </row>
     <row r="43" spans="1:17" ht="17.25" customHeight="1">
       <c r="A43" s="59" t="s">
-        <v>56</v>
+        <v>161</v>
       </c>
       <c r="B43" s="55"/>
       <c r="C43" s="55"/>
@@ -3508,7 +4606,7 @@
     </row>
     <row r="45" spans="1:17" ht="17.25" customHeight="1">
       <c r="A45" s="59" t="s">
-        <v>57</v>
+        <v>162</v>
       </c>
       <c r="B45" s="55"/>
       <c r="C45" s="55"/>
@@ -3548,7 +4646,7 @@
     </row>
     <row r="47" spans="1:17" ht="18" customHeight="1" thickBot="1">
       <c r="A47" s="60" t="s">
-        <v>58</v>
+        <v>163</v>
       </c>
       <c r="B47" s="61"/>
       <c r="C47" s="61"/>
@@ -3571,7 +4669,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -3591,30 +4689,33 @@
   <sheetData>
     <row r="1" spans="1:27" ht="17.25" customHeight="1" thickBot="1">
       <c r="A1" s="1" t="s">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="B1" s="66" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="C1" s="66" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="D1" s="66" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="E1" s="66" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="F1" s="66" t="s">
-        <v>293</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:27">
-      <c r="A2" s="84" t="s">
-        <v>157</v>
+      <c r="A2" s="95" t="s">
+        <v>169</v>
+      </c>
+      <c r="B2" t="s">
+        <v>170</v>
       </c>
       <c r="H2" s="67" t="s">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="I2" s="28"/>
       <c r="J2" s="28"/>
@@ -3638,137 +4739,142 @@
     </row>
     <row r="3" spans="1:27">
       <c r="A3" s="13" t="s">
-        <v>158</v>
+        <v>171</v>
+      </c>
+      <c r="B3" t="s">
+        <v>170</v>
       </c>
       <c r="H3" s="51" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="AA3" s="31"/>
     </row>
     <row r="4" spans="1:27">
-      <c r="A4" s="84" t="s">
-        <v>160</v>
+      <c r="A4" s="95" t="s">
+        <v>173</v>
+      </c>
+      <c r="B4" t="s">
+        <v>170</v>
       </c>
       <c r="H4" s="51" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="AA4" s="31"/>
     </row>
     <row r="5" spans="1:27">
-      <c r="A5" s="13" t="s">
-        <v>162</v>
+      <c r="A5" s="95" t="s">
+        <v>175</v>
+      </c>
+      <c r="B5" t="s">
+        <v>170</v>
       </c>
       <c r="H5" s="51" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="AA5" s="31"/>
     </row>
     <row r="6" spans="1:27">
-      <c r="A6" s="84" t="s">
-        <v>164</v>
+      <c r="A6" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="B6" t="s">
+        <v>170</v>
       </c>
       <c r="H6" s="71"/>
       <c r="AA6" s="31"/>
     </row>
     <row r="7" spans="1:27">
-      <c r="A7" s="13" t="s">
-        <v>165</v>
+      <c r="A7" s="95" t="s">
+        <v>178</v>
+      </c>
+      <c r="B7" t="s">
+        <v>170</v>
       </c>
       <c r="H7" s="71" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="AA7" s="31"/>
     </row>
     <row r="8" spans="1:27">
-      <c r="A8" s="84" t="s">
-        <v>167</v>
+      <c r="A8" s="95" t="s">
+        <v>180</v>
       </c>
       <c r="H8" s="71" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="AA8" s="31"/>
     </row>
     <row r="9" spans="1:27">
       <c r="A9" s="13" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="H9" s="71" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="AA9" s="31"/>
     </row>
     <row r="10" spans="1:27">
-      <c r="A10" s="84" t="s">
-        <v>171</v>
+      <c r="A10" s="95" t="s">
+        <v>184</v>
       </c>
       <c r="H10" s="71"/>
       <c r="AA10" s="31"/>
     </row>
     <row r="11" spans="1:27">
-      <c r="A11" s="13" t="s">
-        <v>172</v>
+      <c r="A11" s="95" t="s">
+        <v>185</v>
       </c>
       <c r="H11" s="71" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="AA11" s="31"/>
     </row>
     <row r="12" spans="1:27">
-      <c r="A12" s="84" t="s">
-        <v>174</v>
+      <c r="A12" s="13" t="s">
+        <v>187</v>
       </c>
       <c r="H12" s="71"/>
       <c r="AA12" s="31"/>
     </row>
     <row r="13" spans="1:27">
-      <c r="A13" s="13" t="s">
-        <v>175</v>
+      <c r="A13" s="95" t="s">
+        <v>188</v>
       </c>
       <c r="H13" s="72" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="AA13" s="31"/>
     </row>
     <row r="14" spans="1:27">
-      <c r="A14" s="84" t="s">
-        <v>253</v>
-      </c>
+      <c r="A14" s="84"/>
       <c r="H14" s="72" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="AA14" s="31"/>
     </row>
     <row r="15" spans="1:27">
-      <c r="A15" s="13" t="s">
-        <v>254</v>
-      </c>
+      <c r="A15" s="13"/>
       <c r="H15" s="73" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="AA15" s="31"/>
     </row>
     <row r="16" spans="1:27" ht="17.25" customHeight="1">
-      <c r="A16" s="84" t="s">
-        <v>255</v>
-      </c>
+      <c r="A16" s="84"/>
       <c r="H16" s="73" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="AA16" s="31"/>
     </row>
     <row r="17" spans="1:27">
-      <c r="A17" s="13" t="s">
-        <v>256</v>
-      </c>
+      <c r="A17" s="13"/>
       <c r="H17" s="73"/>
       <c r="AA17" s="31"/>
     </row>
-    <row r="18" spans="1:27" ht="17.25" thickBot="1">
-      <c r="A18" s="84" t="s">
-        <v>257</v>
-      </c>
-      <c r="H18" s="95" t="s">
-        <v>294</v>
+    <row r="18" spans="1:27" ht="17.25" customHeight="1" thickBot="1">
+      <c r="A18" s="84"/>
+      <c r="H18" s="94" t="s">
+        <v>192</v>
       </c>
       <c r="I18" s="35"/>
       <c r="J18" s="35"/>
@@ -3791,26 +4897,18 @@
       <c r="AA18" s="36"/>
     </row>
     <row r="19" spans="1:27">
-      <c r="A19" s="13" t="s">
-        <v>258</v>
-      </c>
+      <c r="A19" s="13"/>
     </row>
     <row r="20" spans="1:27">
-      <c r="A20" s="84" t="s">
-        <v>259</v>
-      </c>
+      <c r="A20" s="84"/>
     </row>
     <row r="21" spans="1:27">
-      <c r="A21" s="13" t="s">
-        <v>260</v>
-      </c>
+      <c r="A21" s="13"/>
     </row>
     <row r="22" spans="1:27">
-      <c r="A22" s="84" t="s">
-        <v>261</v>
-      </c>
+      <c r="A22" s="84"/>
       <c r="H22" s="17" t="s">
-        <v>91</v>
+        <v>43</v>
       </c>
       <c r="I22" s="64"/>
       <c r="J22" s="64"/>
@@ -3820,9 +4918,7 @@
       <c r="N22" s="64"/>
     </row>
     <row r="23" spans="1:27">
-      <c r="A23" s="13" t="s">
-        <v>262</v>
-      </c>
+      <c r="A23" s="13"/>
       <c r="H23" s="85"/>
       <c r="I23" s="64"/>
       <c r="J23" s="64"/>
@@ -3832,11 +4928,9 @@
       <c r="N23" s="64"/>
     </row>
     <row r="24" spans="1:27">
-      <c r="A24" s="84" t="s">
-        <v>263</v>
-      </c>
+      <c r="A24" s="84"/>
       <c r="H24" s="86" t="s">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="I24" s="64"/>
       <c r="J24" s="64"/>
@@ -3846,9 +4940,7 @@
       <c r="N24" s="64"/>
     </row>
     <row r="25" spans="1:27">
-      <c r="A25" s="13" t="s">
-        <v>264</v>
-      </c>
+      <c r="A25" s="13"/>
       <c r="H25" s="87"/>
       <c r="I25" s="64"/>
       <c r="J25" s="64"/>
@@ -3858,11 +4950,9 @@
       <c r="N25" s="64"/>
     </row>
     <row r="26" spans="1:27">
-      <c r="A26" s="84" t="s">
-        <v>265</v>
-      </c>
+      <c r="A26" s="84"/>
       <c r="H26" s="86" t="s">
-        <v>93</v>
+        <v>45</v>
       </c>
       <c r="I26" s="64"/>
       <c r="J26" s="64"/>
@@ -3872,9 +4962,7 @@
       <c r="N26" s="64"/>
     </row>
     <row r="27" spans="1:27">
-      <c r="A27" s="13" t="s">
-        <v>266</v>
-      </c>
+      <c r="A27" s="13"/>
       <c r="H27" s="87"/>
       <c r="I27" s="64"/>
       <c r="J27" s="64"/>
@@ -3884,11 +4972,9 @@
       <c r="N27" s="64"/>
     </row>
     <row r="28" spans="1:27">
-      <c r="A28" s="84" t="s">
-        <v>267</v>
-      </c>
+      <c r="A28" s="84"/>
       <c r="H28" s="86" t="s">
-        <v>94</v>
+        <v>46</v>
       </c>
       <c r="I28" s="64"/>
       <c r="J28" s="64"/>
@@ -3898,9 +4984,7 @@
       <c r="N28" s="64"/>
     </row>
     <row r="29" spans="1:27">
-      <c r="A29" s="13" t="s">
-        <v>268</v>
-      </c>
+      <c r="A29" s="13"/>
       <c r="H29" s="87"/>
       <c r="I29" s="64"/>
       <c r="J29" s="64"/>
@@ -3910,11 +4994,9 @@
       <c r="N29" s="64"/>
     </row>
     <row r="30" spans="1:27">
-      <c r="A30" s="84" t="s">
-        <v>269</v>
-      </c>
+      <c r="A30" s="84"/>
       <c r="H30" s="86" t="s">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="I30" s="64"/>
       <c r="J30" s="64"/>
@@ -3924,9 +5006,7 @@
       <c r="N30" s="64"/>
     </row>
     <row r="31" spans="1:27">
-      <c r="A31" s="84" t="s">
-        <v>270</v>
-      </c>
+      <c r="A31" s="84"/>
       <c r="H31" s="87"/>
       <c r="I31" s="64"/>
       <c r="J31" s="64"/>
@@ -3936,11 +5016,9 @@
       <c r="N31" s="64"/>
     </row>
     <row r="32" spans="1:27">
-      <c r="A32" s="13" t="s">
-        <v>271</v>
-      </c>
+      <c r="A32" s="13"/>
       <c r="H32" s="86" t="s">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="I32" s="64"/>
       <c r="J32" s="64"/>
@@ -3950,9 +5028,7 @@
       <c r="N32" s="64"/>
     </row>
     <row r="33" spans="1:14">
-      <c r="A33" s="84" t="s">
-        <v>272</v>
-      </c>
+      <c r="A33" s="84"/>
       <c r="H33" s="87"/>
       <c r="I33" s="64"/>
       <c r="J33" s="64"/>
@@ -3962,11 +5038,9 @@
       <c r="N33" s="64"/>
     </row>
     <row r="34" spans="1:14">
-      <c r="A34" s="13" t="s">
-        <v>273</v>
-      </c>
+      <c r="A34" s="13"/>
       <c r="H34" s="86" t="s">
-        <v>97</v>
+        <v>49</v>
       </c>
       <c r="I34" s="64"/>
       <c r="J34" s="64"/>
@@ -3976,95 +5050,61 @@
       <c r="N34" s="64"/>
     </row>
     <row r="35" spans="1:14">
-      <c r="A35" s="84" t="s">
-        <v>274</v>
-      </c>
+      <c r="A35" s="84"/>
     </row>
     <row r="36" spans="1:14">
-      <c r="A36" s="13" t="s">
-        <v>275</v>
-      </c>
+      <c r="A36" s="13"/>
       <c r="H36" s="23" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
     </row>
     <row r="37" spans="1:14">
-      <c r="A37" s="84" t="s">
-        <v>276</v>
-      </c>
+      <c r="A37" s="84"/>
     </row>
     <row r="38" spans="1:14">
-      <c r="A38" s="13" t="s">
-        <v>277</v>
-      </c>
+      <c r="A38" s="13"/>
     </row>
     <row r="39" spans="1:14">
-      <c r="A39" s="84" t="s">
-        <v>278</v>
-      </c>
+      <c r="A39" s="84"/>
     </row>
     <row r="40" spans="1:14">
-      <c r="A40" s="13" t="s">
-        <v>279</v>
-      </c>
+      <c r="A40" s="13"/>
     </row>
     <row r="41" spans="1:14">
-      <c r="A41" s="84" t="s">
-        <v>280</v>
-      </c>
+      <c r="A41" s="84"/>
     </row>
     <row r="42" spans="1:14">
-      <c r="A42" s="13" t="s">
-        <v>281</v>
-      </c>
+      <c r="A42" s="13"/>
     </row>
     <row r="43" spans="1:14">
-      <c r="A43" s="84" t="s">
-        <v>282</v>
-      </c>
+      <c r="A43" s="84"/>
     </row>
     <row r="44" spans="1:14">
-      <c r="A44" s="13" t="s">
-        <v>283</v>
-      </c>
+      <c r="A44" s="13"/>
     </row>
     <row r="45" spans="1:14">
-      <c r="A45" s="84" t="s">
-        <v>284</v>
-      </c>
+      <c r="A45" s="84"/>
     </row>
     <row r="46" spans="1:14">
-      <c r="A46" s="13" t="s">
-        <v>285</v>
-      </c>
+      <c r="A46" s="13"/>
     </row>
     <row r="47" spans="1:14">
-      <c r="A47" s="84" t="s">
-        <v>286</v>
-      </c>
+      <c r="A47" s="84"/>
     </row>
     <row r="48" spans="1:14">
-      <c r="A48" s="13" t="s">
-        <v>287</v>
-      </c>
+      <c r="A48" s="13"/>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="84" t="s">
-        <v>288</v>
-      </c>
+      <c r="A49" s="84"/>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="13" t="s">
-        <v>289</v>
-      </c>
+      <c r="A50" s="13"/>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="13" t="s">
-        <v>290</v>
-      </c>
+      <c r="A51" s="13"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -4081,17 +5121,17 @@
   <sheetData>
     <row r="1" spans="1:19" ht="17.25" customHeight="1" thickBot="1">
       <c r="A1" s="1" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="2" spans="1:19">
       <c r="A2" s="12"/>
       <c r="B2" s="4"/>
       <c r="E2" s="67" t="s">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="F2" s="28"/>
       <c r="G2" s="28"/>
@@ -4112,7 +5152,7 @@
       <c r="A3" s="12"/>
       <c r="B3" s="4"/>
       <c r="E3" s="68" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="S3" s="31"/>
     </row>
@@ -4126,7 +5166,7 @@
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="E5" s="68" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="S5" s="31"/>
     </row>
@@ -4140,7 +5180,7 @@
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="E7" s="68" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="S7" s="31"/>
     </row>
@@ -4148,7 +5188,7 @@
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="E8" s="68" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="S8" s="31"/>
     </row>
@@ -4156,7 +5196,7 @@
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="E9" s="69" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="S9" s="31"/>
     </row>
@@ -4170,7 +5210,7 @@
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="E11" s="68" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="S11" s="31"/>
     </row>
@@ -4178,7 +5218,7 @@
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="E12" s="68" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="S12" s="31"/>
     </row>
@@ -4186,7 +5226,7 @@
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="E13" s="68" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="S13" s="31"/>
     </row>
@@ -4194,7 +5234,7 @@
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="E14" s="69" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="S14" s="31"/>
     </row>
@@ -4208,19 +5248,19 @@
     </row>
     <row r="17" spans="5:19">
       <c r="E17" s="68" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="S17" s="31"/>
     </row>
     <row r="18" spans="5:19">
       <c r="E18" s="68" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="S18" s="31"/>
     </row>
     <row r="19" spans="5:19" ht="17.25" customHeight="1" thickBot="1">
       <c r="E19" s="70" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F19" s="35"/>
       <c r="G19" s="35"/>
@@ -4238,7 +5278,7 @@
       <c r="S19" s="36"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -4256,113 +5296,101 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="84" t="str">
-        <f>IF(Nurses!A2="","",Nurses!A2)</f>
-        <v>간호사1</v>
+      <c r="A2" s="84" t="s">
+        <v>169</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
       <c r="F2" s="23" t="s">
-        <v>51</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="84" t="str">
-        <f>IF(Nurses!A3="","",Nurses!A3)</f>
-        <v>간호사2</v>
+      <c r="A3" s="84" t="s">
+        <v>171</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
       <c r="F3" s="11" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="84" t="str">
-        <f>IF(Nurses!A4="","",Nurses!A4)</f>
-        <v>간호사3</v>
+      <c r="A4" s="84" t="s">
+        <v>173</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="84" t="str">
-        <f>IF(Nurses!A5="","",Nurses!A5)</f>
-        <v>간호사4</v>
+      <c r="A5" s="84" t="s">
+        <v>175</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="84" t="str">
-        <f>IF(Nurses!A6="","",Nurses!A6)</f>
-        <v>간호사5</v>
+      <c r="A6" s="84" t="s">
+        <v>177</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="84" t="str">
-        <f>IF(Nurses!A7="","",Nurses!A7)</f>
-        <v>간호사6</v>
+      <c r="A7" s="84" t="s">
+        <v>178</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="84" t="str">
-        <f>IF(Nurses!A8="","",Nurses!A8)</f>
-        <v>간호사7</v>
+      <c r="A8" s="84" t="s">
+        <v>180</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="84" t="str">
-        <f>IF(Nurses!A9="","",Nurses!A9)</f>
-        <v>간호사8</v>
+      <c r="A9" s="84" t="s">
+        <v>182</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="84" t="str">
-        <f>IF(Nurses!A10="","",Nurses!A10)</f>
-        <v>간호사9</v>
+      <c r="A10" s="84" t="s">
+        <v>184</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="84" t="str">
-        <f>IF(Nurses!A11="","",Nurses!A11)</f>
-        <v>간호사10</v>
+      <c r="A11" s="84" t="s">
+        <v>185</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="84" t="str">
-        <f>IF(Nurses!A12="","",Nurses!A12)</f>
-        <v>간호사11</v>
+      <c r="A12" s="84" t="s">
+        <v>187</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="84" t="str">
-        <f>IF(Nurses!A13="","",Nurses!A13)</f>
-        <v>간호사12</v>
+      <c r="A13" s="84" t="s">
+        <v>188</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -4370,7 +5398,7 @@
     <row r="14" spans="1:6">
       <c r="A14" s="84" t="str">
         <f>IF(Nurses!A14="","",Nurses!A14)</f>
-        <v>간호사13</v>
+        <v/>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
@@ -4378,7 +5406,7 @@
     <row r="15" spans="1:6">
       <c r="A15" s="84" t="str">
         <f>IF(Nurses!A15="","",Nurses!A15)</f>
-        <v>간호사14</v>
+        <v/>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -4386,7 +5414,7 @@
     <row r="16" spans="1:6">
       <c r="A16" s="84" t="str">
         <f>IF(Nurses!A16="","",Nurses!A16)</f>
-        <v>간호사15</v>
+        <v/>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -4394,7 +5422,7 @@
     <row r="17" spans="1:3">
       <c r="A17" s="84" t="str">
         <f>IF(Nurses!A17="","",Nurses!A17)</f>
-        <v>간호사16</v>
+        <v/>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -4402,7 +5430,7 @@
     <row r="18" spans="1:3">
       <c r="A18" s="84" t="str">
         <f>IF(Nurses!A18="","",Nurses!A18)</f>
-        <v>간호사17</v>
+        <v/>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -4410,7 +5438,7 @@
     <row r="19" spans="1:3">
       <c r="A19" s="84" t="str">
         <f>IF(Nurses!A19="","",Nurses!A19)</f>
-        <v>간호사18</v>
+        <v/>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -4418,7 +5446,7 @@
     <row r="20" spans="1:3">
       <c r="A20" s="84" t="str">
         <f>IF(Nurses!A20="","",Nurses!A20)</f>
-        <v>간호사19</v>
+        <v/>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -4426,7 +5454,7 @@
     <row r="21" spans="1:3">
       <c r="A21" s="84" t="str">
         <f>IF(Nurses!A21="","",Nurses!A21)</f>
-        <v>간호사20</v>
+        <v/>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -4434,7 +5462,7 @@
     <row r="22" spans="1:3">
       <c r="A22" s="84" t="str">
         <f>IF(Nurses!A22="","",Nurses!A22)</f>
-        <v>간호사21</v>
+        <v/>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -4442,7 +5470,7 @@
     <row r="23" spans="1:3">
       <c r="A23" s="84" t="str">
         <f>IF(Nurses!A23="","",Nurses!A23)</f>
-        <v>간호사22</v>
+        <v/>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -4450,7 +5478,7 @@
     <row r="24" spans="1:3">
       <c r="A24" s="84" t="str">
         <f>IF(Nurses!A24="","",Nurses!A24)</f>
-        <v>간호사23</v>
+        <v/>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
@@ -4458,7 +5486,7 @@
     <row r="25" spans="1:3">
       <c r="A25" s="84" t="str">
         <f>IF(Nurses!A25="","",Nurses!A25)</f>
-        <v>간호사24</v>
+        <v/>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -4466,7 +5494,7 @@
     <row r="26" spans="1:3">
       <c r="A26" s="84" t="str">
         <f>IF(Nurses!A26="","",Nurses!A26)</f>
-        <v>간호사25</v>
+        <v/>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -4474,7 +5502,7 @@
     <row r="27" spans="1:3">
       <c r="A27" s="84" t="str">
         <f>IF(Nurses!A27="","",Nurses!A27)</f>
-        <v>간호사26</v>
+        <v/>
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
@@ -4482,7 +5510,7 @@
     <row r="28" spans="1:3">
       <c r="A28" s="84" t="str">
         <f>IF(Nurses!A28="","",Nurses!A28)</f>
-        <v>간호사27</v>
+        <v/>
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
@@ -4490,7 +5518,7 @@
     <row r="29" spans="1:3">
       <c r="A29" s="84" t="str">
         <f>IF(Nurses!A29="","",Nurses!A29)</f>
-        <v>간호사28</v>
+        <v/>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -4498,7 +5526,7 @@
     <row r="30" spans="1:3">
       <c r="A30" s="84" t="str">
         <f>IF(Nurses!A30="","",Nurses!A30)</f>
-        <v>간호사29</v>
+        <v/>
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -4506,7 +5534,7 @@
     <row r="31" spans="1:3">
       <c r="A31" s="84" t="str">
         <f>IF(Nurses!A31="","",Nurses!A31)</f>
-        <v>간호사30</v>
+        <v/>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -4514,7 +5542,7 @@
     <row r="32" spans="1:3">
       <c r="A32" s="84" t="str">
         <f>IF(Nurses!A32="","",Nurses!A32)</f>
-        <v>간호사31</v>
+        <v/>
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -4522,7 +5550,7 @@
     <row r="33" spans="1:3">
       <c r="A33" s="84" t="str">
         <f>IF(Nurses!A33="","",Nurses!A33)</f>
-        <v>간호사32</v>
+        <v/>
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -4530,7 +5558,7 @@
     <row r="34" spans="1:3">
       <c r="A34" s="84" t="str">
         <f>IF(Nurses!A34="","",Nurses!A34)</f>
-        <v>간호사33</v>
+        <v/>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -4538,7 +5566,7 @@
     <row r="35" spans="1:3">
       <c r="A35" s="84" t="str">
         <f>IF(Nurses!A35="","",Nurses!A35)</f>
-        <v>간호사34</v>
+        <v/>
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -4546,7 +5574,7 @@
     <row r="36" spans="1:3">
       <c r="A36" s="84" t="str">
         <f>IF(Nurses!A36="","",Nurses!A36)</f>
-        <v>간호사35</v>
+        <v/>
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
@@ -4554,7 +5582,7 @@
     <row r="37" spans="1:3">
       <c r="A37" s="84" t="str">
         <f>IF(Nurses!A37="","",Nurses!A37)</f>
-        <v>간호사36</v>
+        <v/>
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -4562,7 +5590,7 @@
     <row r="38" spans="1:3">
       <c r="A38" s="84" t="str">
         <f>IF(Nurses!A38="","",Nurses!A38)</f>
-        <v>간호사37</v>
+        <v/>
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
@@ -4570,7 +5598,7 @@
     <row r="39" spans="1:3">
       <c r="A39" s="84" t="str">
         <f>IF(Nurses!A39="","",Nurses!A39)</f>
-        <v>간호사38</v>
+        <v/>
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
@@ -4578,7 +5606,7 @@
     <row r="40" spans="1:3">
       <c r="A40" s="84" t="str">
         <f>IF(Nurses!A40="","",Nurses!A40)</f>
-        <v>간호사39</v>
+        <v/>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -4586,7 +5614,7 @@
     <row r="41" spans="1:3">
       <c r="A41" s="84" t="str">
         <f>IF(Nurses!A41="","",Nurses!A41)</f>
-        <v>간호사40</v>
+        <v/>
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -4594,7 +5622,7 @@
     <row r="42" spans="1:3">
       <c r="A42" s="84" t="str">
         <f>IF(Nurses!A42="","",Nurses!A42)</f>
-        <v>간호사41</v>
+        <v/>
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
@@ -4602,7 +5630,7 @@
     <row r="43" spans="1:3">
       <c r="A43" s="84" t="str">
         <f>IF(Nurses!A43="","",Nurses!A43)</f>
-        <v>간호사42</v>
+        <v/>
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -4610,7 +5638,7 @@
     <row r="44" spans="1:3">
       <c r="A44" s="84" t="str">
         <f>IF(Nurses!A44="","",Nurses!A44)</f>
-        <v>간호사43</v>
+        <v/>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -4618,7 +5646,7 @@
     <row r="45" spans="1:3">
       <c r="A45" s="84" t="str">
         <f>IF(Nurses!A45="","",Nurses!A45)</f>
-        <v>간호사44</v>
+        <v/>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -4626,7 +5654,7 @@
     <row r="46" spans="1:3">
       <c r="A46" s="84" t="str">
         <f>IF(Nurses!A46="","",Nurses!A46)</f>
-        <v>간호사45</v>
+        <v/>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -4634,7 +5662,7 @@
     <row r="47" spans="1:3">
       <c r="A47" s="84" t="str">
         <f>IF(Nurses!A47="","",Nurses!A47)</f>
-        <v>간호사46</v>
+        <v/>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -4642,7 +5670,7 @@
     <row r="48" spans="1:3">
       <c r="A48" s="84" t="str">
         <f>IF(Nurses!A48="","",Nurses!A48)</f>
-        <v>간호사47</v>
+        <v/>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -4650,7 +5678,7 @@
     <row r="49" spans="1:3">
       <c r="A49" s="84" t="str">
         <f>IF(Nurses!A49="","",Nurses!A49)</f>
-        <v>간호사48</v>
+        <v/>
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
@@ -4658,7 +5686,7 @@
     <row r="50" spans="1:3">
       <c r="A50" s="84" t="str">
         <f>IF(Nurses!A50="","",Nurses!A50)</f>
-        <v>간호사49</v>
+        <v/>
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
@@ -4666,13 +5694,13 @@
     <row r="51" spans="1:3">
       <c r="A51" s="84" t="str">
         <f>IF(Nurses!A51="","",Nurses!A51)</f>
-        <v>간호사50</v>
+        <v/>
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4688,7 +5716,7 @@
   <sheetData>
     <row r="1" spans="1:45" ht="17.25" customHeight="1">
       <c r="A1" s="5" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="B1" s="5">
         <v>1</v>
@@ -4780,18 +5808,15 @@
       <c r="AE1" s="5">
         <v>30</v>
       </c>
-      <c r="AF1" s="5">
-        <v>31</v>
-      </c>
+      <c r="AF1" s="5"/>
       <c r="AG1" s="6"/>
       <c r="AH1" s="75" t="s">
-        <v>51</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:45" ht="17.25" customHeight="1">
-      <c r="A2" s="84" t="str">
-        <f>IF(Nurses!A2="","",Nurses!A2)</f>
-        <v>간호사1</v>
+      <c r="A2" s="84" t="s">
+        <v>169</v>
       </c>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -4826,7 +5851,7 @@
       <c r="AF2" s="7"/>
       <c r="AG2" s="6"/>
       <c r="AH2" s="76" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="AI2" s="74"/>
       <c r="AJ2" s="74"/>
@@ -4841,9 +5866,8 @@
       <c r="AS2" s="74"/>
     </row>
     <row r="3" spans="1:45" ht="17.25" customHeight="1">
-      <c r="A3" s="84" t="str">
-        <f>IF(Nurses!A3="","",Nurses!A3)</f>
-        <v>간호사2</v>
+      <c r="A3" s="84" t="s">
+        <v>171</v>
       </c>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -4878,7 +5902,7 @@
       <c r="AF3" s="7"/>
       <c r="AG3" s="6"/>
       <c r="AH3" s="77" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="AI3" s="74"/>
       <c r="AJ3" s="74"/>
@@ -4893,9 +5917,8 @@
       <c r="AS3" s="74"/>
     </row>
     <row r="4" spans="1:45" ht="17.25" customHeight="1">
-      <c r="A4" s="84" t="str">
-        <f>IF(Nurses!A4="","",Nurses!A4)</f>
-        <v>간호사3</v>
+      <c r="A4" s="84" t="s">
+        <v>173</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -4930,7 +5953,7 @@
       <c r="AF4" s="7"/>
       <c r="AG4" s="6"/>
       <c r="AH4" s="77" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="AI4" s="74"/>
       <c r="AJ4" s="74"/>
@@ -4945,9 +5968,8 @@
       <c r="AS4" s="74"/>
     </row>
     <row r="5" spans="1:45" ht="17.25" customHeight="1">
-      <c r="A5" s="84" t="str">
-        <f>IF(Nurses!A5="","",Nurses!A5)</f>
-        <v>간호사4</v>
+      <c r="A5" s="84" t="s">
+        <v>175</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -4995,9 +6017,8 @@
       <c r="AS5" s="74"/>
     </row>
     <row r="6" spans="1:45" ht="17.25" customHeight="1">
-      <c r="A6" s="84" t="str">
-        <f>IF(Nurses!A6="","",Nurses!A6)</f>
-        <v>간호사5</v>
+      <c r="A6" s="84" t="s">
+        <v>177</v>
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
@@ -5032,7 +6053,7 @@
       <c r="AF6" s="7"/>
       <c r="AG6" s="6"/>
       <c r="AH6" s="76" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="AI6" s="74"/>
       <c r="AJ6" s="74"/>
@@ -5047,9 +6068,8 @@
       <c r="AS6" s="74"/>
     </row>
     <row r="7" spans="1:45" ht="17.25" customHeight="1">
-      <c r="A7" s="84" t="str">
-        <f>IF(Nurses!A7="","",Nurses!A7)</f>
-        <v>간호사6</v>
+      <c r="A7" s="84" t="s">
+        <v>178</v>
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
@@ -5084,7 +6104,7 @@
       <c r="AF7" s="7"/>
       <c r="AG7" s="6"/>
       <c r="AH7" s="77" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="AI7" s="74"/>
       <c r="AJ7" s="74"/>
@@ -5099,9 +6119,8 @@
       <c r="AS7" s="74"/>
     </row>
     <row r="8" spans="1:45" ht="17.25" customHeight="1">
-      <c r="A8" s="84" t="str">
-        <f>IF(Nurses!A8="","",Nurses!A8)</f>
-        <v>간호사7</v>
+      <c r="A8" s="84" t="s">
+        <v>180</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -5149,9 +6168,8 @@
       <c r="AS8" s="74"/>
     </row>
     <row r="9" spans="1:45" ht="17.25" customHeight="1">
-      <c r="A9" s="84" t="str">
-        <f>IF(Nurses!A9="","",Nurses!A9)</f>
-        <v>간호사8</v>
+      <c r="A9" s="84" t="s">
+        <v>182</v>
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -5186,7 +6204,7 @@
       <c r="AF9" s="7"/>
       <c r="AG9" s="6"/>
       <c r="AH9" s="76" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="AI9" s="74"/>
       <c r="AJ9" s="74"/>
@@ -5201,9 +6219,8 @@
       <c r="AS9" s="74"/>
     </row>
     <row r="10" spans="1:45" ht="17.25" customHeight="1">
-      <c r="A10" s="84" t="str">
-        <f>IF(Nurses!A10="","",Nurses!A10)</f>
-        <v>간호사9</v>
+      <c r="A10" s="84" t="s">
+        <v>184</v>
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -5238,7 +6255,7 @@
       <c r="AF10" s="7"/>
       <c r="AG10" s="6"/>
       <c r="AH10" s="77" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="AI10" s="74"/>
       <c r="AJ10" s="74"/>
@@ -5253,9 +6270,8 @@
       <c r="AS10" s="74"/>
     </row>
     <row r="11" spans="1:45" ht="17.25" customHeight="1">
-      <c r="A11" s="84" t="str">
-        <f>IF(Nurses!A11="","",Nurses!A11)</f>
-        <v>간호사10</v>
+      <c r="A11" s="84" t="s">
+        <v>185</v>
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
@@ -5303,9 +6319,8 @@
       <c r="AS11" s="74"/>
     </row>
     <row r="12" spans="1:45" ht="17.25" customHeight="1">
-      <c r="A12" s="84" t="str">
-        <f>IF(Nurses!A12="","",Nurses!A12)</f>
-        <v>간호사11</v>
+      <c r="A12" s="84" t="s">
+        <v>187</v>
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
@@ -5340,7 +6355,7 @@
       <c r="AF12" s="7"/>
       <c r="AG12" s="6"/>
       <c r="AH12" s="77" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="AI12" s="74"/>
       <c r="AJ12" s="74"/>
@@ -5355,9 +6370,8 @@
       <c r="AS12" s="74"/>
     </row>
     <row r="13" spans="1:45" ht="17.25" customHeight="1">
-      <c r="A13" s="84" t="str">
-        <f>IF(Nurses!A13="","",Nurses!A13)</f>
-        <v>간호사12</v>
+      <c r="A13" s="84" t="s">
+        <v>188</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -5392,7 +6406,7 @@
       <c r="AF13" s="7"/>
       <c r="AG13" s="6"/>
       <c r="AH13" s="78" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="AI13" s="74"/>
       <c r="AJ13" s="74"/>
@@ -5409,7 +6423,7 @@
     <row r="14" spans="1:45" ht="17.25" customHeight="1">
       <c r="A14" s="84" t="str">
         <f>IF(Nurses!A14="","",Nurses!A14)</f>
-        <v>간호사13</v>
+        <v/>
       </c>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -5443,7 +6457,7 @@
       <c r="AE14" s="7"/>
       <c r="AF14" s="7"/>
       <c r="AH14" s="78" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="AI14" s="74"/>
       <c r="AJ14" s="74"/>
@@ -5460,7 +6474,7 @@
     <row r="15" spans="1:45">
       <c r="A15" s="84" t="str">
         <f>IF(Nurses!A15="","",Nurses!A15)</f>
-        <v>간호사14</v>
+        <v/>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -5497,7 +6511,7 @@
     <row r="16" spans="1:45">
       <c r="A16" s="84" t="str">
         <f>IF(Nurses!A16="","",Nurses!A16)</f>
-        <v>간호사15</v>
+        <v/>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -5534,7 +6548,7 @@
     <row r="17" spans="1:34">
       <c r="A17" s="84" t="str">
         <f>IF(Nurses!A17="","",Nurses!A17)</f>
-        <v>간호사16</v>
+        <v/>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -5571,7 +6585,7 @@
     <row r="18" spans="1:34">
       <c r="A18" s="84" t="str">
         <f>IF(Nurses!A18="","",Nurses!A18)</f>
-        <v>간호사17</v>
+        <v/>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -5609,7 +6623,7 @@
     <row r="19" spans="1:34">
       <c r="A19" s="84" t="str">
         <f>IF(Nurses!A19="","",Nurses!A19)</f>
-        <v>간호사18</v>
+        <v/>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -5646,7 +6660,7 @@
     <row r="20" spans="1:34">
       <c r="A20" s="84" t="str">
         <f>IF(Nurses!A20="","",Nurses!A20)</f>
-        <v>간호사19</v>
+        <v/>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -5684,7 +6698,7 @@
     <row r="21" spans="1:34">
       <c r="A21" s="84" t="str">
         <f>IF(Nurses!A21="","",Nurses!A21)</f>
-        <v>간호사20</v>
+        <v/>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -5721,7 +6735,7 @@
     <row r="22" spans="1:34">
       <c r="A22" s="84" t="str">
         <f>IF(Nurses!A22="","",Nurses!A22)</f>
-        <v>간호사21</v>
+        <v/>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -5758,7 +6772,7 @@
     <row r="23" spans="1:34">
       <c r="A23" s="84" t="str">
         <f>IF(Nurses!A23="","",Nurses!A23)</f>
-        <v>간호사22</v>
+        <v/>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -5795,7 +6809,7 @@
     <row r="24" spans="1:34">
       <c r="A24" s="84" t="str">
         <f>IF(Nurses!A24="","",Nurses!A24)</f>
-        <v>간호사23</v>
+        <v/>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -5832,7 +6846,7 @@
     <row r="25" spans="1:34">
       <c r="A25" s="84" t="str">
         <f>IF(Nurses!A25="","",Nurses!A25)</f>
-        <v>간호사24</v>
+        <v/>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -5870,7 +6884,7 @@
     <row r="26" spans="1:34">
       <c r="A26" s="84" t="str">
         <f>IF(Nurses!A26="","",Nurses!A26)</f>
-        <v>간호사25</v>
+        <v/>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
@@ -5908,7 +6922,7 @@
     <row r="27" spans="1:34">
       <c r="A27" s="84" t="str">
         <f>IF(Nurses!A27="","",Nurses!A27)</f>
-        <v>간호사26</v>
+        <v/>
       </c>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
@@ -5945,7 +6959,7 @@
     <row r="28" spans="1:34">
       <c r="A28" s="84" t="str">
         <f>IF(Nurses!A28="","",Nurses!A28)</f>
-        <v>간호사27</v>
+        <v/>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
@@ -5982,7 +6996,7 @@
     <row r="29" spans="1:34">
       <c r="A29" s="84" t="str">
         <f>IF(Nurses!A29="","",Nurses!A29)</f>
-        <v>간호사28</v>
+        <v/>
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
@@ -6019,7 +7033,7 @@
     <row r="30" spans="1:34">
       <c r="A30" s="84" t="str">
         <f>IF(Nurses!A30="","",Nurses!A30)</f>
-        <v>간호사29</v>
+        <v/>
       </c>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
@@ -6056,7 +7070,7 @@
     <row r="31" spans="1:34">
       <c r="A31" s="84" t="str">
         <f>IF(Nurses!A31="","",Nurses!A31)</f>
-        <v>간호사30</v>
+        <v/>
       </c>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
@@ -6093,7 +7107,7 @@
     <row r="32" spans="1:34">
       <c r="A32" s="84" t="str">
         <f>IF(Nurses!A32="","",Nurses!A32)</f>
-        <v>간호사31</v>
+        <v/>
       </c>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
@@ -6130,7 +7144,7 @@
     <row r="33" spans="1:32">
       <c r="A33" s="84" t="str">
         <f>IF(Nurses!A33="","",Nurses!A33)</f>
-        <v>간호사32</v>
+        <v/>
       </c>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
@@ -6167,7 +7181,7 @@
     <row r="34" spans="1:32">
       <c r="A34" s="84" t="str">
         <f>IF(Nurses!A34="","",Nurses!A34)</f>
-        <v>간호사33</v>
+        <v/>
       </c>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
@@ -6204,7 +7218,7 @@
     <row r="35" spans="1:32">
       <c r="A35" s="84" t="str">
         <f>IF(Nurses!A35="","",Nurses!A35)</f>
-        <v>간호사34</v>
+        <v/>
       </c>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
@@ -6241,7 +7255,7 @@
     <row r="36" spans="1:32">
       <c r="A36" s="84" t="str">
         <f>IF(Nurses!A36="","",Nurses!A36)</f>
-        <v>간호사35</v>
+        <v/>
       </c>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
@@ -6278,7 +7292,7 @@
     <row r="37" spans="1:32">
       <c r="A37" s="84" t="str">
         <f>IF(Nurses!A37="","",Nurses!A37)</f>
-        <v>간호사36</v>
+        <v/>
       </c>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
@@ -6315,7 +7329,7 @@
     <row r="38" spans="1:32">
       <c r="A38" s="84" t="str">
         <f>IF(Nurses!A38="","",Nurses!A38)</f>
-        <v>간호사37</v>
+        <v/>
       </c>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
@@ -6352,7 +7366,7 @@
     <row r="39" spans="1:32">
       <c r="A39" s="84" t="str">
         <f>IF(Nurses!A39="","",Nurses!A39)</f>
-        <v>간호사38</v>
+        <v/>
       </c>
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
@@ -6389,7 +7403,7 @@
     <row r="40" spans="1:32">
       <c r="A40" s="84" t="str">
         <f>IF(Nurses!A40="","",Nurses!A40)</f>
-        <v>간호사39</v>
+        <v/>
       </c>
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
@@ -6426,7 +7440,7 @@
     <row r="41" spans="1:32">
       <c r="A41" s="84" t="str">
         <f>IF(Nurses!A41="","",Nurses!A41)</f>
-        <v>간호사40</v>
+        <v/>
       </c>
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
@@ -6463,7 +7477,7 @@
     <row r="42" spans="1:32">
       <c r="A42" s="84" t="str">
         <f>IF(Nurses!A42="","",Nurses!A42)</f>
-        <v>간호사41</v>
+        <v/>
       </c>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
@@ -6500,7 +7514,7 @@
     <row r="43" spans="1:32">
       <c r="A43" s="84" t="str">
         <f>IF(Nurses!A43="","",Nurses!A43)</f>
-        <v>간호사42</v>
+        <v/>
       </c>
       <c r="B43" s="7"/>
       <c r="C43" s="7"/>
@@ -6537,7 +7551,7 @@
     <row r="44" spans="1:32">
       <c r="A44" s="84" t="str">
         <f>IF(Nurses!A44="","",Nurses!A44)</f>
-        <v>간호사43</v>
+        <v/>
       </c>
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
@@ -6574,7 +7588,7 @@
     <row r="45" spans="1:32">
       <c r="A45" s="84" t="str">
         <f>IF(Nurses!A45="","",Nurses!A45)</f>
-        <v>간호사44</v>
+        <v/>
       </c>
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
@@ -6611,7 +7625,7 @@
     <row r="46" spans="1:32">
       <c r="A46" s="84" t="str">
         <f>IF(Nurses!A46="","",Nurses!A46)</f>
-        <v>간호사45</v>
+        <v/>
       </c>
       <c r="B46" s="7"/>
       <c r="C46" s="7"/>
@@ -6648,7 +7662,7 @@
     <row r="47" spans="1:32">
       <c r="A47" s="84" t="str">
         <f>IF(Nurses!A47="","",Nurses!A47)</f>
-        <v>간호사46</v>
+        <v/>
       </c>
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
@@ -6685,7 +7699,7 @@
     <row r="48" spans="1:32">
       <c r="A48" s="84" t="str">
         <f>IF(Nurses!A48="","",Nurses!A48)</f>
-        <v>간호사47</v>
+        <v/>
       </c>
       <c r="B48" s="7"/>
       <c r="C48" s="7"/>
@@ -6722,7 +7736,7 @@
     <row r="49" spans="1:32">
       <c r="A49" s="84" t="str">
         <f>IF(Nurses!A49="","",Nurses!A49)</f>
-        <v>간호사48</v>
+        <v/>
       </c>
       <c r="B49" s="7"/>
       <c r="C49" s="7"/>
@@ -6759,7 +7773,7 @@
     <row r="50" spans="1:32">
       <c r="A50" s="84" t="str">
         <f>IF(Nurses!A50="","",Nurses!A50)</f>
-        <v>간호사49</v>
+        <v/>
       </c>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
@@ -6796,7 +7810,7 @@
     <row r="51" spans="1:32">
       <c r="A51" s="84" t="str">
         <f>IF(Nurses!A51="","",Nurses!A51)</f>
-        <v>간호사50</v>
+        <v/>
       </c>
       <c r="B51" s="7"/>
       <c r="C51" s="7"/>
@@ -6831,7 +7845,7 @@
       <c r="AF51" s="7"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6847,7 +7861,7 @@
   <sheetData>
     <row r="1" spans="1:42">
       <c r="A1" s="5" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="B1" s="5">
         <v>1</v>
@@ -6939,14 +7953,11 @@
       <c r="AE1" s="5">
         <v>30</v>
       </c>
-      <c r="AF1" s="5">
-        <v>31</v>
-      </c>
+      <c r="AF1" s="5"/>
     </row>
     <row r="2" spans="1:42">
-      <c r="A2" s="84" t="str">
-        <f>IF(Nurses!A2="","",Nurses!A2)</f>
-        <v>간호사1</v>
+      <c r="A2" s="84" t="s">
+        <v>169</v>
       </c>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -6981,9 +7992,8 @@
       <c r="AF2" s="7"/>
     </row>
     <row r="3" spans="1:42">
-      <c r="A3" s="84" t="str">
-        <f>IF(Nurses!A3="","",Nurses!A3)</f>
-        <v>간호사2</v>
+      <c r="A3" s="84" t="s">
+        <v>171</v>
       </c>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -7018,13 +8028,12 @@
       <c r="AF3" s="7"/>
       <c r="AG3" s="6"/>
       <c r="AH3" s="40" t="s">
-        <v>51</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:42">
-      <c r="A4" s="84" t="str">
-        <f>IF(Nurses!A4="","",Nurses!A4)</f>
-        <v>간호사3</v>
+      <c r="A4" s="84" t="s">
+        <v>173</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -7059,7 +8068,7 @@
       <c r="AF4" s="7"/>
       <c r="AG4" s="6"/>
       <c r="AH4" s="65" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="AI4" s="80"/>
       <c r="AJ4" s="80"/>
@@ -7071,9 +8080,8 @@
       <c r="AP4" s="80"/>
     </row>
     <row r="5" spans="1:42">
-      <c r="A5" s="84" t="str">
-        <f>IF(Nurses!A5="","",Nurses!A5)</f>
-        <v>간호사4</v>
+      <c r="A5" s="84" t="s">
+        <v>175</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -7118,9 +8126,8 @@
       <c r="AP5" s="80"/>
     </row>
     <row r="6" spans="1:42">
-      <c r="A6" s="84" t="str">
-        <f>IF(Nurses!A6="","",Nurses!A6)</f>
-        <v>간호사5</v>
+      <c r="A6" s="84" t="s">
+        <v>177</v>
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
@@ -7155,7 +8162,7 @@
       <c r="AF6" s="7"/>
       <c r="AG6" s="6"/>
       <c r="AH6" s="79" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="AI6" s="80"/>
       <c r="AJ6" s="80"/>
@@ -7167,9 +8174,8 @@
       <c r="AP6" s="80"/>
     </row>
     <row r="7" spans="1:42">
-      <c r="A7" s="84" t="str">
-        <f>IF(Nurses!A7="","",Nurses!A7)</f>
-        <v>간호사6</v>
+      <c r="A7" s="84" t="s">
+        <v>178</v>
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
@@ -7214,9 +8220,8 @@
       <c r="AP7" s="80"/>
     </row>
     <row r="8" spans="1:42">
-      <c r="A8" s="84" t="str">
-        <f>IF(Nurses!A8="","",Nurses!A8)</f>
-        <v>간호사7</v>
+      <c r="A8" s="84" t="s">
+        <v>180</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -7251,7 +8256,7 @@
       <c r="AF8" s="7"/>
       <c r="AG8" s="6"/>
       <c r="AH8" s="65" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="AI8" s="80"/>
       <c r="AJ8" s="80"/>
@@ -7263,9 +8268,8 @@
       <c r="AP8" s="80"/>
     </row>
     <row r="9" spans="1:42">
-      <c r="A9" s="84" t="str">
-        <f>IF(Nurses!A9="","",Nurses!A9)</f>
-        <v>간호사8</v>
+      <c r="A9" s="84" t="s">
+        <v>182</v>
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -7310,9 +8314,8 @@
       <c r="AP9" s="80"/>
     </row>
     <row r="10" spans="1:42">
-      <c r="A10" s="84" t="str">
-        <f>IF(Nurses!A10="","",Nurses!A10)</f>
-        <v>간호사9</v>
+      <c r="A10" s="84" t="s">
+        <v>184</v>
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -7347,7 +8350,7 @@
       <c r="AF10" s="7"/>
       <c r="AG10" s="6"/>
       <c r="AH10" s="82" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="AI10" s="80"/>
       <c r="AJ10" s="80"/>
@@ -7359,9 +8362,8 @@
       <c r="AP10" s="80"/>
     </row>
     <row r="11" spans="1:42">
-      <c r="A11" s="84" t="str">
-        <f>IF(Nurses!A11="","",Nurses!A11)</f>
-        <v>간호사10</v>
+      <c r="A11" s="84" t="s">
+        <v>185</v>
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
@@ -7397,9 +8399,8 @@
       <c r="AG11" s="6"/>
     </row>
     <row r="12" spans="1:42">
-      <c r="A12" s="84" t="str">
-        <f>IF(Nurses!A12="","",Nurses!A12)</f>
-        <v>간호사11</v>
+      <c r="A12" s="84" t="s">
+        <v>187</v>
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
@@ -7435,9 +8436,8 @@
       <c r="AG12" s="6"/>
     </row>
     <row r="13" spans="1:42">
-      <c r="A13" s="84" t="str">
-        <f>IF(Nurses!A13="","",Nurses!A13)</f>
-        <v>간호사12</v>
+      <c r="A13" s="84" t="s">
+        <v>188</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -7475,7 +8475,7 @@
     <row r="14" spans="1:42">
       <c r="A14" s="84" t="str">
         <f>IF(Nurses!A14="","",Nurses!A14)</f>
-        <v>간호사13</v>
+        <v/>
       </c>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -7512,7 +8512,7 @@
     <row r="15" spans="1:42">
       <c r="A15" s="84" t="str">
         <f>IF(Nurses!A15="","",Nurses!A15)</f>
-        <v>간호사14</v>
+        <v/>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -7549,7 +8549,7 @@
     <row r="16" spans="1:42">
       <c r="A16" s="84" t="str">
         <f>IF(Nurses!A16="","",Nurses!A16)</f>
-        <v>간호사15</v>
+        <v/>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -7586,7 +8586,7 @@
     <row r="17" spans="1:32">
       <c r="A17" s="84" t="str">
         <f>IF(Nurses!A17="","",Nurses!A17)</f>
-        <v>간호사16</v>
+        <v/>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -7623,7 +8623,7 @@
     <row r="18" spans="1:32">
       <c r="A18" s="84" t="str">
         <f>IF(Nurses!A18="","",Nurses!A18)</f>
-        <v>간호사17</v>
+        <v/>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -7660,7 +8660,7 @@
     <row r="19" spans="1:32">
       <c r="A19" s="84" t="str">
         <f>IF(Nurses!A19="","",Nurses!A19)</f>
-        <v>간호사18</v>
+        <v/>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -7697,7 +8697,7 @@
     <row r="20" spans="1:32">
       <c r="A20" s="84" t="str">
         <f>IF(Nurses!A20="","",Nurses!A20)</f>
-        <v>간호사19</v>
+        <v/>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -7734,7 +8734,7 @@
     <row r="21" spans="1:32">
       <c r="A21" s="84" t="str">
         <f>IF(Nurses!A21="","",Nurses!A21)</f>
-        <v>간호사20</v>
+        <v/>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -7771,7 +8771,7 @@
     <row r="22" spans="1:32">
       <c r="A22" s="84" t="str">
         <f>IF(Nurses!A22="","",Nurses!A22)</f>
-        <v>간호사21</v>
+        <v/>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -7808,7 +8808,7 @@
     <row r="23" spans="1:32">
       <c r="A23" s="84" t="str">
         <f>IF(Nurses!A23="","",Nurses!A23)</f>
-        <v>간호사22</v>
+        <v/>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -7845,7 +8845,7 @@
     <row r="24" spans="1:32">
       <c r="A24" s="84" t="str">
         <f>IF(Nurses!A24="","",Nurses!A24)</f>
-        <v>간호사23</v>
+        <v/>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -7882,7 +8882,7 @@
     <row r="25" spans="1:32">
       <c r="A25" s="84" t="str">
         <f>IF(Nurses!A25="","",Nurses!A25)</f>
-        <v>간호사24</v>
+        <v/>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -7919,7 +8919,7 @@
     <row r="26" spans="1:32">
       <c r="A26" s="84" t="str">
         <f>IF(Nurses!A26="","",Nurses!A26)</f>
-        <v>간호사25</v>
+        <v/>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
@@ -7956,7 +8956,7 @@
     <row r="27" spans="1:32">
       <c r="A27" s="84" t="str">
         <f>IF(Nurses!A27="","",Nurses!A27)</f>
-        <v>간호사26</v>
+        <v/>
       </c>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
@@ -7993,7 +8993,7 @@
     <row r="28" spans="1:32">
       <c r="A28" s="84" t="str">
         <f>IF(Nurses!A28="","",Nurses!A28)</f>
-        <v>간호사27</v>
+        <v/>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
@@ -8030,7 +9030,7 @@
     <row r="29" spans="1:32">
       <c r="A29" s="84" t="str">
         <f>IF(Nurses!A29="","",Nurses!A29)</f>
-        <v>간호사28</v>
+        <v/>
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
@@ -8067,7 +9067,7 @@
     <row r="30" spans="1:32">
       <c r="A30" s="84" t="str">
         <f>IF(Nurses!A30="","",Nurses!A30)</f>
-        <v>간호사29</v>
+        <v/>
       </c>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
@@ -8104,7 +9104,7 @@
     <row r="31" spans="1:32">
       <c r="A31" s="84" t="str">
         <f>IF(Nurses!A31="","",Nurses!A31)</f>
-        <v>간호사30</v>
+        <v/>
       </c>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
@@ -8141,7 +9141,7 @@
     <row r="32" spans="1:32">
       <c r="A32" s="84" t="str">
         <f>IF(Nurses!A32="","",Nurses!A32)</f>
-        <v>간호사31</v>
+        <v/>
       </c>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
@@ -8178,7 +9178,7 @@
     <row r="33" spans="1:32">
       <c r="A33" s="84" t="str">
         <f>IF(Nurses!A33="","",Nurses!A33)</f>
-        <v>간호사32</v>
+        <v/>
       </c>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
@@ -8215,7 +9215,7 @@
     <row r="34" spans="1:32">
       <c r="A34" s="84" t="str">
         <f>IF(Nurses!A34="","",Nurses!A34)</f>
-        <v>간호사33</v>
+        <v/>
       </c>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
@@ -8252,7 +9252,7 @@
     <row r="35" spans="1:32">
       <c r="A35" s="84" t="str">
         <f>IF(Nurses!A35="","",Nurses!A35)</f>
-        <v>간호사34</v>
+        <v/>
       </c>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
@@ -8289,7 +9289,7 @@
     <row r="36" spans="1:32">
       <c r="A36" s="84" t="str">
         <f>IF(Nurses!A36="","",Nurses!A36)</f>
-        <v>간호사35</v>
+        <v/>
       </c>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
@@ -8326,7 +9326,7 @@
     <row r="37" spans="1:32">
       <c r="A37" s="84" t="str">
         <f>IF(Nurses!A37="","",Nurses!A37)</f>
-        <v>간호사36</v>
+        <v/>
       </c>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
@@ -8363,7 +9363,7 @@
     <row r="38" spans="1:32">
       <c r="A38" s="84" t="str">
         <f>IF(Nurses!A38="","",Nurses!A38)</f>
-        <v>간호사37</v>
+        <v/>
       </c>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
@@ -8400,7 +9400,7 @@
     <row r="39" spans="1:32">
       <c r="A39" s="84" t="str">
         <f>IF(Nurses!A39="","",Nurses!A39)</f>
-        <v>간호사38</v>
+        <v/>
       </c>
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
@@ -8437,7 +9437,7 @@
     <row r="40" spans="1:32">
       <c r="A40" s="84" t="str">
         <f>IF(Nurses!A40="","",Nurses!A40)</f>
-        <v>간호사39</v>
+        <v/>
       </c>
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
@@ -8474,7 +9474,7 @@
     <row r="41" spans="1:32">
       <c r="A41" s="84" t="str">
         <f>IF(Nurses!A41="","",Nurses!A41)</f>
-        <v>간호사40</v>
+        <v/>
       </c>
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
@@ -8511,7 +9511,7 @@
     <row r="42" spans="1:32">
       <c r="A42" s="84" t="str">
         <f>IF(Nurses!A42="","",Nurses!A42)</f>
-        <v>간호사41</v>
+        <v/>
       </c>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
@@ -8548,7 +9548,7 @@
     <row r="43" spans="1:32">
       <c r="A43" s="84" t="str">
         <f>IF(Nurses!A43="","",Nurses!A43)</f>
-        <v>간호사42</v>
+        <v/>
       </c>
       <c r="B43" s="7"/>
       <c r="C43" s="7"/>
@@ -8585,7 +9585,7 @@
     <row r="44" spans="1:32">
       <c r="A44" s="84" t="str">
         <f>IF(Nurses!A44="","",Nurses!A44)</f>
-        <v>간호사43</v>
+        <v/>
       </c>
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
@@ -8622,7 +9622,7 @@
     <row r="45" spans="1:32">
       <c r="A45" s="84" t="str">
         <f>IF(Nurses!A45="","",Nurses!A45)</f>
-        <v>간호사44</v>
+        <v/>
       </c>
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
@@ -8659,7 +9659,7 @@
     <row r="46" spans="1:32">
       <c r="A46" s="84" t="str">
         <f>IF(Nurses!A46="","",Nurses!A46)</f>
-        <v>간호사45</v>
+        <v/>
       </c>
       <c r="B46" s="7"/>
       <c r="C46" s="7"/>
@@ -8696,7 +9696,7 @@
     <row r="47" spans="1:32">
       <c r="A47" s="84" t="str">
         <f>IF(Nurses!A47="","",Nurses!A47)</f>
-        <v>간호사46</v>
+        <v/>
       </c>
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
@@ -8733,7 +9733,7 @@
     <row r="48" spans="1:32">
       <c r="A48" s="84" t="str">
         <f>IF(Nurses!A48="","",Nurses!A48)</f>
-        <v>간호사47</v>
+        <v/>
       </c>
       <c r="B48" s="7"/>
       <c r="C48" s="7"/>
@@ -8770,7 +9770,7 @@
     <row r="49" spans="1:32">
       <c r="A49" s="84" t="str">
         <f>IF(Nurses!A49="","",Nurses!A49)</f>
-        <v>간호사48</v>
+        <v/>
       </c>
       <c r="B49" s="7"/>
       <c r="C49" s="7"/>
@@ -8807,7 +9807,7 @@
     <row r="50" spans="1:32">
       <c r="A50" s="84" t="str">
         <f>IF(Nurses!A50="","",Nurses!A50)</f>
-        <v>간호사49</v>
+        <v/>
       </c>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
@@ -8844,7 +9844,7 @@
     <row r="51" spans="1:32">
       <c r="A51" s="84" t="str">
         <f>IF(Nurses!A51="","",Nurses!A51)</f>
-        <v>간호사50</v>
+        <v/>
       </c>
       <c r="B51" s="7"/>
       <c r="C51" s="7"/>
@@ -8879,7 +9879,7 @@
       <c r="AF51" s="7"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -8895,22 +9895,22 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="14" t="s">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>212</v>
+        <v>1</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>213</v>
+        <v>2</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>214</v>
+        <v>3</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>215</v>
+        <v>4</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>216</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:17">
@@ -8919,7 +9919,7 @@
         <v>간호사1</v>
       </c>
       <c r="J2" s="23" t="s">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="K2" s="11"/>
       <c r="L2" s="11"/>
@@ -8935,7 +9935,7 @@
         <v>간호사2</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>217</v>
+        <v>7</v>
       </c>
       <c r="K3" s="11"/>
       <c r="L3" s="11"/>
@@ -8951,7 +9951,7 @@
         <v>간호사3</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>218</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -9011,240 +10011,240 @@
     <row r="14" spans="1:17">
       <c r="A14" s="84" t="str">
         <f>IF(Nurses!A14="","",Nurses!A14)</f>
-        <v>간호사13</v>
+        <v/>
       </c>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="84" t="str">
         <f>IF(Nurses!A15="","",Nurses!A15)</f>
-        <v>간호사14</v>
+        <v/>
       </c>
     </row>
     <row r="16" spans="1:17">
       <c r="A16" s="84" t="str">
         <f>IF(Nurses!A16="","",Nurses!A16)</f>
-        <v>간호사15</v>
+        <v/>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="84" t="str">
         <f>IF(Nurses!A17="","",Nurses!A17)</f>
-        <v>간호사16</v>
+        <v/>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="84" t="str">
         <f>IF(Nurses!A18="","",Nurses!A18)</f>
-        <v>간호사17</v>
+        <v/>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="84" t="str">
         <f>IF(Nurses!A19="","",Nurses!A19)</f>
-        <v>간호사18</v>
+        <v/>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="84" t="str">
         <f>IF(Nurses!A20="","",Nurses!A20)</f>
-        <v>간호사19</v>
+        <v/>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="84" t="str">
         <f>IF(Nurses!A21="","",Nurses!A21)</f>
-        <v>간호사20</v>
+        <v/>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="84" t="str">
         <f>IF(Nurses!A22="","",Nurses!A22)</f>
-        <v>간호사21</v>
+        <v/>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="84" t="str">
         <f>IF(Nurses!A23="","",Nurses!A23)</f>
-        <v>간호사22</v>
+        <v/>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="84" t="str">
         <f>IF(Nurses!A24="","",Nurses!A24)</f>
-        <v>간호사23</v>
+        <v/>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="84" t="str">
         <f>IF(Nurses!A25="","",Nurses!A25)</f>
-        <v>간호사24</v>
+        <v/>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="84" t="str">
         <f>IF(Nurses!A26="","",Nurses!A26)</f>
-        <v>간호사25</v>
+        <v/>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="84" t="str">
         <f>IF(Nurses!A27="","",Nurses!A27)</f>
-        <v>간호사26</v>
+        <v/>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="84" t="str">
         <f>IF(Nurses!A28="","",Nurses!A28)</f>
-        <v>간호사27</v>
+        <v/>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="84" t="str">
         <f>IF(Nurses!A29="","",Nurses!A29)</f>
-        <v>간호사28</v>
+        <v/>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="84" t="str">
         <f>IF(Nurses!A30="","",Nurses!A30)</f>
-        <v>간호사29</v>
+        <v/>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="84" t="str">
         <f>IF(Nurses!A31="","",Nurses!A31)</f>
-        <v>간호사30</v>
+        <v/>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="84" t="str">
         <f>IF(Nurses!A32="","",Nurses!A32)</f>
-        <v>간호사31</v>
+        <v/>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="84" t="str">
         <f>IF(Nurses!A33="","",Nurses!A33)</f>
-        <v>간호사32</v>
+        <v/>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="84" t="str">
         <f>IF(Nurses!A34="","",Nurses!A34)</f>
-        <v>간호사33</v>
+        <v/>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="84" t="str">
         <f>IF(Nurses!A35="","",Nurses!A35)</f>
-        <v>간호사34</v>
+        <v/>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="84" t="str">
         <f>IF(Nurses!A36="","",Nurses!A36)</f>
-        <v>간호사35</v>
+        <v/>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="84" t="str">
         <f>IF(Nurses!A37="","",Nurses!A37)</f>
-        <v>간호사36</v>
+        <v/>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="84" t="str">
         <f>IF(Nurses!A38="","",Nurses!A38)</f>
-        <v>간호사37</v>
+        <v/>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="84" t="str">
         <f>IF(Nurses!A39="","",Nurses!A39)</f>
-        <v>간호사38</v>
+        <v/>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="84" t="str">
         <f>IF(Nurses!A40="","",Nurses!A40)</f>
-        <v>간호사39</v>
+        <v/>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="84" t="str">
         <f>IF(Nurses!A41="","",Nurses!A41)</f>
-        <v>간호사40</v>
+        <v/>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="84" t="str">
         <f>IF(Nurses!A42="","",Nurses!A42)</f>
-        <v>간호사41</v>
+        <v/>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="84" t="str">
         <f>IF(Nurses!A43="","",Nurses!A43)</f>
-        <v>간호사42</v>
+        <v/>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="84" t="str">
         <f>IF(Nurses!A44="","",Nurses!A44)</f>
-        <v>간호사43</v>
+        <v/>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="84" t="str">
         <f>IF(Nurses!A45="","",Nurses!A45)</f>
-        <v>간호사44</v>
+        <v/>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="84" t="str">
         <f>IF(Nurses!A46="","",Nurses!A46)</f>
-        <v>간호사45</v>
+        <v/>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="84" t="str">
         <f>IF(Nurses!A47="","",Nurses!A47)</f>
-        <v>간호사46</v>
+        <v/>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="84" t="str">
         <f>IF(Nurses!A48="","",Nurses!A48)</f>
-        <v>간호사47</v>
+        <v/>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="84" t="str">
         <f>IF(Nurses!A49="","",Nurses!A49)</f>
-        <v>간호사48</v>
+        <v/>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="84" t="str">
         <f>IF(Nurses!A50="","",Nurses!A50)</f>
-        <v>간호사49</v>
+        <v/>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="84" t="str">
         <f>IF(Nurses!A51="","",Nurses!A51)</f>
-        <v>간호사50</v>
+        <v/>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:AP30"/>
+  <dimension ref="A1:AP15"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -9253,148 +10253,146 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42">
-      <c r="A1" s="98" t="s">
-        <v>219</v>
-      </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="97"/>
-      <c r="P1" s="97"/>
-      <c r="Q1" s="97"/>
-      <c r="R1" s="97"/>
-      <c r="S1" s="97"/>
-      <c r="T1" s="97"/>
-      <c r="U1" s="97"/>
-      <c r="V1" s="97"/>
-      <c r="W1" s="97"/>
-      <c r="X1" s="97"/>
-      <c r="Y1" s="97"/>
-      <c r="Z1" s="97"/>
-      <c r="AA1" s="97"/>
-      <c r="AB1" s="97"/>
-      <c r="AC1" s="97"/>
-      <c r="AD1" s="97"/>
-      <c r="AE1" s="97"/>
-      <c r="AF1" s="97"/>
-      <c r="AG1" s="97"/>
-      <c r="AH1" s="97"/>
-      <c r="AI1" s="97"/>
-      <c r="AJ1" s="97"/>
-      <c r="AK1" s="97"/>
-      <c r="AL1" s="97"/>
-      <c r="AM1" s="97"/>
-      <c r="AN1" s="97"/>
-      <c r="AO1" s="97"/>
-      <c r="AP1" s="97"/>
+      <c r="A1" s="101" t="s">
+        <v>226</v>
+      </c>
+      <c r="B1" s="100"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="100"/>
+      <c r="F1" s="100"/>
+      <c r="G1" s="100"/>
+      <c r="H1" s="100"/>
+      <c r="I1" s="100"/>
+      <c r="J1" s="100"/>
+      <c r="K1" s="100"/>
+      <c r="L1" s="100"/>
+      <c r="M1" s="100"/>
+      <c r="N1" s="100"/>
+      <c r="O1" s="100"/>
+      <c r="P1" s="100"/>
+      <c r="Q1" s="100"/>
+      <c r="R1" s="100"/>
+      <c r="S1" s="100"/>
+      <c r="T1" s="100"/>
+      <c r="U1" s="100"/>
+      <c r="V1" s="100"/>
+      <c r="W1" s="100"/>
+      <c r="X1" s="100"/>
+      <c r="Y1" s="100"/>
+      <c r="Z1" s="100"/>
+      <c r="AA1" s="100"/>
+      <c r="AB1" s="100"/>
+      <c r="AC1" s="100"/>
+      <c r="AD1" s="100"/>
+      <c r="AE1" s="100"/>
+      <c r="AF1" s="100"/>
+      <c r="AG1" s="100"/>
+      <c r="AH1" s="100"/>
+      <c r="AI1" s="100"/>
+      <c r="AJ1" s="100"/>
+      <c r="AK1" s="100"/>
+      <c r="AL1" s="100"/>
+      <c r="AM1" s="100"/>
+      <c r="AN1" s="100"/>
+      <c r="AO1" s="100"/>
+      <c r="AP1" s="100"/>
     </row>
     <row r="2" spans="1:42">
       <c r="A2" s="8" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="S2" s="6" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="T2" s="6" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="U2" s="6" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="V2" s="6" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="W2" s="6" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="X2" s="6" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="Y2" s="6" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="Z2" s="6" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="AA2" s="6" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="AB2" s="6" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="AC2" s="6" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="AD2" s="6" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="AE2" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="AF2" s="6" t="s">
-        <v>222</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="AF2" s="6"/>
       <c r="AG2" s="6"/>
       <c r="AH2" s="6"/>
       <c r="AI2" s="6"/>
@@ -9408,7 +10406,7 @@
     </row>
     <row r="3" spans="1:42">
       <c r="A3" s="5" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="B3" s="5">
         <v>1</v>
@@ -9500,180 +10498,1543 @@
       <c r="AE3" s="5">
         <v>30</v>
       </c>
-      <c r="AF3" s="5">
-        <v>31</v>
-      </c>
+      <c r="AF3" s="5"/>
       <c r="AG3" s="5" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="AH3" s="5" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="AI3" s="5" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="AJ3" s="5" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="AK3" s="5" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="AL3" s="5" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="AM3" s="5" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="AN3" s="5" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="AO3" s="5" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="AP3" s="5" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4" spans="1:42">
       <c r="A4" t="s">
-        <v>157</v>
+        <v>169</v>
+      </c>
+      <c r="B4" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="C4" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="D4" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="E4" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="F4" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="G4" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="H4" t="s">
+        <v>231</v>
+      </c>
+      <c r="I4" t="s">
+        <v>232</v>
+      </c>
+      <c r="J4" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="K4" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="L4" t="s">
+        <v>231</v>
+      </c>
+      <c r="M4" t="s">
+        <v>232</v>
+      </c>
+      <c r="N4" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="O4" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="P4" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q4" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="R4" t="s">
+        <v>231</v>
+      </c>
+      <c r="S4" t="s">
+        <v>231</v>
+      </c>
+      <c r="T4" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="U4" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="V4" s="96" t="s">
+        <v>235</v>
+      </c>
+      <c r="W4" t="s">
+        <v>231</v>
+      </c>
+      <c r="X4" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="Y4" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z4" s="96" t="s">
+        <v>235</v>
+      </c>
+      <c r="AA4" s="96" t="s">
+        <v>235</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>231</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>232</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>232</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>232</v>
+      </c>
+      <c r="AG4">
+        <v>17</v>
+      </c>
+      <c r="AH4">
+        <v>6</v>
+      </c>
+      <c r="AI4">
+        <v>5</v>
+      </c>
+      <c r="AJ4">
+        <v>6</v>
+      </c>
+      <c r="AK4">
+        <v>13</v>
+      </c>
+      <c r="AL4">
+        <v>3</v>
+      </c>
+      <c r="AM4">
+        <v>4</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:42">
       <c r="A5" t="s">
-        <v>158</v>
+        <v>171</v>
+      </c>
+      <c r="B5" t="s">
+        <v>231</v>
+      </c>
+      <c r="C5" t="s">
+        <v>231</v>
+      </c>
+      <c r="D5" t="s">
+        <v>232</v>
+      </c>
+      <c r="E5" t="s">
+        <v>232</v>
+      </c>
+      <c r="F5" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="G5" t="s">
+        <v>231</v>
+      </c>
+      <c r="H5" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="I5" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="J5" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="K5" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="L5" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="M5" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="N5" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="O5" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="P5" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>231</v>
+      </c>
+      <c r="R5" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="S5" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="T5" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="U5" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="V5" t="s">
+        <v>231</v>
+      </c>
+      <c r="W5" t="s">
+        <v>232</v>
+      </c>
+      <c r="X5" s="96" t="s">
+        <v>235</v>
+      </c>
+      <c r="Y5" s="96" t="s">
+        <v>235</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>231</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>232</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>232</v>
+      </c>
+      <c r="AC5" s="96" t="s">
+        <v>235</v>
+      </c>
+      <c r="AD5" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="AE5" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="AG5">
+        <v>17</v>
+      </c>
+      <c r="AH5">
+        <v>6</v>
+      </c>
+      <c r="AI5">
+        <v>5</v>
+      </c>
+      <c r="AJ5">
+        <v>6</v>
+      </c>
+      <c r="AK5">
+        <v>13</v>
+      </c>
+      <c r="AL5">
+        <v>3</v>
+      </c>
+      <c r="AM5">
+        <v>4</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:42">
       <c r="A6" t="s">
-        <v>160</v>
+        <v>173</v>
+      </c>
+      <c r="B6" t="s">
+        <v>232</v>
+      </c>
+      <c r="C6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D6" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="E6" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="F6" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="G6" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="H6" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="I6" t="s">
+        <v>231</v>
+      </c>
+      <c r="J6" t="s">
+        <v>231</v>
+      </c>
+      <c r="K6" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="L6" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="M6" t="s">
+        <v>231</v>
+      </c>
+      <c r="N6" t="s">
+        <v>232</v>
+      </c>
+      <c r="O6" t="s">
+        <v>232</v>
+      </c>
+      <c r="P6" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q6" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="R6" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="S6" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="T6" t="s">
+        <v>231</v>
+      </c>
+      <c r="U6" t="s">
+        <v>232</v>
+      </c>
+      <c r="V6" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="W6" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="X6" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="Y6" s="96" t="s">
+        <v>235</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>231</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>231</v>
+      </c>
+      <c r="AB6" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="AC6" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="AD6" s="96" t="s">
+        <v>235</v>
+      </c>
+      <c r="AE6" s="96" t="s">
+        <v>235</v>
+      </c>
+      <c r="AG6">
+        <v>17</v>
+      </c>
+      <c r="AH6">
+        <v>6</v>
+      </c>
+      <c r="AI6">
+        <v>5</v>
+      </c>
+      <c r="AJ6">
+        <v>6</v>
+      </c>
+      <c r="AK6">
+        <v>13</v>
+      </c>
+      <c r="AL6">
+        <v>3</v>
+      </c>
+      <c r="AM6">
+        <v>4</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:42">
       <c r="A7" t="s">
-        <v>162</v>
+        <v>175</v>
+      </c>
+      <c r="B7" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="C7" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="D7" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="E7" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="F7" t="s">
+        <v>231</v>
+      </c>
+      <c r="G7" t="s">
+        <v>231</v>
+      </c>
+      <c r="H7" t="s">
+        <v>232</v>
+      </c>
+      <c r="I7" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="J7" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="K7" t="s">
+        <v>231</v>
+      </c>
+      <c r="L7" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="M7" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="N7" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="O7" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="P7" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>232</v>
+      </c>
+      <c r="R7" t="s">
+        <v>232</v>
+      </c>
+      <c r="S7" t="s">
+        <v>232</v>
+      </c>
+      <c r="T7" t="s">
+        <v>232</v>
+      </c>
+      <c r="U7" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="V7" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="W7" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="X7" t="s">
+        <v>231</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>231</v>
+      </c>
+      <c r="Z7" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="AA7" s="96" t="s">
+        <v>235</v>
+      </c>
+      <c r="AB7" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="AC7" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="AD7" s="96" t="s">
+        <v>235</v>
+      </c>
+      <c r="AE7" s="96" t="s">
+        <v>235</v>
+      </c>
+      <c r="AG7">
+        <v>17</v>
+      </c>
+      <c r="AH7">
+        <v>6</v>
+      </c>
+      <c r="AI7">
+        <v>5</v>
+      </c>
+      <c r="AJ7">
+        <v>6</v>
+      </c>
+      <c r="AK7">
+        <v>13</v>
+      </c>
+      <c r="AL7">
+        <v>3</v>
+      </c>
+      <c r="AM7">
+        <v>5</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:42">
       <c r="A8" t="s">
-        <v>164</v>
+        <v>177</v>
+      </c>
+      <c r="B8" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="C8" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="D8" t="s">
+        <v>231</v>
+      </c>
+      <c r="E8" t="s">
+        <v>231</v>
+      </c>
+      <c r="F8" t="s">
+        <v>232</v>
+      </c>
+      <c r="G8" t="s">
+        <v>232</v>
+      </c>
+      <c r="H8" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="I8" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="J8" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="K8" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="L8" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="M8" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="N8" t="s">
+        <v>231</v>
+      </c>
+      <c r="O8" t="s">
+        <v>231</v>
+      </c>
+      <c r="P8" t="s">
+        <v>232</v>
+      </c>
+      <c r="Q8" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="R8" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="S8" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="T8" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="U8" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="V8" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="W8" s="96" t="s">
+        <v>235</v>
+      </c>
+      <c r="X8" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>232</v>
+      </c>
+      <c r="Z8" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA8" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB8" s="96" t="s">
+        <v>235</v>
+      </c>
+      <c r="AC8" s="96" t="s">
+        <v>235</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>231</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>231</v>
+      </c>
+      <c r="AG8">
+        <v>17</v>
+      </c>
+      <c r="AH8">
+        <v>6</v>
+      </c>
+      <c r="AI8">
+        <v>5</v>
+      </c>
+      <c r="AJ8">
+        <v>6</v>
+      </c>
+      <c r="AK8">
+        <v>13</v>
+      </c>
+      <c r="AL8">
+        <v>3</v>
+      </c>
+      <c r="AM8">
+        <v>5</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:42">
       <c r="A9" t="s">
-        <v>165</v>
+        <v>178</v>
+      </c>
+      <c r="B9" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="C9" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="D9" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="E9" t="s">
+        <v>231</v>
+      </c>
+      <c r="F9" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="G9" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="H9" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="I9" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="J9" t="s">
+        <v>232</v>
+      </c>
+      <c r="K9" t="s">
+        <v>232</v>
+      </c>
+      <c r="L9" t="s">
+        <v>232</v>
+      </c>
+      <c r="M9" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="N9" t="s">
+        <v>231</v>
+      </c>
+      <c r="O9" t="s">
+        <v>231</v>
+      </c>
+      <c r="P9" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q9" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="R9" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="S9" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="T9" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="U9" t="s">
+        <v>231</v>
+      </c>
+      <c r="V9" t="s">
+        <v>232</v>
+      </c>
+      <c r="W9" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="X9" s="96" t="s">
+        <v>235</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>231</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA9" s="96" t="s">
+        <v>235</v>
+      </c>
+      <c r="AB9" s="96" t="s">
+        <v>235</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>231</v>
+      </c>
+      <c r="AD9" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="AE9" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="AG9">
+        <v>17</v>
+      </c>
+      <c r="AH9">
+        <v>6</v>
+      </c>
+      <c r="AI9">
+        <v>5</v>
+      </c>
+      <c r="AJ9">
+        <v>6</v>
+      </c>
+      <c r="AK9">
+        <v>13</v>
+      </c>
+      <c r="AL9">
+        <v>3</v>
+      </c>
+      <c r="AM9">
+        <v>4</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:42">
       <c r="A10" t="s">
-        <v>167</v>
+        <v>180</v>
+      </c>
+      <c r="B10" t="s">
+        <v>241</v>
+      </c>
+      <c r="C10" t="s">
+        <v>241</v>
+      </c>
+      <c r="D10" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="E10" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="F10" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="G10" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="H10" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="I10" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="J10" t="s">
+        <v>231</v>
+      </c>
+      <c r="K10" t="s">
+        <v>231</v>
+      </c>
+      <c r="L10" t="s">
+        <v>231</v>
+      </c>
+      <c r="M10" t="s">
+        <v>232</v>
+      </c>
+      <c r="N10" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="O10" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="P10" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>241</v>
+      </c>
+      <c r="R10" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="S10" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="T10" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="U10" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="V10" t="s">
+        <v>241</v>
+      </c>
+      <c r="W10" t="s">
+        <v>241</v>
+      </c>
+      <c r="X10" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y10" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="Z10" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>232</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>232</v>
+      </c>
+      <c r="AC10" s="96" t="s">
+        <v>235</v>
+      </c>
+      <c r="AD10" s="96" t="s">
+        <v>235</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>232</v>
+      </c>
+      <c r="AG10">
+        <v>18</v>
+      </c>
+      <c r="AH10">
+        <v>4</v>
+      </c>
+      <c r="AI10">
+        <v>5</v>
+      </c>
+      <c r="AJ10">
+        <v>4</v>
+      </c>
+      <c r="AK10">
+        <v>12</v>
+      </c>
+      <c r="AL10">
+        <v>2</v>
+      </c>
+      <c r="AM10">
+        <v>5</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:42">
       <c r="A11" t="s">
-        <v>169</v>
+        <v>182</v>
+      </c>
+      <c r="B11" t="s">
+        <v>231</v>
+      </c>
+      <c r="C11" t="s">
+        <v>231</v>
+      </c>
+      <c r="D11" t="s">
+        <v>231</v>
+      </c>
+      <c r="E11" t="s">
+        <v>232</v>
+      </c>
+      <c r="F11" t="s">
+        <v>232</v>
+      </c>
+      <c r="G11" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="H11" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="I11" t="s">
+        <v>241</v>
+      </c>
+      <c r="J11" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="K11" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="L11" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="M11" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="N11" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="O11" t="s">
+        <v>241</v>
+      </c>
+      <c r="P11" t="s">
+        <v>232</v>
+      </c>
+      <c r="Q11" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="R11" t="s">
+        <v>241</v>
+      </c>
+      <c r="S11" t="s">
+        <v>232</v>
+      </c>
+      <c r="T11" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="U11" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="V11" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="W11" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="X11" t="s">
+        <v>241</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>241</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA11" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="AB11" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="AC11" s="96" t="s">
+        <v>235</v>
+      </c>
+      <c r="AD11" s="96" t="s">
+        <v>235</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>231</v>
+      </c>
+      <c r="AG11">
+        <v>18</v>
+      </c>
+      <c r="AH11">
+        <v>4</v>
+      </c>
+      <c r="AI11">
+        <v>5</v>
+      </c>
+      <c r="AJ11">
+        <v>4</v>
+      </c>
+      <c r="AK11">
+        <v>12</v>
+      </c>
+      <c r="AL11">
+        <v>2</v>
+      </c>
+      <c r="AM11">
+        <v>5</v>
+      </c>
+      <c r="AN11">
+        <v>0</v>
+      </c>
+      <c r="AO11">
+        <v>0</v>
+      </c>
+      <c r="AP11">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:42">
       <c r="A12" t="s">
-        <v>171</v>
+        <v>184</v>
+      </c>
+      <c r="B12" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="C12" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="D12" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="E12" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="F12" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="G12" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="H12" t="s">
+        <v>231</v>
+      </c>
+      <c r="I12" t="s">
+        <v>231</v>
+      </c>
+      <c r="J12" t="s">
+        <v>241</v>
+      </c>
+      <c r="K12" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="L12" t="s">
+        <v>241</v>
+      </c>
+      <c r="M12" t="s">
+        <v>241</v>
+      </c>
+      <c r="N12" t="s">
+        <v>232</v>
+      </c>
+      <c r="O12" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="P12" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>232</v>
+      </c>
+      <c r="R12" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="S12" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="T12" t="s">
+        <v>232</v>
+      </c>
+      <c r="U12" t="s">
+        <v>232</v>
+      </c>
+      <c r="V12" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="W12" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="X12" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="Y12" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="Z12" s="96" t="s">
+        <v>235</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>231</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>231</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>241</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>232</v>
+      </c>
+      <c r="AE12" s="96" t="s">
+        <v>235</v>
+      </c>
+      <c r="AG12">
+        <v>18</v>
+      </c>
+      <c r="AH12">
+        <v>4</v>
+      </c>
+      <c r="AI12">
+        <v>5</v>
+      </c>
+      <c r="AJ12">
+        <v>4</v>
+      </c>
+      <c r="AK12">
+        <v>12</v>
+      </c>
+      <c r="AL12">
+        <v>2</v>
+      </c>
+      <c r="AM12">
+        <v>5</v>
+      </c>
+      <c r="AN12">
+        <v>0</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:42">
       <c r="A13" t="s">
-        <v>172</v>
+        <v>185</v>
+      </c>
+      <c r="B13" t="s">
+        <v>232</v>
+      </c>
+      <c r="C13" t="s">
+        <v>232</v>
+      </c>
+      <c r="D13" t="s">
+        <v>232</v>
+      </c>
+      <c r="E13" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="F13" t="s">
+        <v>231</v>
+      </c>
+      <c r="G13" t="s">
+        <v>241</v>
+      </c>
+      <c r="H13" t="s">
+        <v>241</v>
+      </c>
+      <c r="I13" t="s">
+        <v>232</v>
+      </c>
+      <c r="J13" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="K13" t="s">
+        <v>241</v>
+      </c>
+      <c r="L13" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="M13" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="N13" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="O13" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="P13" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q13" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="R13" t="s">
+        <v>231</v>
+      </c>
+      <c r="S13" t="s">
+        <v>231</v>
+      </c>
+      <c r="T13" t="s">
+        <v>231</v>
+      </c>
+      <c r="U13" t="s">
+        <v>241</v>
+      </c>
+      <c r="V13" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="W13" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="X13" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="Y13" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z13" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="AA13" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>241</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>232</v>
+      </c>
+      <c r="AD13" s="96" t="s">
+        <v>235</v>
+      </c>
+      <c r="AE13" s="96" t="s">
+        <v>235</v>
+      </c>
+      <c r="AG13">
+        <v>18</v>
+      </c>
+      <c r="AH13">
+        <v>4</v>
+      </c>
+      <c r="AI13">
+        <v>5</v>
+      </c>
+      <c r="AJ13">
+        <v>4</v>
+      </c>
+      <c r="AK13">
+        <v>12</v>
+      </c>
+      <c r="AL13">
+        <v>2</v>
+      </c>
+      <c r="AM13">
+        <v>5</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:42">
       <c r="A14" t="s">
-        <v>174</v>
+        <v>187</v>
+      </c>
+      <c r="B14" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="C14" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="D14" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="E14" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="F14" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="G14" t="s">
+        <v>232</v>
+      </c>
+      <c r="H14" t="s">
+        <v>232</v>
+      </c>
+      <c r="I14" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="J14" t="s">
+        <v>232</v>
+      </c>
+      <c r="K14" t="s">
+        <v>232</v>
+      </c>
+      <c r="L14" t="s">
+        <v>232</v>
+      </c>
+      <c r="M14" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="N14" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="O14" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="P14" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q14" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="R14" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="S14" t="s">
+        <v>241</v>
+      </c>
+      <c r="T14" t="s">
+        <v>241</v>
+      </c>
+      <c r="U14" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="V14" t="s">
+        <v>231</v>
+      </c>
+      <c r="W14" t="s">
+        <v>231</v>
+      </c>
+      <c r="X14" t="s">
+        <v>231</v>
+      </c>
+      <c r="Y14" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>241</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>241</v>
+      </c>
+      <c r="AB14" s="96" t="s">
+        <v>235</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>231</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>241</v>
+      </c>
+      <c r="AE14" s="96" t="s">
+        <v>235</v>
+      </c>
+      <c r="AG14">
+        <v>18</v>
+      </c>
+      <c r="AH14">
+        <v>4</v>
+      </c>
+      <c r="AI14">
+        <v>5</v>
+      </c>
+      <c r="AJ14">
+        <v>4</v>
+      </c>
+      <c r="AK14">
+        <v>12</v>
+      </c>
+      <c r="AL14">
+        <v>2</v>
+      </c>
+      <c r="AM14">
+        <v>5</v>
+      </c>
+      <c r="AN14">
+        <v>0</v>
+      </c>
+      <c r="AO14">
+        <v>0</v>
+      </c>
+      <c r="AP14">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:42">
       <c r="A15" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="16" spans="1:42">
-      <c r="A16" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" t="s">
-        <v>267</v>
+        <v>188</v>
+      </c>
+      <c r="B15" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="C15" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="D15" t="s">
+        <v>241</v>
+      </c>
+      <c r="E15" t="s">
+        <v>241</v>
+      </c>
+      <c r="F15" t="s">
+        <v>241</v>
+      </c>
+      <c r="G15" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="H15" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="I15" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="J15" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="K15" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="L15" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="M15" t="s">
+        <v>231</v>
+      </c>
+      <c r="N15" t="s">
+        <v>241</v>
+      </c>
+      <c r="O15" t="s">
+        <v>232</v>
+      </c>
+      <c r="P15" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>231</v>
+      </c>
+      <c r="R15" t="s">
+        <v>232</v>
+      </c>
+      <c r="S15" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="T15" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="U15" t="s">
+        <v>231</v>
+      </c>
+      <c r="V15" t="s">
+        <v>232</v>
+      </c>
+      <c r="W15" t="s">
+        <v>232</v>
+      </c>
+      <c r="X15" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>232</v>
+      </c>
+      <c r="Z15" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA15" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB15" s="96" t="s">
+        <v>235</v>
+      </c>
+      <c r="AC15" s="96" t="s">
+        <v>235</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>231</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>241</v>
+      </c>
+      <c r="AG15">
+        <v>18</v>
+      </c>
+      <c r="AH15">
+        <v>4</v>
+      </c>
+      <c r="AI15">
+        <v>5</v>
+      </c>
+      <c r="AJ15">
+        <v>4</v>
+      </c>
+      <c r="AK15">
+        <v>12</v>
+      </c>
+      <c r="AL15">
+        <v>2</v>
+      </c>
+      <c r="AM15">
+        <v>5</v>
+      </c>
+      <c r="AN15">
+        <v>0</v>
+      </c>
+      <c r="AO15">
+        <v>0</v>
+      </c>
+      <c r="AP15">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AP1"/>
   </mergeCells>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>